--- a/agents/compassus-capacity-pm/vendor-evaluation/Vendor-Scorecard-SIMPLE.xlsx
+++ b/agents/compassus-capacity-pm/vendor-evaluation/Vendor-Scorecard-SIMPLE.xlsx
@@ -692,7 +692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D37"/>
+  <dimension ref="B2:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -769,7 +769,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="24" customHeight="1">
+    <row r="13" ht="36" customHeight="1">
       <c r="B13" s="5" t="inlineStr">
         <is>
           <t>Rating  0–100</t>
@@ -782,7 +782,7 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>HOW GOOD IT IS, from what they wrote. Leave it blank where the status is Not available.</t>
+          <t>HOW MUCH OF THE WORK IT DOES. Rate the product, not the write-up — a short answer describing an optimiser still rates high. Blank where the status is Not available.</t>
         </is>
       </c>
     </row>
@@ -811,226 +811,234 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="24" customHeight="1">
+    <row r="17" ht="28" customHeight="1">
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>90–100</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>Proven at scale</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>They gave us numbers — a named customer, a period, a baseline.</t>
+          <t>The same Read / Assist / Control idea as the functional scorecard. If you want to know how a product does something, that is a demo question — not a reason to mark it down.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1">
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>70–89</t>
+          <t>90–100</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Mechanism explained</t>
+          <t>Runs it</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>We can see how it decides, not just that it exists.</t>
+          <t>Decides across the whole picture, and re-decides when things change.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1">
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>50–69</t>
+          <t>70–89</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>Described</t>
+          <t>Recommends it</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>We can picture the feature. Most answers land here.</t>
+          <t>Works out the answer and proposes it. A person confirms.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1">
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>25–49</t>
+          <t>50–69</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Asserted</t>
+          <t>Checks it</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>They say they do it. Nothing behind it.</t>
+          <t>Applies rules and flags problems. A person still does the work.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1">
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>1–24</t>
+          <t>25–49</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Barely touches it</t>
+          <t>Shows it</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Adjacent, or a fragment of what we asked for.</t>
+          <t>Surfaces the information. A person does everything.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1">
       <c r="B22" s="5" t="inlineStr">
         <is>
+          <t>1–24</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>Barely touches it</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>Adjacent, or a fragment of what we asked for.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
           <t>blank</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>Not available</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>Leave the rating empty. Status carries it.</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="10" customHeight="1"/>
-    <row r="24" ht="22" customHeight="1">
-      <c r="B24" s="4" t="inlineStr">
+    <row r="24" ht="10" customHeight="1"/>
+    <row r="25" ht="22" customHeight="1">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>WHAT THE SHEET WORKS OUT</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="36" customHeight="1">
-      <c r="B25" s="5" t="inlineStr">
+    <row r="26" ht="36" customHeight="1">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>Footprint %</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr"/>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>How many of the 11 areas the product reaches at all — any status except Not available. How much of what we care about it even touches.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="24" customHeight="1">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>In production %</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr"/>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>How many of those 11 are live with customers today, rather than promised.</t>
+          <t>How many of the 11 areas the product reaches at all — any status except Not available. How much of what we care about it even touches.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="24" customHeight="1">
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Average rating</t>
+          <t>In production %</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr"/>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Across the areas they reach. Blank areas do not drag it down — Footprint already carries that.</t>
+          <t>How many of those 11 are live with customers today, rather than promised.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1">
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Per-arena rating</t>
+          <t>Average rating</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr"/>
       <c r="D28" s="7" t="inlineStr">
         <is>
+          <t>Across the areas they reach. Blank areas do not drag it down — Footprint already carries that.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="24" customHeight="1">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Per-arena rating</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr"/>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
           <t>Capacity, Scheduling and Engagement separately. Which arena a vendor owns tells us more than the average does.</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="10" customHeight="1"/>
-    <row r="30" ht="22" customHeight="1">
-      <c r="B30" s="4" t="inlineStr">
+    <row r="30" ht="10" customHeight="1"/>
+    <row r="31" ht="22" customHeight="1">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>HOW TO READ IT</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="41" customHeight="1">
-      <c r="B31" s="5" t="inlineStr">
+    <row r="32" ht="41" customHeight="1">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>Footprint and rating answer different questions, and a vendor can be strong on one and weak on the other. High footprint with a low rating is a product that touches everything shallowly. Low footprint with a high rating is a specialist — often the more interesting conversation, and worth a differentiator note rather than a dismissal.</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="28" customHeight="1">
-      <c r="B32" s="5" t="inlineStr">
+    <row r="33" ht="28" customHeight="1">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>HCHB sits at the top of the grid on its own, because it is the one thing leadership named as a priority. A vendor with no HCHB path is a conditional advance whatever else they score: advancing them means accepting an integration still to be built, on their timeline, at our risk.</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="10" customHeight="1"/>
-    <row r="34" ht="22" customHeight="1">
-      <c r="B34" s="4" t="inlineStr">
+    <row r="34" ht="10" customHeight="1"/>
+    <row r="35" ht="22" customHeight="1">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>WHAT THIS CANNOT DO</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="41" customHeight="1">
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>It cannot separate two vendors who both cover an area but do it very differently — that is exactly what the full scorecard's 41 elements and evidence ladder are for. It has no partnership or clinician-adoption score, so Section D and Section E do not reach the number at all; read them and put what matters in Notes. And like the full sheet, it scores a questionnaire, not a product.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="8" t="inlineStr">
+    <row r="36" ht="41" customHeight="1">
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>It cannot separate two vendors who both cover an area but do it very differently — that is exactly what the full scorecard's 41 elements and five sophistication questions are for. It has no partnership or clinician-adoption score, so Section D and Section E do not reach the number at all; read them and put what matters in Notes. And like the full sheet, it scores a questionnaire, not a product.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="8" t="inlineStr">
         <is>
           <t>Backup scorecard v1.0  ·  areas per questionnaire Section B, form_version 2026-08-19</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="13">
+    <mergeCell ref="B33:D33"/>
     <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B36:D36"/>
     <mergeCell ref="B31:D31"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="B32:D32"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B17:D17"/>
     <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B30:D30"/>
     <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B25:D25"/>
     <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B34:D34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2081,7 +2089,7 @@
     <row r="34" ht="21" customHeight="1">
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>2  ·  RATING   —   how good it is, 0–100.  Blank where the status is Not available.</t>
+          <t>2  ·  RATING   —   how much of the work it does, 0–100.  Blank where the status is Not available.</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2108,7 @@
       </c>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>90+ proven · 70+ mechanism · 50+ described · 25+ asserted</t>
+          <t>90+ runs it · 70+ recommends · 50+ checks · 25+ shows it</t>
         </is>
       </c>
       <c r="D36" s="35" t="n"/>
@@ -2128,7 +2136,7 @@
       </c>
       <c r="C37" s="14" t="inlineStr">
         <is>
-          <t>90+ proven · 70+ mechanism · 50+ described · 25+ asserted</t>
+          <t>90+ runs it · 70+ recommends · 50+ checks · 25+ shows it</t>
         </is>
       </c>
       <c r="D37" s="35" t="n"/>
@@ -2156,7 +2164,7 @@
       </c>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>90+ proven · 70+ mechanism · 50+ described · 25+ asserted</t>
+          <t>90+ runs it · 70+ recommends · 50+ checks · 25+ shows it</t>
         </is>
       </c>
       <c r="D38" s="35" t="n"/>
@@ -2191,7 +2199,7 @@
       </c>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>90+ proven · 70+ mechanism · 50+ described · 25+ asserted</t>
+          <t>90+ runs it · 70+ recommends · 50+ checks · 25+ shows it</t>
         </is>
       </c>
       <c r="D40" s="35" t="n"/>
@@ -2219,7 +2227,7 @@
       </c>
       <c r="C41" s="14" t="inlineStr">
         <is>
-          <t>90+ proven · 70+ mechanism · 50+ described · 25+ asserted</t>
+          <t>90+ runs it · 70+ recommends · 50+ checks · 25+ shows it</t>
         </is>
       </c>
       <c r="D41" s="35" t="n"/>
@@ -2247,7 +2255,7 @@
       </c>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>90+ proven · 70+ mechanism · 50+ described · 25+ asserted</t>
+          <t>90+ runs it · 70+ recommends · 50+ checks · 25+ shows it</t>
         </is>
       </c>
       <c r="D42" s="35" t="n"/>
@@ -2275,7 +2283,7 @@
       </c>
       <c r="C43" s="14" t="inlineStr">
         <is>
-          <t>90+ proven · 70+ mechanism · 50+ described · 25+ asserted</t>
+          <t>90+ runs it · 70+ recommends · 50+ checks · 25+ shows it</t>
         </is>
       </c>
       <c r="D43" s="35" t="n"/>
@@ -2310,7 +2318,7 @@
       </c>
       <c r="C45" s="14" t="inlineStr">
         <is>
-          <t>90+ proven · 70+ mechanism · 50+ described · 25+ asserted</t>
+          <t>90+ runs it · 70+ recommends · 50+ checks · 25+ shows it</t>
         </is>
       </c>
       <c r="D45" s="35" t="n"/>
@@ -2338,7 +2346,7 @@
       </c>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>90+ proven · 70+ mechanism · 50+ described · 25+ asserted</t>
+          <t>90+ runs it · 70+ recommends · 50+ checks · 25+ shows it</t>
         </is>
       </c>
       <c r="D46" s="35" t="n"/>
@@ -2366,7 +2374,7 @@
       </c>
       <c r="C47" s="14" t="inlineStr">
         <is>
-          <t>90+ proven · 70+ mechanism · 50+ described · 25+ asserted</t>
+          <t>90+ runs it · 70+ recommends · 50+ checks · 25+ shows it</t>
         </is>
       </c>
       <c r="D47" s="35" t="n"/>
@@ -2394,7 +2402,7 @@
       </c>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>90+ proven · 70+ mechanism · 50+ described · 25+ asserted</t>
+          <t>90+ runs it · 70+ recommends · 50+ checks · 25+ shows it</t>
         </is>
       </c>
       <c r="D48" s="35" t="n"/>
@@ -2703,7 +2711,7 @@
     <dataValidation sqref="D20:S20 D21:S21 D22:S22 D24:S24 D25:S25 D26:S26 D27:S27 D29:S29 D30:S30 D31:S31 D32:S32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Status" prompt="What they have. Their own Section B wording. Section C wins where they differ." type="list">
       <formula1>=Lists!$D$2:$D$7</formula1>
     </dataValidation>
-    <dataValidation sqref="D36:S36 D37:S37 D38:S38 D40:S40 D41:S41 D42:S42 D43:S43 D45:S45 D46:S46 D47:S47 D48:S48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Ratings run 0 to 100. Leave it blank if the area is not available." promptTitle="Rating 0–100" prompt="90+ proven with numbers · 70+ mechanism explained · 50+ described · 25+ asserted · blank if not available." type="whole" operator="between">
+    <dataValidation sqref="D36:S36 D37:S37 D38:S38 D40:S40 D41:S41 D42:S42 D43:S43 D45:S45 D46:S46 D47:S47 D48:S48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Ratings run 0 to 100. Leave it blank if the area is not available." promptTitle="Rating 0–100" prompt="90+ runs it · 70+ recommends it · 50+ checks it · 25+ shows it · blank if not available. Rate what the product does, not how much they wrote about it." type="whole" operator="between">
       <formula1>0</formula1>
       <formula2>100</formula2>
     </dataValidation>

--- a/agents/compassus-capacity-pm/vendor-evaluation/Vendor-Scorecard-SIMPLE.xlsx
+++ b/agents/compassus-capacity-pm/vendor-evaluation/Vendor-Scorecard-SIMPLE.xlsx
@@ -734,7 +734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D74"/>
+  <dimension ref="B2:D80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1033,21 +1033,21 @@
     <row r="30" ht="22" customHeight="1">
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>SECTION B  ·  SCOPE   —   one mark per arena, 0 to 3</t>
+          <t>SECTION B  ·  SCOPE   —   one mark per arena, 0 to 5</t>
         </is>
       </c>
     </row>
     <row r="31" ht="28" customHeight="1">
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Read the eleven areas each vendor rated themselves on, then give one mark per arena. Capacity has 3 areas, Scheduling 4, Engagement 4 — so counting their yeses gets you most of the way there. Where Section C contradicts Section B, believe Section C.</t>
+          <t>Read the eleven areas each vendor rated themselves on, then give one mark per arena. Capacity has 3 areas, Scheduling 4, Engagement 4. Where Section C contradicts Section B, believe Section C.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="21" customHeight="1">
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
@@ -1060,7 +1060,7 @@
     <row r="33" ht="21" customHeight="1">
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -1073,12 +1073,12 @@
     <row r="34" ht="21" customHeight="1">
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>Covers some of it</t>
+          <t>Covers about half</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr"/>
@@ -1086,79 +1086,73 @@
     <row r="35" ht="21" customHeight="1">
       <c r="B35" s="7" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Covers a few pieces</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr"/>
+    </row>
+    <row r="36" ht="21" customHeight="1">
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Touches one corner</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr"/>
+    </row>
+    <row r="37" ht="21" customHeight="1">
+      <c r="B37" s="7" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>Little or none</t>
-        </is>
-      </c>
-      <c r="D35" s="8" t="inlineStr"/>
-    </row>
-    <row r="36" ht="10" customHeight="1"/>
-    <row r="37" ht="22" customHeight="1">
-      <c r="B37" s="4" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Nothing here</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="inlineStr"/>
+    </row>
+    <row r="38" ht="28" customHeight="1">
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>Six rungs because most of these are point solutions, not suites. Expect the field to land between 1 and 3, and expect 4 and 5 to go unused — that lower spread is the useful part, and it is a finding in itself if nobody reaches half of an arena.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="10" customHeight="1"/>
+    <row r="40" ht="22" customHeight="1">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>SECTION C  ·  SOPHISTICATION   —   one mark, 0 to 4</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="41" customHeight="1">
-      <c r="B38" s="5" t="inlineStr">
+    <row r="41" ht="41" customHeight="1">
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>How much of the work the product does. This is the Read / Assist / Control language already in our workbook. Score what the product does, not how much the vendor wrote about it — a short answer describing an optimiser still scores 4. How it does it is a demo question, not a reason to mark it down.</t>
         </is>
       </c>
-    </row>
-    <row r="39" ht="21" customHeight="1">
-      <c r="B39" s="7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t>Runs it — decides across the whole picture, and re-decides when things change</t>
-        </is>
-      </c>
-      <c r="D39" s="8" t="inlineStr"/>
-    </row>
-    <row r="40" ht="21" customHeight="1">
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>Recommends it — works out the answer and proposes it; a person confirms</t>
-        </is>
-      </c>
-      <c r="D40" s="8" t="inlineStr"/>
-    </row>
-    <row r="41" ht="21" customHeight="1">
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C41" s="5" t="inlineStr">
-        <is>
-          <t>Checks it — applies rules and flags problems; a person still works it</t>
-        </is>
-      </c>
-      <c r="D41" s="8" t="inlineStr"/>
     </row>
     <row r="42" ht="21" customHeight="1">
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>Shows it — surfaces the information; a person does all the work</t>
+          <t>Runs it — decides across the whole picture, and re-decides when things change</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr"/>
@@ -1166,113 +1160,125 @@
     <row r="43" ht="21" customHeight="1">
       <c r="B43" s="7" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>Recommends it — works out the answer and proposes it; a person confirms</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="inlineStr"/>
+    </row>
+    <row r="44" ht="21" customHeight="1">
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>Checks it — applies rules and flags problems; a person still works it</t>
+        </is>
+      </c>
+      <c r="D44" s="8" t="inlineStr"/>
+    </row>
+    <row r="45" ht="21" customHeight="1">
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>Shows it — surfaces the information; a person does all the work</t>
+        </is>
+      </c>
+      <c r="D45" s="8" t="inlineStr"/>
+    </row>
+    <row r="46" ht="21" customHeight="1">
+      <c r="B46" s="7" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr">
+      <c r="C46" s="5" t="inlineStr">
         <is>
           <t>Not addressed</t>
         </is>
       </c>
-      <c r="D43" s="8" t="inlineStr"/>
-    </row>
-    <row r="44" ht="15" customHeight="1">
-      <c r="B44" s="5" t="inlineStr">
+      <c r="D46" s="8" t="inlineStr"/>
+    </row>
+    <row r="47" ht="15" customHeight="1">
+      <c r="B47" s="5" t="inlineStr">
         <is>
           <t>A 4 is not automatically what we want. Where we said Assist, a product that decides on its own is a risk worth a note.</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="10" customHeight="1"/>
-    <row r="46" ht="22" customHeight="1">
-      <c r="B46" s="4" t="inlineStr">
+    <row r="48" ht="10" customHeight="1"/>
+    <row r="49" ht="22" customHeight="1">
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>SECTION D  ·  CLINICIAN FIT   —   one mark, 0 to 4</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="21" customHeight="1">
-      <c r="B47" s="7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C47" s="5" t="inlineStr">
-        <is>
-          <t>Clinician keeps real control, and they showed adoption data</t>
-        </is>
-      </c>
-      <c r="D47" s="8" t="inlineStr"/>
-    </row>
-    <row r="48" ht="21" customHeight="1">
-      <c r="B48" s="7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>Clinician keeps real control; adoption claimed but not shown</t>
-        </is>
-      </c>
-      <c r="D48" s="8" t="inlineStr"/>
-    </row>
-    <row r="49" ht="21" customHeight="1">
-      <c r="B49" s="7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C49" s="5" t="inlineStr">
-        <is>
-          <t>System decides, clinician can override</t>
-        </is>
-      </c>
-      <c r="D49" s="8" t="inlineStr"/>
-    </row>
-    <row r="50" ht="21" customHeight="1">
-      <c r="B50" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C50" s="5" t="inlineStr">
-        <is>
-          <t>System decides, clinician cannot override</t>
-        </is>
-      </c>
-      <c r="D50" s="8" t="inlineStr"/>
+    <row r="50" ht="28" customHeight="1">
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>One question only: how much say does the clinician have over their own schedule? Many clinicians come to home health for the control it gives them over their week, so this is the adoption risk.</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="21" customHeight="1">
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>Didn't answer</t>
+          <t>They can shape their own schedule, and the product learns from it</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr"/>
     </row>
-    <row r="52" ht="10" customHeight="1"/>
-    <row r="53" ht="22" customHeight="1">
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>SECTION E  ·  PARTNERSHIP   —   one mark, 0 to 4</t>
-        </is>
-      </c>
+    <row r="52" ht="21" customHeight="1">
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>They can decline or change an assignment themselves</t>
+        </is>
+      </c>
+      <c r="D52" s="8" t="inlineStr"/>
+    </row>
+    <row r="53" ht="21" customHeight="1">
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>They can raise it; someone else makes the change</t>
+        </is>
+      </c>
+      <c r="D53" s="8" t="inlineStr"/>
     </row>
     <row r="54" ht="21" customHeight="1">
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>Specific terms and a real change-management story</t>
+          <t>The schedule is set for them, with no way to change it</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr"/>
@@ -1280,86 +1286,86 @@
     <row r="55" ht="21" customHeight="1">
       <c r="B55" s="7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>Not answered</t>
+        </is>
+      </c>
+      <c r="D55" s="8" t="inlineStr"/>
+    </row>
+    <row r="56" ht="28" customHeight="1">
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>This runs opposite to Sophistication on purpose. A product that decides everything scores 4 there and 1 here — and that is the real trade in this purchase, not a contradiction. A vendor strong on both has solved something hard.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="28" customHeight="1">
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>Whether they showed adoption data is not on this scale. It is a note, not a score — a product can be well designed for clinicians and simply be young.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="10" customHeight="1"/>
+    <row r="59" ht="22" customHeight="1">
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>SECTION E  ·  PARTNERSHIP   —   one mark, 0 to 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="21" customHeight="1">
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>Specific terms and a real change-management story</t>
+        </is>
+      </c>
+      <c r="D60" s="8" t="inlineStr"/>
+    </row>
+    <row r="61" ht="21" customHeight="1">
+      <c r="B61" s="7" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C55" s="5" t="inlineStr">
+      <c r="C61" s="5" t="inlineStr">
         <is>
           <t>One of the two</t>
         </is>
       </c>
-      <c r="D55" s="8" t="inlineStr"/>
-    </row>
-    <row r="56" ht="21" customHeight="1">
-      <c r="B56" s="7" t="inlineStr">
+      <c r="D61" s="8" t="inlineStr"/>
+    </row>
+    <row r="62" ht="21" customHeight="1">
+      <c r="B62" s="7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C56" s="5" t="inlineStr">
+      <c r="C62" s="5" t="inlineStr">
         <is>
           <t>Willing, but no structure offered</t>
         </is>
       </c>
-      <c r="D56" s="8" t="inlineStr"/>
-    </row>
-    <row r="57" ht="21" customHeight="1">
-      <c r="B57" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C57" s="5" t="inlineStr">
-        <is>
-          <t>Standard commercial relationship only</t>
-        </is>
-      </c>
-      <c r="D57" s="8" t="inlineStr"/>
-    </row>
-    <row r="58" ht="21" customHeight="1">
-      <c r="B58" s="7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C58" s="5" t="inlineStr">
-        <is>
-          <t>Didn't answer</t>
-        </is>
-      </c>
-      <c r="D58" s="8" t="inlineStr"/>
-    </row>
-    <row r="59" ht="15" customHeight="1">
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>Specific terms means design-partner pricing, co-development, roadmap governance, or a revenue or equity share. A discount is a discount.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="10" customHeight="1"/>
-    <row r="61" ht="22" customHeight="1">
-      <c r="B61" s="4" t="inlineStr">
-        <is>
-          <t>THE THREE QUESTIONS THAT RAISE A FLAG INSTEAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="28" customHeight="1">
-      <c r="B62" s="5" t="inlineStr">
-        <is>
-          <t>A vendor with no continuity commitment should be stopped and asked, not quietly docked a few points. Same for a vendor with one customer, or impact numbers with no baseline. Mark these OK, Watch or STOP-CHECK.</t>
-        </is>
-      </c>
+      <c r="D62" s="8" t="inlineStr"/>
     </row>
     <row r="63" ht="21" customHeight="1">
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>Customers, scale and references — STOP-CHECK if one customer, or no references offered</t>
+          <t>Standard commercial relationship only</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr"/>
@@ -1367,59 +1373,47 @@
     <row r="64" ht="21" customHeight="1">
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>A3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>Measured impact — Watch if claimed with no baseline or period</t>
+          <t>Didn't answer</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr"/>
     </row>
-    <row r="65" ht="21" customHeight="1">
-      <c r="B65" s="7" t="inlineStr">
-        <is>
-          <t>C6</t>
-        </is>
-      </c>
-      <c r="C65" s="5" t="inlineStr">
-        <is>
-          <t>When your product is down — STOP-CHECK if no uptime figure or contractual commitment</t>
-        </is>
-      </c>
-      <c r="D65" s="8" t="inlineStr"/>
+    <row r="65" ht="15" customHeight="1">
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>Specific terms means design-partner pricing, co-development, roadmap governance, or a revenue or equity share. A discount is a discount.</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="10" customHeight="1"/>
     <row r="67" ht="22" customHeight="1">
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>BANDS   —   the same as the full scorecard</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="21" customHeight="1">
-      <c r="B68" s="7" t="inlineStr">
-        <is>
-          <t>80–100</t>
-        </is>
-      </c>
-      <c r="C68" s="5" t="inlineStr">
-        <is>
-          <t>Advance — demo, references, deeper diligence</t>
-        </is>
-      </c>
-      <c r="D68" s="8" t="inlineStr"/>
+          <t>THE THREE QUESTIONS THAT RAISE A FLAG INSTEAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="28" customHeight="1">
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>A vendor with no continuity commitment should be stopped and asked, not quietly docked a few points. Same for a vendor with one customer, or impact numbers with no baseline. Mark these OK, Watch or STOP-CHECK.</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="21" customHeight="1">
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>65–79</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>Consider — only if something specific justifies it</t>
+          <t>Customers, scale and references — STOP-CHECK if one customer, or no references offered</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr"/>
@@ -1427,12 +1421,12 @@
     <row r="70" ht="21" customHeight="1">
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>50–64</t>
+          <t>A3</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>Hold — park unless the field thins</t>
+          <t>Measured impact — Watch if claimed with no baseline or period</t>
         </is>
       </c>
       <c r="D70" s="8" t="inlineStr"/>
@@ -1440,55 +1434,119 @@
     <row r="71" ht="21" customHeight="1">
       <c r="B71" s="7" t="inlineStr">
         <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>When your product is down — STOP-CHECK if no uptime figure or contractual commitment</t>
+        </is>
+      </c>
+      <c r="D71" s="8" t="inlineStr"/>
+    </row>
+    <row r="72" ht="10" customHeight="1"/>
+    <row r="73" ht="22" customHeight="1">
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>BANDS   —   the same as the full scorecard</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="21" customHeight="1">
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>80–100</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>Advance — demo, references, deeper diligence</t>
+        </is>
+      </c>
+      <c r="D74" s="8" t="inlineStr"/>
+    </row>
+    <row r="75" ht="21" customHeight="1">
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>65–79</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>Consider — only if something specific justifies it</t>
+        </is>
+      </c>
+      <c r="D75" s="8" t="inlineStr"/>
+    </row>
+    <row r="76" ht="21" customHeight="1">
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>50–64</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>Hold — park unless the field thins</t>
+        </is>
+      </c>
+      <c r="D76" s="8" t="inlineStr"/>
+    </row>
+    <row r="77" ht="21" customHeight="1">
+      <c r="B77" s="7" t="inlineStr">
+        <is>
           <t>&lt; 50</t>
         </is>
       </c>
-      <c r="C71" s="5" t="inlineStr">
+      <c r="C77" s="5" t="inlineStr">
         <is>
           <t>Decline — close out with thanks</t>
         </is>
       </c>
-      <c r="D71" s="8" t="inlineStr"/>
-    </row>
-    <row r="72" ht="34" customHeight="1">
-      <c r="B72" s="7" t="inlineStr">
+      <c r="D77" s="8" t="inlineStr"/>
+    </row>
+    <row r="78" ht="34" customHeight="1">
+      <c r="B78" s="7" t="inlineStr">
         <is>
           <t>Conditional</t>
         </is>
       </c>
-      <c r="C72" s="5" t="inlineStr">
+      <c r="C78" s="5" t="inlineStr">
         <is>
           <t>Shown whenever A1 scores under 12. Advancing means accepting an integration still to be built, on their timeline, at our risk.</t>
         </is>
       </c>
-      <c r="D72" s="8" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="B74" s="10" t="inlineStr">
+      <c r="D78" s="8" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="B80" s="10" t="inlineStr">
         <is>
           <t>Fast scorecard v2.0  ·  questionnaire form_version 2026-08-19</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="21">
     <mergeCell ref="B11:D11"/>
-    <mergeCell ref="B59:D59"/>
-    <mergeCell ref="B37:D37"/>
     <mergeCell ref="B67:D67"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B61:D61"/>
-    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B57:D57"/>
     <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B73:D73"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B49:D49"/>
+    <mergeCell ref="B40:D40"/>
     <mergeCell ref="B9:D9"/>
     <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B53:D53"/>
-    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B65:D65"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B50:D50"/>
     <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="B59:D59"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B56:D56"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1653,67 +1711,67 @@
         </is>
       </c>
       <c r="E9" s="17">
-        <f>IFERROR(VLOOKUP(E14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(E19,1)),0)/3*10+IFERROR(VALUE(LEFT(E20,1)),0)/3*10+IFERROR(VALUE(LEFT(E21,1)),0)/3*10+IFERROR(VALUE(LEFT(E24,1)),0)/4*20+IFERROR(VALUE(LEFT(E28,1)),0)/4*10+IFERROR(VALUE(LEFT(E31,1)),0)/4*15</f>
+        <f>IFERROR(VLOOKUP(E14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(E19,1)),0)/5*10+IFERROR(VALUE(LEFT(E20,1)),0)/5*10+IFERROR(VALUE(LEFT(E21,1)),0)/5*10+IFERROR(VALUE(LEFT(E24,1)),0)/4*20+IFERROR(VALUE(LEFT(E28,1)),0)/4*10+IFERROR(VALUE(LEFT(E31,1)),0)/4*15</f>
         <v/>
       </c>
       <c r="F9" s="17">
-        <f>IFERROR(VLOOKUP(F14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(F19,1)),0)/3*10+IFERROR(VALUE(LEFT(F20,1)),0)/3*10+IFERROR(VALUE(LEFT(F21,1)),0)/3*10+IFERROR(VALUE(LEFT(F24,1)),0)/4*20+IFERROR(VALUE(LEFT(F28,1)),0)/4*10+IFERROR(VALUE(LEFT(F31,1)),0)/4*15</f>
+        <f>IFERROR(VLOOKUP(F14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(F19,1)),0)/5*10+IFERROR(VALUE(LEFT(F20,1)),0)/5*10+IFERROR(VALUE(LEFT(F21,1)),0)/5*10+IFERROR(VALUE(LEFT(F24,1)),0)/4*20+IFERROR(VALUE(LEFT(F28,1)),0)/4*10+IFERROR(VALUE(LEFT(F31,1)),0)/4*15</f>
         <v/>
       </c>
       <c r="G9" s="17">
-        <f>IFERROR(VLOOKUP(G14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(G19,1)),0)/3*10+IFERROR(VALUE(LEFT(G20,1)),0)/3*10+IFERROR(VALUE(LEFT(G21,1)),0)/3*10+IFERROR(VALUE(LEFT(G24,1)),0)/4*20+IFERROR(VALUE(LEFT(G28,1)),0)/4*10+IFERROR(VALUE(LEFT(G31,1)),0)/4*15</f>
+        <f>IFERROR(VLOOKUP(G14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(G19,1)),0)/5*10+IFERROR(VALUE(LEFT(G20,1)),0)/5*10+IFERROR(VALUE(LEFT(G21,1)),0)/5*10+IFERROR(VALUE(LEFT(G24,1)),0)/4*20+IFERROR(VALUE(LEFT(G28,1)),0)/4*10+IFERROR(VALUE(LEFT(G31,1)),0)/4*15</f>
         <v/>
       </c>
       <c r="H9" s="17">
-        <f>IFERROR(VLOOKUP(H14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(H19,1)),0)/3*10+IFERROR(VALUE(LEFT(H20,1)),0)/3*10+IFERROR(VALUE(LEFT(H21,1)),0)/3*10+IFERROR(VALUE(LEFT(H24,1)),0)/4*20+IFERROR(VALUE(LEFT(H28,1)),0)/4*10+IFERROR(VALUE(LEFT(H31,1)),0)/4*15</f>
+        <f>IFERROR(VLOOKUP(H14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(H19,1)),0)/5*10+IFERROR(VALUE(LEFT(H20,1)),0)/5*10+IFERROR(VALUE(LEFT(H21,1)),0)/5*10+IFERROR(VALUE(LEFT(H24,1)),0)/4*20+IFERROR(VALUE(LEFT(H28,1)),0)/4*10+IFERROR(VALUE(LEFT(H31,1)),0)/4*15</f>
         <v/>
       </c>
       <c r="I9" s="17">
-        <f>IFERROR(VLOOKUP(I14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(I19,1)),0)/3*10+IFERROR(VALUE(LEFT(I20,1)),0)/3*10+IFERROR(VALUE(LEFT(I21,1)),0)/3*10+IFERROR(VALUE(LEFT(I24,1)),0)/4*20+IFERROR(VALUE(LEFT(I28,1)),0)/4*10+IFERROR(VALUE(LEFT(I31,1)),0)/4*15</f>
+        <f>IFERROR(VLOOKUP(I14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(I19,1)),0)/5*10+IFERROR(VALUE(LEFT(I20,1)),0)/5*10+IFERROR(VALUE(LEFT(I21,1)),0)/5*10+IFERROR(VALUE(LEFT(I24,1)),0)/4*20+IFERROR(VALUE(LEFT(I28,1)),0)/4*10+IFERROR(VALUE(LEFT(I31,1)),0)/4*15</f>
         <v/>
       </c>
       <c r="J9" s="17">
-        <f>IFERROR(VLOOKUP(J14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(J19,1)),0)/3*10+IFERROR(VALUE(LEFT(J20,1)),0)/3*10+IFERROR(VALUE(LEFT(J21,1)),0)/3*10+IFERROR(VALUE(LEFT(J24,1)),0)/4*20+IFERROR(VALUE(LEFT(J28,1)),0)/4*10+IFERROR(VALUE(LEFT(J31,1)),0)/4*15</f>
+        <f>IFERROR(VLOOKUP(J14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(J19,1)),0)/5*10+IFERROR(VALUE(LEFT(J20,1)),0)/5*10+IFERROR(VALUE(LEFT(J21,1)),0)/5*10+IFERROR(VALUE(LEFT(J24,1)),0)/4*20+IFERROR(VALUE(LEFT(J28,1)),0)/4*10+IFERROR(VALUE(LEFT(J31,1)),0)/4*15</f>
         <v/>
       </c>
       <c r="K9" s="17">
-        <f>IFERROR(VLOOKUP(K14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(K19,1)),0)/3*10+IFERROR(VALUE(LEFT(K20,1)),0)/3*10+IFERROR(VALUE(LEFT(K21,1)),0)/3*10+IFERROR(VALUE(LEFT(K24,1)),0)/4*20+IFERROR(VALUE(LEFT(K28,1)),0)/4*10+IFERROR(VALUE(LEFT(K31,1)),0)/4*15</f>
+        <f>IFERROR(VLOOKUP(K14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(K19,1)),0)/5*10+IFERROR(VALUE(LEFT(K20,1)),0)/5*10+IFERROR(VALUE(LEFT(K21,1)),0)/5*10+IFERROR(VALUE(LEFT(K24,1)),0)/4*20+IFERROR(VALUE(LEFT(K28,1)),0)/4*10+IFERROR(VALUE(LEFT(K31,1)),0)/4*15</f>
         <v/>
       </c>
       <c r="L9" s="17">
-        <f>IFERROR(VLOOKUP(L14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(L19,1)),0)/3*10+IFERROR(VALUE(LEFT(L20,1)),0)/3*10+IFERROR(VALUE(LEFT(L21,1)),0)/3*10+IFERROR(VALUE(LEFT(L24,1)),0)/4*20+IFERROR(VALUE(LEFT(L28,1)),0)/4*10+IFERROR(VALUE(LEFT(L31,1)),0)/4*15</f>
+        <f>IFERROR(VLOOKUP(L14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(L19,1)),0)/5*10+IFERROR(VALUE(LEFT(L20,1)),0)/5*10+IFERROR(VALUE(LEFT(L21,1)),0)/5*10+IFERROR(VALUE(LEFT(L24,1)),0)/4*20+IFERROR(VALUE(LEFT(L28,1)),0)/4*10+IFERROR(VALUE(LEFT(L31,1)),0)/4*15</f>
         <v/>
       </c>
       <c r="M9" s="17">
-        <f>IFERROR(VLOOKUP(M14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(M19,1)),0)/3*10+IFERROR(VALUE(LEFT(M20,1)),0)/3*10+IFERROR(VALUE(LEFT(M21,1)),0)/3*10+IFERROR(VALUE(LEFT(M24,1)),0)/4*20+IFERROR(VALUE(LEFT(M28,1)),0)/4*10+IFERROR(VALUE(LEFT(M31,1)),0)/4*15</f>
+        <f>IFERROR(VLOOKUP(M14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(M19,1)),0)/5*10+IFERROR(VALUE(LEFT(M20,1)),0)/5*10+IFERROR(VALUE(LEFT(M21,1)),0)/5*10+IFERROR(VALUE(LEFT(M24,1)),0)/4*20+IFERROR(VALUE(LEFT(M28,1)),0)/4*10+IFERROR(VALUE(LEFT(M31,1)),0)/4*15</f>
         <v/>
       </c>
       <c r="N9" s="17">
-        <f>IFERROR(VLOOKUP(N14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(N19,1)),0)/3*10+IFERROR(VALUE(LEFT(N20,1)),0)/3*10+IFERROR(VALUE(LEFT(N21,1)),0)/3*10+IFERROR(VALUE(LEFT(N24,1)),0)/4*20+IFERROR(VALUE(LEFT(N28,1)),0)/4*10+IFERROR(VALUE(LEFT(N31,1)),0)/4*15</f>
+        <f>IFERROR(VLOOKUP(N14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(N19,1)),0)/5*10+IFERROR(VALUE(LEFT(N20,1)),0)/5*10+IFERROR(VALUE(LEFT(N21,1)),0)/5*10+IFERROR(VALUE(LEFT(N24,1)),0)/4*20+IFERROR(VALUE(LEFT(N28,1)),0)/4*10+IFERROR(VALUE(LEFT(N31,1)),0)/4*15</f>
         <v/>
       </c>
       <c r="O9" s="17">
-        <f>IFERROR(VLOOKUP(O14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(O19,1)),0)/3*10+IFERROR(VALUE(LEFT(O20,1)),0)/3*10+IFERROR(VALUE(LEFT(O21,1)),0)/3*10+IFERROR(VALUE(LEFT(O24,1)),0)/4*20+IFERROR(VALUE(LEFT(O28,1)),0)/4*10+IFERROR(VALUE(LEFT(O31,1)),0)/4*15</f>
+        <f>IFERROR(VLOOKUP(O14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(O19,1)),0)/5*10+IFERROR(VALUE(LEFT(O20,1)),0)/5*10+IFERROR(VALUE(LEFT(O21,1)),0)/5*10+IFERROR(VALUE(LEFT(O24,1)),0)/4*20+IFERROR(VALUE(LEFT(O28,1)),0)/4*10+IFERROR(VALUE(LEFT(O31,1)),0)/4*15</f>
         <v/>
       </c>
       <c r="P9" s="17">
-        <f>IFERROR(VLOOKUP(P14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(P19,1)),0)/3*10+IFERROR(VALUE(LEFT(P20,1)),0)/3*10+IFERROR(VALUE(LEFT(P21,1)),0)/3*10+IFERROR(VALUE(LEFT(P24,1)),0)/4*20+IFERROR(VALUE(LEFT(P28,1)),0)/4*10+IFERROR(VALUE(LEFT(P31,1)),0)/4*15</f>
+        <f>IFERROR(VLOOKUP(P14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(P19,1)),0)/5*10+IFERROR(VALUE(LEFT(P20,1)),0)/5*10+IFERROR(VALUE(LEFT(P21,1)),0)/5*10+IFERROR(VALUE(LEFT(P24,1)),0)/4*20+IFERROR(VALUE(LEFT(P28,1)),0)/4*10+IFERROR(VALUE(LEFT(P31,1)),0)/4*15</f>
         <v/>
       </c>
       <c r="Q9" s="17">
-        <f>IFERROR(VLOOKUP(Q14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(Q19,1)),0)/3*10+IFERROR(VALUE(LEFT(Q20,1)),0)/3*10+IFERROR(VALUE(LEFT(Q21,1)),0)/3*10+IFERROR(VALUE(LEFT(Q24,1)),0)/4*20+IFERROR(VALUE(LEFT(Q28,1)),0)/4*10+IFERROR(VALUE(LEFT(Q31,1)),0)/4*15</f>
+        <f>IFERROR(VLOOKUP(Q14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(Q19,1)),0)/5*10+IFERROR(VALUE(LEFT(Q20,1)),0)/5*10+IFERROR(VALUE(LEFT(Q21,1)),0)/5*10+IFERROR(VALUE(LEFT(Q24,1)),0)/4*20+IFERROR(VALUE(LEFT(Q28,1)),0)/4*10+IFERROR(VALUE(LEFT(Q31,1)),0)/4*15</f>
         <v/>
       </c>
       <c r="R9" s="17">
-        <f>IFERROR(VLOOKUP(R14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(R19,1)),0)/3*10+IFERROR(VALUE(LEFT(R20,1)),0)/3*10+IFERROR(VALUE(LEFT(R21,1)),0)/3*10+IFERROR(VALUE(LEFT(R24,1)),0)/4*20+IFERROR(VALUE(LEFT(R28,1)),0)/4*10+IFERROR(VALUE(LEFT(R31,1)),0)/4*15</f>
+        <f>IFERROR(VLOOKUP(R14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(R19,1)),0)/5*10+IFERROR(VALUE(LEFT(R20,1)),0)/5*10+IFERROR(VALUE(LEFT(R21,1)),0)/5*10+IFERROR(VALUE(LEFT(R24,1)),0)/4*20+IFERROR(VALUE(LEFT(R28,1)),0)/4*10+IFERROR(VALUE(LEFT(R31,1)),0)/4*15</f>
         <v/>
       </c>
       <c r="S9" s="17">
-        <f>IFERROR(VLOOKUP(S14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(S19,1)),0)/3*10+IFERROR(VALUE(LEFT(S20,1)),0)/3*10+IFERROR(VALUE(LEFT(S21,1)),0)/3*10+IFERROR(VALUE(LEFT(S24,1)),0)/4*20+IFERROR(VALUE(LEFT(S28,1)),0)/4*10+IFERROR(VALUE(LEFT(S31,1)),0)/4*15</f>
+        <f>IFERROR(VLOOKUP(S14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(S19,1)),0)/5*10+IFERROR(VALUE(LEFT(S20,1)),0)/5*10+IFERROR(VALUE(LEFT(S21,1)),0)/5*10+IFERROR(VALUE(LEFT(S24,1)),0)/4*20+IFERROR(VALUE(LEFT(S28,1)),0)/4*10+IFERROR(VALUE(LEFT(S31,1)),0)/4*15</f>
         <v/>
       </c>
       <c r="T9" s="17">
-        <f>IFERROR(VLOOKUP(T14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(T19,1)),0)/3*10+IFERROR(VALUE(LEFT(T20,1)),0)/3*10+IFERROR(VALUE(LEFT(T21,1)),0)/3*10+IFERROR(VALUE(LEFT(T24,1)),0)/4*20+IFERROR(VALUE(LEFT(T28,1)),0)/4*10+IFERROR(VALUE(LEFT(T31,1)),0)/4*15</f>
+        <f>IFERROR(VLOOKUP(T14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(T19,1)),0)/5*10+IFERROR(VALUE(LEFT(T20,1)),0)/5*10+IFERROR(VALUE(LEFT(T21,1)),0)/5*10+IFERROR(VALUE(LEFT(T24,1)),0)/4*20+IFERROR(VALUE(LEFT(T28,1)),0)/4*10+IFERROR(VALUE(LEFT(T31,1)),0)/4*15</f>
         <v/>
       </c>
     </row>
@@ -1995,7 +2053,7 @@
       </c>
       <c r="D19" s="16" t="inlineStr">
         <is>
-          <t>Workforce supply · availability &amp; reach · the capacity math  ·  0–3  ·  10 points</t>
+          <t>Workforce supply · availability &amp; reach · the capacity math  ·  0–5  ·  10 points</t>
         </is>
       </c>
       <c r="E19" s="28" t="n"/>
@@ -2028,7 +2086,7 @@
       </c>
       <c r="D20" s="16" t="inlineStr">
         <is>
-          <t>Demand · matching · routing &amp; the week · exceptions  ·  0–3  ·  10 points</t>
+          <t>Demand · matching · routing &amp; the week · exceptions  ·  0–5  ·  10 points</t>
         </is>
       </c>
       <c r="E20" s="28" t="n"/>
@@ -2061,7 +2119,7 @@
       </c>
       <c r="D21" s="16" t="inlineStr">
         <is>
-          <t>Before the visit · when plans change · incentives · care team  ·  0–3  ·  10 points</t>
+          <t>Before the visit · when plans change · incentives · care team  ·  0–5  ·  10 points</t>
         </is>
       </c>
       <c r="E21" s="28" t="n"/>
@@ -2174,7 +2232,7 @@
       </c>
       <c r="D28" s="16" t="inlineStr">
         <is>
-          <t>Control, and whether adoption is shown  ·  0–4  ·  10 points</t>
+          <t>How much say the clinician has  ·  0–4  ·  10 points</t>
         </is>
       </c>
       <c r="E28" s="28" t="n"/>
@@ -2380,7 +2438,7 @@
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="num" val="0"/>
-        <cfvo type="num" val="3"/>
+        <cfvo type="num" val="5"/>
         <color rgb="00FFFFFF"/>
         <color rgb="001F6F78"/>
       </colorScale>
@@ -2390,7 +2448,7 @@
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="num" val="0"/>
-        <cfvo type="num" val="3"/>
+        <cfvo type="num" val="5"/>
         <color rgb="00FFFFFF"/>
         <color rgb="002E599D"/>
       </colorScale>
@@ -2400,7 +2458,7 @@
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="num" val="0"/>
-        <cfvo type="num" val="3"/>
+        <cfvo type="num" val="5"/>
         <color rgb="00FFFFFF"/>
         <color rgb="004E8A5B"/>
       </colorScale>
@@ -2410,13 +2468,13 @@
     <dataValidation sqref="E14:T14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="A1 — Home Care Home Base" prompt="Pick one line. Ambiguous? Take the lower one and say so in Notes." type="list">
       <formula1>=Lists!$B$2:$B$7</formula1>
     </dataValidation>
-    <dataValidation sqref="E19:T19 E20:T20 E21:T21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Scope, 0–3" prompt="How much of this arena they cover. Counting their Section B yeses gets you most of the way there." type="list">
-      <formula1>=Lists!$E$2:$E$5</formula1>
+    <dataValidation sqref="E19:T19 E20:T20 E21:T21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Scope, 0–5" prompt="How much of this arena they cover. Most point solutions land between 1 and 3 — that spread is the useful part." type="list">
+      <formula1>=Lists!$E$2:$E$7</formula1>
     </dataValidation>
     <dataValidation sqref="E24:T24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Sophistication, 0–4" prompt="1 shows it · 2 checks it · 3 recommends it · 4 runs it. Score what the product does, not how much they wrote about it." type="list">
       <formula1>=Lists!$G$2:$G$6</formula1>
     </dataValidation>
-    <dataValidation sqref="E28:T28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Clinician fit, 0–4" prompt="Does the clinician keep real control, and did they show adoption data?" type="list">
+    <dataValidation sqref="E28:T28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Clinician fit, 0–4" prompt="How much say does the clinician have over their own schedule? This runs opposite to Sophistication on purpose." type="list">
       <formula1>=Lists!$I$2:$I$6</formula1>
     </dataValidation>
     <dataValidation sqref="E31:T31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Partnership, 0–4" prompt="Specific terms means design-partner pricing, co-development, roadmap governance or a revenue share. A discount is a discount." type="list">
@@ -2489,7 +2547,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0 — Little or none</t>
+          <t>0 — Nothing here</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -2499,7 +2557,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0 — Didn't answer</t>
+          <t>0 — Not answered</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -2519,7 +2577,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1 — Covers some of it</t>
+          <t>1 — Touches one corner</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -2529,7 +2587,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1 — System decides, clinician cannot override</t>
+          <t>1 — The schedule is set for them, with no way to change it</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -2549,7 +2607,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2 — Covers most of it</t>
+          <t>2 — Covers a few pieces</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -2559,7 +2617,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2 — System decides, clinician can override</t>
+          <t>2 — They can raise it; someone else makes the change</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2579,7 +2637,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3 — Covers essentially all of it</t>
+          <t>3 — Covers about half</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2589,7 +2647,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3 — Clinician keeps real control; adoption claimed</t>
+          <t>3 — They can decline or change an assignment themselves</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2607,6 +2665,11 @@
       <c r="C6" t="n">
         <v>2</v>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>4 — Covers most of it</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>4 — Runs it</t>
@@ -2614,7 +2677,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4 — Clinician keeps real control; adoption shown with data</t>
+          <t>4 — They can shape their own schedule, and the product learns from it</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2631,6 +2694,11 @@
       </c>
       <c r="C7" t="n">
         <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>5 — Covers essentially all of it</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/agents/compassus-capacity-pm/vendor-evaluation/Vendor-Scorecard-SIMPLE.xlsx
+++ b/agents/compassus-capacity-pm/vendor-evaluation/Vendor-Scorecard-SIMPLE.xlsx
@@ -824,7 +824,7 @@
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -875,7 +875,7 @@
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -951,18 +951,12 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="21" customHeight="1">
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>Live — reads and writes, several customers</t>
-        </is>
-      </c>
-      <c r="D23" s="8" t="inlineStr"/>
+    <row r="23" ht="28" customHeight="1">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Three of the six rungs are live integrations, because live through a partner is still live. Anything not yet live shows as Conditional on the score, whatever the total.</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="21" customHeight="1">
       <c r="B24" s="7" t="inlineStr">
@@ -972,7 +966,7 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Live — one customer, or one-way only</t>
+          <t>Live — established customer base</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr"/>
@@ -980,12 +974,12 @@
     <row r="25" ht="21" customHeight="1">
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Live — via a partner, flat file or screen scraping</t>
+          <t>Live — small customer base</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr"/>
@@ -993,12 +987,12 @@
     <row r="26" ht="21" customHeight="1">
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>In development — with a date</t>
+          <t>Live — through a partner</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr"/>
@@ -1006,12 +1000,12 @@
     <row r="27" ht="21" customHeight="1">
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Roadmap — no date</t>
+          <t>In development — with a date</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr"/>
@@ -1019,53 +1013,53 @@
     <row r="28" ht="21" customHeight="1">
       <c r="B28" s="7" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>On the roadmap — no date</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr"/>
+    </row>
+    <row r="29" ht="21" customHeight="1">
+      <c r="B29" s="7" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>None, and no path to one</t>
         </is>
       </c>
-      <c r="D28" s="8" t="inlineStr"/>
-    </row>
-    <row r="29" ht="10" customHeight="1"/>
-    <row r="30" ht="22" customHeight="1">
-      <c r="B30" s="4" t="inlineStr">
+      <c r="D29" s="8" t="inlineStr"/>
+    </row>
+    <row r="30" ht="10" customHeight="1"/>
+    <row r="31" ht="22" customHeight="1">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>SECTION B  ·  SCOPE   —   one mark per arena, 0 to 5</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="28" customHeight="1">
-      <c r="B31" s="5" t="inlineStr">
+    <row r="32" ht="28" customHeight="1">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>Read the eleven areas each vendor rated themselves on, then give one mark per arena. Capacity has 3 areas, Scheduling 4, Engagement 4. Where Section C contradicts Section B, believe Section C.</t>
         </is>
       </c>
-    </row>
-    <row r="32" ht="21" customHeight="1">
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>Covers essentially all of it</t>
-        </is>
-      </c>
-      <c r="D32" s="8" t="inlineStr"/>
     </row>
     <row r="33" ht="21" customHeight="1">
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Covers most of it</t>
+          <t>Most of it</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr"/>
@@ -1073,12 +1067,12 @@
     <row r="34" ht="21" customHeight="1">
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>Covers about half</t>
+          <t>More than half</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr"/>
@@ -1086,12 +1080,12 @@
     <row r="35" ht="21" customHeight="1">
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Covers a few pieces</t>
+          <t>About half</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr"/>
@@ -1099,12 +1093,12 @@
     <row r="36" ht="21" customHeight="1">
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>Touches one corner</t>
+          <t>Less than half</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr"/>
@@ -1112,60 +1106,60 @@
     <row r="37" ht="21" customHeight="1">
       <c r="B37" s="7" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>A corner of it</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="inlineStr"/>
+    </row>
+    <row r="38" ht="21" customHeight="1">
+      <c r="B38" s="7" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>Nothing here</t>
         </is>
       </c>
-      <c r="D37" s="8" t="inlineStr"/>
-    </row>
-    <row r="38" ht="28" customHeight="1">
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>Six rungs because most of these are point solutions, not suites. Expect the field to land between 1 and 3, and expect 4 and 5 to go unused — that lower spread is the useful part, and it is a finding in itself if nobody reaches half of an arena.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="10" customHeight="1"/>
-    <row r="40" ht="22" customHeight="1">
-      <c r="B40" s="4" t="inlineStr">
+      <c r="D38" s="8" t="inlineStr"/>
+    </row>
+    <row r="39" ht="28" customHeight="1">
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Most of it is the ceiling on purpose. The scope on our one-pager is original and these are point solutions, so nobody will cover all of it — a rung for that would sit unused and squeeze everyone else into the bottom half of the scale. All six rungs here are live.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="10" customHeight="1"/>
+    <row r="41" ht="22" customHeight="1">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>SECTION C  ·  SOPHISTICATION   —   one mark, 0 to 4</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="41" customHeight="1">
-      <c r="B41" s="5" t="inlineStr">
+    <row r="42" ht="41" customHeight="1">
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>How much of the work the product does. This is the Read / Assist / Control language already in our workbook. Score what the product does, not how much the vendor wrote about it — a short answer describing an optimiser still scores 4. How it does it is a demo question, not a reason to mark it down.</t>
         </is>
       </c>
-    </row>
-    <row r="42" ht="21" customHeight="1">
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C42" s="5" t="inlineStr">
-        <is>
-          <t>Runs it — decides across the whole picture, and re-decides when things change</t>
-        </is>
-      </c>
-      <c r="D42" s="8" t="inlineStr"/>
     </row>
     <row r="43" ht="21" customHeight="1">
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Recommends it — works out the answer and proposes it; a person confirms</t>
+          <t>Runs it — decides across the whole picture, and re-decides when things change</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr"/>
@@ -1173,12 +1167,12 @@
     <row r="44" ht="21" customHeight="1">
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>Checks it — applies rules and flags problems; a person still works it</t>
+          <t>Recommends it — works out the answer and proposes it; a person confirms</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr"/>
@@ -1186,12 +1180,12 @@
     <row r="45" ht="21" customHeight="1">
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Shows it — surfaces the information; a person does all the work</t>
+          <t>Checks it — applies rules and flags problems; a person still works it</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr"/>
@@ -1199,35 +1193,41 @@
     <row r="46" ht="21" customHeight="1">
       <c r="B46" s="7" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>Shows it — surfaces the information; a person does all the work</t>
+        </is>
+      </c>
+      <c r="D46" s="8" t="inlineStr"/>
+    </row>
+    <row r="47" ht="21" customHeight="1">
+      <c r="B47" s="7" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr">
+      <c r="C47" s="5" t="inlineStr">
         <is>
           <t>Not addressed</t>
         </is>
       </c>
-      <c r="D46" s="8" t="inlineStr"/>
-    </row>
-    <row r="47" ht="15" customHeight="1">
-      <c r="B47" s="5" t="inlineStr">
+      <c r="D47" s="8" t="inlineStr"/>
+    </row>
+    <row r="48" ht="15" customHeight="1">
+      <c r="B48" s="5" t="inlineStr">
         <is>
           <t>A 4 is not automatically what we want. Where we said Assist, a product that decides on its own is a risk worth a note.</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="10" customHeight="1"/>
-    <row r="49" ht="22" customHeight="1">
-      <c r="B49" s="4" t="inlineStr">
+    <row r="49" ht="10" customHeight="1"/>
+    <row r="50" ht="22" customHeight="1">
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>SECTION D  ·  CLINICIAN FIT   —   one mark, 0 to 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="28" customHeight="1">
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>One question only: how much say does the clinician have over their own schedule? Many clinicians come to home health for the control it gives them over their week, so this is the adoption risk.</t>
         </is>
       </c>
     </row>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>They can shape their own schedule, and the product learns from it</t>
+          <t>Strong fit</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr"/>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>They can decline or change an assignment themselves</t>
+          <t>Good fit</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr"/>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>They can raise it; someone else makes the change</t>
+          <t>Workable</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr"/>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>The schedule is set for them, with no way to change it</t>
+          <t>Poor fit</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr"/>
@@ -1299,14 +1299,14 @@
     <row r="56" ht="28" customHeight="1">
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>This runs opposite to Sophistication on purpose. A product that decides everything scores 4 there and 1 here — and that is the real trade in this purchase, not a contradiction. A vendor strong on both has solved something hard.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="28" customHeight="1">
+          <t>No descriptions here on purpose. Read D1 to D3 and give it your own read. We know how our clinicians work and what they will accept; a rubric that spelled out what earns a 4 would only substitute a guess for that.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="15" customHeight="1">
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>Whether they showed adoption data is not on this scale. It is a note, not a score — a product can be well designed for clinicians and simply be young.</t>
+          <t>Say why in the Notes, though — that one line is what a colleague reads when they score the same vendor differently.</t>
         </is>
       </c>
     </row>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>Shown whenever A1 scores under 12. Advancing means accepting an integration still to be built, on their timeline, at our risk.</t>
+          <t>Shown whenever the integration is not yet live. Advancing means accepting an integration still to be built, on their timeline, at our risk.</t>
         </is>
       </c>
       <c r="D78" s="8" t="inlineStr"/>
@@ -1527,26 +1527,26 @@
   </sheetData>
   <mergeCells count="21">
     <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B42:D42"/>
     <mergeCell ref="B67:D67"/>
+    <mergeCell ref="B23:D23"/>
     <mergeCell ref="B57:D57"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="B73:D73"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B49:D49"/>
-    <mergeCell ref="B40:D40"/>
     <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B30:D30"/>
     <mergeCell ref="B65:D65"/>
     <mergeCell ref="B68:D68"/>
     <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B32:D32"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B50:D50"/>
     <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B47:D47"/>
     <mergeCell ref="B59:D59"/>
     <mergeCell ref="B31:D31"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="B48:D48"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1711,67 +1711,67 @@
         </is>
       </c>
       <c r="E9" s="17">
-        <f>IFERROR(VLOOKUP(E14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(E19,1)),0)/5*10+IFERROR(VALUE(LEFT(E20,1)),0)/5*10+IFERROR(VALUE(LEFT(E21,1)),0)/5*10+IFERROR(VALUE(LEFT(E24,1)),0)/4*20+IFERROR(VALUE(LEFT(E28,1)),0)/4*10+IFERROR(VALUE(LEFT(E31,1)),0)/4*15</f>
+        <f>IFERROR(VLOOKUP(E14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(E19,1)),0)/5*12+IFERROR(VALUE(LEFT(E20,1)),0)/5*12+IFERROR(VALUE(LEFT(E21,1)),0)/5*12+IFERROR(VALUE(LEFT(E24,1)),0)/4*20+IFERROR(VALUE(LEFT(E28,1)),0)/4*12+IFERROR(VALUE(LEFT(E31,1)),0)/4*12</f>
         <v/>
       </c>
       <c r="F9" s="17">
-        <f>IFERROR(VLOOKUP(F14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(F19,1)),0)/5*10+IFERROR(VALUE(LEFT(F20,1)),0)/5*10+IFERROR(VALUE(LEFT(F21,1)),0)/5*10+IFERROR(VALUE(LEFT(F24,1)),0)/4*20+IFERROR(VALUE(LEFT(F28,1)),0)/4*10+IFERROR(VALUE(LEFT(F31,1)),0)/4*15</f>
+        <f>IFERROR(VLOOKUP(F14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(F19,1)),0)/5*12+IFERROR(VALUE(LEFT(F20,1)),0)/5*12+IFERROR(VALUE(LEFT(F21,1)),0)/5*12+IFERROR(VALUE(LEFT(F24,1)),0)/4*20+IFERROR(VALUE(LEFT(F28,1)),0)/4*12+IFERROR(VALUE(LEFT(F31,1)),0)/4*12</f>
         <v/>
       </c>
       <c r="G9" s="17">
-        <f>IFERROR(VLOOKUP(G14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(G19,1)),0)/5*10+IFERROR(VALUE(LEFT(G20,1)),0)/5*10+IFERROR(VALUE(LEFT(G21,1)),0)/5*10+IFERROR(VALUE(LEFT(G24,1)),0)/4*20+IFERROR(VALUE(LEFT(G28,1)),0)/4*10+IFERROR(VALUE(LEFT(G31,1)),0)/4*15</f>
+        <f>IFERROR(VLOOKUP(G14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(G19,1)),0)/5*12+IFERROR(VALUE(LEFT(G20,1)),0)/5*12+IFERROR(VALUE(LEFT(G21,1)),0)/5*12+IFERROR(VALUE(LEFT(G24,1)),0)/4*20+IFERROR(VALUE(LEFT(G28,1)),0)/4*12+IFERROR(VALUE(LEFT(G31,1)),0)/4*12</f>
         <v/>
       </c>
       <c r="H9" s="17">
-        <f>IFERROR(VLOOKUP(H14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(H19,1)),0)/5*10+IFERROR(VALUE(LEFT(H20,1)),0)/5*10+IFERROR(VALUE(LEFT(H21,1)),0)/5*10+IFERROR(VALUE(LEFT(H24,1)),0)/4*20+IFERROR(VALUE(LEFT(H28,1)),0)/4*10+IFERROR(VALUE(LEFT(H31,1)),0)/4*15</f>
+        <f>IFERROR(VLOOKUP(H14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(H19,1)),0)/5*12+IFERROR(VALUE(LEFT(H20,1)),0)/5*12+IFERROR(VALUE(LEFT(H21,1)),0)/5*12+IFERROR(VALUE(LEFT(H24,1)),0)/4*20+IFERROR(VALUE(LEFT(H28,1)),0)/4*12+IFERROR(VALUE(LEFT(H31,1)),0)/4*12</f>
         <v/>
       </c>
       <c r="I9" s="17">
-        <f>IFERROR(VLOOKUP(I14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(I19,1)),0)/5*10+IFERROR(VALUE(LEFT(I20,1)),0)/5*10+IFERROR(VALUE(LEFT(I21,1)),0)/5*10+IFERROR(VALUE(LEFT(I24,1)),0)/4*20+IFERROR(VALUE(LEFT(I28,1)),0)/4*10+IFERROR(VALUE(LEFT(I31,1)),0)/4*15</f>
+        <f>IFERROR(VLOOKUP(I14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(I19,1)),0)/5*12+IFERROR(VALUE(LEFT(I20,1)),0)/5*12+IFERROR(VALUE(LEFT(I21,1)),0)/5*12+IFERROR(VALUE(LEFT(I24,1)),0)/4*20+IFERROR(VALUE(LEFT(I28,1)),0)/4*12+IFERROR(VALUE(LEFT(I31,1)),0)/4*12</f>
         <v/>
       </c>
       <c r="J9" s="17">
-        <f>IFERROR(VLOOKUP(J14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(J19,1)),0)/5*10+IFERROR(VALUE(LEFT(J20,1)),0)/5*10+IFERROR(VALUE(LEFT(J21,1)),0)/5*10+IFERROR(VALUE(LEFT(J24,1)),0)/4*20+IFERROR(VALUE(LEFT(J28,1)),0)/4*10+IFERROR(VALUE(LEFT(J31,1)),0)/4*15</f>
+        <f>IFERROR(VLOOKUP(J14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(J19,1)),0)/5*12+IFERROR(VALUE(LEFT(J20,1)),0)/5*12+IFERROR(VALUE(LEFT(J21,1)),0)/5*12+IFERROR(VALUE(LEFT(J24,1)),0)/4*20+IFERROR(VALUE(LEFT(J28,1)),0)/4*12+IFERROR(VALUE(LEFT(J31,1)),0)/4*12</f>
         <v/>
       </c>
       <c r="K9" s="17">
-        <f>IFERROR(VLOOKUP(K14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(K19,1)),0)/5*10+IFERROR(VALUE(LEFT(K20,1)),0)/5*10+IFERROR(VALUE(LEFT(K21,1)),0)/5*10+IFERROR(VALUE(LEFT(K24,1)),0)/4*20+IFERROR(VALUE(LEFT(K28,1)),0)/4*10+IFERROR(VALUE(LEFT(K31,1)),0)/4*15</f>
+        <f>IFERROR(VLOOKUP(K14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(K19,1)),0)/5*12+IFERROR(VALUE(LEFT(K20,1)),0)/5*12+IFERROR(VALUE(LEFT(K21,1)),0)/5*12+IFERROR(VALUE(LEFT(K24,1)),0)/4*20+IFERROR(VALUE(LEFT(K28,1)),0)/4*12+IFERROR(VALUE(LEFT(K31,1)),0)/4*12</f>
         <v/>
       </c>
       <c r="L9" s="17">
-        <f>IFERROR(VLOOKUP(L14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(L19,1)),0)/5*10+IFERROR(VALUE(LEFT(L20,1)),0)/5*10+IFERROR(VALUE(LEFT(L21,1)),0)/5*10+IFERROR(VALUE(LEFT(L24,1)),0)/4*20+IFERROR(VALUE(LEFT(L28,1)),0)/4*10+IFERROR(VALUE(LEFT(L31,1)),0)/4*15</f>
+        <f>IFERROR(VLOOKUP(L14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(L19,1)),0)/5*12+IFERROR(VALUE(LEFT(L20,1)),0)/5*12+IFERROR(VALUE(LEFT(L21,1)),0)/5*12+IFERROR(VALUE(LEFT(L24,1)),0)/4*20+IFERROR(VALUE(LEFT(L28,1)),0)/4*12+IFERROR(VALUE(LEFT(L31,1)),0)/4*12</f>
         <v/>
       </c>
       <c r="M9" s="17">
-        <f>IFERROR(VLOOKUP(M14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(M19,1)),0)/5*10+IFERROR(VALUE(LEFT(M20,1)),0)/5*10+IFERROR(VALUE(LEFT(M21,1)),0)/5*10+IFERROR(VALUE(LEFT(M24,1)),0)/4*20+IFERROR(VALUE(LEFT(M28,1)),0)/4*10+IFERROR(VALUE(LEFT(M31,1)),0)/4*15</f>
+        <f>IFERROR(VLOOKUP(M14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(M19,1)),0)/5*12+IFERROR(VALUE(LEFT(M20,1)),0)/5*12+IFERROR(VALUE(LEFT(M21,1)),0)/5*12+IFERROR(VALUE(LEFT(M24,1)),0)/4*20+IFERROR(VALUE(LEFT(M28,1)),0)/4*12+IFERROR(VALUE(LEFT(M31,1)),0)/4*12</f>
         <v/>
       </c>
       <c r="N9" s="17">
-        <f>IFERROR(VLOOKUP(N14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(N19,1)),0)/5*10+IFERROR(VALUE(LEFT(N20,1)),0)/5*10+IFERROR(VALUE(LEFT(N21,1)),0)/5*10+IFERROR(VALUE(LEFT(N24,1)),0)/4*20+IFERROR(VALUE(LEFT(N28,1)),0)/4*10+IFERROR(VALUE(LEFT(N31,1)),0)/4*15</f>
+        <f>IFERROR(VLOOKUP(N14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(N19,1)),0)/5*12+IFERROR(VALUE(LEFT(N20,1)),0)/5*12+IFERROR(VALUE(LEFT(N21,1)),0)/5*12+IFERROR(VALUE(LEFT(N24,1)),0)/4*20+IFERROR(VALUE(LEFT(N28,1)),0)/4*12+IFERROR(VALUE(LEFT(N31,1)),0)/4*12</f>
         <v/>
       </c>
       <c r="O9" s="17">
-        <f>IFERROR(VLOOKUP(O14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(O19,1)),0)/5*10+IFERROR(VALUE(LEFT(O20,1)),0)/5*10+IFERROR(VALUE(LEFT(O21,1)),0)/5*10+IFERROR(VALUE(LEFT(O24,1)),0)/4*20+IFERROR(VALUE(LEFT(O28,1)),0)/4*10+IFERROR(VALUE(LEFT(O31,1)),0)/4*15</f>
+        <f>IFERROR(VLOOKUP(O14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(O19,1)),0)/5*12+IFERROR(VALUE(LEFT(O20,1)),0)/5*12+IFERROR(VALUE(LEFT(O21,1)),0)/5*12+IFERROR(VALUE(LEFT(O24,1)),0)/4*20+IFERROR(VALUE(LEFT(O28,1)),0)/4*12+IFERROR(VALUE(LEFT(O31,1)),0)/4*12</f>
         <v/>
       </c>
       <c r="P9" s="17">
-        <f>IFERROR(VLOOKUP(P14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(P19,1)),0)/5*10+IFERROR(VALUE(LEFT(P20,1)),0)/5*10+IFERROR(VALUE(LEFT(P21,1)),0)/5*10+IFERROR(VALUE(LEFT(P24,1)),0)/4*20+IFERROR(VALUE(LEFT(P28,1)),0)/4*10+IFERROR(VALUE(LEFT(P31,1)),0)/4*15</f>
+        <f>IFERROR(VLOOKUP(P14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(P19,1)),0)/5*12+IFERROR(VALUE(LEFT(P20,1)),0)/5*12+IFERROR(VALUE(LEFT(P21,1)),0)/5*12+IFERROR(VALUE(LEFT(P24,1)),0)/4*20+IFERROR(VALUE(LEFT(P28,1)),0)/4*12+IFERROR(VALUE(LEFT(P31,1)),0)/4*12</f>
         <v/>
       </c>
       <c r="Q9" s="17">
-        <f>IFERROR(VLOOKUP(Q14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(Q19,1)),0)/5*10+IFERROR(VALUE(LEFT(Q20,1)),0)/5*10+IFERROR(VALUE(LEFT(Q21,1)),0)/5*10+IFERROR(VALUE(LEFT(Q24,1)),0)/4*20+IFERROR(VALUE(LEFT(Q28,1)),0)/4*10+IFERROR(VALUE(LEFT(Q31,1)),0)/4*15</f>
+        <f>IFERROR(VLOOKUP(Q14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(Q19,1)),0)/5*12+IFERROR(VALUE(LEFT(Q20,1)),0)/5*12+IFERROR(VALUE(LEFT(Q21,1)),0)/5*12+IFERROR(VALUE(LEFT(Q24,1)),0)/4*20+IFERROR(VALUE(LEFT(Q28,1)),0)/4*12+IFERROR(VALUE(LEFT(Q31,1)),0)/4*12</f>
         <v/>
       </c>
       <c r="R9" s="17">
-        <f>IFERROR(VLOOKUP(R14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(R19,1)),0)/5*10+IFERROR(VALUE(LEFT(R20,1)),0)/5*10+IFERROR(VALUE(LEFT(R21,1)),0)/5*10+IFERROR(VALUE(LEFT(R24,1)),0)/4*20+IFERROR(VALUE(LEFT(R28,1)),0)/4*10+IFERROR(VALUE(LEFT(R31,1)),0)/4*15</f>
+        <f>IFERROR(VLOOKUP(R14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(R19,1)),0)/5*12+IFERROR(VALUE(LEFT(R20,1)),0)/5*12+IFERROR(VALUE(LEFT(R21,1)),0)/5*12+IFERROR(VALUE(LEFT(R24,1)),0)/4*20+IFERROR(VALUE(LEFT(R28,1)),0)/4*12+IFERROR(VALUE(LEFT(R31,1)),0)/4*12</f>
         <v/>
       </c>
       <c r="S9" s="17">
-        <f>IFERROR(VLOOKUP(S14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(S19,1)),0)/5*10+IFERROR(VALUE(LEFT(S20,1)),0)/5*10+IFERROR(VALUE(LEFT(S21,1)),0)/5*10+IFERROR(VALUE(LEFT(S24,1)),0)/4*20+IFERROR(VALUE(LEFT(S28,1)),0)/4*10+IFERROR(VALUE(LEFT(S31,1)),0)/4*15</f>
+        <f>IFERROR(VLOOKUP(S14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(S19,1)),0)/5*12+IFERROR(VALUE(LEFT(S20,1)),0)/5*12+IFERROR(VALUE(LEFT(S21,1)),0)/5*12+IFERROR(VALUE(LEFT(S24,1)),0)/4*20+IFERROR(VALUE(LEFT(S28,1)),0)/4*12+IFERROR(VALUE(LEFT(S31,1)),0)/4*12</f>
         <v/>
       </c>
       <c r="T9" s="17">
-        <f>IFERROR(VLOOKUP(T14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(T19,1)),0)/5*10+IFERROR(VALUE(LEFT(T20,1)),0)/5*10+IFERROR(VALUE(LEFT(T21,1)),0)/5*10+IFERROR(VALUE(LEFT(T24,1)),0)/4*20+IFERROR(VALUE(LEFT(T28,1)),0)/4*10+IFERROR(VALUE(LEFT(T31,1)),0)/4*15</f>
+        <f>IFERROR(VLOOKUP(T14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(T19,1)),0)/5*12+IFERROR(VALUE(LEFT(T20,1)),0)/5*12+IFERROR(VALUE(LEFT(T21,1)),0)/5*12+IFERROR(VALUE(LEFT(T24,1)),0)/4*20+IFERROR(VALUE(LEFT(T28,1)),0)/4*12+IFERROR(VALUE(LEFT(T31,1)),0)/4*12</f>
         <v/>
       </c>
     </row>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="D14" s="16" t="inlineStr">
         <is>
-          <t>Pick one line  ·  25 points</t>
+          <t>Pick one line  ·  20 points</t>
         </is>
       </c>
       <c r="E14" s="24" t="n"/>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="D19" s="16" t="inlineStr">
         <is>
-          <t>Workforce supply · availability &amp; reach · the capacity math  ·  0–5  ·  10 points</t>
+          <t>Workforce supply · availability &amp; reach · the capacity math  ·  0–5  ·  12 points</t>
         </is>
       </c>
       <c r="E19" s="28" t="n"/>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="D20" s="16" t="inlineStr">
         <is>
-          <t>Demand · matching · routing &amp; the week · exceptions  ·  0–5  ·  10 points</t>
+          <t>Demand · matching · routing &amp; the week · exceptions  ·  0–5  ·  12 points</t>
         </is>
       </c>
       <c r="E20" s="28" t="n"/>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="D21" s="16" t="inlineStr">
         <is>
-          <t>Before the visit · when plans change · incentives · care team  ·  0–5  ·  10 points</t>
+          <t>Before the visit · when plans change · incentives · care team  ·  0–5  ·  12 points</t>
         </is>
       </c>
       <c r="E21" s="28" t="n"/>
@@ -2232,7 +2232,7 @@
       </c>
       <c r="D28" s="16" t="inlineStr">
         <is>
-          <t>How much say the clinician has  ·  0–4  ·  10 points</t>
+          <t>Our read of fit  ·  0–4  ·  12 points</t>
         </is>
       </c>
       <c r="E28" s="28" t="n"/>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="D31" s="16" t="inlineStr">
         <is>
-          <t>Terms offered, and the change-management story  ·  0–4  ·  15 points</t>
+          <t>Terms offered, and the change-management story  ·  0–4  ·  12 points</t>
         </is>
       </c>
       <c r="E31" s="28" t="n"/>
@@ -2468,13 +2468,13 @@
     <dataValidation sqref="E14:T14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="A1 — Home Care Home Base" prompt="Pick one line. Ambiguous? Take the lower one and say so in Notes." type="list">
       <formula1>=Lists!$B$2:$B$7</formula1>
     </dataValidation>
-    <dataValidation sqref="E19:T19 E20:T20 E21:T21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Scope, 0–5" prompt="How much of this arena they cover. Most point solutions land between 1 and 3 — that spread is the useful part." type="list">
+    <dataValidation sqref="E19:T19 E20:T20 E21:T21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Scope, 0–5" prompt="How much of this arena they cover. Most of it is the ceiling — our spec is original, so nobody covers all of it." type="list">
       <formula1>=Lists!$E$2:$E$7</formula1>
     </dataValidation>
     <dataValidation sqref="E24:T24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Sophistication, 0–4" prompt="1 shows it · 2 checks it · 3 recommends it · 4 runs it. Score what the product does, not how much they wrote about it." type="list">
       <formula1>=Lists!$G$2:$G$6</formula1>
     </dataValidation>
-    <dataValidation sqref="E28:T28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Clinician fit, 0–4" prompt="How much say does the clinician have over their own schedule? This runs opposite to Sophistication on purpose." type="list">
+    <dataValidation sqref="E28:T28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Clinician fit, 0–4" prompt="Read D1 to D3 and give it your own read of fit. There is no checklist here on purpose." type="list">
       <formula1>=Lists!$I$2:$I$6</formula1>
     </dataValidation>
     <dataValidation sqref="E31:T31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Partnership, 0–4" prompt="Specific terms means design-partner pricing, co-development, roadmap governance or a revenue share. A discount is a discount." type="list">
@@ -2539,11 +2539,11 @@
     <row r="2">
       <c r="B2" t="inlineStr">
         <is>
-          <t>Live — reads and writes, several customers</t>
+          <t>Live — established customer base</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -2569,15 +2569,15 @@
     <row r="3">
       <c r="B3" t="inlineStr">
         <is>
-          <t>Live — one customer, or one-way only</t>
+          <t>Live — small customer base</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1 — Touches one corner</t>
+          <t>1 — A corner of it</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1 — The schedule is set for them, with no way to change it</t>
+          <t>1 — Poor fit</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -2599,7 +2599,7 @@
     <row r="4">
       <c r="B4" t="inlineStr">
         <is>
-          <t>Live — via a partner, flat file or screen scraping</t>
+          <t>Live — through a partner</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2 — Covers a few pieces</t>
+          <t>2 — Less than half</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2 — They can raise it; someone else makes the change</t>
+          <t>2 — Workable</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2637,7 +2637,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3 — Covers about half</t>
+          <t>3 — About half</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3 — They can decline or change an assignment themselves</t>
+          <t>3 — Good fit</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2659,7 +2659,7 @@
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
-          <t>Roadmap — no date</t>
+          <t>On the roadmap — no date</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -2667,7 +2667,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>4 — Covers most of it</t>
+          <t>4 — More than half</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4 — They can shape their own schedule, and the product learns from it</t>
+          <t>4 — Strong fit</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>5 — Covers essentially all of it</t>
+          <t>5 — Most of it</t>
         </is>
       </c>
     </row>

--- a/agents/compassus-capacity-pm/vendor-evaluation/Vendor-Scorecard-SIMPLE.xlsx
+++ b/agents/compassus-capacity-pm/vendor-evaluation/Vendor-Scorecard-SIMPLE.xlsx
@@ -734,7 +734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D80"/>
+  <dimension ref="B2:D81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1318,28 +1318,22 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="21" customHeight="1">
-      <c r="B60" s="7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C60" s="5" t="inlineStr">
-        <is>
-          <t>Specific terms and a real change-management story</t>
-        </is>
-      </c>
-      <c r="D60" s="8" t="inlineStr"/>
+    <row r="60" ht="28" customHeight="1">
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>What we are looking for is a company with the willingness and the environment to build this with us around our needs — and open to us holding equity, so that a product for the general market becomes a real possibility. The rungs run from vendor to co-owner.</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="21" customHeight="1">
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>One of the two</t>
+          <t>Open to equity or a stake in what we build, and set up to build it with us</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr"/>
@@ -1347,12 +1341,12 @@
     <row r="62" ht="21" customHeight="1">
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>Willing, but no structure offered</t>
+          <t>Ready to build to our needs as a design partner; ownership not addressed</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr"/>
@@ -1360,12 +1354,12 @@
     <row r="63" ht="21" customHeight="1">
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>Standard commercial relationship only</t>
+          <t>Will take our input, but they own the roadmap and the product</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr"/>
@@ -1373,60 +1367,60 @@
     <row r="64" ht="21" customHeight="1">
       <c r="B64" s="7" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>A standard customer relationship — we buy what already exists</t>
+        </is>
+      </c>
+      <c r="D64" s="8" t="inlineStr"/>
+    </row>
+    <row r="65" ht="21" customHeight="1">
+      <c r="B65" s="7" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C64" s="5" t="inlineStr">
-        <is>
-          <t>Didn't answer</t>
-        </is>
-      </c>
-      <c r="D64" s="8" t="inlineStr"/>
-    </row>
-    <row r="65" ht="15" customHeight="1">
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>Specific terms means design-partner pricing, co-development, roadmap governance, or a revenue or equity share. A discount is a discount.</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="10" customHeight="1"/>
-    <row r="67" ht="22" customHeight="1">
-      <c r="B67" s="4" t="inlineStr">
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>Not answered</t>
+        </is>
+      </c>
+      <c r="D65" s="8" t="inlineStr"/>
+    </row>
+    <row r="66" ht="28" customHeight="1">
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>Read all four E answers, not only E2. A vendor who never mentions ownership but describes a real co-development practice is a 3, and worth the conversation. A discount is a discount.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="10" customHeight="1"/>
+    <row r="68" ht="22" customHeight="1">
+      <c r="B68" s="4" t="inlineStr">
         <is>
           <t>THE THREE QUESTIONS THAT RAISE A FLAG INSTEAD</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="28" customHeight="1">
-      <c r="B68" s="5" t="inlineStr">
+    <row r="69" ht="28" customHeight="1">
+      <c r="B69" s="5" t="inlineStr">
         <is>
           <t>A vendor with no continuity commitment should be stopped and asked, not quietly docked a few points. Same for a vendor with one customer, or impact numbers with no baseline. Mark these OK, Watch or STOP-CHECK.</t>
         </is>
       </c>
-    </row>
-    <row r="69" ht="21" customHeight="1">
-      <c r="B69" s="7" t="inlineStr">
-        <is>
-          <t>A2</t>
-        </is>
-      </c>
-      <c r="C69" s="5" t="inlineStr">
-        <is>
-          <t>Customers, scale and references — STOP-CHECK if one customer, or no references offered</t>
-        </is>
-      </c>
-      <c r="D69" s="8" t="inlineStr"/>
     </row>
     <row r="70" ht="21" customHeight="1">
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>A3</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>Measured impact — Watch if claimed with no baseline or period</t>
+          <t>Customers, scale and references — STOP-CHECK if one customer, or no references offered</t>
         </is>
       </c>
       <c r="D70" s="8" t="inlineStr"/>
@@ -1434,46 +1428,46 @@
     <row r="71" ht="21" customHeight="1">
       <c r="B71" s="7" t="inlineStr">
         <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>Measured impact — Watch if claimed with no baseline or period</t>
+        </is>
+      </c>
+      <c r="D71" s="8" t="inlineStr"/>
+    </row>
+    <row r="72" ht="21" customHeight="1">
+      <c r="B72" s="7" t="inlineStr">
+        <is>
           <t>C6</t>
         </is>
       </c>
-      <c r="C71" s="5" t="inlineStr">
+      <c r="C72" s="5" t="inlineStr">
         <is>
           <t>When your product is down — STOP-CHECK if no uptime figure or contractual commitment</t>
         </is>
       </c>
-      <c r="D71" s="8" t="inlineStr"/>
-    </row>
-    <row r="72" ht="10" customHeight="1"/>
-    <row r="73" ht="22" customHeight="1">
-      <c r="B73" s="4" t="inlineStr">
+      <c r="D72" s="8" t="inlineStr"/>
+    </row>
+    <row r="73" ht="10" customHeight="1"/>
+    <row r="74" ht="22" customHeight="1">
+      <c r="B74" s="4" t="inlineStr">
         <is>
           <t>BANDS   —   the same as the full scorecard</t>
         </is>
       </c>
-    </row>
-    <row r="74" ht="21" customHeight="1">
-      <c r="B74" s="7" t="inlineStr">
-        <is>
-          <t>80–100</t>
-        </is>
-      </c>
-      <c r="C74" s="5" t="inlineStr">
-        <is>
-          <t>Advance — demo, references, deeper diligence</t>
-        </is>
-      </c>
-      <c r="D74" s="8" t="inlineStr"/>
     </row>
     <row r="75" ht="21" customHeight="1">
       <c r="B75" s="7" t="inlineStr">
         <is>
-          <t>65–79</t>
+          <t>80–100</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>Consider — only if something specific justifies it</t>
+          <t>Advance — demo, references, deeper diligence</t>
         </is>
       </c>
       <c r="D75" s="8" t="inlineStr"/>
@@ -1481,12 +1475,12 @@
     <row r="76" ht="21" customHeight="1">
       <c r="B76" s="7" t="inlineStr">
         <is>
-          <t>50–64</t>
+          <t>65–79</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>Hold — park unless the field thins</t>
+          <t>Consider — only if something specific justifies it</t>
         </is>
       </c>
       <c r="D76" s="8" t="inlineStr"/>
@@ -1494,47 +1488,60 @@
     <row r="77" ht="21" customHeight="1">
       <c r="B77" s="7" t="inlineStr">
         <is>
+          <t>50–64</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>Hold — park unless the field thins</t>
+        </is>
+      </c>
+      <c r="D77" s="8" t="inlineStr"/>
+    </row>
+    <row r="78" ht="21" customHeight="1">
+      <c r="B78" s="7" t="inlineStr">
+        <is>
           <t>&lt; 50</t>
         </is>
       </c>
-      <c r="C77" s="5" t="inlineStr">
+      <c r="C78" s="5" t="inlineStr">
         <is>
           <t>Decline — close out with thanks</t>
         </is>
       </c>
-      <c r="D77" s="8" t="inlineStr"/>
-    </row>
-    <row r="78" ht="34" customHeight="1">
-      <c r="B78" s="7" t="inlineStr">
+      <c r="D78" s="8" t="inlineStr"/>
+    </row>
+    <row r="79" ht="34" customHeight="1">
+      <c r="B79" s="7" t="inlineStr">
         <is>
           <t>Conditional</t>
         </is>
       </c>
-      <c r="C78" s="5" t="inlineStr">
+      <c r="C79" s="5" t="inlineStr">
         <is>
           <t>Shown whenever the integration is not yet live. Advancing means accepting an integration still to be built, on their timeline, at our risk.</t>
         </is>
       </c>
-      <c r="D78" s="8" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="B80" s="10" t="inlineStr">
+      <c r="D79" s="8" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="B81" s="10" t="inlineStr">
         <is>
           <t>Fast scorecard v2.0  ·  questionnaire form_version 2026-08-19</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="22">
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B67:D67"/>
+    <mergeCell ref="B60:D60"/>
     <mergeCell ref="B23:D23"/>
     <mergeCell ref="B57:D57"/>
     <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B73:D73"/>
+    <mergeCell ref="B69:D69"/>
     <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B65:D65"/>
+    <mergeCell ref="B74:D74"/>
     <mergeCell ref="B68:D68"/>
     <mergeCell ref="B41:D41"/>
     <mergeCell ref="B32:D32"/>
@@ -1542,6 +1549,7 @@
     <mergeCell ref="B50:D50"/>
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="B59:D59"/>
+    <mergeCell ref="B66:D66"/>
     <mergeCell ref="B31:D31"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="B56:D56"/>
@@ -2272,7 +2280,7 @@
       </c>
       <c r="D31" s="16" t="inlineStr">
         <is>
-          <t>Terms offered, and the change-management story  ·  0–4  ·  12 points</t>
+          <t>Willing to build it with us, and open to a stake  ·  0–4  ·  12 points</t>
         </is>
       </c>
       <c r="E31" s="28" t="n"/>
@@ -2477,7 +2485,7 @@
     <dataValidation sqref="E28:T28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Clinician fit, 0–4" prompt="Read D1 to D3 and give it your own read of fit. There is no checklist here on purpose." type="list">
       <formula1>=Lists!$I$2:$I$6</formula1>
     </dataValidation>
-    <dataValidation sqref="E31:T31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Partnership, 0–4" prompt="Specific terms means design-partner pricing, co-development, roadmap governance or a revenue share. A discount is a discount." type="list">
+    <dataValidation sqref="E31:T31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Partnership, 0–4" prompt="Are they able and willing to build this with us, and open to us holding a stake in what a wider market might buy? A discount is a discount." type="list">
       <formula1>=Lists!$K$2:$K$6</formula1>
     </dataValidation>
     <dataValidation sqref="E15:T15 E16:T16 E25:T25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Flag" prompt="A stop-check is resolved before advancing, not traded against points." type="list">
@@ -2562,7 +2570,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0 — Didn't answer</t>
+          <t>0 — Not answered</t>
         </is>
       </c>
     </row>
@@ -2592,7 +2600,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1 — Standard commercial relationship only</t>
+          <t>1 — A standard customer relationship — we buy what already exists</t>
         </is>
       </c>
     </row>
@@ -2622,7 +2630,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2 — Willing, but no structure offered</t>
+          <t>2 — Will take our input, but they own the roadmap and the product</t>
         </is>
       </c>
     </row>
@@ -2652,7 +2660,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>3 — Specific terms, or a real change-management story</t>
+          <t>3 — Ready to build to our needs as a design partner; ownership not addressed</t>
         </is>
       </c>
     </row>
@@ -2682,7 +2690,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>4 — Specific terms and a real change-management story</t>
+          <t>4 — Open to equity or a stake in what we build, and set up to build it with us</t>
         </is>
       </c>
     </row>

--- a/agents/compassus-capacity-pm/vendor-evaluation/Vendor-Scorecard-SIMPLE.xlsx
+++ b/agents/compassus-capacity-pm/vendor-evaluation/Vendor-Scorecard-SIMPLE.xlsx
@@ -734,7 +734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D81"/>
+  <dimension ref="B2:D82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -882,7 +882,7 @@
     <row r="17" ht="21" customHeight="1">
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>C1–C5, C7</t>
+          <t>Section C</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -1047,32 +1047,26 @@
     <row r="32" ht="28" customHeight="1">
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Read the eleven areas each vendor rated themselves on, then give one mark per arena. Capacity has 3 areas, Scheduling 4, Engagement 4. Where Section C contradicts Section B, believe Section C.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="21" customHeight="1">
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>Most of it</t>
-        </is>
-      </c>
-      <c r="D33" s="8" t="inlineStr"/>
+          <t>Read the eleven areas each vendor rated themselves on, then give one mark per arena. The areas in each arena are printed on the row, so the checklist is in front of you. Where Section C contradicts Section B, believe Section C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="41" customHeight="1">
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>The mark is your read of how much of that arena — as our one-pager describes it — the product reaches. It is not a count of areas: Capacity has 3 and the others 4, so counting would never divide cleanly, and an area covered thinly is not the same as one covered properly. Weigh breadth and depth together.</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="21" customHeight="1">
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>More than half</t>
+          <t>Most of it</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr"/>
@@ -1080,12 +1074,12 @@
     <row r="35" ht="21" customHeight="1">
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>About half</t>
+          <t>More than half</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr"/>
@@ -1093,12 +1087,12 @@
     <row r="36" ht="21" customHeight="1">
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>Less than half</t>
+          <t>About half</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr"/>
@@ -1106,12 +1100,12 @@
     <row r="37" ht="21" customHeight="1">
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>A corner of it</t>
+          <t>Less than half</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr"/>
@@ -1119,60 +1113,60 @@
     <row r="38" ht="21" customHeight="1">
       <c r="B38" s="7" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>A corner of it</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="inlineStr"/>
+    </row>
+    <row r="39" ht="21" customHeight="1">
+      <c r="B39" s="7" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>Nothing here</t>
         </is>
       </c>
-      <c r="D38" s="8" t="inlineStr"/>
-    </row>
-    <row r="39" ht="28" customHeight="1">
-      <c r="B39" s="5" t="inlineStr">
+      <c r="D39" s="8" t="inlineStr"/>
+    </row>
+    <row r="40" ht="28" customHeight="1">
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>Most of it is the ceiling on purpose. The scope on our one-pager is original and these are point solutions, so nobody will cover all of it — a rung for that would sit unused and squeeze everyone else into the bottom half of the scale. All six rungs here are live.</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="10" customHeight="1"/>
-    <row r="41" ht="22" customHeight="1">
-      <c r="B41" s="4" t="inlineStr">
+    <row r="41" ht="10" customHeight="1"/>
+    <row r="42" ht="22" customHeight="1">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>SECTION C  ·  SOPHISTICATION   —   one mark, 0 to 4</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="41" customHeight="1">
-      <c r="B42" s="5" t="inlineStr">
+    <row r="43" ht="41" customHeight="1">
+      <c r="B43" s="5" t="inlineStr">
         <is>
           <t>How much of the work the product does. This is the Read / Assist / Control language already in our workbook. Score what the product does, not how much the vendor wrote about it — a short answer describing an optimiser still scores 4. How it does it is a demo question, not a reason to mark it down.</t>
         </is>
       </c>
-    </row>
-    <row r="43" ht="21" customHeight="1">
-      <c r="B43" s="7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C43" s="5" t="inlineStr">
-        <is>
-          <t>Runs it — decides across the whole picture, and re-decides when things change</t>
-        </is>
-      </c>
-      <c r="D43" s="8" t="inlineStr"/>
     </row>
     <row r="44" ht="21" customHeight="1">
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>Recommends it — works out the answer and proposes it; a person confirms</t>
+          <t>Runs it — decides across the whole picture, and re-decides when things change</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr"/>
@@ -1180,12 +1174,12 @@
     <row r="45" ht="21" customHeight="1">
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Checks it — applies rules and flags problems; a person still works it</t>
+          <t>Recommends it — works out the answer and proposes it; a person confirms</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr"/>
@@ -1193,12 +1187,12 @@
     <row r="46" ht="21" customHeight="1">
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>Shows it — surfaces the information; a person does all the work</t>
+          <t>Checks it — applies rules and flags problems; a person still works it</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr"/>
@@ -1206,53 +1200,53 @@
     <row r="47" ht="21" customHeight="1">
       <c r="B47" s="7" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Shows it — surfaces the information; a person does all the work</t>
+        </is>
+      </c>
+      <c r="D47" s="8" t="inlineStr"/>
+    </row>
+    <row r="48" ht="21" customHeight="1">
+      <c r="B48" s="7" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
         <is>
           <t>Not addressed</t>
         </is>
       </c>
-      <c r="D47" s="8" t="inlineStr"/>
-    </row>
-    <row r="48" ht="15" customHeight="1">
-      <c r="B48" s="5" t="inlineStr">
+      <c r="D48" s="8" t="inlineStr"/>
+    </row>
+    <row r="49" ht="15" customHeight="1">
+      <c r="B49" s="5" t="inlineStr">
         <is>
           <t>A 4 is not automatically what we want. Where we said Assist, a product that decides on its own is a risk worth a note.</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="10" customHeight="1"/>
-    <row r="50" ht="22" customHeight="1">
-      <c r="B50" s="4" t="inlineStr">
+    <row r="50" ht="10" customHeight="1"/>
+    <row r="51" ht="22" customHeight="1">
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>SECTION D  ·  CLINICIAN FIT   —   one mark, 0 to 4</t>
         </is>
       </c>
-    </row>
-    <row r="51" ht="21" customHeight="1">
-      <c r="B51" s="7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C51" s="5" t="inlineStr">
-        <is>
-          <t>Strong fit</t>
-        </is>
-      </c>
-      <c r="D51" s="8" t="inlineStr"/>
     </row>
     <row r="52" ht="21" customHeight="1">
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>Good fit</t>
+          <t>Strong fit</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr"/>
@@ -1260,12 +1254,12 @@
     <row r="53" ht="21" customHeight="1">
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>Workable</t>
+          <t>Good fit</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr"/>
@@ -1273,12 +1267,12 @@
     <row r="54" ht="21" customHeight="1">
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>Poor fit</t>
+          <t>Workable</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr"/>
@@ -1286,67 +1280,67 @@
     <row r="55" ht="21" customHeight="1">
       <c r="B55" s="7" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>Poor fit</t>
+        </is>
+      </c>
+      <c r="D55" s="8" t="inlineStr"/>
+    </row>
+    <row r="56" ht="21" customHeight="1">
+      <c r="B56" s="7" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C55" s="5" t="inlineStr">
+      <c r="C56" s="5" t="inlineStr">
         <is>
           <t>Not answered</t>
         </is>
       </c>
-      <c r="D55" s="8" t="inlineStr"/>
-    </row>
-    <row r="56" ht="28" customHeight="1">
-      <c r="B56" s="5" t="inlineStr">
+      <c r="D56" s="8" t="inlineStr"/>
+    </row>
+    <row r="57" ht="28" customHeight="1">
+      <c r="B57" s="5" t="inlineStr">
         <is>
           <t>No descriptions here on purpose. Read D1 to D3 and give it your own read. We know how our clinicians work and what they will accept; a rubric that spelled out what earns a 4 would only substitute a guess for that.</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="15" customHeight="1">
-      <c r="B57" s="5" t="inlineStr">
+    <row r="58" ht="15" customHeight="1">
+      <c r="B58" s="5" t="inlineStr">
         <is>
           <t>Say why in the Notes, though — that one line is what a colleague reads when they score the same vendor differently.</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="10" customHeight="1"/>
-    <row r="59" ht="22" customHeight="1">
-      <c r="B59" s="4" t="inlineStr">
+    <row r="59" ht="10" customHeight="1"/>
+    <row r="60" ht="22" customHeight="1">
+      <c r="B60" s="4" t="inlineStr">
         <is>
           <t>SECTION E  ·  PARTNERSHIP   —   one mark, 0 to 4</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="28" customHeight="1">
-      <c r="B60" s="5" t="inlineStr">
+    <row r="61" ht="28" customHeight="1">
+      <c r="B61" s="5" t="inlineStr">
         <is>
           <t>What we are looking for is a company with the willingness and the environment to build this with us around our needs — and open to us holding equity, so that a product for the general market becomes a real possibility. The rungs run from vendor to co-owner.</t>
         </is>
       </c>
-    </row>
-    <row r="61" ht="21" customHeight="1">
-      <c r="B61" s="7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C61" s="5" t="inlineStr">
-        <is>
-          <t>Open to equity or a stake in what we build, and set up to build it with us</t>
-        </is>
-      </c>
-      <c r="D61" s="8" t="inlineStr"/>
     </row>
     <row r="62" ht="21" customHeight="1">
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>Ready to build to our needs as a design partner; ownership not addressed</t>
+          <t>Open to equity or a stake in what we build, and set up to build it with us</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr"/>
@@ -1354,12 +1348,12 @@
     <row r="63" ht="21" customHeight="1">
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>Will take our input, but they own the roadmap and the product</t>
+          <t>Ready to build to our needs as a design partner; ownership not addressed</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr"/>
@@ -1367,12 +1361,12 @@
     <row r="64" ht="21" customHeight="1">
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>A standard customer relationship — we buy what already exists</t>
+          <t>Will take our input, but they own the roadmap and the product</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr"/>
@@ -1380,60 +1374,60 @@
     <row r="65" ht="21" customHeight="1">
       <c r="B65" s="7" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>A standard customer relationship — we buy what already exists</t>
+        </is>
+      </c>
+      <c r="D65" s="8" t="inlineStr"/>
+    </row>
+    <row r="66" ht="21" customHeight="1">
+      <c r="B66" s="7" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C65" s="5" t="inlineStr">
+      <c r="C66" s="5" t="inlineStr">
         <is>
           <t>Not answered</t>
         </is>
       </c>
-      <c r="D65" s="8" t="inlineStr"/>
-    </row>
-    <row r="66" ht="28" customHeight="1">
-      <c r="B66" s="5" t="inlineStr">
+      <c r="D66" s="8" t="inlineStr"/>
+    </row>
+    <row r="67" ht="28" customHeight="1">
+      <c r="B67" s="5" t="inlineStr">
         <is>
           <t>Read all four E answers, not only E2. A vendor who never mentions ownership but describes a real co-development practice is a 3, and worth the conversation. A discount is a discount.</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="10" customHeight="1"/>
-    <row r="68" ht="22" customHeight="1">
-      <c r="B68" s="4" t="inlineStr">
+    <row r="68" ht="10" customHeight="1"/>
+    <row r="69" ht="22" customHeight="1">
+      <c r="B69" s="4" t="inlineStr">
         <is>
           <t>THE THREE QUESTIONS THAT RAISE A FLAG INSTEAD</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="28" customHeight="1">
-      <c r="B69" s="5" t="inlineStr">
+    <row r="70" ht="28" customHeight="1">
+      <c r="B70" s="5" t="inlineStr">
         <is>
           <t>A vendor with no continuity commitment should be stopped and asked, not quietly docked a few points. Same for a vendor with one customer, or impact numbers with no baseline. Mark these OK, Watch or STOP-CHECK.</t>
         </is>
       </c>
-    </row>
-    <row r="70" ht="21" customHeight="1">
-      <c r="B70" s="7" t="inlineStr">
-        <is>
-          <t>A2</t>
-        </is>
-      </c>
-      <c r="C70" s="5" t="inlineStr">
-        <is>
-          <t>Customers, scale and references — STOP-CHECK if one customer, or no references offered</t>
-        </is>
-      </c>
-      <c r="D70" s="8" t="inlineStr"/>
     </row>
     <row r="71" ht="21" customHeight="1">
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>A3</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>Measured impact — Watch if claimed with no baseline or period</t>
+          <t>Customers, scale and references — STOP-CHECK if one customer, or no references offered</t>
         </is>
       </c>
       <c r="D71" s="8" t="inlineStr"/>
@@ -1441,46 +1435,46 @@
     <row r="72" ht="21" customHeight="1">
       <c r="B72" s="7" t="inlineStr">
         <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>Measured impact — Watch if claimed with no baseline or period</t>
+        </is>
+      </c>
+      <c r="D72" s="8" t="inlineStr"/>
+    </row>
+    <row r="73" ht="21" customHeight="1">
+      <c r="B73" s="7" t="inlineStr">
+        <is>
           <t>C6</t>
         </is>
       </c>
-      <c r="C72" s="5" t="inlineStr">
+      <c r="C73" s="5" t="inlineStr">
         <is>
           <t>When your product is down — STOP-CHECK if no uptime figure or contractual commitment</t>
         </is>
       </c>
-      <c r="D72" s="8" t="inlineStr"/>
-    </row>
-    <row r="73" ht="10" customHeight="1"/>
-    <row r="74" ht="22" customHeight="1">
-      <c r="B74" s="4" t="inlineStr">
+      <c r="D73" s="8" t="inlineStr"/>
+    </row>
+    <row r="74" ht="10" customHeight="1"/>
+    <row r="75" ht="22" customHeight="1">
+      <c r="B75" s="4" t="inlineStr">
         <is>
           <t>BANDS   —   the same as the full scorecard</t>
         </is>
       </c>
-    </row>
-    <row r="75" ht="21" customHeight="1">
-      <c r="B75" s="7" t="inlineStr">
-        <is>
-          <t>80–100</t>
-        </is>
-      </c>
-      <c r="C75" s="5" t="inlineStr">
-        <is>
-          <t>Advance — demo, references, deeper diligence</t>
-        </is>
-      </c>
-      <c r="D75" s="8" t="inlineStr"/>
     </row>
     <row r="76" ht="21" customHeight="1">
       <c r="B76" s="7" t="inlineStr">
         <is>
-          <t>65–79</t>
+          <t>80–100</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>Consider — only if something specific justifies it</t>
+          <t>Advance — demo, references, deeper diligence</t>
         </is>
       </c>
       <c r="D76" s="8" t="inlineStr"/>
@@ -1488,12 +1482,12 @@
     <row r="77" ht="21" customHeight="1">
       <c r="B77" s="7" t="inlineStr">
         <is>
-          <t>50–64</t>
+          <t>65–79</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>Hold — park unless the field thins</t>
+          <t>Consider — only if something specific justifies it</t>
         </is>
       </c>
       <c r="D77" s="8" t="inlineStr"/>
@@ -1501,60 +1495,74 @@
     <row r="78" ht="21" customHeight="1">
       <c r="B78" s="7" t="inlineStr">
         <is>
+          <t>50–64</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>Hold — park unless the field thins</t>
+        </is>
+      </c>
+      <c r="D78" s="8" t="inlineStr"/>
+    </row>
+    <row r="79" ht="21" customHeight="1">
+      <c r="B79" s="7" t="inlineStr">
+        <is>
           <t>&lt; 50</t>
         </is>
       </c>
-      <c r="C78" s="5" t="inlineStr">
+      <c r="C79" s="5" t="inlineStr">
         <is>
           <t>Decline — close out with thanks</t>
         </is>
       </c>
-      <c r="D78" s="8" t="inlineStr"/>
-    </row>
-    <row r="79" ht="34" customHeight="1">
-      <c r="B79" s="7" t="inlineStr">
+      <c r="D79" s="8" t="inlineStr"/>
+    </row>
+    <row r="80" ht="34" customHeight="1">
+      <c r="B80" s="7" t="inlineStr">
         <is>
           <t>Conditional</t>
         </is>
       </c>
-      <c r="C79" s="5" t="inlineStr">
+      <c r="C80" s="5" t="inlineStr">
         <is>
           <t>Shown whenever the integration is not yet live. Advancing means accepting an integration still to be built, on their timeline, at our risk.</t>
         </is>
       </c>
-      <c r="D79" s="8" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="B81" s="10" t="inlineStr">
+      <c r="D80" s="8" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="B82" s="10" t="inlineStr">
         <is>
           <t>Fast scorecard v2.0  ·  questionnaire form_version 2026-08-19</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="23">
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="B42:D42"/>
     <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B67:D67"/>
     <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B61:D61"/>
     <mergeCell ref="B57:D57"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="B69:D69"/>
+    <mergeCell ref="B49:D49"/>
+    <mergeCell ref="B40:D40"/>
     <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B51:D51"/>
+    <mergeCell ref="B33:D33"/>
     <mergeCell ref="B32:D32"/>
     <mergeCell ref="B4:D4"/>
-    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B75:D75"/>
     <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B59:D59"/>
-    <mergeCell ref="B66:D66"/>
     <mergeCell ref="B31:D31"/>
     <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B43:D43"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2157,7 +2165,7 @@
     <row r="24" ht="24" customHeight="1">
       <c r="B24" s="31" t="inlineStr">
         <is>
-          <t>C1–C5, C7</t>
+          <t>Section C</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">

--- a/agents/compassus-capacity-pm/vendor-evaluation/Vendor-Scorecard-SIMPLE.xlsx
+++ b/agents/compassus-capacity-pm/vendor-evaluation/Vendor-Scorecard-SIMPLE.xlsx
@@ -760,7 +760,7 @@
     <row r="4">
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>The questionnaire is the rubric. Read the return top to bottom and fill the sheet top to bottom. Seven marks a vendor, about two minutes.</t>
+          <t>The questionnaire is the rubric. Read the return top to bottom and fill the sheet top to bottom. Seven marks a vendor.</t>
         </is>
       </c>
     </row>

--- a/agents/compassus-capacity-pm/vendor-evaluation/Vendor-Scorecard-SIMPLE.xlsx
+++ b/agents/compassus-capacity-pm/vendor-evaluation/Vendor-Scorecard-SIMPLE.xlsx
@@ -7,9 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Start Here" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Example" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Scorecard" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Lists" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet name="Start Here" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Lists" sheetId="4" state="hidden" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -244,29 +245,6 @@
   <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -276,6 +254,9 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -344,6 +325,26 @@
     <xf numFmtId="0" fontId="15" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -730,17 +731,33 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00C6A01F"/>
+    <tabColor rgb="00792E2E"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D82"/>
+  <dimension ref="B2:T36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="100" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -750,7 +767,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="32" customHeight="1">
+    <row r="3" ht="26" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Vendor Scorecard — Fast</t>
@@ -760,810 +777,1045 @@
     <row r="4">
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>The questionnaire is the rubric. Read the return top to bottom and fill the sheet top to bottom. Seven marks a vendor.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="10" customHeight="1"/>
-    <row r="7" ht="22" customHeight="1">
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>HOW IT WORKS</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="28" customHeight="1">
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>Every one of the 17 questions on the questionnaire has a row on the Scorecard tab, in the order it appears on the form. Seven rows take a mark. The rest raise a flag or a note — and they say so, so nothing looks forgotten. What isn't scored becomes what we go and ask at the demo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="28" customHeight="1">
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>Scored on the same 100 points and the same bands as the full scorecard, so the two are directly comparable. This one is coarser, not different: it gives one mark where the full sheet gives several, so the two can disagree on a close call. That is the trade for speed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="10" customHeight="1"/>
-    <row r="11" ht="22" customHeight="1">
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>THE SEVEN MARKS</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>Question</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>Mark</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>Points</t>
-        </is>
+          <t>A worked example. These three vendors are invented — the scores beside them are this sheet's own formulas. Score on the Scorecard tab, not this one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="42" customHeight="1">
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>VENDOR</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Arbor Health Logistics</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Wayfinder Scheduling</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Northlight Health</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>Vendor 04</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>Vendor 05</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>Vendor 06</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>Vendor 07</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>Vendor 08</t>
+        </is>
+      </c>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>Vendor 09</t>
+        </is>
+      </c>
+      <c r="N6" s="5" t="inlineStr">
+        <is>
+          <t>Vendor 10</t>
+        </is>
+      </c>
+      <c r="O6" s="5" t="inlineStr">
+        <is>
+          <t>Vendor 11</t>
+        </is>
+      </c>
+      <c r="P6" s="5" t="inlineStr">
+        <is>
+          <t>Vendor 12</t>
+        </is>
+      </c>
+      <c r="Q6" s="5" t="inlineStr">
+        <is>
+          <t>Vendor 13</t>
+        </is>
+      </c>
+      <c r="R6" s="5" t="inlineStr">
+        <is>
+          <t>Vendor 14</t>
+        </is>
+      </c>
+      <c r="S6" s="5" t="inlineStr">
+        <is>
+          <t>Vendor 15</t>
+        </is>
+      </c>
+      <c r="T6" s="5" t="inlineStr">
+        <is>
+          <t>Vendor 16</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="21" customHeight="1">
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>SCORE</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>of 100</t>
+        </is>
+      </c>
+      <c r="E9" s="9">
+        <f>IF(E14="","",IFERROR(VLOOKUP(E14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(E19,1)),0)/5*12+IFERROR(VALUE(LEFT(E20,1)),0)/5*12+IFERROR(VALUE(LEFT(E21,1)),0)/5*12+IFERROR(VALUE(LEFT(E24,1)),0)/4*20+IFERROR(VALUE(LEFT(E28,1)),0)/4*12+IFERROR(VALUE(LEFT(E31,1)),0)/4*12)</f>
+        <v/>
+      </c>
+      <c r="F9" s="9">
+        <f>IF(F14="","",IFERROR(VLOOKUP(F14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(F19,1)),0)/5*12+IFERROR(VALUE(LEFT(F20,1)),0)/5*12+IFERROR(VALUE(LEFT(F21,1)),0)/5*12+IFERROR(VALUE(LEFT(F24,1)),0)/4*20+IFERROR(VALUE(LEFT(F28,1)),0)/4*12+IFERROR(VALUE(LEFT(F31,1)),0)/4*12)</f>
+        <v/>
+      </c>
+      <c r="G9" s="9">
+        <f>IF(G14="","",IFERROR(VLOOKUP(G14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(G19,1)),0)/5*12+IFERROR(VALUE(LEFT(G20,1)),0)/5*12+IFERROR(VALUE(LEFT(G21,1)),0)/5*12+IFERROR(VALUE(LEFT(G24,1)),0)/4*20+IFERROR(VALUE(LEFT(G28,1)),0)/4*12+IFERROR(VALUE(LEFT(G31,1)),0)/4*12)</f>
+        <v/>
+      </c>
+      <c r="H9" s="9">
+        <f>IF(H14="","",IFERROR(VLOOKUP(H14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(H19,1)),0)/5*12+IFERROR(VALUE(LEFT(H20,1)),0)/5*12+IFERROR(VALUE(LEFT(H21,1)),0)/5*12+IFERROR(VALUE(LEFT(H24,1)),0)/4*20+IFERROR(VALUE(LEFT(H28,1)),0)/4*12+IFERROR(VALUE(LEFT(H31,1)),0)/4*12)</f>
+        <v/>
+      </c>
+      <c r="I9" s="9">
+        <f>IF(I14="","",IFERROR(VLOOKUP(I14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(I19,1)),0)/5*12+IFERROR(VALUE(LEFT(I20,1)),0)/5*12+IFERROR(VALUE(LEFT(I21,1)),0)/5*12+IFERROR(VALUE(LEFT(I24,1)),0)/4*20+IFERROR(VALUE(LEFT(I28,1)),0)/4*12+IFERROR(VALUE(LEFT(I31,1)),0)/4*12)</f>
+        <v/>
+      </c>
+      <c r="J9" s="9">
+        <f>IF(J14="","",IFERROR(VLOOKUP(J14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(J19,1)),0)/5*12+IFERROR(VALUE(LEFT(J20,1)),0)/5*12+IFERROR(VALUE(LEFT(J21,1)),0)/5*12+IFERROR(VALUE(LEFT(J24,1)),0)/4*20+IFERROR(VALUE(LEFT(J28,1)),0)/4*12+IFERROR(VALUE(LEFT(J31,1)),0)/4*12)</f>
+        <v/>
+      </c>
+      <c r="K9" s="9">
+        <f>IF(K14="","",IFERROR(VLOOKUP(K14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(K19,1)),0)/5*12+IFERROR(VALUE(LEFT(K20,1)),0)/5*12+IFERROR(VALUE(LEFT(K21,1)),0)/5*12+IFERROR(VALUE(LEFT(K24,1)),0)/4*20+IFERROR(VALUE(LEFT(K28,1)),0)/4*12+IFERROR(VALUE(LEFT(K31,1)),0)/4*12)</f>
+        <v/>
+      </c>
+      <c r="L9" s="9">
+        <f>IF(L14="","",IFERROR(VLOOKUP(L14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(L19,1)),0)/5*12+IFERROR(VALUE(LEFT(L20,1)),0)/5*12+IFERROR(VALUE(LEFT(L21,1)),0)/5*12+IFERROR(VALUE(LEFT(L24,1)),0)/4*20+IFERROR(VALUE(LEFT(L28,1)),0)/4*12+IFERROR(VALUE(LEFT(L31,1)),0)/4*12)</f>
+        <v/>
+      </c>
+      <c r="M9" s="9">
+        <f>IF(M14="","",IFERROR(VLOOKUP(M14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(M19,1)),0)/5*12+IFERROR(VALUE(LEFT(M20,1)),0)/5*12+IFERROR(VALUE(LEFT(M21,1)),0)/5*12+IFERROR(VALUE(LEFT(M24,1)),0)/4*20+IFERROR(VALUE(LEFT(M28,1)),0)/4*12+IFERROR(VALUE(LEFT(M31,1)),0)/4*12)</f>
+        <v/>
+      </c>
+      <c r="N9" s="9">
+        <f>IF(N14="","",IFERROR(VLOOKUP(N14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(N19,1)),0)/5*12+IFERROR(VALUE(LEFT(N20,1)),0)/5*12+IFERROR(VALUE(LEFT(N21,1)),0)/5*12+IFERROR(VALUE(LEFT(N24,1)),0)/4*20+IFERROR(VALUE(LEFT(N28,1)),0)/4*12+IFERROR(VALUE(LEFT(N31,1)),0)/4*12)</f>
+        <v/>
+      </c>
+      <c r="O9" s="9">
+        <f>IF(O14="","",IFERROR(VLOOKUP(O14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(O19,1)),0)/5*12+IFERROR(VALUE(LEFT(O20,1)),0)/5*12+IFERROR(VALUE(LEFT(O21,1)),0)/5*12+IFERROR(VALUE(LEFT(O24,1)),0)/4*20+IFERROR(VALUE(LEFT(O28,1)),0)/4*12+IFERROR(VALUE(LEFT(O31,1)),0)/4*12)</f>
+        <v/>
+      </c>
+      <c r="P9" s="9">
+        <f>IF(P14="","",IFERROR(VLOOKUP(P14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(P19,1)),0)/5*12+IFERROR(VALUE(LEFT(P20,1)),0)/5*12+IFERROR(VALUE(LEFT(P21,1)),0)/5*12+IFERROR(VALUE(LEFT(P24,1)),0)/4*20+IFERROR(VALUE(LEFT(P28,1)),0)/4*12+IFERROR(VALUE(LEFT(P31,1)),0)/4*12)</f>
+        <v/>
+      </c>
+      <c r="Q9" s="9">
+        <f>IF(Q14="","",IFERROR(VLOOKUP(Q14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(Q19,1)),0)/5*12+IFERROR(VALUE(LEFT(Q20,1)),0)/5*12+IFERROR(VALUE(LEFT(Q21,1)),0)/5*12+IFERROR(VALUE(LEFT(Q24,1)),0)/4*20+IFERROR(VALUE(LEFT(Q28,1)),0)/4*12+IFERROR(VALUE(LEFT(Q31,1)),0)/4*12)</f>
+        <v/>
+      </c>
+      <c r="R9" s="9">
+        <f>IF(R14="","",IFERROR(VLOOKUP(R14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(R19,1)),0)/5*12+IFERROR(VALUE(LEFT(R20,1)),0)/5*12+IFERROR(VALUE(LEFT(R21,1)),0)/5*12+IFERROR(VALUE(LEFT(R24,1)),0)/4*20+IFERROR(VALUE(LEFT(R28,1)),0)/4*12+IFERROR(VALUE(LEFT(R31,1)),0)/4*12)</f>
+        <v/>
+      </c>
+      <c r="S9" s="9">
+        <f>IF(S14="","",IFERROR(VLOOKUP(S14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(S19,1)),0)/5*12+IFERROR(VALUE(LEFT(S20,1)),0)/5*12+IFERROR(VALUE(LEFT(S21,1)),0)/5*12+IFERROR(VALUE(LEFT(S24,1)),0)/4*20+IFERROR(VALUE(LEFT(S28,1)),0)/4*12+IFERROR(VALUE(LEFT(S31,1)),0)/4*12)</f>
+        <v/>
+      </c>
+      <c r="T9" s="9">
+        <f>IF(T14="","",IFERROR(VLOOKUP(T14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(T19,1)),0)/5*12+IFERROR(VALUE(LEFT(T20,1)),0)/5*12+IFERROR(VALUE(LEFT(T21,1)),0)/5*12+IFERROR(VALUE(LEFT(T24,1)),0)/4*20+IFERROR(VALUE(LEFT(T28,1)),0)/4*12+IFERROR(VALUE(LEFT(T31,1)),0)/4*12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>Band</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>80 Advance · 65 Consider · 50 Hold</t>
+        </is>
+      </c>
+      <c r="E10" s="11">
+        <f>IF(E14="","",IF(IFERROR(VLOOKUP(E14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(E9&gt;=80,"Advance",IF(E9&gt;=65,"Consider",IF(E9&gt;=50,"Hold","Decline"))))</f>
+        <v/>
+      </c>
+      <c r="F10" s="11">
+        <f>IF(F14="","",IF(IFERROR(VLOOKUP(F14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(F9&gt;=80,"Advance",IF(F9&gt;=65,"Consider",IF(F9&gt;=50,"Hold","Decline"))))</f>
+        <v/>
+      </c>
+      <c r="G10" s="11">
+        <f>IF(G14="","",IF(IFERROR(VLOOKUP(G14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(G9&gt;=80,"Advance",IF(G9&gt;=65,"Consider",IF(G9&gt;=50,"Hold","Decline"))))</f>
+        <v/>
+      </c>
+      <c r="H10" s="11">
+        <f>IF(H14="","",IF(IFERROR(VLOOKUP(H14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(H9&gt;=80,"Advance",IF(H9&gt;=65,"Consider",IF(H9&gt;=50,"Hold","Decline"))))</f>
+        <v/>
+      </c>
+      <c r="I10" s="11">
+        <f>IF(I14="","",IF(IFERROR(VLOOKUP(I14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(I9&gt;=80,"Advance",IF(I9&gt;=65,"Consider",IF(I9&gt;=50,"Hold","Decline"))))</f>
+        <v/>
+      </c>
+      <c r="J10" s="11">
+        <f>IF(J14="","",IF(IFERROR(VLOOKUP(J14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(J9&gt;=80,"Advance",IF(J9&gt;=65,"Consider",IF(J9&gt;=50,"Hold","Decline"))))</f>
+        <v/>
+      </c>
+      <c r="K10" s="11">
+        <f>IF(K14="","",IF(IFERROR(VLOOKUP(K14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(K9&gt;=80,"Advance",IF(K9&gt;=65,"Consider",IF(K9&gt;=50,"Hold","Decline"))))</f>
+        <v/>
+      </c>
+      <c r="L10" s="11">
+        <f>IF(L14="","",IF(IFERROR(VLOOKUP(L14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(L9&gt;=80,"Advance",IF(L9&gt;=65,"Consider",IF(L9&gt;=50,"Hold","Decline"))))</f>
+        <v/>
+      </c>
+      <c r="M10" s="11">
+        <f>IF(M14="","",IF(IFERROR(VLOOKUP(M14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(M9&gt;=80,"Advance",IF(M9&gt;=65,"Consider",IF(M9&gt;=50,"Hold","Decline"))))</f>
+        <v/>
+      </c>
+      <c r="N10" s="11">
+        <f>IF(N14="","",IF(IFERROR(VLOOKUP(N14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(N9&gt;=80,"Advance",IF(N9&gt;=65,"Consider",IF(N9&gt;=50,"Hold","Decline"))))</f>
+        <v/>
+      </c>
+      <c r="O10" s="11">
+        <f>IF(O14="","",IF(IFERROR(VLOOKUP(O14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(O9&gt;=80,"Advance",IF(O9&gt;=65,"Consider",IF(O9&gt;=50,"Hold","Decline"))))</f>
+        <v/>
+      </c>
+      <c r="P10" s="11">
+        <f>IF(P14="","",IF(IFERROR(VLOOKUP(P14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(P9&gt;=80,"Advance",IF(P9&gt;=65,"Consider",IF(P9&gt;=50,"Hold","Decline"))))</f>
+        <v/>
+      </c>
+      <c r="Q10" s="11">
+        <f>IF(Q14="","",IF(IFERROR(VLOOKUP(Q14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(Q9&gt;=80,"Advance",IF(Q9&gt;=65,"Consider",IF(Q9&gt;=50,"Hold","Decline"))))</f>
+        <v/>
+      </c>
+      <c r="R10" s="11">
+        <f>IF(R14="","",IF(IFERROR(VLOOKUP(R14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(R9&gt;=80,"Advance",IF(R9&gt;=65,"Consider",IF(R9&gt;=50,"Hold","Decline"))))</f>
+        <v/>
+      </c>
+      <c r="S10" s="11">
+        <f>IF(S14="","",IF(IFERROR(VLOOKUP(S14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(S9&gt;=80,"Advance",IF(S9&gt;=65,"Consider",IF(S9&gt;=50,"Hold","Decline"))))</f>
+        <v/>
+      </c>
+      <c r="T10" s="11">
+        <f>IF(T14="","",IF(IFERROR(VLOOKUP(T14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(T9&gt;=80,"Advance",IF(T9&gt;=65,"Consider",IF(T9&gt;=50,"Hold","Decline"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>Flags</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>stop-checks raised, of three</t>
+        </is>
+      </c>
+      <c r="E11" s="13">
+        <f>IF(E14="","",IF(E15="STOP-CHECK",1,0)+IF(E16="STOP-CHECK",1,0)+IF(E25="STOP-CHECK",1,0))</f>
+        <v/>
+      </c>
+      <c r="F11" s="13">
+        <f>IF(F14="","",IF(F15="STOP-CHECK",1,0)+IF(F16="STOP-CHECK",1,0)+IF(F25="STOP-CHECK",1,0))</f>
+        <v/>
+      </c>
+      <c r="G11" s="13">
+        <f>IF(G14="","",IF(G15="STOP-CHECK",1,0)+IF(G16="STOP-CHECK",1,0)+IF(G25="STOP-CHECK",1,0))</f>
+        <v/>
+      </c>
+      <c r="H11" s="13">
+        <f>IF(H14="","",IF(H15="STOP-CHECK",1,0)+IF(H16="STOP-CHECK",1,0)+IF(H25="STOP-CHECK",1,0))</f>
+        <v/>
+      </c>
+      <c r="I11" s="13">
+        <f>IF(I14="","",IF(I15="STOP-CHECK",1,0)+IF(I16="STOP-CHECK",1,0)+IF(I25="STOP-CHECK",1,0))</f>
+        <v/>
+      </c>
+      <c r="J11" s="13">
+        <f>IF(J14="","",IF(J15="STOP-CHECK",1,0)+IF(J16="STOP-CHECK",1,0)+IF(J25="STOP-CHECK",1,0))</f>
+        <v/>
+      </c>
+      <c r="K11" s="13">
+        <f>IF(K14="","",IF(K15="STOP-CHECK",1,0)+IF(K16="STOP-CHECK",1,0)+IF(K25="STOP-CHECK",1,0))</f>
+        <v/>
+      </c>
+      <c r="L11" s="13">
+        <f>IF(L14="","",IF(L15="STOP-CHECK",1,0)+IF(L16="STOP-CHECK",1,0)+IF(L25="STOP-CHECK",1,0))</f>
+        <v/>
+      </c>
+      <c r="M11" s="13">
+        <f>IF(M14="","",IF(M15="STOP-CHECK",1,0)+IF(M16="STOP-CHECK",1,0)+IF(M25="STOP-CHECK",1,0))</f>
+        <v/>
+      </c>
+      <c r="N11" s="13">
+        <f>IF(N14="","",IF(N15="STOP-CHECK",1,0)+IF(N16="STOP-CHECK",1,0)+IF(N25="STOP-CHECK",1,0))</f>
+        <v/>
+      </c>
+      <c r="O11" s="13">
+        <f>IF(O14="","",IF(O15="STOP-CHECK",1,0)+IF(O16="STOP-CHECK",1,0)+IF(O25="STOP-CHECK",1,0))</f>
+        <v/>
+      </c>
+      <c r="P11" s="13">
+        <f>IF(P14="","",IF(P15="STOP-CHECK",1,0)+IF(P16="STOP-CHECK",1,0)+IF(P25="STOP-CHECK",1,0))</f>
+        <v/>
+      </c>
+      <c r="Q11" s="13">
+        <f>IF(Q14="","",IF(Q15="STOP-CHECK",1,0)+IF(Q16="STOP-CHECK",1,0)+IF(Q25="STOP-CHECK",1,0))</f>
+        <v/>
+      </c>
+      <c r="R11" s="13">
+        <f>IF(R14="","",IF(R15="STOP-CHECK",1,0)+IF(R16="STOP-CHECK",1,0)+IF(R25="STOP-CHECK",1,0))</f>
+        <v/>
+      </c>
+      <c r="S11" s="13">
+        <f>IF(S14="","",IF(S15="STOP-CHECK",1,0)+IF(S16="STOP-CHECK",1,0)+IF(S25="STOP-CHECK",1,0))</f>
+        <v/>
+      </c>
+      <c r="T11" s="13">
+        <f>IF(T14="","",IF(T15="STOP-CHECK",1,0)+IF(T16="STOP-CHECK",1,0)+IF(T25="STOP-CHECK",1,0))</f>
+        <v/>
       </c>
     </row>
     <row r="13" ht="21" customHeight="1">
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>A  ·  COMPANY AND PRODUCT</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C14" s="15" t="inlineStr">
         <is>
           <t>Home Care Home Base integration</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="21" customHeight="1">
-      <c r="B14" s="7" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>Pick one line  ·  20 points</t>
+        </is>
+      </c>
+      <c r="E14" s="16" t="inlineStr">
+        <is>
+          <t>Live — established customer base</t>
+        </is>
+      </c>
+      <c r="F14" s="16" t="inlineStr">
+        <is>
+          <t>Live — small customer base</t>
+        </is>
+      </c>
+      <c r="G14" s="16" t="inlineStr">
+        <is>
+          <t>In development — with a date</t>
+        </is>
+      </c>
+      <c r="H14" s="16" t="n"/>
+      <c r="I14" s="16" t="n"/>
+      <c r="J14" s="16" t="n"/>
+      <c r="K14" s="16" t="n"/>
+      <c r="L14" s="16" t="n"/>
+      <c r="M14" s="16" t="n"/>
+      <c r="N14" s="16" t="n"/>
+      <c r="O14" s="16" t="n"/>
+      <c r="P14" s="16" t="n"/>
+      <c r="Q14" s="16" t="n"/>
+      <c r="R14" s="16" t="n"/>
+      <c r="S14" s="16" t="n"/>
+      <c r="T14" s="16" t="n"/>
+    </row>
+    <row r="15" ht="19" customHeight="1">
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="inlineStr">
+        <is>
+          <t>Customers, scale and references</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>Flag  ·  stop-check if one customer or no references</t>
+        </is>
+      </c>
+      <c r="E15" s="18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F15" s="18" t="inlineStr">
+        <is>
+          <t>STOP-CHECK</t>
+        </is>
+      </c>
+      <c r="G15" s="18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H15" s="18" t="n"/>
+      <c r="I15" s="18" t="n"/>
+      <c r="J15" s="18" t="n"/>
+      <c r="K15" s="18" t="n"/>
+      <c r="L15" s="18" t="n"/>
+      <c r="M15" s="18" t="n"/>
+      <c r="N15" s="18" t="n"/>
+      <c r="O15" s="18" t="n"/>
+      <c r="P15" s="18" t="n"/>
+      <c r="Q15" s="18" t="n"/>
+      <c r="R15" s="18" t="n"/>
+      <c r="S15" s="18" t="n"/>
+      <c r="T15" s="18" t="n"/>
+    </row>
+    <row r="16" ht="19" customHeight="1">
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="inlineStr">
+        <is>
+          <t>Measured impact</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>Flag  ·  watch if no baseline or period</t>
+        </is>
+      </c>
+      <c r="E16" s="18" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="F16" s="18" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="G16" s="18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H16" s="18" t="n"/>
+      <c r="I16" s="18" t="n"/>
+      <c r="J16" s="18" t="n"/>
+      <c r="K16" s="18" t="n"/>
+      <c r="L16" s="18" t="n"/>
+      <c r="M16" s="18" t="n"/>
+      <c r="N16" s="18" t="n"/>
+      <c r="O16" s="18" t="n"/>
+      <c r="P16" s="18" t="n"/>
+      <c r="Q16" s="18" t="n"/>
+      <c r="R16" s="18" t="n"/>
+      <c r="S16" s="18" t="n"/>
+      <c r="T16" s="18" t="n"/>
+    </row>
+    <row r="18" ht="21" customHeight="1">
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>B  ·  COVERAGE SELF-ASSESSMENT   —   how much of our scope they cover</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="19" customHeight="1">
+      <c r="B19" s="19" t="inlineStr">
         <is>
           <t>Section B</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>Capacity — how much of it they cover</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="21" customHeight="1">
-      <c r="B15" s="7" t="inlineStr">
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>Capacity</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>Workforce supply · availability &amp; reach · the capacity math  ·  0–5  ·  12 points</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
+        <is>
+          <t>4 — More than half</t>
+        </is>
+      </c>
+      <c r="F19" s="20" t="inlineStr">
+        <is>
+          <t>2 — Less than half</t>
+        </is>
+      </c>
+      <c r="G19" s="20" t="inlineStr">
+        <is>
+          <t>3 — About half</t>
+        </is>
+      </c>
+      <c r="H19" s="20" t="n"/>
+      <c r="I19" s="20" t="n"/>
+      <c r="J19" s="20" t="n"/>
+      <c r="K19" s="20" t="n"/>
+      <c r="L19" s="20" t="n"/>
+      <c r="M19" s="20" t="n"/>
+      <c r="N19" s="20" t="n"/>
+      <c r="O19" s="20" t="n"/>
+      <c r="P19" s="20" t="n"/>
+      <c r="Q19" s="20" t="n"/>
+      <c r="R19" s="20" t="n"/>
+      <c r="S19" s="20" t="n"/>
+      <c r="T19" s="20" t="n"/>
+    </row>
+    <row r="20" ht="19" customHeight="1">
+      <c r="B20" s="21" t="inlineStr">
         <is>
           <t>Section B</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>Scheduling — how much of it they cover</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="21" customHeight="1">
-      <c r="B16" s="7" t="inlineStr">
+      <c r="C20" s="15" t="inlineStr">
+        <is>
+          <t>Scheduling</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>Demand · matching · routing &amp; the week · exceptions  ·  0–5  ·  12 points</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="inlineStr">
+        <is>
+          <t>5 — Most of it</t>
+        </is>
+      </c>
+      <c r="F20" s="20" t="inlineStr">
+        <is>
+          <t>3 — About half</t>
+        </is>
+      </c>
+      <c r="G20" s="20" t="inlineStr">
+        <is>
+          <t>4 — More than half</t>
+        </is>
+      </c>
+      <c r="H20" s="20" t="n"/>
+      <c r="I20" s="20" t="n"/>
+      <c r="J20" s="20" t="n"/>
+      <c r="K20" s="20" t="n"/>
+      <c r="L20" s="20" t="n"/>
+      <c r="M20" s="20" t="n"/>
+      <c r="N20" s="20" t="n"/>
+      <c r="O20" s="20" t="n"/>
+      <c r="P20" s="20" t="n"/>
+      <c r="Q20" s="20" t="n"/>
+      <c r="R20" s="20" t="n"/>
+      <c r="S20" s="20" t="n"/>
+      <c r="T20" s="20" t="n"/>
+    </row>
+    <row r="21" ht="19" customHeight="1">
+      <c r="B21" s="22" t="inlineStr">
         <is>
           <t>Section B</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>Engagement — how much of it they cover</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="21" customHeight="1">
-      <c r="B17" s="7" t="inlineStr">
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>Before the visit · when plans change · incentives · care team  ·  0–5  ·  12 points</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="inlineStr">
+        <is>
+          <t>2 — Less than half</t>
+        </is>
+      </c>
+      <c r="F21" s="20" t="inlineStr">
+        <is>
+          <t>1 — A corner of it</t>
+        </is>
+      </c>
+      <c r="G21" s="20" t="inlineStr">
+        <is>
+          <t>3 — About half</t>
+        </is>
+      </c>
+      <c r="H21" s="20" t="n"/>
+      <c r="I21" s="20" t="n"/>
+      <c r="J21" s="20" t="n"/>
+      <c r="K21" s="20" t="n"/>
+      <c r="L21" s="20" t="n"/>
+      <c r="M21" s="20" t="n"/>
+      <c r="N21" s="20" t="n"/>
+      <c r="O21" s="20" t="n"/>
+      <c r="P21" s="20" t="n"/>
+      <c r="Q21" s="20" t="n"/>
+      <c r="R21" s="20" t="n"/>
+      <c r="S21" s="20" t="n"/>
+      <c r="T21" s="20" t="n"/>
+    </row>
+    <row r="23" ht="21" customHeight="1">
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>C  ·  HOW YOUR PRODUCT WORKS</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1">
+      <c r="B24" s="23" t="inlineStr">
         <is>
           <t>Section C</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>Sophistication — how much of the work the product does</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="21" customHeight="1">
-      <c r="B18" s="7" t="inlineStr">
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>Sophistication</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>How much of the work it does  ·  0–4  ·  20 points</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr">
+        <is>
+          <t>4 — Runs it</t>
+        </is>
+      </c>
+      <c r="F24" s="20" t="inlineStr">
+        <is>
+          <t>3 — Recommends it</t>
+        </is>
+      </c>
+      <c r="G24" s="20" t="inlineStr">
+        <is>
+          <t>3 — Recommends it</t>
+        </is>
+      </c>
+      <c r="H24" s="20" t="n"/>
+      <c r="I24" s="20" t="n"/>
+      <c r="J24" s="20" t="n"/>
+      <c r="K24" s="20" t="n"/>
+      <c r="L24" s="20" t="n"/>
+      <c r="M24" s="20" t="n"/>
+      <c r="N24" s="20" t="n"/>
+      <c r="O24" s="20" t="n"/>
+      <c r="P24" s="20" t="n"/>
+      <c r="Q24" s="20" t="n"/>
+      <c r="R24" s="20" t="n"/>
+      <c r="S24" s="20" t="n"/>
+      <c r="T24" s="20" t="n"/>
+    </row>
+    <row r="25" ht="19" customHeight="1">
+      <c r="B25" s="17" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="C25" s="15" t="inlineStr">
+        <is>
+          <t>When your product is down</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>Flag  ·  stop-check if no uptime figure or commitment</t>
+        </is>
+      </c>
+      <c r="E25" s="18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F25" s="18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G25" s="18" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="H25" s="18" t="n"/>
+      <c r="I25" s="18" t="n"/>
+      <c r="J25" s="18" t="n"/>
+      <c r="K25" s="18" t="n"/>
+      <c r="L25" s="18" t="n"/>
+      <c r="M25" s="18" t="n"/>
+      <c r="N25" s="18" t="n"/>
+      <c r="O25" s="18" t="n"/>
+      <c r="P25" s="18" t="n"/>
+      <c r="Q25" s="18" t="n"/>
+      <c r="R25" s="18" t="n"/>
+      <c r="S25" s="18" t="n"/>
+      <c r="T25" s="18" t="n"/>
+    </row>
+    <row r="27" ht="21" customHeight="1">
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>D  ·  THE CLINICIAN'S PLACE IN THE MODEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="24" customHeight="1">
+      <c r="B28" s="24" t="inlineStr">
         <is>
           <t>D1–D3</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C28" s="15" t="inlineStr">
         <is>
           <t>Clinician fit</t>
         </is>
       </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="21" customHeight="1">
-      <c r="B19" s="7" t="inlineStr">
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>Our read of fit  ·  0–4  ·  12 points</t>
+        </is>
+      </c>
+      <c r="E28" s="20" t="inlineStr">
+        <is>
+          <t>3 — Good fit</t>
+        </is>
+      </c>
+      <c r="F28" s="20" t="inlineStr">
+        <is>
+          <t>2 — Workable</t>
+        </is>
+      </c>
+      <c r="G28" s="20" t="inlineStr">
+        <is>
+          <t>3 — Good fit</t>
+        </is>
+      </c>
+      <c r="H28" s="20" t="n"/>
+      <c r="I28" s="20" t="n"/>
+      <c r="J28" s="20" t="n"/>
+      <c r="K28" s="20" t="n"/>
+      <c r="L28" s="20" t="n"/>
+      <c r="M28" s="20" t="n"/>
+      <c r="N28" s="20" t="n"/>
+      <c r="O28" s="20" t="n"/>
+      <c r="P28" s="20" t="n"/>
+      <c r="Q28" s="20" t="n"/>
+      <c r="R28" s="20" t="n"/>
+      <c r="S28" s="20" t="n"/>
+      <c r="T28" s="20" t="n"/>
+    </row>
+    <row r="30" ht="21" customHeight="1">
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>E  ·  FIT AND PARTNERSHIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="24" customHeight="1">
+      <c r="B31" s="24" t="inlineStr">
         <is>
           <t>E1–E4</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C31" s="15" t="inlineStr">
         <is>
           <t>Partnership</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="21" customHeight="1">
-      <c r="B20" s="7" t="inlineStr"/>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="10" customHeight="1"/>
-    <row r="22" ht="22" customHeight="1">
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>A1  ·  HOME CARE HOME BASE   —   pick one line</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="28" customHeight="1">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Three of the six rungs are live integrations, because live through a partner is still live. Anything not yet live shows as Conditional on the score, whatever the total.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="21" customHeight="1">
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>Live — established customer base</t>
-        </is>
-      </c>
-      <c r="D24" s="8" t="inlineStr"/>
-    </row>
-    <row r="25" ht="21" customHeight="1">
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>Live — small customer base</t>
-        </is>
-      </c>
-      <c r="D25" s="8" t="inlineStr"/>
-    </row>
-    <row r="26" ht="21" customHeight="1">
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>Live — through a partner</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="inlineStr"/>
-    </row>
-    <row r="27" ht="21" customHeight="1">
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>In development — with a date</t>
-        </is>
-      </c>
-      <c r="D27" s="8" t="inlineStr"/>
-    </row>
-    <row r="28" ht="21" customHeight="1">
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>On the roadmap — no date</t>
-        </is>
-      </c>
-      <c r="D28" s="8" t="inlineStr"/>
-    </row>
-    <row r="29" ht="21" customHeight="1">
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>None, and no path to one</t>
-        </is>
-      </c>
-      <c r="D29" s="8" t="inlineStr"/>
-    </row>
-    <row r="30" ht="10" customHeight="1"/>
-    <row r="31" ht="22" customHeight="1">
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>SECTION B  ·  SCOPE   —   one mark per arena, 0 to 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="28" customHeight="1">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>Read the eleven areas each vendor rated themselves on, then give one mark per arena. The areas in each arena are printed on the row, so the checklist is in front of you. Where Section C contradicts Section B, believe Section C.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="41" customHeight="1">
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>The mark is your read of how much of that arena — as our one-pager describes it — the product reaches. It is not a count of areas: Capacity has 3 and the others 4, so counting would never divide cleanly, and an area covered thinly is not the same as one covered properly. Weigh breadth and depth together.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="21" customHeight="1">
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>Most of it</t>
-        </is>
-      </c>
-      <c r="D34" s="8" t="inlineStr"/>
-    </row>
-    <row r="35" ht="21" customHeight="1">
-      <c r="B35" s="7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>More than half</t>
-        </is>
-      </c>
-      <c r="D35" s="8" t="inlineStr"/>
-    </row>
-    <row r="36" ht="21" customHeight="1">
-      <c r="B36" s="7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>About half</t>
-        </is>
-      </c>
-      <c r="D36" s="8" t="inlineStr"/>
-    </row>
-    <row r="37" ht="21" customHeight="1">
-      <c r="B37" s="7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>Less than half</t>
-        </is>
-      </c>
-      <c r="D37" s="8" t="inlineStr"/>
-    </row>
-    <row r="38" ht="21" customHeight="1">
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>A corner of it</t>
-        </is>
-      </c>
-      <c r="D38" s="8" t="inlineStr"/>
-    </row>
-    <row r="39" ht="21" customHeight="1">
-      <c r="B39" s="7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t>Nothing here</t>
-        </is>
-      </c>
-      <c r="D39" s="8" t="inlineStr"/>
-    </row>
-    <row r="40" ht="28" customHeight="1">
-      <c r="B40" s="5" t="inlineStr">
-        <is>
-          <t>Most of it is the ceiling on purpose. The scope on our one-pager is original and these are point solutions, so nobody will cover all of it — a rung for that would sit unused and squeeze everyone else into the bottom half of the scale. All six rungs here are live.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="10" customHeight="1"/>
-    <row r="42" ht="22" customHeight="1">
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>SECTION C  ·  SOPHISTICATION   —   one mark, 0 to 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="41" customHeight="1">
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>How much of the work the product does. This is the Read / Assist / Control language already in our workbook. Score what the product does, not how much the vendor wrote about it — a short answer describing an optimiser still scores 4. How it does it is a demo question, not a reason to mark it down.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="21" customHeight="1">
-      <c r="B44" s="7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>Runs it — decides across the whole picture, and re-decides when things change</t>
-        </is>
-      </c>
-      <c r="D44" s="8" t="inlineStr"/>
-    </row>
-    <row r="45" ht="21" customHeight="1">
-      <c r="B45" s="7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t>Recommends it — works out the answer and proposes it; a person confirms</t>
-        </is>
-      </c>
-      <c r="D45" s="8" t="inlineStr"/>
-    </row>
-    <row r="46" ht="21" customHeight="1">
-      <c r="B46" s="7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>Checks it — applies rules and flags problems; a person still works it</t>
-        </is>
-      </c>
-      <c r="D46" s="8" t="inlineStr"/>
-    </row>
-    <row r="47" ht="21" customHeight="1">
-      <c r="B47" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C47" s="5" t="inlineStr">
-        <is>
-          <t>Shows it — surfaces the information; a person does all the work</t>
-        </is>
-      </c>
-      <c r="D47" s="8" t="inlineStr"/>
-    </row>
-    <row r="48" ht="21" customHeight="1">
-      <c r="B48" s="7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>Not addressed</t>
-        </is>
-      </c>
-      <c r="D48" s="8" t="inlineStr"/>
-    </row>
-    <row r="49" ht="15" customHeight="1">
-      <c r="B49" s="5" t="inlineStr">
-        <is>
-          <t>A 4 is not automatically what we want. Where we said Assist, a product that decides on its own is a risk worth a note.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="10" customHeight="1"/>
-    <row r="51" ht="22" customHeight="1">
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>SECTION D  ·  CLINICIAN FIT   —   one mark, 0 to 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="21" customHeight="1">
-      <c r="B52" s="7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C52" s="5" t="inlineStr">
-        <is>
-          <t>Strong fit</t>
-        </is>
-      </c>
-      <c r="D52" s="8" t="inlineStr"/>
-    </row>
-    <row r="53" ht="21" customHeight="1">
-      <c r="B53" s="7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C53" s="5" t="inlineStr">
-        <is>
-          <t>Good fit</t>
-        </is>
-      </c>
-      <c r="D53" s="8" t="inlineStr"/>
-    </row>
-    <row r="54" ht="21" customHeight="1">
-      <c r="B54" s="7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C54" s="5" t="inlineStr">
-        <is>
-          <t>Workable</t>
-        </is>
-      </c>
-      <c r="D54" s="8" t="inlineStr"/>
-    </row>
-    <row r="55" ht="21" customHeight="1">
-      <c r="B55" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C55" s="5" t="inlineStr">
-        <is>
-          <t>Poor fit</t>
-        </is>
-      </c>
-      <c r="D55" s="8" t="inlineStr"/>
-    </row>
-    <row r="56" ht="21" customHeight="1">
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C56" s="5" t="inlineStr">
-        <is>
-          <t>Not answered</t>
-        </is>
-      </c>
-      <c r="D56" s="8" t="inlineStr"/>
-    </row>
-    <row r="57" ht="28" customHeight="1">
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>No descriptions here on purpose. Read D1 to D3 and give it your own read. We know how our clinicians work and what they will accept; a rubric that spelled out what earns a 4 would only substitute a guess for that.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="15" customHeight="1">
-      <c r="B58" s="5" t="inlineStr">
-        <is>
-          <t>Say why in the Notes, though — that one line is what a colleague reads when they score the same vendor differently.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="10" customHeight="1"/>
-    <row r="60" ht="22" customHeight="1">
-      <c r="B60" s="4" t="inlineStr">
-        <is>
-          <t>SECTION E  ·  PARTNERSHIP   —   one mark, 0 to 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="28" customHeight="1">
-      <c r="B61" s="5" t="inlineStr">
-        <is>
-          <t>What we are looking for is a company with the willingness and the environment to build this with us around our needs — and open to us holding equity, so that a product for the general market becomes a real possibility. The rungs run from vendor to co-owner.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="21" customHeight="1">
-      <c r="B62" s="7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C62" s="5" t="inlineStr">
-        <is>
-          <t>Open to equity or a stake in what we build, and set up to build it with us</t>
-        </is>
-      </c>
-      <c r="D62" s="8" t="inlineStr"/>
-    </row>
-    <row r="63" ht="21" customHeight="1">
-      <c r="B63" s="7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C63" s="5" t="inlineStr">
-        <is>
-          <t>Ready to build to our needs as a design partner; ownership not addressed</t>
-        </is>
-      </c>
-      <c r="D63" s="8" t="inlineStr"/>
-    </row>
-    <row r="64" ht="21" customHeight="1">
-      <c r="B64" s="7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C64" s="5" t="inlineStr">
-        <is>
-          <t>Will take our input, but they own the roadmap and the product</t>
-        </is>
-      </c>
-      <c r="D64" s="8" t="inlineStr"/>
-    </row>
-    <row r="65" ht="21" customHeight="1">
-      <c r="B65" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C65" s="5" t="inlineStr">
-        <is>
-          <t>A standard customer relationship — we buy what already exists</t>
-        </is>
-      </c>
-      <c r="D65" s="8" t="inlineStr"/>
-    </row>
-    <row r="66" ht="21" customHeight="1">
-      <c r="B66" s="7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C66" s="5" t="inlineStr">
-        <is>
-          <t>Not answered</t>
-        </is>
-      </c>
-      <c r="D66" s="8" t="inlineStr"/>
-    </row>
-    <row r="67" ht="28" customHeight="1">
-      <c r="B67" s="5" t="inlineStr">
-        <is>
-          <t>Read all four E answers, not only E2. A vendor who never mentions ownership but describes a real co-development practice is a 3, and worth the conversation. A discount is a discount.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="10" customHeight="1"/>
-    <row r="69" ht="22" customHeight="1">
-      <c r="B69" s="4" t="inlineStr">
-        <is>
-          <t>THE THREE QUESTIONS THAT RAISE A FLAG INSTEAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="28" customHeight="1">
-      <c r="B70" s="5" t="inlineStr">
-        <is>
-          <t>A vendor with no continuity commitment should be stopped and asked, not quietly docked a few points. Same for a vendor with one customer, or impact numbers with no baseline. Mark these OK, Watch or STOP-CHECK.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="21" customHeight="1">
-      <c r="B71" s="7" t="inlineStr">
-        <is>
-          <t>A2</t>
-        </is>
-      </c>
-      <c r="C71" s="5" t="inlineStr">
-        <is>
-          <t>Customers, scale and references — STOP-CHECK if one customer, or no references offered</t>
-        </is>
-      </c>
-      <c r="D71" s="8" t="inlineStr"/>
-    </row>
-    <row r="72" ht="21" customHeight="1">
-      <c r="B72" s="7" t="inlineStr">
-        <is>
-          <t>A3</t>
-        </is>
-      </c>
-      <c r="C72" s="5" t="inlineStr">
-        <is>
-          <t>Measured impact — Watch if claimed with no baseline or period</t>
-        </is>
-      </c>
-      <c r="D72" s="8" t="inlineStr"/>
-    </row>
-    <row r="73" ht="21" customHeight="1">
-      <c r="B73" s="7" t="inlineStr">
-        <is>
-          <t>C6</t>
-        </is>
-      </c>
-      <c r="C73" s="5" t="inlineStr">
-        <is>
-          <t>When your product is down — STOP-CHECK if no uptime figure or contractual commitment</t>
-        </is>
-      </c>
-      <c r="D73" s="8" t="inlineStr"/>
-    </row>
-    <row r="74" ht="10" customHeight="1"/>
-    <row r="75" ht="22" customHeight="1">
-      <c r="B75" s="4" t="inlineStr">
-        <is>
-          <t>BANDS   —   the same as the full scorecard</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="21" customHeight="1">
-      <c r="B76" s="7" t="inlineStr">
-        <is>
-          <t>80–100</t>
-        </is>
-      </c>
-      <c r="C76" s="5" t="inlineStr">
-        <is>
-          <t>Advance — demo, references, deeper diligence</t>
-        </is>
-      </c>
-      <c r="D76" s="8" t="inlineStr"/>
-    </row>
-    <row r="77" ht="21" customHeight="1">
-      <c r="B77" s="7" t="inlineStr">
-        <is>
-          <t>65–79</t>
-        </is>
-      </c>
-      <c r="C77" s="5" t="inlineStr">
-        <is>
-          <t>Consider — only if something specific justifies it</t>
-        </is>
-      </c>
-      <c r="D77" s="8" t="inlineStr"/>
-    </row>
-    <row r="78" ht="21" customHeight="1">
-      <c r="B78" s="7" t="inlineStr">
-        <is>
-          <t>50–64</t>
-        </is>
-      </c>
-      <c r="C78" s="5" t="inlineStr">
-        <is>
-          <t>Hold — park unless the field thins</t>
-        </is>
-      </c>
-      <c r="D78" s="8" t="inlineStr"/>
-    </row>
-    <row r="79" ht="21" customHeight="1">
-      <c r="B79" s="7" t="inlineStr">
-        <is>
-          <t>&lt; 50</t>
-        </is>
-      </c>
-      <c r="C79" s="5" t="inlineStr">
-        <is>
-          <t>Decline — close out with thanks</t>
-        </is>
-      </c>
-      <c r="D79" s="8" t="inlineStr"/>
-    </row>
-    <row r="80" ht="34" customHeight="1">
-      <c r="B80" s="7" t="inlineStr">
-        <is>
-          <t>Conditional</t>
-        </is>
-      </c>
-      <c r="C80" s="5" t="inlineStr">
-        <is>
-          <t>Shown whenever the integration is not yet live. Advancing means accepting an integration still to be built, on their timeline, at our risk.</t>
-        </is>
-      </c>
-      <c r="D80" s="8" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="B82" s="10" t="inlineStr">
-        <is>
-          <t>Fast scorecard v2.0  ·  questionnaire form_version 2026-08-19</t>
-        </is>
-      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>Willing to build it with us, and open to a stake  ·  0–4  ·  12 points</t>
+        </is>
+      </c>
+      <c r="E31" s="20" t="inlineStr">
+        <is>
+          <t>3 — Ready to build to our needs as a design partner; ownership not addressed</t>
+        </is>
+      </c>
+      <c r="F31" s="20" t="inlineStr">
+        <is>
+          <t>2 — Will take our input, but they own the roadmap and the product</t>
+        </is>
+      </c>
+      <c r="G31" s="20" t="inlineStr">
+        <is>
+          <t>4 — Open to equity or a stake in what we build, and set up to build it with us</t>
+        </is>
+      </c>
+      <c r="H31" s="20" t="n"/>
+      <c r="I31" s="20" t="n"/>
+      <c r="J31" s="20" t="n"/>
+      <c r="K31" s="20" t="n"/>
+      <c r="L31" s="20" t="n"/>
+      <c r="M31" s="20" t="n"/>
+      <c r="N31" s="20" t="n"/>
+      <c r="O31" s="20" t="n"/>
+      <c r="P31" s="20" t="n"/>
+      <c r="Q31" s="20" t="n"/>
+      <c r="R31" s="20" t="n"/>
+      <c r="S31" s="20" t="n"/>
+      <c r="T31" s="20" t="n"/>
+    </row>
+    <row r="33" ht="21" customHeight="1">
+      <c r="B33" s="25" t="inlineStr">
+        <is>
+          <t>NOTES   —   one line each.  This is what we go and ask.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="62" customHeight="1">
+      <c r="B34" s="26" t="inlineStr"/>
+      <c r="C34" s="27" t="inlineStr">
+        <is>
+          <t>What stands out</t>
+        </is>
+      </c>
+      <c r="D34" s="28" t="inlineStr">
+        <is>
+          <t>against the field, or against our own thinking</t>
+        </is>
+      </c>
+      <c r="E34" s="29" t="inlineStr">
+        <is>
+          <t>Only answer that shows a branch leader the envelope impact of a referral before accepting it.</t>
+        </is>
+      </c>
+      <c r="F34" s="29" t="inlineStr">
+        <is>
+          <t>Strong routing engine, almost nothing on the patient side.</t>
+        </is>
+      </c>
+      <c r="G34" s="29" t="inlineStr">
+        <is>
+          <t>Raised payer-mix-aware sequencing — not on our one-pager, probably should be.</t>
+        </is>
+      </c>
+      <c r="H34" s="29" t="n"/>
+      <c r="I34" s="29" t="n"/>
+      <c r="J34" s="29" t="n"/>
+      <c r="K34" s="29" t="n"/>
+      <c r="L34" s="29" t="n"/>
+      <c r="M34" s="29" t="n"/>
+      <c r="N34" s="29" t="n"/>
+      <c r="O34" s="29" t="n"/>
+      <c r="P34" s="29" t="n"/>
+      <c r="Q34" s="29" t="n"/>
+      <c r="R34" s="29" t="n"/>
+      <c r="S34" s="29" t="n"/>
+      <c r="T34" s="29" t="n"/>
+    </row>
+    <row r="35" ht="62" customHeight="1">
+      <c r="B35" s="26" t="inlineStr"/>
+      <c r="C35" s="27" t="inlineStr">
+        <is>
+          <t>What worries me</t>
+        </is>
+      </c>
+      <c r="D35" s="28" t="inlineStr">
+        <is>
+          <t>including anything flagged above</t>
+        </is>
+      </c>
+      <c r="E35" s="29" t="inlineStr">
+        <is>
+          <t>Impact figures come from one site.</t>
+        </is>
+      </c>
+      <c r="F35" s="29" t="inlineStr">
+        <is>
+          <t>One customer, references not offered.</t>
+        </is>
+      </c>
+      <c r="G35" s="29" t="inlineStr">
+        <is>
+          <t>Integration is a promise on their timeline, not ours.</t>
+        </is>
+      </c>
+      <c r="H35" s="29" t="n"/>
+      <c r="I35" s="29" t="n"/>
+      <c r="J35" s="29" t="n"/>
+      <c r="K35" s="29" t="n"/>
+      <c r="L35" s="29" t="n"/>
+      <c r="M35" s="29" t="n"/>
+      <c r="N35" s="29" t="n"/>
+      <c r="O35" s="29" t="n"/>
+      <c r="P35" s="29" t="n"/>
+      <c r="Q35" s="29" t="n"/>
+      <c r="R35" s="29" t="n"/>
+      <c r="S35" s="29" t="n"/>
+      <c r="T35" s="29" t="n"/>
+    </row>
+    <row r="36" ht="62" customHeight="1">
+      <c r="B36" s="26" t="inlineStr"/>
+      <c r="C36" s="27" t="inlineStr">
+        <is>
+          <t>What to go and ask</t>
+        </is>
+      </c>
+      <c r="D36" s="28" t="inlineStr">
+        <is>
+          <t>the demo agenda</t>
+        </is>
+      </c>
+      <c r="E36" s="29" t="inlineStr">
+        <is>
+          <t>Would they discuss a stake? Never mentioned it.</t>
+        </is>
+      </c>
+      <c r="F36" s="29" t="inlineStr">
+        <is>
+          <t>What does the day-before confirmation round cost in staff hours at our scale?</t>
+        </is>
+      </c>
+      <c r="G36" s="29" t="inlineStr">
+        <is>
+          <t>What exactly is committed on the integration date, and by whom?</t>
+        </is>
+      </c>
+      <c r="H36" s="29" t="n"/>
+      <c r="I36" s="29" t="n"/>
+      <c r="J36" s="29" t="n"/>
+      <c r="K36" s="29" t="n"/>
+      <c r="L36" s="29" t="n"/>
+      <c r="M36" s="29" t="n"/>
+      <c r="N36" s="29" t="n"/>
+      <c r="O36" s="29" t="n"/>
+      <c r="P36" s="29" t="n"/>
+      <c r="Q36" s="29" t="n"/>
+      <c r="R36" s="29" t="n"/>
+      <c r="S36" s="29" t="n"/>
+      <c r="T36" s="29" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="23">
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B67:D67"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B61:D61"/>
-    <mergeCell ref="B57:D57"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B69:D69"/>
-    <mergeCell ref="B49:D49"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B51:D51"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="B75:D75"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B43:D43"/>
+  <mergeCells count="8">
+    <mergeCell ref="B23:T23"/>
+    <mergeCell ref="B8:T8"/>
+    <mergeCell ref="B18:T18"/>
+    <mergeCell ref="B13:T13"/>
+    <mergeCell ref="B27:T27"/>
+    <mergeCell ref="B4:T4"/>
+    <mergeCell ref="B30:T30"/>
+    <mergeCell ref="B33:T33"/>
   </mergeCells>
+  <conditionalFormatting sqref="E9:T9">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="num" val="40"/>
+        <cfvo type="num" val="65"/>
+        <cfvo type="num" val="90"/>
+        <color rgb="00F5E3E3"/>
+        <color rgb="00FBF3DD"/>
+        <color rgb="00DDEBE0"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E10:T10">
+    <cfRule type="expression" priority="2" dxfId="0">
+      <formula>ISNUMBER(SEARCH("Conditional",E10))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E11:T11">
+    <cfRule type="expression" priority="3" dxfId="0">
+      <formula>E11&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E15:T15">
+    <cfRule type="expression" priority="4" dxfId="1">
+      <formula>E15="STOP-CHECK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E16:T16">
+    <cfRule type="expression" priority="5" dxfId="1">
+      <formula>E16="STOP-CHECK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E25:T25">
+    <cfRule type="expression" priority="6" dxfId="1">
+      <formula>E25="STOP-CHECK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E19:T19">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="5"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="001F6F78"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E20:T20">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="5"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="002E599D"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E21:T21">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="5"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="004E8A5B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="6">
+    <dataValidation sqref="E14:T14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="A1 — Home Care Home Base" prompt="Pick one line. Ambiguous? Take the lower one and say so in Notes." type="list">
+      <formula1>=Lists!$B$2:$B$7</formula1>
+    </dataValidation>
+    <dataValidation sqref="E19:T19 E20:T20 E21:T21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Scope, 0–5" prompt="How much of this arena they cover. Most of it is the ceiling — our spec is original, so nobody covers all of it." type="list">
+      <formula1>=Lists!$E$2:$E$7</formula1>
+    </dataValidation>
+    <dataValidation sqref="E24:T24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Sophistication, 0–4" prompt="1 shows it · 2 checks it · 3 recommends it · 4 runs it. Score what the product does, not how much they wrote about it." type="list">
+      <formula1>=Lists!$G$2:$G$6</formula1>
+    </dataValidation>
+    <dataValidation sqref="E28:T28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Clinician fit, 0–4" prompt="Read D1 to D3 and give it your own read of fit. There is no checklist here on purpose." type="list">
+      <formula1>=Lists!$I$2:$I$6</formula1>
+    </dataValidation>
+    <dataValidation sqref="E31:T31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Partnership, 0–4" prompt="Are they able and willing to build this with us, and open to us holding a stake in what a wider market might buy? A discount is a discount." type="list">
+      <formula1>=Lists!$K$2:$K$6</formula1>
+    </dataValidation>
+    <dataValidation sqref="E15:T15 E16:T16 E25:T25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Flag" prompt="A stop-check is resolved before advancing, not traded against points." type="list">
+      <formula1>"OK,Watch,STOP-CHECK"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1608,799 +1860,799 @@
       </c>
     </row>
     <row r="3" ht="26" customHeight="1">
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Vendor Scorecard — Fast</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>The rows are the questionnaire, in order. Seven take a mark; three raise a flag; the rest are notes. Grey cells are formulas.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="42" customHeight="1">
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>VENDOR</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Vendor 01</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>Vendor 02</t>
         </is>
       </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>Vendor 03</t>
         </is>
       </c>
-      <c r="H6" s="14" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>Vendor 04</t>
         </is>
       </c>
-      <c r="I6" s="14" t="inlineStr">
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>Vendor 05</t>
         </is>
       </c>
-      <c r="J6" s="14" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>Vendor 06</t>
         </is>
       </c>
-      <c r="K6" s="14" t="inlineStr">
+      <c r="K6" s="5" t="inlineStr">
         <is>
           <t>Vendor 07</t>
         </is>
       </c>
-      <c r="L6" s="14" t="inlineStr">
+      <c r="L6" s="5" t="inlineStr">
         <is>
           <t>Vendor 08</t>
         </is>
       </c>
-      <c r="M6" s="14" t="inlineStr">
+      <c r="M6" s="5" t="inlineStr">
         <is>
           <t>Vendor 09</t>
         </is>
       </c>
-      <c r="N6" s="14" t="inlineStr">
+      <c r="N6" s="5" t="inlineStr">
         <is>
           <t>Vendor 10</t>
         </is>
       </c>
-      <c r="O6" s="14" t="inlineStr">
+      <c r="O6" s="5" t="inlineStr">
         <is>
           <t>Vendor 11</t>
         </is>
       </c>
-      <c r="P6" s="14" t="inlineStr">
+      <c r="P6" s="5" t="inlineStr">
         <is>
           <t>Vendor 12</t>
         </is>
       </c>
-      <c r="Q6" s="14" t="inlineStr">
+      <c r="Q6" s="5" t="inlineStr">
         <is>
           <t>Vendor 13</t>
         </is>
       </c>
-      <c r="R6" s="14" t="inlineStr">
+      <c r="R6" s="5" t="inlineStr">
         <is>
           <t>Vendor 14</t>
         </is>
       </c>
-      <c r="S6" s="14" t="inlineStr">
+      <c r="S6" s="5" t="inlineStr">
         <is>
           <t>Vendor 15</t>
         </is>
       </c>
-      <c r="T6" s="14" t="inlineStr">
+      <c r="T6" s="5" t="inlineStr">
         <is>
           <t>Vendor 16</t>
         </is>
       </c>
     </row>
     <row r="8" ht="21" customHeight="1">
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>SCORE</t>
         </is>
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>of 100</t>
         </is>
       </c>
-      <c r="E9" s="17">
-        <f>IFERROR(VLOOKUP(E14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(E19,1)),0)/5*12+IFERROR(VALUE(LEFT(E20,1)),0)/5*12+IFERROR(VALUE(LEFT(E21,1)),0)/5*12+IFERROR(VALUE(LEFT(E24,1)),0)/4*20+IFERROR(VALUE(LEFT(E28,1)),0)/4*12+IFERROR(VALUE(LEFT(E31,1)),0)/4*12</f>
-        <v/>
-      </c>
-      <c r="F9" s="17">
-        <f>IFERROR(VLOOKUP(F14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(F19,1)),0)/5*12+IFERROR(VALUE(LEFT(F20,1)),0)/5*12+IFERROR(VALUE(LEFT(F21,1)),0)/5*12+IFERROR(VALUE(LEFT(F24,1)),0)/4*20+IFERROR(VALUE(LEFT(F28,1)),0)/4*12+IFERROR(VALUE(LEFT(F31,1)),0)/4*12</f>
-        <v/>
-      </c>
-      <c r="G9" s="17">
-        <f>IFERROR(VLOOKUP(G14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(G19,1)),0)/5*12+IFERROR(VALUE(LEFT(G20,1)),0)/5*12+IFERROR(VALUE(LEFT(G21,1)),0)/5*12+IFERROR(VALUE(LEFT(G24,1)),0)/4*20+IFERROR(VALUE(LEFT(G28,1)),0)/4*12+IFERROR(VALUE(LEFT(G31,1)),0)/4*12</f>
-        <v/>
-      </c>
-      <c r="H9" s="17">
-        <f>IFERROR(VLOOKUP(H14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(H19,1)),0)/5*12+IFERROR(VALUE(LEFT(H20,1)),0)/5*12+IFERROR(VALUE(LEFT(H21,1)),0)/5*12+IFERROR(VALUE(LEFT(H24,1)),0)/4*20+IFERROR(VALUE(LEFT(H28,1)),0)/4*12+IFERROR(VALUE(LEFT(H31,1)),0)/4*12</f>
-        <v/>
-      </c>
-      <c r="I9" s="17">
-        <f>IFERROR(VLOOKUP(I14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(I19,1)),0)/5*12+IFERROR(VALUE(LEFT(I20,1)),0)/5*12+IFERROR(VALUE(LEFT(I21,1)),0)/5*12+IFERROR(VALUE(LEFT(I24,1)),0)/4*20+IFERROR(VALUE(LEFT(I28,1)),0)/4*12+IFERROR(VALUE(LEFT(I31,1)),0)/4*12</f>
-        <v/>
-      </c>
-      <c r="J9" s="17">
-        <f>IFERROR(VLOOKUP(J14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(J19,1)),0)/5*12+IFERROR(VALUE(LEFT(J20,1)),0)/5*12+IFERROR(VALUE(LEFT(J21,1)),0)/5*12+IFERROR(VALUE(LEFT(J24,1)),0)/4*20+IFERROR(VALUE(LEFT(J28,1)),0)/4*12+IFERROR(VALUE(LEFT(J31,1)),0)/4*12</f>
-        <v/>
-      </c>
-      <c r="K9" s="17">
-        <f>IFERROR(VLOOKUP(K14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(K19,1)),0)/5*12+IFERROR(VALUE(LEFT(K20,1)),0)/5*12+IFERROR(VALUE(LEFT(K21,1)),0)/5*12+IFERROR(VALUE(LEFT(K24,1)),0)/4*20+IFERROR(VALUE(LEFT(K28,1)),0)/4*12+IFERROR(VALUE(LEFT(K31,1)),0)/4*12</f>
-        <v/>
-      </c>
-      <c r="L9" s="17">
-        <f>IFERROR(VLOOKUP(L14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(L19,1)),0)/5*12+IFERROR(VALUE(LEFT(L20,1)),0)/5*12+IFERROR(VALUE(LEFT(L21,1)),0)/5*12+IFERROR(VALUE(LEFT(L24,1)),0)/4*20+IFERROR(VALUE(LEFT(L28,1)),0)/4*12+IFERROR(VALUE(LEFT(L31,1)),0)/4*12</f>
-        <v/>
-      </c>
-      <c r="M9" s="17">
-        <f>IFERROR(VLOOKUP(M14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(M19,1)),0)/5*12+IFERROR(VALUE(LEFT(M20,1)),0)/5*12+IFERROR(VALUE(LEFT(M21,1)),0)/5*12+IFERROR(VALUE(LEFT(M24,1)),0)/4*20+IFERROR(VALUE(LEFT(M28,1)),0)/4*12+IFERROR(VALUE(LEFT(M31,1)),0)/4*12</f>
-        <v/>
-      </c>
-      <c r="N9" s="17">
-        <f>IFERROR(VLOOKUP(N14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(N19,1)),0)/5*12+IFERROR(VALUE(LEFT(N20,1)),0)/5*12+IFERROR(VALUE(LEFT(N21,1)),0)/5*12+IFERROR(VALUE(LEFT(N24,1)),0)/4*20+IFERROR(VALUE(LEFT(N28,1)),0)/4*12+IFERROR(VALUE(LEFT(N31,1)),0)/4*12</f>
-        <v/>
-      </c>
-      <c r="O9" s="17">
-        <f>IFERROR(VLOOKUP(O14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(O19,1)),0)/5*12+IFERROR(VALUE(LEFT(O20,1)),0)/5*12+IFERROR(VALUE(LEFT(O21,1)),0)/5*12+IFERROR(VALUE(LEFT(O24,1)),0)/4*20+IFERROR(VALUE(LEFT(O28,1)),0)/4*12+IFERROR(VALUE(LEFT(O31,1)),0)/4*12</f>
-        <v/>
-      </c>
-      <c r="P9" s="17">
-        <f>IFERROR(VLOOKUP(P14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(P19,1)),0)/5*12+IFERROR(VALUE(LEFT(P20,1)),0)/5*12+IFERROR(VALUE(LEFT(P21,1)),0)/5*12+IFERROR(VALUE(LEFT(P24,1)),0)/4*20+IFERROR(VALUE(LEFT(P28,1)),0)/4*12+IFERROR(VALUE(LEFT(P31,1)),0)/4*12</f>
-        <v/>
-      </c>
-      <c r="Q9" s="17">
-        <f>IFERROR(VLOOKUP(Q14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(Q19,1)),0)/5*12+IFERROR(VALUE(LEFT(Q20,1)),0)/5*12+IFERROR(VALUE(LEFT(Q21,1)),0)/5*12+IFERROR(VALUE(LEFT(Q24,1)),0)/4*20+IFERROR(VALUE(LEFT(Q28,1)),0)/4*12+IFERROR(VALUE(LEFT(Q31,1)),0)/4*12</f>
-        <v/>
-      </c>
-      <c r="R9" s="17">
-        <f>IFERROR(VLOOKUP(R14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(R19,1)),0)/5*12+IFERROR(VALUE(LEFT(R20,1)),0)/5*12+IFERROR(VALUE(LEFT(R21,1)),0)/5*12+IFERROR(VALUE(LEFT(R24,1)),0)/4*20+IFERROR(VALUE(LEFT(R28,1)),0)/4*12+IFERROR(VALUE(LEFT(R31,1)),0)/4*12</f>
-        <v/>
-      </c>
-      <c r="S9" s="17">
-        <f>IFERROR(VLOOKUP(S14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(S19,1)),0)/5*12+IFERROR(VALUE(LEFT(S20,1)),0)/5*12+IFERROR(VALUE(LEFT(S21,1)),0)/5*12+IFERROR(VALUE(LEFT(S24,1)),0)/4*20+IFERROR(VALUE(LEFT(S28,1)),0)/4*12+IFERROR(VALUE(LEFT(S31,1)),0)/4*12</f>
-        <v/>
-      </c>
-      <c r="T9" s="17">
-        <f>IFERROR(VLOOKUP(T14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(T19,1)),0)/5*12+IFERROR(VALUE(LEFT(T20,1)),0)/5*12+IFERROR(VALUE(LEFT(T21,1)),0)/5*12+IFERROR(VALUE(LEFT(T24,1)),0)/4*20+IFERROR(VALUE(LEFT(T28,1)),0)/4*12+IFERROR(VALUE(LEFT(T31,1)),0)/4*12</f>
+      <c r="E9" s="9">
+        <f>IF(E14="","",IFERROR(VLOOKUP(E14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(E19,1)),0)/5*12+IFERROR(VALUE(LEFT(E20,1)),0)/5*12+IFERROR(VALUE(LEFT(E21,1)),0)/5*12+IFERROR(VALUE(LEFT(E24,1)),0)/4*20+IFERROR(VALUE(LEFT(E28,1)),0)/4*12+IFERROR(VALUE(LEFT(E31,1)),0)/4*12)</f>
+        <v/>
+      </c>
+      <c r="F9" s="9">
+        <f>IF(F14="","",IFERROR(VLOOKUP(F14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(F19,1)),0)/5*12+IFERROR(VALUE(LEFT(F20,1)),0)/5*12+IFERROR(VALUE(LEFT(F21,1)),0)/5*12+IFERROR(VALUE(LEFT(F24,1)),0)/4*20+IFERROR(VALUE(LEFT(F28,1)),0)/4*12+IFERROR(VALUE(LEFT(F31,1)),0)/4*12)</f>
+        <v/>
+      </c>
+      <c r="G9" s="9">
+        <f>IF(G14="","",IFERROR(VLOOKUP(G14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(G19,1)),0)/5*12+IFERROR(VALUE(LEFT(G20,1)),0)/5*12+IFERROR(VALUE(LEFT(G21,1)),0)/5*12+IFERROR(VALUE(LEFT(G24,1)),0)/4*20+IFERROR(VALUE(LEFT(G28,1)),0)/4*12+IFERROR(VALUE(LEFT(G31,1)),0)/4*12)</f>
+        <v/>
+      </c>
+      <c r="H9" s="9">
+        <f>IF(H14="","",IFERROR(VLOOKUP(H14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(H19,1)),0)/5*12+IFERROR(VALUE(LEFT(H20,1)),0)/5*12+IFERROR(VALUE(LEFT(H21,1)),0)/5*12+IFERROR(VALUE(LEFT(H24,1)),0)/4*20+IFERROR(VALUE(LEFT(H28,1)),0)/4*12+IFERROR(VALUE(LEFT(H31,1)),0)/4*12)</f>
+        <v/>
+      </c>
+      <c r="I9" s="9">
+        <f>IF(I14="","",IFERROR(VLOOKUP(I14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(I19,1)),0)/5*12+IFERROR(VALUE(LEFT(I20,1)),0)/5*12+IFERROR(VALUE(LEFT(I21,1)),0)/5*12+IFERROR(VALUE(LEFT(I24,1)),0)/4*20+IFERROR(VALUE(LEFT(I28,1)),0)/4*12+IFERROR(VALUE(LEFT(I31,1)),0)/4*12)</f>
+        <v/>
+      </c>
+      <c r="J9" s="9">
+        <f>IF(J14="","",IFERROR(VLOOKUP(J14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(J19,1)),0)/5*12+IFERROR(VALUE(LEFT(J20,1)),0)/5*12+IFERROR(VALUE(LEFT(J21,1)),0)/5*12+IFERROR(VALUE(LEFT(J24,1)),0)/4*20+IFERROR(VALUE(LEFT(J28,1)),0)/4*12+IFERROR(VALUE(LEFT(J31,1)),0)/4*12)</f>
+        <v/>
+      </c>
+      <c r="K9" s="9">
+        <f>IF(K14="","",IFERROR(VLOOKUP(K14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(K19,1)),0)/5*12+IFERROR(VALUE(LEFT(K20,1)),0)/5*12+IFERROR(VALUE(LEFT(K21,1)),0)/5*12+IFERROR(VALUE(LEFT(K24,1)),0)/4*20+IFERROR(VALUE(LEFT(K28,1)),0)/4*12+IFERROR(VALUE(LEFT(K31,1)),0)/4*12)</f>
+        <v/>
+      </c>
+      <c r="L9" s="9">
+        <f>IF(L14="","",IFERROR(VLOOKUP(L14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(L19,1)),0)/5*12+IFERROR(VALUE(LEFT(L20,1)),0)/5*12+IFERROR(VALUE(LEFT(L21,1)),0)/5*12+IFERROR(VALUE(LEFT(L24,1)),0)/4*20+IFERROR(VALUE(LEFT(L28,1)),0)/4*12+IFERROR(VALUE(LEFT(L31,1)),0)/4*12)</f>
+        <v/>
+      </c>
+      <c r="M9" s="9">
+        <f>IF(M14="","",IFERROR(VLOOKUP(M14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(M19,1)),0)/5*12+IFERROR(VALUE(LEFT(M20,1)),0)/5*12+IFERROR(VALUE(LEFT(M21,1)),0)/5*12+IFERROR(VALUE(LEFT(M24,1)),0)/4*20+IFERROR(VALUE(LEFT(M28,1)),0)/4*12+IFERROR(VALUE(LEFT(M31,1)),0)/4*12)</f>
+        <v/>
+      </c>
+      <c r="N9" s="9">
+        <f>IF(N14="","",IFERROR(VLOOKUP(N14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(N19,1)),0)/5*12+IFERROR(VALUE(LEFT(N20,1)),0)/5*12+IFERROR(VALUE(LEFT(N21,1)),0)/5*12+IFERROR(VALUE(LEFT(N24,1)),0)/4*20+IFERROR(VALUE(LEFT(N28,1)),0)/4*12+IFERROR(VALUE(LEFT(N31,1)),0)/4*12)</f>
+        <v/>
+      </c>
+      <c r="O9" s="9">
+        <f>IF(O14="","",IFERROR(VLOOKUP(O14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(O19,1)),0)/5*12+IFERROR(VALUE(LEFT(O20,1)),0)/5*12+IFERROR(VALUE(LEFT(O21,1)),0)/5*12+IFERROR(VALUE(LEFT(O24,1)),0)/4*20+IFERROR(VALUE(LEFT(O28,1)),0)/4*12+IFERROR(VALUE(LEFT(O31,1)),0)/4*12)</f>
+        <v/>
+      </c>
+      <c r="P9" s="9">
+        <f>IF(P14="","",IFERROR(VLOOKUP(P14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(P19,1)),0)/5*12+IFERROR(VALUE(LEFT(P20,1)),0)/5*12+IFERROR(VALUE(LEFT(P21,1)),0)/5*12+IFERROR(VALUE(LEFT(P24,1)),0)/4*20+IFERROR(VALUE(LEFT(P28,1)),0)/4*12+IFERROR(VALUE(LEFT(P31,1)),0)/4*12)</f>
+        <v/>
+      </c>
+      <c r="Q9" s="9">
+        <f>IF(Q14="","",IFERROR(VLOOKUP(Q14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(Q19,1)),0)/5*12+IFERROR(VALUE(LEFT(Q20,1)),0)/5*12+IFERROR(VALUE(LEFT(Q21,1)),0)/5*12+IFERROR(VALUE(LEFT(Q24,1)),0)/4*20+IFERROR(VALUE(LEFT(Q28,1)),0)/4*12+IFERROR(VALUE(LEFT(Q31,1)),0)/4*12)</f>
+        <v/>
+      </c>
+      <c r="R9" s="9">
+        <f>IF(R14="","",IFERROR(VLOOKUP(R14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(R19,1)),0)/5*12+IFERROR(VALUE(LEFT(R20,1)),0)/5*12+IFERROR(VALUE(LEFT(R21,1)),0)/5*12+IFERROR(VALUE(LEFT(R24,1)),0)/4*20+IFERROR(VALUE(LEFT(R28,1)),0)/4*12+IFERROR(VALUE(LEFT(R31,1)),0)/4*12)</f>
+        <v/>
+      </c>
+      <c r="S9" s="9">
+        <f>IF(S14="","",IFERROR(VLOOKUP(S14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(S19,1)),0)/5*12+IFERROR(VALUE(LEFT(S20,1)),0)/5*12+IFERROR(VALUE(LEFT(S21,1)),0)/5*12+IFERROR(VALUE(LEFT(S24,1)),0)/4*20+IFERROR(VALUE(LEFT(S28,1)),0)/4*12+IFERROR(VALUE(LEFT(S31,1)),0)/4*12)</f>
+        <v/>
+      </c>
+      <c r="T9" s="9">
+        <f>IF(T14="","",IFERROR(VLOOKUP(T14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(T19,1)),0)/5*12+IFERROR(VALUE(LEFT(T20,1)),0)/5*12+IFERROR(VALUE(LEFT(T21,1)),0)/5*12+IFERROR(VALUE(LEFT(T24,1)),0)/4*20+IFERROR(VALUE(LEFT(T28,1)),0)/4*12+IFERROR(VALUE(LEFT(T31,1)),0)/4*12)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>Band</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>80 Advance · 65 Consider · 50 Hold</t>
         </is>
       </c>
-      <c r="E10" s="19">
-        <f>IF(IFERROR(VLOOKUP(E14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(E9&gt;=80,"Advance",IF(E9&gt;=65,"Consider",IF(E9&gt;=50,"Hold","Decline")))</f>
-        <v/>
-      </c>
-      <c r="F10" s="19">
-        <f>IF(IFERROR(VLOOKUP(F14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(F9&gt;=80,"Advance",IF(F9&gt;=65,"Consider",IF(F9&gt;=50,"Hold","Decline")))</f>
-        <v/>
-      </c>
-      <c r="G10" s="19">
-        <f>IF(IFERROR(VLOOKUP(G14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(G9&gt;=80,"Advance",IF(G9&gt;=65,"Consider",IF(G9&gt;=50,"Hold","Decline")))</f>
-        <v/>
-      </c>
-      <c r="H10" s="19">
-        <f>IF(IFERROR(VLOOKUP(H14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(H9&gt;=80,"Advance",IF(H9&gt;=65,"Consider",IF(H9&gt;=50,"Hold","Decline")))</f>
-        <v/>
-      </c>
-      <c r="I10" s="19">
-        <f>IF(IFERROR(VLOOKUP(I14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(I9&gt;=80,"Advance",IF(I9&gt;=65,"Consider",IF(I9&gt;=50,"Hold","Decline")))</f>
-        <v/>
-      </c>
-      <c r="J10" s="19">
-        <f>IF(IFERROR(VLOOKUP(J14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(J9&gt;=80,"Advance",IF(J9&gt;=65,"Consider",IF(J9&gt;=50,"Hold","Decline")))</f>
-        <v/>
-      </c>
-      <c r="K10" s="19">
-        <f>IF(IFERROR(VLOOKUP(K14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(K9&gt;=80,"Advance",IF(K9&gt;=65,"Consider",IF(K9&gt;=50,"Hold","Decline")))</f>
-        <v/>
-      </c>
-      <c r="L10" s="19">
-        <f>IF(IFERROR(VLOOKUP(L14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(L9&gt;=80,"Advance",IF(L9&gt;=65,"Consider",IF(L9&gt;=50,"Hold","Decline")))</f>
-        <v/>
-      </c>
-      <c r="M10" s="19">
-        <f>IF(IFERROR(VLOOKUP(M14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(M9&gt;=80,"Advance",IF(M9&gt;=65,"Consider",IF(M9&gt;=50,"Hold","Decline")))</f>
-        <v/>
-      </c>
-      <c r="N10" s="19">
-        <f>IF(IFERROR(VLOOKUP(N14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(N9&gt;=80,"Advance",IF(N9&gt;=65,"Consider",IF(N9&gt;=50,"Hold","Decline")))</f>
-        <v/>
-      </c>
-      <c r="O10" s="19">
-        <f>IF(IFERROR(VLOOKUP(O14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(O9&gt;=80,"Advance",IF(O9&gt;=65,"Consider",IF(O9&gt;=50,"Hold","Decline")))</f>
-        <v/>
-      </c>
-      <c r="P10" s="19">
-        <f>IF(IFERROR(VLOOKUP(P14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(P9&gt;=80,"Advance",IF(P9&gt;=65,"Consider",IF(P9&gt;=50,"Hold","Decline")))</f>
-        <v/>
-      </c>
-      <c r="Q10" s="19">
-        <f>IF(IFERROR(VLOOKUP(Q14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(Q9&gt;=80,"Advance",IF(Q9&gt;=65,"Consider",IF(Q9&gt;=50,"Hold","Decline")))</f>
-        <v/>
-      </c>
-      <c r="R10" s="19">
-        <f>IF(IFERROR(VLOOKUP(R14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(R9&gt;=80,"Advance",IF(R9&gt;=65,"Consider",IF(R9&gt;=50,"Hold","Decline")))</f>
-        <v/>
-      </c>
-      <c r="S10" s="19">
-        <f>IF(IFERROR(VLOOKUP(S14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(S9&gt;=80,"Advance",IF(S9&gt;=65,"Consider",IF(S9&gt;=50,"Hold","Decline")))</f>
-        <v/>
-      </c>
-      <c r="T10" s="19">
-        <f>IF(IFERROR(VLOOKUP(T14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(T9&gt;=80,"Advance",IF(T9&gt;=65,"Consider",IF(T9&gt;=50,"Hold","Decline")))</f>
+      <c r="E10" s="11">
+        <f>IF(E14="","",IF(IFERROR(VLOOKUP(E14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(E9&gt;=80,"Advance",IF(E9&gt;=65,"Consider",IF(E9&gt;=50,"Hold","Decline"))))</f>
+        <v/>
+      </c>
+      <c r="F10" s="11">
+        <f>IF(F14="","",IF(IFERROR(VLOOKUP(F14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(F9&gt;=80,"Advance",IF(F9&gt;=65,"Consider",IF(F9&gt;=50,"Hold","Decline"))))</f>
+        <v/>
+      </c>
+      <c r="G10" s="11">
+        <f>IF(G14="","",IF(IFERROR(VLOOKUP(G14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(G9&gt;=80,"Advance",IF(G9&gt;=65,"Consider",IF(G9&gt;=50,"Hold","Decline"))))</f>
+        <v/>
+      </c>
+      <c r="H10" s="11">
+        <f>IF(H14="","",IF(IFERROR(VLOOKUP(H14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(H9&gt;=80,"Advance",IF(H9&gt;=65,"Consider",IF(H9&gt;=50,"Hold","Decline"))))</f>
+        <v/>
+      </c>
+      <c r="I10" s="11">
+        <f>IF(I14="","",IF(IFERROR(VLOOKUP(I14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(I9&gt;=80,"Advance",IF(I9&gt;=65,"Consider",IF(I9&gt;=50,"Hold","Decline"))))</f>
+        <v/>
+      </c>
+      <c r="J10" s="11">
+        <f>IF(J14="","",IF(IFERROR(VLOOKUP(J14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(J9&gt;=80,"Advance",IF(J9&gt;=65,"Consider",IF(J9&gt;=50,"Hold","Decline"))))</f>
+        <v/>
+      </c>
+      <c r="K10" s="11">
+        <f>IF(K14="","",IF(IFERROR(VLOOKUP(K14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(K9&gt;=80,"Advance",IF(K9&gt;=65,"Consider",IF(K9&gt;=50,"Hold","Decline"))))</f>
+        <v/>
+      </c>
+      <c r="L10" s="11">
+        <f>IF(L14="","",IF(IFERROR(VLOOKUP(L14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(L9&gt;=80,"Advance",IF(L9&gt;=65,"Consider",IF(L9&gt;=50,"Hold","Decline"))))</f>
+        <v/>
+      </c>
+      <c r="M10" s="11">
+        <f>IF(M14="","",IF(IFERROR(VLOOKUP(M14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(M9&gt;=80,"Advance",IF(M9&gt;=65,"Consider",IF(M9&gt;=50,"Hold","Decline"))))</f>
+        <v/>
+      </c>
+      <c r="N10" s="11">
+        <f>IF(N14="","",IF(IFERROR(VLOOKUP(N14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(N9&gt;=80,"Advance",IF(N9&gt;=65,"Consider",IF(N9&gt;=50,"Hold","Decline"))))</f>
+        <v/>
+      </c>
+      <c r="O10" s="11">
+        <f>IF(O14="","",IF(IFERROR(VLOOKUP(O14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(O9&gt;=80,"Advance",IF(O9&gt;=65,"Consider",IF(O9&gt;=50,"Hold","Decline"))))</f>
+        <v/>
+      </c>
+      <c r="P10" s="11">
+        <f>IF(P14="","",IF(IFERROR(VLOOKUP(P14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(P9&gt;=80,"Advance",IF(P9&gt;=65,"Consider",IF(P9&gt;=50,"Hold","Decline"))))</f>
+        <v/>
+      </c>
+      <c r="Q10" s="11">
+        <f>IF(Q14="","",IF(IFERROR(VLOOKUP(Q14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(Q9&gt;=80,"Advance",IF(Q9&gt;=65,"Consider",IF(Q9&gt;=50,"Hold","Decline"))))</f>
+        <v/>
+      </c>
+      <c r="R10" s="11">
+        <f>IF(R14="","",IF(IFERROR(VLOOKUP(R14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(R9&gt;=80,"Advance",IF(R9&gt;=65,"Consider",IF(R9&gt;=50,"Hold","Decline"))))</f>
+        <v/>
+      </c>
+      <c r="S10" s="11">
+        <f>IF(S14="","",IF(IFERROR(VLOOKUP(S14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(S9&gt;=80,"Advance",IF(S9&gt;=65,"Consider",IF(S9&gt;=50,"Hold","Decline"))))</f>
+        <v/>
+      </c>
+      <c r="T10" s="11">
+        <f>IF(T14="","",IF(IFERROR(VLOOKUP(T14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(T9&gt;=80,"Advance",IF(T9&gt;=65,"Consider",IF(T9&gt;=50,"Hold","Decline"))))</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="20" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>Flags</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>stop-checks raised, of three</t>
         </is>
       </c>
-      <c r="E11" s="21">
-        <f>(IF(E15="STOP-CHECK",1,0)+IF(E16="STOP-CHECK",1,0)+IF(E25="STOP-CHECK",1,0))</f>
-        <v/>
-      </c>
-      <c r="F11" s="21">
-        <f>(IF(F15="STOP-CHECK",1,0)+IF(F16="STOP-CHECK",1,0)+IF(F25="STOP-CHECK",1,0))</f>
-        <v/>
-      </c>
-      <c r="G11" s="21">
-        <f>(IF(G15="STOP-CHECK",1,0)+IF(G16="STOP-CHECK",1,0)+IF(G25="STOP-CHECK",1,0))</f>
-        <v/>
-      </c>
-      <c r="H11" s="21">
-        <f>(IF(H15="STOP-CHECK",1,0)+IF(H16="STOP-CHECK",1,0)+IF(H25="STOP-CHECK",1,0))</f>
-        <v/>
-      </c>
-      <c r="I11" s="21">
-        <f>(IF(I15="STOP-CHECK",1,0)+IF(I16="STOP-CHECK",1,0)+IF(I25="STOP-CHECK",1,0))</f>
-        <v/>
-      </c>
-      <c r="J11" s="21">
-        <f>(IF(J15="STOP-CHECK",1,0)+IF(J16="STOP-CHECK",1,0)+IF(J25="STOP-CHECK",1,0))</f>
-        <v/>
-      </c>
-      <c r="K11" s="21">
-        <f>(IF(K15="STOP-CHECK",1,0)+IF(K16="STOP-CHECK",1,0)+IF(K25="STOP-CHECK",1,0))</f>
-        <v/>
-      </c>
-      <c r="L11" s="21">
-        <f>(IF(L15="STOP-CHECK",1,0)+IF(L16="STOP-CHECK",1,0)+IF(L25="STOP-CHECK",1,0))</f>
-        <v/>
-      </c>
-      <c r="M11" s="21">
-        <f>(IF(M15="STOP-CHECK",1,0)+IF(M16="STOP-CHECK",1,0)+IF(M25="STOP-CHECK",1,0))</f>
-        <v/>
-      </c>
-      <c r="N11" s="21">
-        <f>(IF(N15="STOP-CHECK",1,0)+IF(N16="STOP-CHECK",1,0)+IF(N25="STOP-CHECK",1,0))</f>
-        <v/>
-      </c>
-      <c r="O11" s="21">
-        <f>(IF(O15="STOP-CHECK",1,0)+IF(O16="STOP-CHECK",1,0)+IF(O25="STOP-CHECK",1,0))</f>
-        <v/>
-      </c>
-      <c r="P11" s="21">
-        <f>(IF(P15="STOP-CHECK",1,0)+IF(P16="STOP-CHECK",1,0)+IF(P25="STOP-CHECK",1,0))</f>
-        <v/>
-      </c>
-      <c r="Q11" s="21">
-        <f>(IF(Q15="STOP-CHECK",1,0)+IF(Q16="STOP-CHECK",1,0)+IF(Q25="STOP-CHECK",1,0))</f>
-        <v/>
-      </c>
-      <c r="R11" s="21">
-        <f>(IF(R15="STOP-CHECK",1,0)+IF(R16="STOP-CHECK",1,0)+IF(R25="STOP-CHECK",1,0))</f>
-        <v/>
-      </c>
-      <c r="S11" s="21">
-        <f>(IF(S15="STOP-CHECK",1,0)+IF(S16="STOP-CHECK",1,0)+IF(S25="STOP-CHECK",1,0))</f>
-        <v/>
-      </c>
-      <c r="T11" s="21">
-        <f>(IF(T15="STOP-CHECK",1,0)+IF(T16="STOP-CHECK",1,0)+IF(T25="STOP-CHECK",1,0))</f>
+      <c r="E11" s="13">
+        <f>IF(E14="","",IF(E15="STOP-CHECK",1,0)+IF(E16="STOP-CHECK",1,0)+IF(E25="STOP-CHECK",1,0))</f>
+        <v/>
+      </c>
+      <c r="F11" s="13">
+        <f>IF(F14="","",IF(F15="STOP-CHECK",1,0)+IF(F16="STOP-CHECK",1,0)+IF(F25="STOP-CHECK",1,0))</f>
+        <v/>
+      </c>
+      <c r="G11" s="13">
+        <f>IF(G14="","",IF(G15="STOP-CHECK",1,0)+IF(G16="STOP-CHECK",1,0)+IF(G25="STOP-CHECK",1,0))</f>
+        <v/>
+      </c>
+      <c r="H11" s="13">
+        <f>IF(H14="","",IF(H15="STOP-CHECK",1,0)+IF(H16="STOP-CHECK",1,0)+IF(H25="STOP-CHECK",1,0))</f>
+        <v/>
+      </c>
+      <c r="I11" s="13">
+        <f>IF(I14="","",IF(I15="STOP-CHECK",1,0)+IF(I16="STOP-CHECK",1,0)+IF(I25="STOP-CHECK",1,0))</f>
+        <v/>
+      </c>
+      <c r="J11" s="13">
+        <f>IF(J14="","",IF(J15="STOP-CHECK",1,0)+IF(J16="STOP-CHECK",1,0)+IF(J25="STOP-CHECK",1,0))</f>
+        <v/>
+      </c>
+      <c r="K11" s="13">
+        <f>IF(K14="","",IF(K15="STOP-CHECK",1,0)+IF(K16="STOP-CHECK",1,0)+IF(K25="STOP-CHECK",1,0))</f>
+        <v/>
+      </c>
+      <c r="L11" s="13">
+        <f>IF(L14="","",IF(L15="STOP-CHECK",1,0)+IF(L16="STOP-CHECK",1,0)+IF(L25="STOP-CHECK",1,0))</f>
+        <v/>
+      </c>
+      <c r="M11" s="13">
+        <f>IF(M14="","",IF(M15="STOP-CHECK",1,0)+IF(M16="STOP-CHECK",1,0)+IF(M25="STOP-CHECK",1,0))</f>
+        <v/>
+      </c>
+      <c r="N11" s="13">
+        <f>IF(N14="","",IF(N15="STOP-CHECK",1,0)+IF(N16="STOP-CHECK",1,0)+IF(N25="STOP-CHECK",1,0))</f>
+        <v/>
+      </c>
+      <c r="O11" s="13">
+        <f>IF(O14="","",IF(O15="STOP-CHECK",1,0)+IF(O16="STOP-CHECK",1,0)+IF(O25="STOP-CHECK",1,0))</f>
+        <v/>
+      </c>
+      <c r="P11" s="13">
+        <f>IF(P14="","",IF(P15="STOP-CHECK",1,0)+IF(P16="STOP-CHECK",1,0)+IF(P25="STOP-CHECK",1,0))</f>
+        <v/>
+      </c>
+      <c r="Q11" s="13">
+        <f>IF(Q14="","",IF(Q15="STOP-CHECK",1,0)+IF(Q16="STOP-CHECK",1,0)+IF(Q25="STOP-CHECK",1,0))</f>
+        <v/>
+      </c>
+      <c r="R11" s="13">
+        <f>IF(R14="","",IF(R15="STOP-CHECK",1,0)+IF(R16="STOP-CHECK",1,0)+IF(R25="STOP-CHECK",1,0))</f>
+        <v/>
+      </c>
+      <c r="S11" s="13">
+        <f>IF(S14="","",IF(S15="STOP-CHECK",1,0)+IF(S16="STOP-CHECK",1,0)+IF(S25="STOP-CHECK",1,0))</f>
+        <v/>
+      </c>
+      <c r="T11" s="13">
+        <f>IF(T14="","",IF(T15="STOP-CHECK",1,0)+IF(T16="STOP-CHECK",1,0)+IF(T25="STOP-CHECK",1,0))</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="21" customHeight="1">
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>A  ·  COMPANY AND PRODUCT</t>
         </is>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="B14" s="22" t="inlineStr">
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
-      <c r="C14" s="23" t="inlineStr">
+      <c r="C14" s="15" t="inlineStr">
         <is>
           <t>Home Care Home Base integration</t>
         </is>
       </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>Pick one line  ·  20 points</t>
         </is>
       </c>
-      <c r="E14" s="24" t="n"/>
-      <c r="F14" s="24" t="n"/>
-      <c r="G14" s="24" t="n"/>
-      <c r="H14" s="24" t="n"/>
-      <c r="I14" s="24" t="n"/>
-      <c r="J14" s="24" t="n"/>
-      <c r="K14" s="24" t="n"/>
-      <c r="L14" s="24" t="n"/>
-      <c r="M14" s="24" t="n"/>
-      <c r="N14" s="24" t="n"/>
-      <c r="O14" s="24" t="n"/>
-      <c r="P14" s="24" t="n"/>
-      <c r="Q14" s="24" t="n"/>
-      <c r="R14" s="24" t="n"/>
-      <c r="S14" s="24" t="n"/>
-      <c r="T14" s="24" t="n"/>
+      <c r="E14" s="16" t="n"/>
+      <c r="F14" s="16" t="n"/>
+      <c r="G14" s="16" t="n"/>
+      <c r="H14" s="16" t="n"/>
+      <c r="I14" s="16" t="n"/>
+      <c r="J14" s="16" t="n"/>
+      <c r="K14" s="16" t="n"/>
+      <c r="L14" s="16" t="n"/>
+      <c r="M14" s="16" t="n"/>
+      <c r="N14" s="16" t="n"/>
+      <c r="O14" s="16" t="n"/>
+      <c r="P14" s="16" t="n"/>
+      <c r="Q14" s="16" t="n"/>
+      <c r="R14" s="16" t="n"/>
+      <c r="S14" s="16" t="n"/>
+      <c r="T14" s="16" t="n"/>
     </row>
     <row r="15" ht="19" customHeight="1">
-      <c r="B15" s="25" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>A2</t>
         </is>
       </c>
-      <c r="C15" s="23" t="inlineStr">
+      <c r="C15" s="15" t="inlineStr">
         <is>
           <t>Customers, scale and references</t>
         </is>
       </c>
-      <c r="D15" s="16" t="inlineStr">
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>Flag  ·  stop-check if one customer or no references</t>
         </is>
       </c>
-      <c r="E15" s="26" t="n"/>
-      <c r="F15" s="26" t="n"/>
-      <c r="G15" s="26" t="n"/>
-      <c r="H15" s="26" t="n"/>
-      <c r="I15" s="26" t="n"/>
-      <c r="J15" s="26" t="n"/>
-      <c r="K15" s="26" t="n"/>
-      <c r="L15" s="26" t="n"/>
-      <c r="M15" s="26" t="n"/>
-      <c r="N15" s="26" t="n"/>
-      <c r="O15" s="26" t="n"/>
-      <c r="P15" s="26" t="n"/>
-      <c r="Q15" s="26" t="n"/>
-      <c r="R15" s="26" t="n"/>
-      <c r="S15" s="26" t="n"/>
-      <c r="T15" s="26" t="n"/>
+      <c r="E15" s="18" t="n"/>
+      <c r="F15" s="18" t="n"/>
+      <c r="G15" s="18" t="n"/>
+      <c r="H15" s="18" t="n"/>
+      <c r="I15" s="18" t="n"/>
+      <c r="J15" s="18" t="n"/>
+      <c r="K15" s="18" t="n"/>
+      <c r="L15" s="18" t="n"/>
+      <c r="M15" s="18" t="n"/>
+      <c r="N15" s="18" t="n"/>
+      <c r="O15" s="18" t="n"/>
+      <c r="P15" s="18" t="n"/>
+      <c r="Q15" s="18" t="n"/>
+      <c r="R15" s="18" t="n"/>
+      <c r="S15" s="18" t="n"/>
+      <c r="T15" s="18" t="n"/>
     </row>
     <row r="16" ht="19" customHeight="1">
-      <c r="B16" s="25" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="C16" s="23" t="inlineStr">
+      <c r="C16" s="15" t="inlineStr">
         <is>
           <t>Measured impact</t>
         </is>
       </c>
-      <c r="D16" s="16" t="inlineStr">
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>Flag  ·  watch if no baseline or period</t>
         </is>
       </c>
-      <c r="E16" s="26" t="n"/>
-      <c r="F16" s="26" t="n"/>
-      <c r="G16" s="26" t="n"/>
-      <c r="H16" s="26" t="n"/>
-      <c r="I16" s="26" t="n"/>
-      <c r="J16" s="26" t="n"/>
-      <c r="K16" s="26" t="n"/>
-      <c r="L16" s="26" t="n"/>
-      <c r="M16" s="26" t="n"/>
-      <c r="N16" s="26" t="n"/>
-      <c r="O16" s="26" t="n"/>
-      <c r="P16" s="26" t="n"/>
-      <c r="Q16" s="26" t="n"/>
-      <c r="R16" s="26" t="n"/>
-      <c r="S16" s="26" t="n"/>
-      <c r="T16" s="26" t="n"/>
+      <c r="E16" s="18" t="n"/>
+      <c r="F16" s="18" t="n"/>
+      <c r="G16" s="18" t="n"/>
+      <c r="H16" s="18" t="n"/>
+      <c r="I16" s="18" t="n"/>
+      <c r="J16" s="18" t="n"/>
+      <c r="K16" s="18" t="n"/>
+      <c r="L16" s="18" t="n"/>
+      <c r="M16" s="18" t="n"/>
+      <c r="N16" s="18" t="n"/>
+      <c r="O16" s="18" t="n"/>
+      <c r="P16" s="18" t="n"/>
+      <c r="Q16" s="18" t="n"/>
+      <c r="R16" s="18" t="n"/>
+      <c r="S16" s="18" t="n"/>
+      <c r="T16" s="18" t="n"/>
     </row>
     <row r="18" ht="21" customHeight="1">
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>B  ·  COVERAGE SELF-ASSESSMENT   —   how much of our scope they cover</t>
         </is>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1">
-      <c r="B19" s="27" t="inlineStr">
+      <c r="B19" s="19" t="inlineStr">
         <is>
           <t>Section B</t>
         </is>
       </c>
-      <c r="C19" s="23" t="inlineStr">
+      <c r="C19" s="15" t="inlineStr">
         <is>
           <t>Capacity</t>
         </is>
       </c>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="D19" s="8" t="inlineStr">
         <is>
           <t>Workforce supply · availability &amp; reach · the capacity math  ·  0–5  ·  12 points</t>
         </is>
       </c>
-      <c r="E19" s="28" t="n"/>
-      <c r="F19" s="28" t="n"/>
-      <c r="G19" s="28" t="n"/>
-      <c r="H19" s="28" t="n"/>
-      <c r="I19" s="28" t="n"/>
-      <c r="J19" s="28" t="n"/>
-      <c r="K19" s="28" t="n"/>
-      <c r="L19" s="28" t="n"/>
-      <c r="M19" s="28" t="n"/>
-      <c r="N19" s="28" t="n"/>
-      <c r="O19" s="28" t="n"/>
-      <c r="P19" s="28" t="n"/>
-      <c r="Q19" s="28" t="n"/>
-      <c r="R19" s="28" t="n"/>
-      <c r="S19" s="28" t="n"/>
-      <c r="T19" s="28" t="n"/>
+      <c r="E19" s="20" t="n"/>
+      <c r="F19" s="20" t="n"/>
+      <c r="G19" s="20" t="n"/>
+      <c r="H19" s="20" t="n"/>
+      <c r="I19" s="20" t="n"/>
+      <c r="J19" s="20" t="n"/>
+      <c r="K19" s="20" t="n"/>
+      <c r="L19" s="20" t="n"/>
+      <c r="M19" s="20" t="n"/>
+      <c r="N19" s="20" t="n"/>
+      <c r="O19" s="20" t="n"/>
+      <c r="P19" s="20" t="n"/>
+      <c r="Q19" s="20" t="n"/>
+      <c r="R19" s="20" t="n"/>
+      <c r="S19" s="20" t="n"/>
+      <c r="T19" s="20" t="n"/>
     </row>
     <row r="20" ht="19" customHeight="1">
-      <c r="B20" s="29" t="inlineStr">
+      <c r="B20" s="21" t="inlineStr">
         <is>
           <t>Section B</t>
         </is>
       </c>
-      <c r="C20" s="23" t="inlineStr">
+      <c r="C20" s="15" t="inlineStr">
         <is>
           <t>Scheduling</t>
         </is>
       </c>
-      <c r="D20" s="16" t="inlineStr">
+      <c r="D20" s="8" t="inlineStr">
         <is>
           <t>Demand · matching · routing &amp; the week · exceptions  ·  0–5  ·  12 points</t>
         </is>
       </c>
-      <c r="E20" s="28" t="n"/>
-      <c r="F20" s="28" t="n"/>
-      <c r="G20" s="28" t="n"/>
-      <c r="H20" s="28" t="n"/>
-      <c r="I20" s="28" t="n"/>
-      <c r="J20" s="28" t="n"/>
-      <c r="K20" s="28" t="n"/>
-      <c r="L20" s="28" t="n"/>
-      <c r="M20" s="28" t="n"/>
-      <c r="N20" s="28" t="n"/>
-      <c r="O20" s="28" t="n"/>
-      <c r="P20" s="28" t="n"/>
-      <c r="Q20" s="28" t="n"/>
-      <c r="R20" s="28" t="n"/>
-      <c r="S20" s="28" t="n"/>
-      <c r="T20" s="28" t="n"/>
+      <c r="E20" s="20" t="n"/>
+      <c r="F20" s="20" t="n"/>
+      <c r="G20" s="20" t="n"/>
+      <c r="H20" s="20" t="n"/>
+      <c r="I20" s="20" t="n"/>
+      <c r="J20" s="20" t="n"/>
+      <c r="K20" s="20" t="n"/>
+      <c r="L20" s="20" t="n"/>
+      <c r="M20" s="20" t="n"/>
+      <c r="N20" s="20" t="n"/>
+      <c r="O20" s="20" t="n"/>
+      <c r="P20" s="20" t="n"/>
+      <c r="Q20" s="20" t="n"/>
+      <c r="R20" s="20" t="n"/>
+      <c r="S20" s="20" t="n"/>
+      <c r="T20" s="20" t="n"/>
     </row>
     <row r="21" ht="19" customHeight="1">
-      <c r="B21" s="30" t="inlineStr">
+      <c r="B21" s="22" t="inlineStr">
         <is>
           <t>Section B</t>
         </is>
       </c>
-      <c r="C21" s="23" t="inlineStr">
+      <c r="C21" s="15" t="inlineStr">
         <is>
           <t>Engagement</t>
         </is>
       </c>
-      <c r="D21" s="16" t="inlineStr">
+      <c r="D21" s="8" t="inlineStr">
         <is>
           <t>Before the visit · when plans change · incentives · care team  ·  0–5  ·  12 points</t>
         </is>
       </c>
-      <c r="E21" s="28" t="n"/>
-      <c r="F21" s="28" t="n"/>
-      <c r="G21" s="28" t="n"/>
-      <c r="H21" s="28" t="n"/>
-      <c r="I21" s="28" t="n"/>
-      <c r="J21" s="28" t="n"/>
-      <c r="K21" s="28" t="n"/>
-      <c r="L21" s="28" t="n"/>
-      <c r="M21" s="28" t="n"/>
-      <c r="N21" s="28" t="n"/>
-      <c r="O21" s="28" t="n"/>
-      <c r="P21" s="28" t="n"/>
-      <c r="Q21" s="28" t="n"/>
-      <c r="R21" s="28" t="n"/>
-      <c r="S21" s="28" t="n"/>
-      <c r="T21" s="28" t="n"/>
+      <c r="E21" s="20" t="n"/>
+      <c r="F21" s="20" t="n"/>
+      <c r="G21" s="20" t="n"/>
+      <c r="H21" s="20" t="n"/>
+      <c r="I21" s="20" t="n"/>
+      <c r="J21" s="20" t="n"/>
+      <c r="K21" s="20" t="n"/>
+      <c r="L21" s="20" t="n"/>
+      <c r="M21" s="20" t="n"/>
+      <c r="N21" s="20" t="n"/>
+      <c r="O21" s="20" t="n"/>
+      <c r="P21" s="20" t="n"/>
+      <c r="Q21" s="20" t="n"/>
+      <c r="R21" s="20" t="n"/>
+      <c r="S21" s="20" t="n"/>
+      <c r="T21" s="20" t="n"/>
     </row>
     <row r="23" ht="21" customHeight="1">
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>C  ·  HOW YOUR PRODUCT WORKS</t>
         </is>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1">
-      <c r="B24" s="31" t="inlineStr">
+      <c r="B24" s="23" t="inlineStr">
         <is>
           <t>Section C</t>
         </is>
       </c>
-      <c r="C24" s="23" t="inlineStr">
+      <c r="C24" s="15" t="inlineStr">
         <is>
           <t>Sophistication</t>
         </is>
       </c>
-      <c r="D24" s="16" t="inlineStr">
+      <c r="D24" s="8" t="inlineStr">
         <is>
           <t>How much of the work it does  ·  0–4  ·  20 points</t>
         </is>
       </c>
-      <c r="E24" s="28" t="n"/>
-      <c r="F24" s="28" t="n"/>
-      <c r="G24" s="28" t="n"/>
-      <c r="H24" s="28" t="n"/>
-      <c r="I24" s="28" t="n"/>
-      <c r="J24" s="28" t="n"/>
-      <c r="K24" s="28" t="n"/>
-      <c r="L24" s="28" t="n"/>
-      <c r="M24" s="28" t="n"/>
-      <c r="N24" s="28" t="n"/>
-      <c r="O24" s="28" t="n"/>
-      <c r="P24" s="28" t="n"/>
-      <c r="Q24" s="28" t="n"/>
-      <c r="R24" s="28" t="n"/>
-      <c r="S24" s="28" t="n"/>
-      <c r="T24" s="28" t="n"/>
+      <c r="E24" s="20" t="n"/>
+      <c r="F24" s="20" t="n"/>
+      <c r="G24" s="20" t="n"/>
+      <c r="H24" s="20" t="n"/>
+      <c r="I24" s="20" t="n"/>
+      <c r="J24" s="20" t="n"/>
+      <c r="K24" s="20" t="n"/>
+      <c r="L24" s="20" t="n"/>
+      <c r="M24" s="20" t="n"/>
+      <c r="N24" s="20" t="n"/>
+      <c r="O24" s="20" t="n"/>
+      <c r="P24" s="20" t="n"/>
+      <c r="Q24" s="20" t="n"/>
+      <c r="R24" s="20" t="n"/>
+      <c r="S24" s="20" t="n"/>
+      <c r="T24" s="20" t="n"/>
     </row>
     <row r="25" ht="19" customHeight="1">
-      <c r="B25" s="25" t="inlineStr">
+      <c r="B25" s="17" t="inlineStr">
         <is>
           <t>C6</t>
         </is>
       </c>
-      <c r="C25" s="23" t="inlineStr">
+      <c r="C25" s="15" t="inlineStr">
         <is>
           <t>When your product is down</t>
         </is>
       </c>
-      <c r="D25" s="16" t="inlineStr">
+      <c r="D25" s="8" t="inlineStr">
         <is>
           <t>Flag  ·  stop-check if no uptime figure or commitment</t>
         </is>
       </c>
-      <c r="E25" s="26" t="n"/>
-      <c r="F25" s="26" t="n"/>
-      <c r="G25" s="26" t="n"/>
-      <c r="H25" s="26" t="n"/>
-      <c r="I25" s="26" t="n"/>
-      <c r="J25" s="26" t="n"/>
-      <c r="K25" s="26" t="n"/>
-      <c r="L25" s="26" t="n"/>
-      <c r="M25" s="26" t="n"/>
-      <c r="N25" s="26" t="n"/>
-      <c r="O25" s="26" t="n"/>
-      <c r="P25" s="26" t="n"/>
-      <c r="Q25" s="26" t="n"/>
-      <c r="R25" s="26" t="n"/>
-      <c r="S25" s="26" t="n"/>
-      <c r="T25" s="26" t="n"/>
+      <c r="E25" s="18" t="n"/>
+      <c r="F25" s="18" t="n"/>
+      <c r="G25" s="18" t="n"/>
+      <c r="H25" s="18" t="n"/>
+      <c r="I25" s="18" t="n"/>
+      <c r="J25" s="18" t="n"/>
+      <c r="K25" s="18" t="n"/>
+      <c r="L25" s="18" t="n"/>
+      <c r="M25" s="18" t="n"/>
+      <c r="N25" s="18" t="n"/>
+      <c r="O25" s="18" t="n"/>
+      <c r="P25" s="18" t="n"/>
+      <c r="Q25" s="18" t="n"/>
+      <c r="R25" s="18" t="n"/>
+      <c r="S25" s="18" t="n"/>
+      <c r="T25" s="18" t="n"/>
     </row>
     <row r="27" ht="21" customHeight="1">
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>D  ·  THE CLINICIAN'S PLACE IN THE MODEL</t>
         </is>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1">
-      <c r="B28" s="32" t="inlineStr">
+      <c r="B28" s="24" t="inlineStr">
         <is>
           <t>D1–D3</t>
         </is>
       </c>
-      <c r="C28" s="23" t="inlineStr">
+      <c r="C28" s="15" t="inlineStr">
         <is>
           <t>Clinician fit</t>
         </is>
       </c>
-      <c r="D28" s="16" t="inlineStr">
+      <c r="D28" s="8" t="inlineStr">
         <is>
           <t>Our read of fit  ·  0–4  ·  12 points</t>
         </is>
       </c>
-      <c r="E28" s="28" t="n"/>
-      <c r="F28" s="28" t="n"/>
-      <c r="G28" s="28" t="n"/>
-      <c r="H28" s="28" t="n"/>
-      <c r="I28" s="28" t="n"/>
-      <c r="J28" s="28" t="n"/>
-      <c r="K28" s="28" t="n"/>
-      <c r="L28" s="28" t="n"/>
-      <c r="M28" s="28" t="n"/>
-      <c r="N28" s="28" t="n"/>
-      <c r="O28" s="28" t="n"/>
-      <c r="P28" s="28" t="n"/>
-      <c r="Q28" s="28" t="n"/>
-      <c r="R28" s="28" t="n"/>
-      <c r="S28" s="28" t="n"/>
-      <c r="T28" s="28" t="n"/>
+      <c r="E28" s="20" t="n"/>
+      <c r="F28" s="20" t="n"/>
+      <c r="G28" s="20" t="n"/>
+      <c r="H28" s="20" t="n"/>
+      <c r="I28" s="20" t="n"/>
+      <c r="J28" s="20" t="n"/>
+      <c r="K28" s="20" t="n"/>
+      <c r="L28" s="20" t="n"/>
+      <c r="M28" s="20" t="n"/>
+      <c r="N28" s="20" t="n"/>
+      <c r="O28" s="20" t="n"/>
+      <c r="P28" s="20" t="n"/>
+      <c r="Q28" s="20" t="n"/>
+      <c r="R28" s="20" t="n"/>
+      <c r="S28" s="20" t="n"/>
+      <c r="T28" s="20" t="n"/>
     </row>
     <row r="30" ht="21" customHeight="1">
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>E  ·  FIT AND PARTNERSHIP</t>
         </is>
       </c>
     </row>
     <row r="31" ht="24" customHeight="1">
-      <c r="B31" s="32" t="inlineStr">
+      <c r="B31" s="24" t="inlineStr">
         <is>
           <t>E1–E4</t>
         </is>
       </c>
-      <c r="C31" s="23" t="inlineStr">
+      <c r="C31" s="15" t="inlineStr">
         <is>
           <t>Partnership</t>
         </is>
       </c>
-      <c r="D31" s="16" t="inlineStr">
+      <c r="D31" s="8" t="inlineStr">
         <is>
           <t>Willing to build it with us, and open to a stake  ·  0–4  ·  12 points</t>
         </is>
       </c>
-      <c r="E31" s="28" t="n"/>
-      <c r="F31" s="28" t="n"/>
-      <c r="G31" s="28" t="n"/>
-      <c r="H31" s="28" t="n"/>
-      <c r="I31" s="28" t="n"/>
-      <c r="J31" s="28" t="n"/>
-      <c r="K31" s="28" t="n"/>
-      <c r="L31" s="28" t="n"/>
-      <c r="M31" s="28" t="n"/>
-      <c r="N31" s="28" t="n"/>
-      <c r="O31" s="28" t="n"/>
-      <c r="P31" s="28" t="n"/>
-      <c r="Q31" s="28" t="n"/>
-      <c r="R31" s="28" t="n"/>
-      <c r="S31" s="28" t="n"/>
-      <c r="T31" s="28" t="n"/>
+      <c r="E31" s="20" t="n"/>
+      <c r="F31" s="20" t="n"/>
+      <c r="G31" s="20" t="n"/>
+      <c r="H31" s="20" t="n"/>
+      <c r="I31" s="20" t="n"/>
+      <c r="J31" s="20" t="n"/>
+      <c r="K31" s="20" t="n"/>
+      <c r="L31" s="20" t="n"/>
+      <c r="M31" s="20" t="n"/>
+      <c r="N31" s="20" t="n"/>
+      <c r="O31" s="20" t="n"/>
+      <c r="P31" s="20" t="n"/>
+      <c r="Q31" s="20" t="n"/>
+      <c r="R31" s="20" t="n"/>
+      <c r="S31" s="20" t="n"/>
+      <c r="T31" s="20" t="n"/>
     </row>
     <row r="33" ht="21" customHeight="1">
-      <c r="B33" s="33" t="inlineStr">
+      <c r="B33" s="25" t="inlineStr">
         <is>
           <t>NOTES   —   one line each.  This is what we go and ask.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="62" customHeight="1">
-      <c r="B34" s="34" t="inlineStr"/>
-      <c r="C34" s="35" t="inlineStr">
+      <c r="B34" s="26" t="inlineStr"/>
+      <c r="C34" s="27" t="inlineStr">
         <is>
           <t>What stands out</t>
         </is>
       </c>
-      <c r="D34" s="36" t="inlineStr">
+      <c r="D34" s="28" t="inlineStr">
         <is>
           <t>against the field, or against our own thinking</t>
         </is>
       </c>
-      <c r="E34" s="37" t="n"/>
-      <c r="F34" s="37" t="n"/>
-      <c r="G34" s="37" t="n"/>
-      <c r="H34" s="37" t="n"/>
-      <c r="I34" s="37" t="n"/>
-      <c r="J34" s="37" t="n"/>
-      <c r="K34" s="37" t="n"/>
-      <c r="L34" s="37" t="n"/>
-      <c r="M34" s="37" t="n"/>
-      <c r="N34" s="37" t="n"/>
-      <c r="O34" s="37" t="n"/>
-      <c r="P34" s="37" t="n"/>
-      <c r="Q34" s="37" t="n"/>
-      <c r="R34" s="37" t="n"/>
-      <c r="S34" s="37" t="n"/>
-      <c r="T34" s="37" t="n"/>
+      <c r="E34" s="29" t="n"/>
+      <c r="F34" s="29" t="n"/>
+      <c r="G34" s="29" t="n"/>
+      <c r="H34" s="29" t="n"/>
+      <c r="I34" s="29" t="n"/>
+      <c r="J34" s="29" t="n"/>
+      <c r="K34" s="29" t="n"/>
+      <c r="L34" s="29" t="n"/>
+      <c r="M34" s="29" t="n"/>
+      <c r="N34" s="29" t="n"/>
+      <c r="O34" s="29" t="n"/>
+      <c r="P34" s="29" t="n"/>
+      <c r="Q34" s="29" t="n"/>
+      <c r="R34" s="29" t="n"/>
+      <c r="S34" s="29" t="n"/>
+      <c r="T34" s="29" t="n"/>
     </row>
     <row r="35" ht="62" customHeight="1">
-      <c r="B35" s="34" t="inlineStr"/>
-      <c r="C35" s="35" t="inlineStr">
+      <c r="B35" s="26" t="inlineStr"/>
+      <c r="C35" s="27" t="inlineStr">
         <is>
           <t>What worries me</t>
         </is>
       </c>
-      <c r="D35" s="36" t="inlineStr">
+      <c r="D35" s="28" t="inlineStr">
         <is>
           <t>including anything flagged above</t>
         </is>
       </c>
-      <c r="E35" s="37" t="n"/>
-      <c r="F35" s="37" t="n"/>
-      <c r="G35" s="37" t="n"/>
-      <c r="H35" s="37" t="n"/>
-      <c r="I35" s="37" t="n"/>
-      <c r="J35" s="37" t="n"/>
-      <c r="K35" s="37" t="n"/>
-      <c r="L35" s="37" t="n"/>
-      <c r="M35" s="37" t="n"/>
-      <c r="N35" s="37" t="n"/>
-      <c r="O35" s="37" t="n"/>
-      <c r="P35" s="37" t="n"/>
-      <c r="Q35" s="37" t="n"/>
-      <c r="R35" s="37" t="n"/>
-      <c r="S35" s="37" t="n"/>
-      <c r="T35" s="37" t="n"/>
+      <c r="E35" s="29" t="n"/>
+      <c r="F35" s="29" t="n"/>
+      <c r="G35" s="29" t="n"/>
+      <c r="H35" s="29" t="n"/>
+      <c r="I35" s="29" t="n"/>
+      <c r="J35" s="29" t="n"/>
+      <c r="K35" s="29" t="n"/>
+      <c r="L35" s="29" t="n"/>
+      <c r="M35" s="29" t="n"/>
+      <c r="N35" s="29" t="n"/>
+      <c r="O35" s="29" t="n"/>
+      <c r="P35" s="29" t="n"/>
+      <c r="Q35" s="29" t="n"/>
+      <c r="R35" s="29" t="n"/>
+      <c r="S35" s="29" t="n"/>
+      <c r="T35" s="29" t="n"/>
     </row>
     <row r="36" ht="62" customHeight="1">
-      <c r="B36" s="34" t="inlineStr"/>
-      <c r="C36" s="35" t="inlineStr">
+      <c r="B36" s="26" t="inlineStr"/>
+      <c r="C36" s="27" t="inlineStr">
         <is>
           <t>What to go and ask</t>
         </is>
       </c>
-      <c r="D36" s="36" t="inlineStr">
+      <c r="D36" s="28" t="inlineStr">
         <is>
           <t>the demo agenda</t>
         </is>
       </c>
-      <c r="E36" s="37" t="n"/>
-      <c r="F36" s="37" t="n"/>
-      <c r="G36" s="37" t="n"/>
-      <c r="H36" s="37" t="n"/>
-      <c r="I36" s="37" t="n"/>
-      <c r="J36" s="37" t="n"/>
-      <c r="K36" s="37" t="n"/>
-      <c r="L36" s="37" t="n"/>
-      <c r="M36" s="37" t="n"/>
-      <c r="N36" s="37" t="n"/>
-      <c r="O36" s="37" t="n"/>
-      <c r="P36" s="37" t="n"/>
-      <c r="Q36" s="37" t="n"/>
-      <c r="R36" s="37" t="n"/>
-      <c r="S36" s="37" t="n"/>
-      <c r="T36" s="37" t="n"/>
+      <c r="E36" s="29" t="n"/>
+      <c r="F36" s="29" t="n"/>
+      <c r="G36" s="29" t="n"/>
+      <c r="H36" s="29" t="n"/>
+      <c r="I36" s="29" t="n"/>
+      <c r="J36" s="29" t="n"/>
+      <c r="K36" s="29" t="n"/>
+      <c r="L36" s="29" t="n"/>
+      <c r="M36" s="29" t="n"/>
+      <c r="N36" s="29" t="n"/>
+      <c r="O36" s="29" t="n"/>
+      <c r="P36" s="29" t="n"/>
+      <c r="Q36" s="29" t="n"/>
+      <c r="R36" s="29" t="n"/>
+      <c r="S36" s="29" t="n"/>
+      <c r="T36" s="29" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -2507,6 +2759,847 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00C6A01F"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:D82"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="100" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>COMPASSUS  ·  HOME HEALTH</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="B3" s="30" t="inlineStr">
+        <is>
+          <t>Vendor Scorecard — Fast</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="31" t="inlineStr">
+        <is>
+          <t>The questionnaire is the rubric. Read the return top to bottom and fill the sheet top to bottom. Seven marks a vendor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="10" customHeight="1"/>
+    <row r="7" ht="22" customHeight="1">
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>HOW IT WORKS</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="B8" s="32" t="inlineStr">
+        <is>
+          <t>Every one of the 17 questions on the questionnaire has a row on the Scorecard tab, in the order it appears on the form. Seven rows take a mark. The rest raise a flag or a note — and they say so, so nothing looks forgotten. What isn't scored becomes what we go and ask at the demo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="B9" s="32" t="inlineStr">
+        <is>
+          <t>Scored on the same 100 points and the same bands as the full scorecard, so the two are directly comparable. This one is coarser, not different: it gives one mark where the full sheet gives several, so the two can disagree on a close call. That is the trade for speed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="10" customHeight="1"/>
+    <row r="11" ht="22" customHeight="1">
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>THE SEVEN MARKS</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="33" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="C12" s="33" t="inlineStr">
+        <is>
+          <t>Mark</t>
+        </is>
+      </c>
+      <c r="D12" s="33" t="inlineStr">
+        <is>
+          <t>Points</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="21" customHeight="1">
+      <c r="B13" s="34" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C13" s="32" t="inlineStr">
+        <is>
+          <t>Home Care Home Base integration</t>
+        </is>
+      </c>
+      <c r="D13" s="35" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="21" customHeight="1">
+      <c r="B14" s="34" t="inlineStr">
+        <is>
+          <t>Section B</t>
+        </is>
+      </c>
+      <c r="C14" s="32" t="inlineStr">
+        <is>
+          <t>Capacity — how much of it they cover</t>
+        </is>
+      </c>
+      <c r="D14" s="35" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="21" customHeight="1">
+      <c r="B15" s="34" t="inlineStr">
+        <is>
+          <t>Section B</t>
+        </is>
+      </c>
+      <c r="C15" s="32" t="inlineStr">
+        <is>
+          <t>Scheduling — how much of it they cover</t>
+        </is>
+      </c>
+      <c r="D15" s="35" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="21" customHeight="1">
+      <c r="B16" s="34" t="inlineStr">
+        <is>
+          <t>Section B</t>
+        </is>
+      </c>
+      <c r="C16" s="32" t="inlineStr">
+        <is>
+          <t>Engagement — how much of it they cover</t>
+        </is>
+      </c>
+      <c r="D16" s="35" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="21" customHeight="1">
+      <c r="B17" s="34" t="inlineStr">
+        <is>
+          <t>Section C</t>
+        </is>
+      </c>
+      <c r="C17" s="32" t="inlineStr">
+        <is>
+          <t>Sophistication — how much of the work the product does</t>
+        </is>
+      </c>
+      <c r="D17" s="35" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="21" customHeight="1">
+      <c r="B18" s="34" t="inlineStr">
+        <is>
+          <t>D1–D3</t>
+        </is>
+      </c>
+      <c r="C18" s="32" t="inlineStr">
+        <is>
+          <t>Clinician fit</t>
+        </is>
+      </c>
+      <c r="D18" s="35" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="21" customHeight="1">
+      <c r="B19" s="34" t="inlineStr">
+        <is>
+          <t>E1–E4</t>
+        </is>
+      </c>
+      <c r="C19" s="32" t="inlineStr">
+        <is>
+          <t>Partnership</t>
+        </is>
+      </c>
+      <c r="D19" s="35" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="21" customHeight="1">
+      <c r="B20" s="34" t="inlineStr"/>
+      <c r="C20" s="36" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="D20" s="35" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="10" customHeight="1"/>
+    <row r="22" ht="22" customHeight="1">
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>A1  ·  HOME CARE HOME BASE   —   pick one line</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="B23" s="32" t="inlineStr">
+        <is>
+          <t>Three of the six rungs are live integrations, because live through a partner is still live. Anything not yet live shows as Conditional on the score, whatever the total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="21" customHeight="1">
+      <c r="B24" s="34" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C24" s="32" t="inlineStr">
+        <is>
+          <t>Live — established customer base</t>
+        </is>
+      </c>
+      <c r="D24" s="35" t="inlineStr"/>
+    </row>
+    <row r="25" ht="21" customHeight="1">
+      <c r="B25" s="34" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C25" s="32" t="inlineStr">
+        <is>
+          <t>Live — small customer base</t>
+        </is>
+      </c>
+      <c r="D25" s="35" t="inlineStr"/>
+    </row>
+    <row r="26" ht="21" customHeight="1">
+      <c r="B26" s="34" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C26" s="32" t="inlineStr">
+        <is>
+          <t>Live — through a partner</t>
+        </is>
+      </c>
+      <c r="D26" s="35" t="inlineStr"/>
+    </row>
+    <row r="27" ht="21" customHeight="1">
+      <c r="B27" s="34" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C27" s="32" t="inlineStr">
+        <is>
+          <t>In development — with a date</t>
+        </is>
+      </c>
+      <c r="D27" s="35" t="inlineStr"/>
+    </row>
+    <row r="28" ht="21" customHeight="1">
+      <c r="B28" s="34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C28" s="32" t="inlineStr">
+        <is>
+          <t>On the roadmap — no date</t>
+        </is>
+      </c>
+      <c r="D28" s="35" t="inlineStr"/>
+    </row>
+    <row r="29" ht="21" customHeight="1">
+      <c r="B29" s="34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C29" s="32" t="inlineStr">
+        <is>
+          <t>None, and no path to one</t>
+        </is>
+      </c>
+      <c r="D29" s="35" t="inlineStr"/>
+    </row>
+    <row r="30" ht="10" customHeight="1"/>
+    <row r="31" ht="22" customHeight="1">
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>SECTION B  ·  SCOPE   —   one mark per arena, 0 to 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="28" customHeight="1">
+      <c r="B32" s="32" t="inlineStr">
+        <is>
+          <t>Read the eleven areas each vendor rated themselves on, then give one mark per arena. The areas in each arena are printed on the row, so the checklist is in front of you. Where Section C contradicts Section B, believe Section C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="41" customHeight="1">
+      <c r="B33" s="32" t="inlineStr">
+        <is>
+          <t>The mark is your read of how much of that arena — as our one-pager describes it — the product reaches. It is not a count of areas: Capacity has 3 and the others 4, so counting would never divide cleanly, and an area covered thinly is not the same as one covered properly. Weigh breadth and depth together.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="21" customHeight="1">
+      <c r="B34" s="34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C34" s="32" t="inlineStr">
+        <is>
+          <t>Most of it</t>
+        </is>
+      </c>
+      <c r="D34" s="35" t="inlineStr"/>
+    </row>
+    <row r="35" ht="21" customHeight="1">
+      <c r="B35" s="34" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C35" s="32" t="inlineStr">
+        <is>
+          <t>More than half</t>
+        </is>
+      </c>
+      <c r="D35" s="35" t="inlineStr"/>
+    </row>
+    <row r="36" ht="21" customHeight="1">
+      <c r="B36" s="34" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C36" s="32" t="inlineStr">
+        <is>
+          <t>About half</t>
+        </is>
+      </c>
+      <c r="D36" s="35" t="inlineStr"/>
+    </row>
+    <row r="37" ht="21" customHeight="1">
+      <c r="B37" s="34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C37" s="32" t="inlineStr">
+        <is>
+          <t>Less than half</t>
+        </is>
+      </c>
+      <c r="D37" s="35" t="inlineStr"/>
+    </row>
+    <row r="38" ht="21" customHeight="1">
+      <c r="B38" s="34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C38" s="32" t="inlineStr">
+        <is>
+          <t>A corner of it</t>
+        </is>
+      </c>
+      <c r="D38" s="35" t="inlineStr"/>
+    </row>
+    <row r="39" ht="21" customHeight="1">
+      <c r="B39" s="34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C39" s="32" t="inlineStr">
+        <is>
+          <t>Nothing here</t>
+        </is>
+      </c>
+      <c r="D39" s="35" t="inlineStr"/>
+    </row>
+    <row r="40" ht="28" customHeight="1">
+      <c r="B40" s="32" t="inlineStr">
+        <is>
+          <t>Most of it is the ceiling on purpose. The scope on our one-pager is original and these are point solutions, so nobody will cover all of it — a rung for that would sit unused and squeeze everyone else into the bottom half of the scale. All six rungs here are live.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="10" customHeight="1"/>
+    <row r="42" ht="22" customHeight="1">
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>SECTION C  ·  SOPHISTICATION   —   one mark, 0 to 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="41" customHeight="1">
+      <c r="B43" s="32" t="inlineStr">
+        <is>
+          <t>How much of the work the product does. This is the Read / Assist / Control language already in our workbook. Score what the product does, not how much the vendor wrote about it — a short answer describing an optimiser still scores 4. How it does it is a demo question, not a reason to mark it down.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="21" customHeight="1">
+      <c r="B44" s="34" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C44" s="32" t="inlineStr">
+        <is>
+          <t>Runs it — decides across the whole picture, and re-decides when things change</t>
+        </is>
+      </c>
+      <c r="D44" s="35" t="inlineStr"/>
+    </row>
+    <row r="45" ht="21" customHeight="1">
+      <c r="B45" s="34" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C45" s="32" t="inlineStr">
+        <is>
+          <t>Recommends it — works out the answer and proposes it; a person confirms</t>
+        </is>
+      </c>
+      <c r="D45" s="35" t="inlineStr"/>
+    </row>
+    <row r="46" ht="21" customHeight="1">
+      <c r="B46" s="34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C46" s="32" t="inlineStr">
+        <is>
+          <t>Checks it — applies rules and flags problems; a person still works it</t>
+        </is>
+      </c>
+      <c r="D46" s="35" t="inlineStr"/>
+    </row>
+    <row r="47" ht="21" customHeight="1">
+      <c r="B47" s="34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C47" s="32" t="inlineStr">
+        <is>
+          <t>Shows it — surfaces the information; a person does all the work</t>
+        </is>
+      </c>
+      <c r="D47" s="35" t="inlineStr"/>
+    </row>
+    <row r="48" ht="21" customHeight="1">
+      <c r="B48" s="34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C48" s="32" t="inlineStr">
+        <is>
+          <t>Not addressed</t>
+        </is>
+      </c>
+      <c r="D48" s="35" t="inlineStr"/>
+    </row>
+    <row r="49" ht="15" customHeight="1">
+      <c r="B49" s="32" t="inlineStr">
+        <is>
+          <t>A 4 is not automatically what we want. Where we said Assist, a product that decides on its own is a risk worth a note.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="10" customHeight="1"/>
+    <row r="51" ht="22" customHeight="1">
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>SECTION D  ·  CLINICIAN FIT   —   one mark, 0 to 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="21" customHeight="1">
+      <c r="B52" s="34" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C52" s="32" t="inlineStr">
+        <is>
+          <t>Strong fit</t>
+        </is>
+      </c>
+      <c r="D52" s="35" t="inlineStr"/>
+    </row>
+    <row r="53" ht="21" customHeight="1">
+      <c r="B53" s="34" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C53" s="32" t="inlineStr">
+        <is>
+          <t>Good fit</t>
+        </is>
+      </c>
+      <c r="D53" s="35" t="inlineStr"/>
+    </row>
+    <row r="54" ht="21" customHeight="1">
+      <c r="B54" s="34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C54" s="32" t="inlineStr">
+        <is>
+          <t>Workable</t>
+        </is>
+      </c>
+      <c r="D54" s="35" t="inlineStr"/>
+    </row>
+    <row r="55" ht="21" customHeight="1">
+      <c r="B55" s="34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C55" s="32" t="inlineStr">
+        <is>
+          <t>Poor fit</t>
+        </is>
+      </c>
+      <c r="D55" s="35" t="inlineStr"/>
+    </row>
+    <row r="56" ht="21" customHeight="1">
+      <c r="B56" s="34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C56" s="32" t="inlineStr">
+        <is>
+          <t>Not answered</t>
+        </is>
+      </c>
+      <c r="D56" s="35" t="inlineStr"/>
+    </row>
+    <row r="57" ht="28" customHeight="1">
+      <c r="B57" s="32" t="inlineStr">
+        <is>
+          <t>No descriptions here on purpose. Read D1 to D3 and give it your own read. We know how our clinicians work and what they will accept; a rubric that spelled out what earns a 4 would only substitute a guess for that.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="15" customHeight="1">
+      <c r="B58" s="32" t="inlineStr">
+        <is>
+          <t>Say why in the Notes, though — that one line is what a colleague reads when they score the same vendor differently.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="10" customHeight="1"/>
+    <row r="60" ht="22" customHeight="1">
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>SECTION E  ·  PARTNERSHIP   —   one mark, 0 to 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="28" customHeight="1">
+      <c r="B61" s="32" t="inlineStr">
+        <is>
+          <t>What we are looking for is a company with the willingness and the environment to build this with us around our needs — and open to us holding equity, so that a product for the general market becomes a real possibility. The rungs run from vendor to co-owner.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="21" customHeight="1">
+      <c r="B62" s="34" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C62" s="32" t="inlineStr">
+        <is>
+          <t>Open to equity or a stake in what we build, and set up to build it with us</t>
+        </is>
+      </c>
+      <c r="D62" s="35" t="inlineStr"/>
+    </row>
+    <row r="63" ht="21" customHeight="1">
+      <c r="B63" s="34" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C63" s="32" t="inlineStr">
+        <is>
+          <t>Ready to build to our needs as a design partner; ownership not addressed</t>
+        </is>
+      </c>
+      <c r="D63" s="35" t="inlineStr"/>
+    </row>
+    <row r="64" ht="21" customHeight="1">
+      <c r="B64" s="34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C64" s="32" t="inlineStr">
+        <is>
+          <t>Will take our input, but they own the roadmap and the product</t>
+        </is>
+      </c>
+      <c r="D64" s="35" t="inlineStr"/>
+    </row>
+    <row r="65" ht="21" customHeight="1">
+      <c r="B65" s="34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C65" s="32" t="inlineStr">
+        <is>
+          <t>A standard customer relationship — we buy what already exists</t>
+        </is>
+      </c>
+      <c r="D65" s="35" t="inlineStr"/>
+    </row>
+    <row r="66" ht="21" customHeight="1">
+      <c r="B66" s="34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C66" s="32" t="inlineStr">
+        <is>
+          <t>Not answered</t>
+        </is>
+      </c>
+      <c r="D66" s="35" t="inlineStr"/>
+    </row>
+    <row r="67" ht="28" customHeight="1">
+      <c r="B67" s="32" t="inlineStr">
+        <is>
+          <t>Read all four E answers, not only E2. A vendor who never mentions ownership but describes a real co-development practice is a 3, and worth the conversation. A discount is a discount.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="10" customHeight="1"/>
+    <row r="69" ht="22" customHeight="1">
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>THE THREE QUESTIONS THAT RAISE A FLAG INSTEAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="28" customHeight="1">
+      <c r="B70" s="32" t="inlineStr">
+        <is>
+          <t>A vendor with no continuity commitment should be stopped and asked, not quietly docked a few points. Same for a vendor with one customer, or impact numbers with no baseline. Mark these OK, Watch or STOP-CHECK.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="21" customHeight="1">
+      <c r="B71" s="34" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C71" s="32" t="inlineStr">
+        <is>
+          <t>Customers, scale and references — STOP-CHECK if one customer, or no references offered</t>
+        </is>
+      </c>
+      <c r="D71" s="35" t="inlineStr"/>
+    </row>
+    <row r="72" ht="21" customHeight="1">
+      <c r="B72" s="34" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C72" s="32" t="inlineStr">
+        <is>
+          <t>Measured impact — Watch if claimed with no baseline or period</t>
+        </is>
+      </c>
+      <c r="D72" s="35" t="inlineStr"/>
+    </row>
+    <row r="73" ht="21" customHeight="1">
+      <c r="B73" s="34" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="C73" s="32" t="inlineStr">
+        <is>
+          <t>When your product is down — STOP-CHECK if no uptime figure or contractual commitment</t>
+        </is>
+      </c>
+      <c r="D73" s="35" t="inlineStr"/>
+    </row>
+    <row r="74" ht="10" customHeight="1"/>
+    <row r="75" ht="22" customHeight="1">
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>BANDS   —   the same as the full scorecard</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="21" customHeight="1">
+      <c r="B76" s="34" t="inlineStr">
+        <is>
+          <t>80–100</t>
+        </is>
+      </c>
+      <c r="C76" s="32" t="inlineStr">
+        <is>
+          <t>Advance — demo, references, deeper diligence</t>
+        </is>
+      </c>
+      <c r="D76" s="35" t="inlineStr"/>
+    </row>
+    <row r="77" ht="21" customHeight="1">
+      <c r="B77" s="34" t="inlineStr">
+        <is>
+          <t>65–79</t>
+        </is>
+      </c>
+      <c r="C77" s="32" t="inlineStr">
+        <is>
+          <t>Consider — only if something specific justifies it</t>
+        </is>
+      </c>
+      <c r="D77" s="35" t="inlineStr"/>
+    </row>
+    <row r="78" ht="21" customHeight="1">
+      <c r="B78" s="34" t="inlineStr">
+        <is>
+          <t>50–64</t>
+        </is>
+      </c>
+      <c r="C78" s="32" t="inlineStr">
+        <is>
+          <t>Hold — park unless the field thins</t>
+        </is>
+      </c>
+      <c r="D78" s="35" t="inlineStr"/>
+    </row>
+    <row r="79" ht="21" customHeight="1">
+      <c r="B79" s="34" t="inlineStr">
+        <is>
+          <t>&lt; 50</t>
+        </is>
+      </c>
+      <c r="C79" s="32" t="inlineStr">
+        <is>
+          <t>Decline — close out with thanks</t>
+        </is>
+      </c>
+      <c r="D79" s="35" t="inlineStr"/>
+    </row>
+    <row r="80" ht="34" customHeight="1">
+      <c r="B80" s="34" t="inlineStr">
+        <is>
+          <t>Conditional</t>
+        </is>
+      </c>
+      <c r="C80" s="32" t="inlineStr">
+        <is>
+          <t>Shown whenever the integration is not yet live. Advancing means accepting an integration still to be built, on their timeline, at our risk.</t>
+        </is>
+      </c>
+      <c r="D80" s="35" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="B82" s="37" t="inlineStr">
+        <is>
+          <t>Fast scorecard v2.0  ·  questionnaire form_version 2026-08-19</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="23">
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B67:D67"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B61:D61"/>
+    <mergeCell ref="B57:D57"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B69:D69"/>
+    <mergeCell ref="B49:D49"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B51:D51"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B75:D75"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B43:D43"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>

--- a/agents/compassus-capacity-pm/vendor-evaluation/Vendor-Scorecard-SIMPLE.xlsx
+++ b/agents/compassus-capacity-pm/vendor-evaluation/Vendor-Scorecard-SIMPLE.xlsx
@@ -12,7 +12,13 @@
     <sheet name="Start Here" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Lists" sheetId="4" state="hidden" r:id="rId4"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="HCHB_List">Lists!$B$2:$B$7</definedName>
+    <definedName name="Scope_List">Lists!$E$2:$E$7</definedName>
+    <definedName name="Soph_List">Lists!$G$2:$G$6</definedName>
+    <definedName name="Clin_List">Lists!$I$2:$I$6</definedName>
+    <definedName name="Part_List">Lists!$K$2:$K$6</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -22,7 +28,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -116,6 +122,11 @@
       <name val="Aptos Narrow"/>
       <color rgb="001B211E"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <color rgb="005A6560"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Aptos Narrow"/>
@@ -242,7 +253,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -251,6 +262,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom" wrapText="1"/>
@@ -264,13 +278,13 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="21" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -291,22 +305,25 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -735,14 +752,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:T36"/>
+  <dimension ref="B2:U36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
@@ -758,6 +775,7 @@
     <col width="13" customWidth="1" min="18" max="18"/>
     <col width="13" customWidth="1" min="19" max="19"/>
     <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -789,947 +807,1003 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
           <t>Arbor Health Logistics</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>Wayfinder Scheduling</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>Northlight Health</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="I6" s="6" t="inlineStr">
         <is>
           <t>Vendor 04</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="J6" s="6" t="inlineStr">
         <is>
           <t>Vendor 05</t>
         </is>
       </c>
-      <c r="J6" s="5" t="inlineStr">
+      <c r="K6" s="6" t="inlineStr">
         <is>
           <t>Vendor 06</t>
         </is>
       </c>
-      <c r="K6" s="5" t="inlineStr">
+      <c r="L6" s="6" t="inlineStr">
         <is>
           <t>Vendor 07</t>
         </is>
       </c>
-      <c r="L6" s="5" t="inlineStr">
+      <c r="M6" s="6" t="inlineStr">
         <is>
           <t>Vendor 08</t>
         </is>
       </c>
-      <c r="M6" s="5" t="inlineStr">
+      <c r="N6" s="6" t="inlineStr">
         <is>
           <t>Vendor 09</t>
         </is>
       </c>
-      <c r="N6" s="5" t="inlineStr">
+      <c r="O6" s="6" t="inlineStr">
         <is>
           <t>Vendor 10</t>
         </is>
       </c>
-      <c r="O6" s="5" t="inlineStr">
+      <c r="P6" s="6" t="inlineStr">
         <is>
           <t>Vendor 11</t>
         </is>
       </c>
-      <c r="P6" s="5" t="inlineStr">
+      <c r="Q6" s="6" t="inlineStr">
         <is>
           <t>Vendor 12</t>
         </is>
       </c>
-      <c r="Q6" s="5" t="inlineStr">
+      <c r="R6" s="6" t="inlineStr">
         <is>
           <t>Vendor 13</t>
         </is>
       </c>
-      <c r="R6" s="5" t="inlineStr">
+      <c r="S6" s="6" t="inlineStr">
         <is>
           <t>Vendor 14</t>
         </is>
       </c>
-      <c r="S6" s="5" t="inlineStr">
+      <c r="T6" s="6" t="inlineStr">
         <is>
           <t>Vendor 15</t>
         </is>
       </c>
-      <c r="T6" s="5" t="inlineStr">
+      <c r="U6" s="6" t="inlineStr">
         <is>
           <t>Vendor 16</t>
         </is>
       </c>
     </row>
     <row r="8" ht="21" customHeight="1">
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>SCORE</t>
         </is>
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>of 100</t>
         </is>
       </c>
-      <c r="E9" s="9">
-        <f>IF(E14="","",IFERROR(VLOOKUP(E14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(E19,1)),0)/5*12+IFERROR(VALUE(LEFT(E20,1)),0)/5*12+IFERROR(VALUE(LEFT(E21,1)),0)/5*12+IFERROR(VALUE(LEFT(E24,1)),0)/4*20+IFERROR(VALUE(LEFT(E28,1)),0)/4*12+IFERROR(VALUE(LEFT(E31,1)),0)/4*12)</f>
-        <v/>
-      </c>
-      <c r="F9" s="9">
+      <c r="F9" s="10">
         <f>IF(F14="","",IFERROR(VLOOKUP(F14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(F19,1)),0)/5*12+IFERROR(VALUE(LEFT(F20,1)),0)/5*12+IFERROR(VALUE(LEFT(F21,1)),0)/5*12+IFERROR(VALUE(LEFT(F24,1)),0)/4*20+IFERROR(VALUE(LEFT(F28,1)),0)/4*12+IFERROR(VALUE(LEFT(F31,1)),0)/4*12)</f>
         <v/>
       </c>
-      <c r="G9" s="9">
+      <c r="G9" s="10">
         <f>IF(G14="","",IFERROR(VLOOKUP(G14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(G19,1)),0)/5*12+IFERROR(VALUE(LEFT(G20,1)),0)/5*12+IFERROR(VALUE(LEFT(G21,1)),0)/5*12+IFERROR(VALUE(LEFT(G24,1)),0)/4*20+IFERROR(VALUE(LEFT(G28,1)),0)/4*12+IFERROR(VALUE(LEFT(G31,1)),0)/4*12)</f>
         <v/>
       </c>
-      <c r="H9" s="9">
+      <c r="H9" s="10">
         <f>IF(H14="","",IFERROR(VLOOKUP(H14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(H19,1)),0)/5*12+IFERROR(VALUE(LEFT(H20,1)),0)/5*12+IFERROR(VALUE(LEFT(H21,1)),0)/5*12+IFERROR(VALUE(LEFT(H24,1)),0)/4*20+IFERROR(VALUE(LEFT(H28,1)),0)/4*12+IFERROR(VALUE(LEFT(H31,1)),0)/4*12)</f>
         <v/>
       </c>
-      <c r="I9" s="9">
+      <c r="I9" s="10">
         <f>IF(I14="","",IFERROR(VLOOKUP(I14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(I19,1)),0)/5*12+IFERROR(VALUE(LEFT(I20,1)),0)/5*12+IFERROR(VALUE(LEFT(I21,1)),0)/5*12+IFERROR(VALUE(LEFT(I24,1)),0)/4*20+IFERROR(VALUE(LEFT(I28,1)),0)/4*12+IFERROR(VALUE(LEFT(I31,1)),0)/4*12)</f>
         <v/>
       </c>
-      <c r="J9" s="9">
+      <c r="J9" s="10">
         <f>IF(J14="","",IFERROR(VLOOKUP(J14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(J19,1)),0)/5*12+IFERROR(VALUE(LEFT(J20,1)),0)/5*12+IFERROR(VALUE(LEFT(J21,1)),0)/5*12+IFERROR(VALUE(LEFT(J24,1)),0)/4*20+IFERROR(VALUE(LEFT(J28,1)),0)/4*12+IFERROR(VALUE(LEFT(J31,1)),0)/4*12)</f>
         <v/>
       </c>
-      <c r="K9" s="9">
+      <c r="K9" s="10">
         <f>IF(K14="","",IFERROR(VLOOKUP(K14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(K19,1)),0)/5*12+IFERROR(VALUE(LEFT(K20,1)),0)/5*12+IFERROR(VALUE(LEFT(K21,1)),0)/5*12+IFERROR(VALUE(LEFT(K24,1)),0)/4*20+IFERROR(VALUE(LEFT(K28,1)),0)/4*12+IFERROR(VALUE(LEFT(K31,1)),0)/4*12)</f>
         <v/>
       </c>
-      <c r="L9" s="9">
+      <c r="L9" s="10">
         <f>IF(L14="","",IFERROR(VLOOKUP(L14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(L19,1)),0)/5*12+IFERROR(VALUE(LEFT(L20,1)),0)/5*12+IFERROR(VALUE(LEFT(L21,1)),0)/5*12+IFERROR(VALUE(LEFT(L24,1)),0)/4*20+IFERROR(VALUE(LEFT(L28,1)),0)/4*12+IFERROR(VALUE(LEFT(L31,1)),0)/4*12)</f>
         <v/>
       </c>
-      <c r="M9" s="9">
+      <c r="M9" s="10">
         <f>IF(M14="","",IFERROR(VLOOKUP(M14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(M19,1)),0)/5*12+IFERROR(VALUE(LEFT(M20,1)),0)/5*12+IFERROR(VALUE(LEFT(M21,1)),0)/5*12+IFERROR(VALUE(LEFT(M24,1)),0)/4*20+IFERROR(VALUE(LEFT(M28,1)),0)/4*12+IFERROR(VALUE(LEFT(M31,1)),0)/4*12)</f>
         <v/>
       </c>
-      <c r="N9" s="9">
+      <c r="N9" s="10">
         <f>IF(N14="","",IFERROR(VLOOKUP(N14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(N19,1)),0)/5*12+IFERROR(VALUE(LEFT(N20,1)),0)/5*12+IFERROR(VALUE(LEFT(N21,1)),0)/5*12+IFERROR(VALUE(LEFT(N24,1)),0)/4*20+IFERROR(VALUE(LEFT(N28,1)),0)/4*12+IFERROR(VALUE(LEFT(N31,1)),0)/4*12)</f>
         <v/>
       </c>
-      <c r="O9" s="9">
+      <c r="O9" s="10">
         <f>IF(O14="","",IFERROR(VLOOKUP(O14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(O19,1)),0)/5*12+IFERROR(VALUE(LEFT(O20,1)),0)/5*12+IFERROR(VALUE(LEFT(O21,1)),0)/5*12+IFERROR(VALUE(LEFT(O24,1)),0)/4*20+IFERROR(VALUE(LEFT(O28,1)),0)/4*12+IFERROR(VALUE(LEFT(O31,1)),0)/4*12)</f>
         <v/>
       </c>
-      <c r="P9" s="9">
+      <c r="P9" s="10">
         <f>IF(P14="","",IFERROR(VLOOKUP(P14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(P19,1)),0)/5*12+IFERROR(VALUE(LEFT(P20,1)),0)/5*12+IFERROR(VALUE(LEFT(P21,1)),0)/5*12+IFERROR(VALUE(LEFT(P24,1)),0)/4*20+IFERROR(VALUE(LEFT(P28,1)),0)/4*12+IFERROR(VALUE(LEFT(P31,1)),0)/4*12)</f>
         <v/>
       </c>
-      <c r="Q9" s="9">
+      <c r="Q9" s="10">
         <f>IF(Q14="","",IFERROR(VLOOKUP(Q14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(Q19,1)),0)/5*12+IFERROR(VALUE(LEFT(Q20,1)),0)/5*12+IFERROR(VALUE(LEFT(Q21,1)),0)/5*12+IFERROR(VALUE(LEFT(Q24,1)),0)/4*20+IFERROR(VALUE(LEFT(Q28,1)),0)/4*12+IFERROR(VALUE(LEFT(Q31,1)),0)/4*12)</f>
         <v/>
       </c>
-      <c r="R9" s="9">
+      <c r="R9" s="10">
         <f>IF(R14="","",IFERROR(VLOOKUP(R14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(R19,1)),0)/5*12+IFERROR(VALUE(LEFT(R20,1)),0)/5*12+IFERROR(VALUE(LEFT(R21,1)),0)/5*12+IFERROR(VALUE(LEFT(R24,1)),0)/4*20+IFERROR(VALUE(LEFT(R28,1)),0)/4*12+IFERROR(VALUE(LEFT(R31,1)),0)/4*12)</f>
         <v/>
       </c>
-      <c r="S9" s="9">
+      <c r="S9" s="10">
         <f>IF(S14="","",IFERROR(VLOOKUP(S14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(S19,1)),0)/5*12+IFERROR(VALUE(LEFT(S20,1)),0)/5*12+IFERROR(VALUE(LEFT(S21,1)),0)/5*12+IFERROR(VALUE(LEFT(S24,1)),0)/4*20+IFERROR(VALUE(LEFT(S28,1)),0)/4*12+IFERROR(VALUE(LEFT(S31,1)),0)/4*12)</f>
         <v/>
       </c>
-      <c r="T9" s="9">
+      <c r="T9" s="10">
         <f>IF(T14="","",IFERROR(VLOOKUP(T14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(T19,1)),0)/5*12+IFERROR(VALUE(LEFT(T20,1)),0)/5*12+IFERROR(VALUE(LEFT(T21,1)),0)/5*12+IFERROR(VALUE(LEFT(T24,1)),0)/4*20+IFERROR(VALUE(LEFT(T28,1)),0)/4*12+IFERROR(VALUE(LEFT(T31,1)),0)/4*12)</f>
         <v/>
       </c>
+      <c r="U9" s="10">
+        <f>IF(U14="","",IFERROR(VLOOKUP(U14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(U19,1)),0)/5*12+IFERROR(VALUE(LEFT(U20,1)),0)/5*12+IFERROR(VALUE(LEFT(U21,1)),0)/5*12+IFERROR(VALUE(LEFT(U24,1)),0)/4*20+IFERROR(VALUE(LEFT(U28,1)),0)/4*12+IFERROR(VALUE(LEFT(U31,1)),0)/4*12)</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>Band</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>80 Advance · 65 Consider · 50 Hold</t>
         </is>
       </c>
-      <c r="E10" s="11">
-        <f>IF(E14="","",IF(IFERROR(VLOOKUP(E14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(E9&gt;=80,"Advance",IF(E9&gt;=65,"Consider",IF(E9&gt;=50,"Hold","Decline"))))</f>
-        <v/>
-      </c>
-      <c r="F10" s="11">
+      <c r="F10" s="12">
         <f>IF(F14="","",IF(IFERROR(VLOOKUP(F14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(F9&gt;=80,"Advance",IF(F9&gt;=65,"Consider",IF(F9&gt;=50,"Hold","Decline"))))</f>
         <v/>
       </c>
-      <c r="G10" s="11">
+      <c r="G10" s="12">
         <f>IF(G14="","",IF(IFERROR(VLOOKUP(G14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(G9&gt;=80,"Advance",IF(G9&gt;=65,"Consider",IF(G9&gt;=50,"Hold","Decline"))))</f>
         <v/>
       </c>
-      <c r="H10" s="11">
+      <c r="H10" s="12">
         <f>IF(H14="","",IF(IFERROR(VLOOKUP(H14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(H9&gt;=80,"Advance",IF(H9&gt;=65,"Consider",IF(H9&gt;=50,"Hold","Decline"))))</f>
         <v/>
       </c>
-      <c r="I10" s="11">
+      <c r="I10" s="12">
         <f>IF(I14="","",IF(IFERROR(VLOOKUP(I14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(I9&gt;=80,"Advance",IF(I9&gt;=65,"Consider",IF(I9&gt;=50,"Hold","Decline"))))</f>
         <v/>
       </c>
-      <c r="J10" s="11">
+      <c r="J10" s="12">
         <f>IF(J14="","",IF(IFERROR(VLOOKUP(J14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(J9&gt;=80,"Advance",IF(J9&gt;=65,"Consider",IF(J9&gt;=50,"Hold","Decline"))))</f>
         <v/>
       </c>
-      <c r="K10" s="11">
+      <c r="K10" s="12">
         <f>IF(K14="","",IF(IFERROR(VLOOKUP(K14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(K9&gt;=80,"Advance",IF(K9&gt;=65,"Consider",IF(K9&gt;=50,"Hold","Decline"))))</f>
         <v/>
       </c>
-      <c r="L10" s="11">
+      <c r="L10" s="12">
         <f>IF(L14="","",IF(IFERROR(VLOOKUP(L14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(L9&gt;=80,"Advance",IF(L9&gt;=65,"Consider",IF(L9&gt;=50,"Hold","Decline"))))</f>
         <v/>
       </c>
-      <c r="M10" s="11">
+      <c r="M10" s="12">
         <f>IF(M14="","",IF(IFERROR(VLOOKUP(M14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(M9&gt;=80,"Advance",IF(M9&gt;=65,"Consider",IF(M9&gt;=50,"Hold","Decline"))))</f>
         <v/>
       </c>
-      <c r="N10" s="11">
+      <c r="N10" s="12">
         <f>IF(N14="","",IF(IFERROR(VLOOKUP(N14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(N9&gt;=80,"Advance",IF(N9&gt;=65,"Consider",IF(N9&gt;=50,"Hold","Decline"))))</f>
         <v/>
       </c>
-      <c r="O10" s="11">
+      <c r="O10" s="12">
         <f>IF(O14="","",IF(IFERROR(VLOOKUP(O14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(O9&gt;=80,"Advance",IF(O9&gt;=65,"Consider",IF(O9&gt;=50,"Hold","Decline"))))</f>
         <v/>
       </c>
-      <c r="P10" s="11">
+      <c r="P10" s="12">
         <f>IF(P14="","",IF(IFERROR(VLOOKUP(P14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(P9&gt;=80,"Advance",IF(P9&gt;=65,"Consider",IF(P9&gt;=50,"Hold","Decline"))))</f>
         <v/>
       </c>
-      <c r="Q10" s="11">
+      <c r="Q10" s="12">
         <f>IF(Q14="","",IF(IFERROR(VLOOKUP(Q14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(Q9&gt;=80,"Advance",IF(Q9&gt;=65,"Consider",IF(Q9&gt;=50,"Hold","Decline"))))</f>
         <v/>
       </c>
-      <c r="R10" s="11">
+      <c r="R10" s="12">
         <f>IF(R14="","",IF(IFERROR(VLOOKUP(R14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(R9&gt;=80,"Advance",IF(R9&gt;=65,"Consider",IF(R9&gt;=50,"Hold","Decline"))))</f>
         <v/>
       </c>
-      <c r="S10" s="11">
+      <c r="S10" s="12">
         <f>IF(S14="","",IF(IFERROR(VLOOKUP(S14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(S9&gt;=80,"Advance",IF(S9&gt;=65,"Consider",IF(S9&gt;=50,"Hold","Decline"))))</f>
         <v/>
       </c>
-      <c r="T10" s="11">
+      <c r="T10" s="12">
         <f>IF(T14="","",IF(IFERROR(VLOOKUP(T14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(T9&gt;=80,"Advance",IF(T9&gt;=65,"Consider",IF(T9&gt;=50,"Hold","Decline"))))</f>
         <v/>
       </c>
+      <c r="U10" s="12">
+        <f>IF(U14="","",IF(IFERROR(VLOOKUP(U14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(U9&gt;=80,"Advance",IF(U9&gt;=65,"Consider",IF(U9&gt;=50,"Hold","Decline"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>Flags</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>stop-checks raised, of three</t>
         </is>
       </c>
-      <c r="E11" s="13">
-        <f>IF(E14="","",IF(E15="STOP-CHECK",1,0)+IF(E16="STOP-CHECK",1,0)+IF(E25="STOP-CHECK",1,0))</f>
-        <v/>
-      </c>
-      <c r="F11" s="13">
+      <c r="F11" s="14">
         <f>IF(F14="","",IF(F15="STOP-CHECK",1,0)+IF(F16="STOP-CHECK",1,0)+IF(F25="STOP-CHECK",1,0))</f>
         <v/>
       </c>
-      <c r="G11" s="13">
+      <c r="G11" s="14">
         <f>IF(G14="","",IF(G15="STOP-CHECK",1,0)+IF(G16="STOP-CHECK",1,0)+IF(G25="STOP-CHECK",1,0))</f>
         <v/>
       </c>
-      <c r="H11" s="13">
+      <c r="H11" s="14">
         <f>IF(H14="","",IF(H15="STOP-CHECK",1,0)+IF(H16="STOP-CHECK",1,0)+IF(H25="STOP-CHECK",1,0))</f>
         <v/>
       </c>
-      <c r="I11" s="13">
+      <c r="I11" s="14">
         <f>IF(I14="","",IF(I15="STOP-CHECK",1,0)+IF(I16="STOP-CHECK",1,0)+IF(I25="STOP-CHECK",1,0))</f>
         <v/>
       </c>
-      <c r="J11" s="13">
+      <c r="J11" s="14">
         <f>IF(J14="","",IF(J15="STOP-CHECK",1,0)+IF(J16="STOP-CHECK",1,0)+IF(J25="STOP-CHECK",1,0))</f>
         <v/>
       </c>
-      <c r="K11" s="13">
+      <c r="K11" s="14">
         <f>IF(K14="","",IF(K15="STOP-CHECK",1,0)+IF(K16="STOP-CHECK",1,0)+IF(K25="STOP-CHECK",1,0))</f>
         <v/>
       </c>
-      <c r="L11" s="13">
+      <c r="L11" s="14">
         <f>IF(L14="","",IF(L15="STOP-CHECK",1,0)+IF(L16="STOP-CHECK",1,0)+IF(L25="STOP-CHECK",1,0))</f>
         <v/>
       </c>
-      <c r="M11" s="13">
+      <c r="M11" s="14">
         <f>IF(M14="","",IF(M15="STOP-CHECK",1,0)+IF(M16="STOP-CHECK",1,0)+IF(M25="STOP-CHECK",1,0))</f>
         <v/>
       </c>
-      <c r="N11" s="13">
+      <c r="N11" s="14">
         <f>IF(N14="","",IF(N15="STOP-CHECK",1,0)+IF(N16="STOP-CHECK",1,0)+IF(N25="STOP-CHECK",1,0))</f>
         <v/>
       </c>
-      <c r="O11" s="13">
+      <c r="O11" s="14">
         <f>IF(O14="","",IF(O15="STOP-CHECK",1,0)+IF(O16="STOP-CHECK",1,0)+IF(O25="STOP-CHECK",1,0))</f>
         <v/>
       </c>
-      <c r="P11" s="13">
+      <c r="P11" s="14">
         <f>IF(P14="","",IF(P15="STOP-CHECK",1,0)+IF(P16="STOP-CHECK",1,0)+IF(P25="STOP-CHECK",1,0))</f>
         <v/>
       </c>
-      <c r="Q11" s="13">
+      <c r="Q11" s="14">
         <f>IF(Q14="","",IF(Q15="STOP-CHECK",1,0)+IF(Q16="STOP-CHECK",1,0)+IF(Q25="STOP-CHECK",1,0))</f>
         <v/>
       </c>
-      <c r="R11" s="13">
+      <c r="R11" s="14">
         <f>IF(R14="","",IF(R15="STOP-CHECK",1,0)+IF(R16="STOP-CHECK",1,0)+IF(R25="STOP-CHECK",1,0))</f>
         <v/>
       </c>
-      <c r="S11" s="13">
+      <c r="S11" s="14">
         <f>IF(S14="","",IF(S15="STOP-CHECK",1,0)+IF(S16="STOP-CHECK",1,0)+IF(S25="STOP-CHECK",1,0))</f>
         <v/>
       </c>
-      <c r="T11" s="13">
+      <c r="T11" s="14">
         <f>IF(T14="","",IF(T15="STOP-CHECK",1,0)+IF(T16="STOP-CHECK",1,0)+IF(T25="STOP-CHECK",1,0))</f>
         <v/>
       </c>
+      <c r="U11" s="14">
+        <f>IF(U14="","",IF(U15="STOP-CHECK",1,0)+IF(U16="STOP-CHECK",1,0)+IF(U25="STOP-CHECK",1,0))</f>
+        <v/>
+      </c>
     </row>
     <row r="13" ht="21" customHeight="1">
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>A  ·  COMPANY AND PRODUCT</t>
         </is>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="B14" s="14" t="inlineStr">
+      <c r="B14" s="15" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
-      <c r="C14" s="15" t="inlineStr">
+      <c r="C14" s="16" t="inlineStr">
         <is>
           <t>Home Care Home Base integration</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>Pick one line  ·  20 points</t>
-        </is>
-      </c>
-      <c r="E14" s="16" t="inlineStr">
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>Pick the line that matches their answer</t>
+        </is>
+      </c>
+      <c r="E14" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="F14" s="17" t="inlineStr">
         <is>
           <t>Live — established customer base</t>
         </is>
       </c>
-      <c r="F14" s="16" t="inlineStr">
+      <c r="G14" s="17" t="inlineStr">
         <is>
           <t>Live — small customer base</t>
         </is>
       </c>
-      <c r="G14" s="16" t="inlineStr">
+      <c r="H14" s="17" t="inlineStr">
         <is>
           <t>In development — with a date</t>
         </is>
       </c>
-      <c r="H14" s="16" t="n"/>
-      <c r="I14" s="16" t="n"/>
-      <c r="J14" s="16" t="n"/>
-      <c r="K14" s="16" t="n"/>
-      <c r="L14" s="16" t="n"/>
-      <c r="M14" s="16" t="n"/>
-      <c r="N14" s="16" t="n"/>
-      <c r="O14" s="16" t="n"/>
-      <c r="P14" s="16" t="n"/>
-      <c r="Q14" s="16" t="n"/>
-      <c r="R14" s="16" t="n"/>
-      <c r="S14" s="16" t="n"/>
-      <c r="T14" s="16" t="n"/>
+      <c r="I14" s="17" t="n"/>
+      <c r="J14" s="17" t="n"/>
+      <c r="K14" s="17" t="n"/>
+      <c r="L14" s="17" t="n"/>
+      <c r="M14" s="17" t="n"/>
+      <c r="N14" s="17" t="n"/>
+      <c r="O14" s="17" t="n"/>
+      <c r="P14" s="17" t="n"/>
+      <c r="Q14" s="17" t="n"/>
+      <c r="R14" s="17" t="n"/>
+      <c r="S14" s="17" t="n"/>
+      <c r="T14" s="17" t="n"/>
+      <c r="U14" s="17" t="n"/>
     </row>
     <row r="15" ht="19" customHeight="1">
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="18" t="inlineStr">
         <is>
           <t>A2</t>
         </is>
       </c>
-      <c r="C15" s="15" t="inlineStr">
+      <c r="C15" s="16" t="inlineStr">
         <is>
           <t>Customers, scale and references</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>Flag  ·  stop-check if one customer or no references</t>
-        </is>
-      </c>
-      <c r="E15" s="18" t="inlineStr">
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>Stop-check if one customer, or no references offered</t>
+        </is>
+      </c>
+      <c r="E15" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" s="20" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="F15" s="18" t="inlineStr">
+      <c r="G15" s="20" t="inlineStr">
         <is>
           <t>STOP-CHECK</t>
         </is>
       </c>
-      <c r="G15" s="18" t="inlineStr">
+      <c r="H15" s="20" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="H15" s="18" t="n"/>
-      <c r="I15" s="18" t="n"/>
-      <c r="J15" s="18" t="n"/>
-      <c r="K15" s="18" t="n"/>
-      <c r="L15" s="18" t="n"/>
-      <c r="M15" s="18" t="n"/>
-      <c r="N15" s="18" t="n"/>
-      <c r="O15" s="18" t="n"/>
-      <c r="P15" s="18" t="n"/>
-      <c r="Q15" s="18" t="n"/>
-      <c r="R15" s="18" t="n"/>
-      <c r="S15" s="18" t="n"/>
-      <c r="T15" s="18" t="n"/>
+      <c r="I15" s="20" t="n"/>
+      <c r="J15" s="20" t="n"/>
+      <c r="K15" s="20" t="n"/>
+      <c r="L15" s="20" t="n"/>
+      <c r="M15" s="20" t="n"/>
+      <c r="N15" s="20" t="n"/>
+      <c r="O15" s="20" t="n"/>
+      <c r="P15" s="20" t="n"/>
+      <c r="Q15" s="20" t="n"/>
+      <c r="R15" s="20" t="n"/>
+      <c r="S15" s="20" t="n"/>
+      <c r="T15" s="20" t="n"/>
+      <c r="U15" s="20" t="n"/>
     </row>
     <row r="16" ht="19" customHeight="1">
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="18" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="C16" s="15" t="inlineStr">
+      <c r="C16" s="16" t="inlineStr">
         <is>
           <t>Measured impact</t>
         </is>
       </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>Flag  ·  watch if no baseline or period</t>
-        </is>
-      </c>
-      <c r="E16" s="18" t="inlineStr">
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>Watch if claimed with no baseline or period</t>
+        </is>
+      </c>
+      <c r="E16" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="20" t="inlineStr">
         <is>
           <t>Watch</t>
         </is>
       </c>
-      <c r="F16" s="18" t="inlineStr">
+      <c r="G16" s="20" t="inlineStr">
         <is>
           <t>Watch</t>
         </is>
       </c>
-      <c r="G16" s="18" t="inlineStr">
+      <c r="H16" s="20" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="H16" s="18" t="n"/>
-      <c r="I16" s="18" t="n"/>
-      <c r="J16" s="18" t="n"/>
-      <c r="K16" s="18" t="n"/>
-      <c r="L16" s="18" t="n"/>
-      <c r="M16" s="18" t="n"/>
-      <c r="N16" s="18" t="n"/>
-      <c r="O16" s="18" t="n"/>
-      <c r="P16" s="18" t="n"/>
-      <c r="Q16" s="18" t="n"/>
-      <c r="R16" s="18" t="n"/>
-      <c r="S16" s="18" t="n"/>
-      <c r="T16" s="18" t="n"/>
+      <c r="I16" s="20" t="n"/>
+      <c r="J16" s="20" t="n"/>
+      <c r="K16" s="20" t="n"/>
+      <c r="L16" s="20" t="n"/>
+      <c r="M16" s="20" t="n"/>
+      <c r="N16" s="20" t="n"/>
+      <c r="O16" s="20" t="n"/>
+      <c r="P16" s="20" t="n"/>
+      <c r="Q16" s="20" t="n"/>
+      <c r="R16" s="20" t="n"/>
+      <c r="S16" s="20" t="n"/>
+      <c r="T16" s="20" t="n"/>
+      <c r="U16" s="20" t="n"/>
     </row>
     <row r="18" ht="21" customHeight="1">
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>B  ·  COVERAGE SELF-ASSESSMENT   —   how much of our scope they cover</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="19" customHeight="1">
-      <c r="B19" s="19" t="inlineStr">
+    <row r="19" ht="30" customHeight="1">
+      <c r="B19" s="21" t="inlineStr">
         <is>
           <t>Section B</t>
         </is>
       </c>
-      <c r="C19" s="15" t="inlineStr">
+      <c r="C19" s="16" t="inlineStr">
         <is>
           <t>Capacity</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>Workforce supply · availability &amp; reach · the capacity math  ·  0–5  ·  12 points</t>
-        </is>
-      </c>
-      <c r="E19" s="20" t="inlineStr">
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>Workforce supply · availability &amp; reach · the capacity math</t>
+        </is>
+      </c>
+      <c r="E19" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="F19" s="22" t="inlineStr">
         <is>
           <t>4 — More than half</t>
         </is>
       </c>
-      <c r="F19" s="20" t="inlineStr">
+      <c r="G19" s="22" t="inlineStr">
         <is>
           <t>2 — Less than half</t>
         </is>
       </c>
-      <c r="G19" s="20" t="inlineStr">
+      <c r="H19" s="22" t="inlineStr">
         <is>
           <t>3 — About half</t>
         </is>
       </c>
-      <c r="H19" s="20" t="n"/>
-      <c r="I19" s="20" t="n"/>
-      <c r="J19" s="20" t="n"/>
-      <c r="K19" s="20" t="n"/>
-      <c r="L19" s="20" t="n"/>
-      <c r="M19" s="20" t="n"/>
-      <c r="N19" s="20" t="n"/>
-      <c r="O19" s="20" t="n"/>
-      <c r="P19" s="20" t="n"/>
-      <c r="Q19" s="20" t="n"/>
-      <c r="R19" s="20" t="n"/>
-      <c r="S19" s="20" t="n"/>
-      <c r="T19" s="20" t="n"/>
-    </row>
-    <row r="20" ht="19" customHeight="1">
-      <c r="B20" s="21" t="inlineStr">
+      <c r="I19" s="22" t="n"/>
+      <c r="J19" s="22" t="n"/>
+      <c r="K19" s="22" t="n"/>
+      <c r="L19" s="22" t="n"/>
+      <c r="M19" s="22" t="n"/>
+      <c r="N19" s="22" t="n"/>
+      <c r="O19" s="22" t="n"/>
+      <c r="P19" s="22" t="n"/>
+      <c r="Q19" s="22" t="n"/>
+      <c r="R19" s="22" t="n"/>
+      <c r="S19" s="22" t="n"/>
+      <c r="T19" s="22" t="n"/>
+      <c r="U19" s="22" t="n"/>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>Section B</t>
         </is>
       </c>
-      <c r="C20" s="15" t="inlineStr">
+      <c r="C20" s="16" t="inlineStr">
         <is>
           <t>Scheduling</t>
         </is>
       </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>Demand · matching · routing &amp; the week · exceptions  ·  0–5  ·  12 points</t>
-        </is>
-      </c>
-      <c r="E20" s="20" t="inlineStr">
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>Demand · matching · routing &amp; the week · exceptions</t>
+        </is>
+      </c>
+      <c r="E20" s="23" t="n">
+        <v>12</v>
+      </c>
+      <c r="F20" s="22" t="inlineStr">
         <is>
           <t>5 — Most of it</t>
         </is>
       </c>
-      <c r="F20" s="20" t="inlineStr">
+      <c r="G20" s="22" t="inlineStr">
         <is>
           <t>3 — About half</t>
         </is>
       </c>
-      <c r="G20" s="20" t="inlineStr">
+      <c r="H20" s="22" t="inlineStr">
         <is>
           <t>4 — More than half</t>
         </is>
       </c>
-      <c r="H20" s="20" t="n"/>
-      <c r="I20" s="20" t="n"/>
-      <c r="J20" s="20" t="n"/>
-      <c r="K20" s="20" t="n"/>
-      <c r="L20" s="20" t="n"/>
-      <c r="M20" s="20" t="n"/>
-      <c r="N20" s="20" t="n"/>
-      <c r="O20" s="20" t="n"/>
-      <c r="P20" s="20" t="n"/>
-      <c r="Q20" s="20" t="n"/>
-      <c r="R20" s="20" t="n"/>
-      <c r="S20" s="20" t="n"/>
-      <c r="T20" s="20" t="n"/>
-    </row>
-    <row r="21" ht="19" customHeight="1">
-      <c r="B21" s="22" t="inlineStr">
+      <c r="I20" s="22" t="n"/>
+      <c r="J20" s="22" t="n"/>
+      <c r="K20" s="22" t="n"/>
+      <c r="L20" s="22" t="n"/>
+      <c r="M20" s="22" t="n"/>
+      <c r="N20" s="22" t="n"/>
+      <c r="O20" s="22" t="n"/>
+      <c r="P20" s="22" t="n"/>
+      <c r="Q20" s="22" t="n"/>
+      <c r="R20" s="22" t="n"/>
+      <c r="S20" s="22" t="n"/>
+      <c r="T20" s="22" t="n"/>
+      <c r="U20" s="22" t="n"/>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="B21" s="24" t="inlineStr">
         <is>
           <t>Section B</t>
         </is>
       </c>
-      <c r="C21" s="15" t="inlineStr">
+      <c r="C21" s="16" t="inlineStr">
         <is>
           <t>Engagement</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>Before the visit · when plans change · incentives · care team  ·  0–5  ·  12 points</t>
-        </is>
-      </c>
-      <c r="E21" s="20" t="inlineStr">
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>Before the visit · when plans change · incentives · care team</t>
+        </is>
+      </c>
+      <c r="E21" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="F21" s="22" t="inlineStr">
         <is>
           <t>2 — Less than half</t>
         </is>
       </c>
-      <c r="F21" s="20" t="inlineStr">
+      <c r="G21" s="22" t="inlineStr">
         <is>
           <t>1 — A corner of it</t>
         </is>
       </c>
-      <c r="G21" s="20" t="inlineStr">
+      <c r="H21" s="22" t="inlineStr">
         <is>
           <t>3 — About half</t>
         </is>
       </c>
-      <c r="H21" s="20" t="n"/>
-      <c r="I21" s="20" t="n"/>
-      <c r="J21" s="20" t="n"/>
-      <c r="K21" s="20" t="n"/>
-      <c r="L21" s="20" t="n"/>
-      <c r="M21" s="20" t="n"/>
-      <c r="N21" s="20" t="n"/>
-      <c r="O21" s="20" t="n"/>
-      <c r="P21" s="20" t="n"/>
-      <c r="Q21" s="20" t="n"/>
-      <c r="R21" s="20" t="n"/>
-      <c r="S21" s="20" t="n"/>
-      <c r="T21" s="20" t="n"/>
+      <c r="I21" s="22" t="n"/>
+      <c r="J21" s="22" t="n"/>
+      <c r="K21" s="22" t="n"/>
+      <c r="L21" s="22" t="n"/>
+      <c r="M21" s="22" t="n"/>
+      <c r="N21" s="22" t="n"/>
+      <c r="O21" s="22" t="n"/>
+      <c r="P21" s="22" t="n"/>
+      <c r="Q21" s="22" t="n"/>
+      <c r="R21" s="22" t="n"/>
+      <c r="S21" s="22" t="n"/>
+      <c r="T21" s="22" t="n"/>
+      <c r="U21" s="22" t="n"/>
     </row>
     <row r="23" ht="21" customHeight="1">
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>C  ·  HOW YOUR PRODUCT WORKS</t>
         </is>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1">
-      <c r="B24" s="23" t="inlineStr">
+      <c r="B24" s="25" t="inlineStr">
         <is>
           <t>Section C</t>
         </is>
       </c>
-      <c r="C24" s="15" t="inlineStr">
+      <c r="C24" s="16" t="inlineStr">
         <is>
           <t>Sophistication</t>
         </is>
       </c>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t>How much of the work it does  ·  0–4  ·  20 points</t>
-        </is>
-      </c>
-      <c r="E24" s="20" t="inlineStr">
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>How much of the work the product does</t>
+        </is>
+      </c>
+      <c r="E24" s="25" t="n">
+        <v>20</v>
+      </c>
+      <c r="F24" s="22" t="inlineStr">
         <is>
           <t>4 — Runs it</t>
         </is>
       </c>
-      <c r="F24" s="20" t="inlineStr">
+      <c r="G24" s="22" t="inlineStr">
         <is>
           <t>3 — Recommends it</t>
         </is>
       </c>
-      <c r="G24" s="20" t="inlineStr">
+      <c r="H24" s="22" t="inlineStr">
         <is>
           <t>3 — Recommends it</t>
         </is>
       </c>
-      <c r="H24" s="20" t="n"/>
-      <c r="I24" s="20" t="n"/>
-      <c r="J24" s="20" t="n"/>
-      <c r="K24" s="20" t="n"/>
-      <c r="L24" s="20" t="n"/>
-      <c r="M24" s="20" t="n"/>
-      <c r="N24" s="20" t="n"/>
-      <c r="O24" s="20" t="n"/>
-      <c r="P24" s="20" t="n"/>
-      <c r="Q24" s="20" t="n"/>
-      <c r="R24" s="20" t="n"/>
-      <c r="S24" s="20" t="n"/>
-      <c r="T24" s="20" t="n"/>
+      <c r="I24" s="22" t="n"/>
+      <c r="J24" s="22" t="n"/>
+      <c r="K24" s="22" t="n"/>
+      <c r="L24" s="22" t="n"/>
+      <c r="M24" s="22" t="n"/>
+      <c r="N24" s="22" t="n"/>
+      <c r="O24" s="22" t="n"/>
+      <c r="P24" s="22" t="n"/>
+      <c r="Q24" s="22" t="n"/>
+      <c r="R24" s="22" t="n"/>
+      <c r="S24" s="22" t="n"/>
+      <c r="T24" s="22" t="n"/>
+      <c r="U24" s="22" t="n"/>
     </row>
     <row r="25" ht="19" customHeight="1">
-      <c r="B25" s="17" t="inlineStr">
+      <c r="B25" s="18" t="inlineStr">
         <is>
           <t>C6</t>
         </is>
       </c>
-      <c r="C25" s="15" t="inlineStr">
+      <c r="C25" s="16" t="inlineStr">
         <is>
           <t>When your product is down</t>
         </is>
       </c>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>Flag  ·  stop-check if no uptime figure or commitment</t>
-        </is>
-      </c>
-      <c r="E25" s="18" t="inlineStr">
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>Stop-check if no uptime figure or contractual commitment</t>
+        </is>
+      </c>
+      <c r="E25" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F25" s="20" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="F25" s="18" t="inlineStr">
+      <c r="G25" s="20" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="G25" s="18" t="inlineStr">
+      <c r="H25" s="20" t="inlineStr">
         <is>
           <t>Watch</t>
         </is>
       </c>
-      <c r="H25" s="18" t="n"/>
-      <c r="I25" s="18" t="n"/>
-      <c r="J25" s="18" t="n"/>
-      <c r="K25" s="18" t="n"/>
-      <c r="L25" s="18" t="n"/>
-      <c r="M25" s="18" t="n"/>
-      <c r="N25" s="18" t="n"/>
-      <c r="O25" s="18" t="n"/>
-      <c r="P25" s="18" t="n"/>
-      <c r="Q25" s="18" t="n"/>
-      <c r="R25" s="18" t="n"/>
-      <c r="S25" s="18" t="n"/>
-      <c r="T25" s="18" t="n"/>
+      <c r="I25" s="20" t="n"/>
+      <c r="J25" s="20" t="n"/>
+      <c r="K25" s="20" t="n"/>
+      <c r="L25" s="20" t="n"/>
+      <c r="M25" s="20" t="n"/>
+      <c r="N25" s="20" t="n"/>
+      <c r="O25" s="20" t="n"/>
+      <c r="P25" s="20" t="n"/>
+      <c r="Q25" s="20" t="n"/>
+      <c r="R25" s="20" t="n"/>
+      <c r="S25" s="20" t="n"/>
+      <c r="T25" s="20" t="n"/>
+      <c r="U25" s="20" t="n"/>
     </row>
     <row r="27" ht="21" customHeight="1">
-      <c r="B27" s="6" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>D  ·  THE CLINICIAN'S PLACE IN THE MODEL</t>
         </is>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1">
-      <c r="B28" s="24" t="inlineStr">
+      <c r="B28" s="26" t="inlineStr">
         <is>
           <t>D1–D3</t>
         </is>
       </c>
-      <c r="C28" s="15" t="inlineStr">
+      <c r="C28" s="16" t="inlineStr">
         <is>
           <t>Clinician fit</t>
         </is>
       </c>
-      <c r="D28" s="8" t="inlineStr">
-        <is>
-          <t>Our read of fit  ·  0–4  ·  12 points</t>
-        </is>
-      </c>
-      <c r="E28" s="20" t="inlineStr">
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>Our own read of fit — no checklist, on purpose</t>
+        </is>
+      </c>
+      <c r="E28" s="26" t="n">
+        <v>12</v>
+      </c>
+      <c r="F28" s="22" t="inlineStr">
         <is>
           <t>3 — Good fit</t>
         </is>
       </c>
-      <c r="F28" s="20" t="inlineStr">
+      <c r="G28" s="22" t="inlineStr">
         <is>
           <t>2 — Workable</t>
         </is>
       </c>
-      <c r="G28" s="20" t="inlineStr">
+      <c r="H28" s="22" t="inlineStr">
         <is>
           <t>3 — Good fit</t>
         </is>
       </c>
-      <c r="H28" s="20" t="n"/>
-      <c r="I28" s="20" t="n"/>
-      <c r="J28" s="20" t="n"/>
-      <c r="K28" s="20" t="n"/>
-      <c r="L28" s="20" t="n"/>
-      <c r="M28" s="20" t="n"/>
-      <c r="N28" s="20" t="n"/>
-      <c r="O28" s="20" t="n"/>
-      <c r="P28" s="20" t="n"/>
-      <c r="Q28" s="20" t="n"/>
-      <c r="R28" s="20" t="n"/>
-      <c r="S28" s="20" t="n"/>
-      <c r="T28" s="20" t="n"/>
+      <c r="I28" s="22" t="n"/>
+      <c r="J28" s="22" t="n"/>
+      <c r="K28" s="22" t="n"/>
+      <c r="L28" s="22" t="n"/>
+      <c r="M28" s="22" t="n"/>
+      <c r="N28" s="22" t="n"/>
+      <c r="O28" s="22" t="n"/>
+      <c r="P28" s="22" t="n"/>
+      <c r="Q28" s="22" t="n"/>
+      <c r="R28" s="22" t="n"/>
+      <c r="S28" s="22" t="n"/>
+      <c r="T28" s="22" t="n"/>
+      <c r="U28" s="22" t="n"/>
     </row>
     <row r="30" ht="21" customHeight="1">
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>E  ·  FIT AND PARTNERSHIP</t>
         </is>
       </c>
     </row>
     <row r="31" ht="24" customHeight="1">
-      <c r="B31" s="24" t="inlineStr">
+      <c r="B31" s="26" t="inlineStr">
         <is>
           <t>E1–E4</t>
         </is>
       </c>
-      <c r="C31" s="15" t="inlineStr">
+      <c r="C31" s="16" t="inlineStr">
         <is>
           <t>Partnership</t>
         </is>
       </c>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t>Willing to build it with us, and open to a stake  ·  0–4  ·  12 points</t>
-        </is>
-      </c>
-      <c r="E31" s="20" t="inlineStr">
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>Willing to build it with us, and open to a stake</t>
+        </is>
+      </c>
+      <c r="E31" s="26" t="n">
+        <v>12</v>
+      </c>
+      <c r="F31" s="22" t="inlineStr">
         <is>
           <t>3 — Ready to build to our needs as a design partner; ownership not addressed</t>
         </is>
       </c>
-      <c r="F31" s="20" t="inlineStr">
+      <c r="G31" s="22" t="inlineStr">
         <is>
           <t>2 — Will take our input, but they own the roadmap and the product</t>
         </is>
       </c>
-      <c r="G31" s="20" t="inlineStr">
+      <c r="H31" s="22" t="inlineStr">
         <is>
           <t>4 — Open to equity or a stake in what we build, and set up to build it with us</t>
         </is>
       </c>
-      <c r="H31" s="20" t="n"/>
-      <c r="I31" s="20" t="n"/>
-      <c r="J31" s="20" t="n"/>
-      <c r="K31" s="20" t="n"/>
-      <c r="L31" s="20" t="n"/>
-      <c r="M31" s="20" t="n"/>
-      <c r="N31" s="20" t="n"/>
-      <c r="O31" s="20" t="n"/>
-      <c r="P31" s="20" t="n"/>
-      <c r="Q31" s="20" t="n"/>
-      <c r="R31" s="20" t="n"/>
-      <c r="S31" s="20" t="n"/>
-      <c r="T31" s="20" t="n"/>
+      <c r="I31" s="22" t="n"/>
+      <c r="J31" s="22" t="n"/>
+      <c r="K31" s="22" t="n"/>
+      <c r="L31" s="22" t="n"/>
+      <c r="M31" s="22" t="n"/>
+      <c r="N31" s="22" t="n"/>
+      <c r="O31" s="22" t="n"/>
+      <c r="P31" s="22" t="n"/>
+      <c r="Q31" s="22" t="n"/>
+      <c r="R31" s="22" t="n"/>
+      <c r="S31" s="22" t="n"/>
+      <c r="T31" s="22" t="n"/>
+      <c r="U31" s="22" t="n"/>
     </row>
     <row r="33" ht="21" customHeight="1">
-      <c r="B33" s="25" t="inlineStr">
+      <c r="B33" s="27" t="inlineStr">
         <is>
           <t>NOTES   —   one line each.  This is what we go and ask.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="62" customHeight="1">
-      <c r="B34" s="26" t="inlineStr"/>
-      <c r="C34" s="27" t="inlineStr">
+      <c r="B34" s="28" t="inlineStr"/>
+      <c r="C34" s="29" t="inlineStr">
         <is>
           <t>What stands out</t>
         </is>
       </c>
-      <c r="D34" s="28" t="inlineStr">
+      <c r="D34" s="30" t="inlineStr">
         <is>
           <t>against the field, or against our own thinking</t>
         </is>
       </c>
-      <c r="E34" s="29" t="inlineStr">
+      <c r="E34" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F34" s="31" t="inlineStr">
         <is>
           <t>Only answer that shows a branch leader the envelope impact of a referral before accepting it.</t>
         </is>
       </c>
-      <c r="F34" s="29" t="inlineStr">
+      <c r="G34" s="31" t="inlineStr">
         <is>
           <t>Strong routing engine, almost nothing on the patient side.</t>
         </is>
       </c>
-      <c r="G34" s="29" t="inlineStr">
+      <c r="H34" s="31" t="inlineStr">
         <is>
           <t>Raised payer-mix-aware sequencing — not on our one-pager, probably should be.</t>
         </is>
       </c>
-      <c r="H34" s="29" t="n"/>
-      <c r="I34" s="29" t="n"/>
-      <c r="J34" s="29" t="n"/>
-      <c r="K34" s="29" t="n"/>
-      <c r="L34" s="29" t="n"/>
-      <c r="M34" s="29" t="n"/>
-      <c r="N34" s="29" t="n"/>
-      <c r="O34" s="29" t="n"/>
-      <c r="P34" s="29" t="n"/>
-      <c r="Q34" s="29" t="n"/>
-      <c r="R34" s="29" t="n"/>
-      <c r="S34" s="29" t="n"/>
-      <c r="T34" s="29" t="n"/>
+      <c r="I34" s="31" t="n"/>
+      <c r="J34" s="31" t="n"/>
+      <c r="K34" s="31" t="n"/>
+      <c r="L34" s="31" t="n"/>
+      <c r="M34" s="31" t="n"/>
+      <c r="N34" s="31" t="n"/>
+      <c r="O34" s="31" t="n"/>
+      <c r="P34" s="31" t="n"/>
+      <c r="Q34" s="31" t="n"/>
+      <c r="R34" s="31" t="n"/>
+      <c r="S34" s="31" t="n"/>
+      <c r="T34" s="31" t="n"/>
+      <c r="U34" s="31" t="n"/>
     </row>
     <row r="35" ht="62" customHeight="1">
-      <c r="B35" s="26" t="inlineStr"/>
-      <c r="C35" s="27" t="inlineStr">
+      <c r="B35" s="28" t="inlineStr"/>
+      <c r="C35" s="29" t="inlineStr">
         <is>
           <t>What worries me</t>
         </is>
       </c>
-      <c r="D35" s="28" t="inlineStr">
+      <c r="D35" s="30" t="inlineStr">
         <is>
           <t>including anything flagged above</t>
         </is>
       </c>
-      <c r="E35" s="29" t="inlineStr">
+      <c r="E35" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F35" s="31" t="inlineStr">
         <is>
           <t>Impact figures come from one site.</t>
         </is>
       </c>
-      <c r="F35" s="29" t="inlineStr">
+      <c r="G35" s="31" t="inlineStr">
         <is>
           <t>One customer, references not offered.</t>
         </is>
       </c>
-      <c r="G35" s="29" t="inlineStr">
+      <c r="H35" s="31" t="inlineStr">
         <is>
           <t>Integration is a promise on their timeline, not ours.</t>
         </is>
       </c>
-      <c r="H35" s="29" t="n"/>
-      <c r="I35" s="29" t="n"/>
-      <c r="J35" s="29" t="n"/>
-      <c r="K35" s="29" t="n"/>
-      <c r="L35" s="29" t="n"/>
-      <c r="M35" s="29" t="n"/>
-      <c r="N35" s="29" t="n"/>
-      <c r="O35" s="29" t="n"/>
-      <c r="P35" s="29" t="n"/>
-      <c r="Q35" s="29" t="n"/>
-      <c r="R35" s="29" t="n"/>
-      <c r="S35" s="29" t="n"/>
-      <c r="T35" s="29" t="n"/>
+      <c r="I35" s="31" t="n"/>
+      <c r="J35" s="31" t="n"/>
+      <c r="K35" s="31" t="n"/>
+      <c r="L35" s="31" t="n"/>
+      <c r="M35" s="31" t="n"/>
+      <c r="N35" s="31" t="n"/>
+      <c r="O35" s="31" t="n"/>
+      <c r="P35" s="31" t="n"/>
+      <c r="Q35" s="31" t="n"/>
+      <c r="R35" s="31" t="n"/>
+      <c r="S35" s="31" t="n"/>
+      <c r="T35" s="31" t="n"/>
+      <c r="U35" s="31" t="n"/>
     </row>
     <row r="36" ht="62" customHeight="1">
-      <c r="B36" s="26" t="inlineStr"/>
-      <c r="C36" s="27" t="inlineStr">
+      <c r="B36" s="28" t="inlineStr"/>
+      <c r="C36" s="29" t="inlineStr">
         <is>
           <t>What to go and ask</t>
         </is>
       </c>
-      <c r="D36" s="28" t="inlineStr">
+      <c r="D36" s="30" t="inlineStr">
         <is>
           <t>the demo agenda</t>
         </is>
       </c>
-      <c r="E36" s="29" t="inlineStr">
+      <c r="E36" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F36" s="31" t="inlineStr">
         <is>
           <t>Would they discuss a stake? Never mentioned it.</t>
         </is>
       </c>
-      <c r="F36" s="29" t="inlineStr">
+      <c r="G36" s="31" t="inlineStr">
         <is>
           <t>What does the day-before confirmation round cost in staff hours at our scale?</t>
         </is>
       </c>
-      <c r="G36" s="29" t="inlineStr">
+      <c r="H36" s="31" t="inlineStr">
         <is>
           <t>What exactly is committed on the integration date, and by whom?</t>
         </is>
       </c>
-      <c r="H36" s="29" t="n"/>
-      <c r="I36" s="29" t="n"/>
-      <c r="J36" s="29" t="n"/>
-      <c r="K36" s="29" t="n"/>
-      <c r="L36" s="29" t="n"/>
-      <c r="M36" s="29" t="n"/>
-      <c r="N36" s="29" t="n"/>
-      <c r="O36" s="29" t="n"/>
-      <c r="P36" s="29" t="n"/>
-      <c r="Q36" s="29" t="n"/>
-      <c r="R36" s="29" t="n"/>
-      <c r="S36" s="29" t="n"/>
-      <c r="T36" s="29" t="n"/>
+      <c r="I36" s="31" t="n"/>
+      <c r="J36" s="31" t="n"/>
+      <c r="K36" s="31" t="n"/>
+      <c r="L36" s="31" t="n"/>
+      <c r="M36" s="31" t="n"/>
+      <c r="N36" s="31" t="n"/>
+      <c r="O36" s="31" t="n"/>
+      <c r="P36" s="31" t="n"/>
+      <c r="Q36" s="31" t="n"/>
+      <c r="R36" s="31" t="n"/>
+      <c r="S36" s="31" t="n"/>
+      <c r="T36" s="31" t="n"/>
+      <c r="U36" s="31" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="B23:T23"/>
-    <mergeCell ref="B8:T8"/>
-    <mergeCell ref="B18:T18"/>
-    <mergeCell ref="B13:T13"/>
-    <mergeCell ref="B27:T27"/>
-    <mergeCell ref="B4:T4"/>
-    <mergeCell ref="B30:T30"/>
-    <mergeCell ref="B33:T33"/>
+    <mergeCell ref="B23:U23"/>
+    <mergeCell ref="B27:U27"/>
+    <mergeCell ref="B8:U8"/>
+    <mergeCell ref="B4:U4"/>
+    <mergeCell ref="B18:U18"/>
+    <mergeCell ref="B13:U13"/>
+    <mergeCell ref="B30:U30"/>
+    <mergeCell ref="B33:U33"/>
   </mergeCells>
-  <conditionalFormatting sqref="E9:T9">
+  <conditionalFormatting sqref="F9:U9">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="40"/>
@@ -1741,32 +1815,32 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E10:T10">
+  <conditionalFormatting sqref="F10:U10">
     <cfRule type="expression" priority="2" dxfId="0">
-      <formula>ISNUMBER(SEARCH("Conditional",E10))</formula>
+      <formula>ISNUMBER(SEARCH("Conditional",F10))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E11:T11">
+  <conditionalFormatting sqref="F11:U11">
     <cfRule type="expression" priority="3" dxfId="0">
-      <formula>E11&gt;0</formula>
+      <formula>F11&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E15:T15">
+  <conditionalFormatting sqref="F15:U15">
     <cfRule type="expression" priority="4" dxfId="1">
-      <formula>E15="STOP-CHECK"</formula>
+      <formula>F15="STOP-CHECK"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E16:T16">
+  <conditionalFormatting sqref="F16:U16">
     <cfRule type="expression" priority="5" dxfId="1">
-      <formula>E16="STOP-CHECK"</formula>
+      <formula>F16="STOP-CHECK"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E25:T25">
+  <conditionalFormatting sqref="F25:U25">
     <cfRule type="expression" priority="6" dxfId="1">
-      <formula>E25="STOP-CHECK"</formula>
+      <formula>F25="STOP-CHECK"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E19:T19">
+  <conditionalFormatting sqref="F19:U19">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -1776,7 +1850,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E20:T20">
+  <conditionalFormatting sqref="F20:U20">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -1786,7 +1860,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E21:T21">
+  <conditionalFormatting sqref="F21:U21">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -1797,22 +1871,22 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="6">
-    <dataValidation sqref="E14:T14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="A1 — Home Care Home Base" prompt="Pick one line. Ambiguous? Take the lower one and say so in Notes." type="list">
-      <formula1>=Lists!$B$2:$B$7</formula1>
+    <dataValidation sqref="F14:U14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="A1 — Home Care Home Base" prompt="Pick one line. Ambiguous? Take the lower one and say so in Notes." type="list">
+      <formula1>=HCHB_List</formula1>
     </dataValidation>
-    <dataValidation sqref="E19:T19 E20:T20 E21:T21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Scope, 0–5" prompt="How much of this arena they cover. Most of it is the ceiling — our spec is original, so nobody covers all of it." type="list">
-      <formula1>=Lists!$E$2:$E$7</formula1>
+    <dataValidation sqref="F19:U19 F20:U20 F21:U21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Scope, 0–5" prompt="How much of this arena they cover. Most of it is the ceiling — our spec is original, so nobody covers all of it." type="list">
+      <formula1>=Scope_List</formula1>
     </dataValidation>
-    <dataValidation sqref="E24:T24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Sophistication, 0–4" prompt="1 shows it · 2 checks it · 3 recommends it · 4 runs it. Score what the product does, not how much they wrote about it." type="list">
-      <formula1>=Lists!$G$2:$G$6</formula1>
+    <dataValidation sqref="F24:U24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Sophistication, 0–4" prompt="1 shows it · 2 checks it · 3 recommends it · 4 runs it. Score what the product does, not how much they wrote about it." type="list">
+      <formula1>=Soph_List</formula1>
     </dataValidation>
-    <dataValidation sqref="E28:T28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Clinician fit, 0–4" prompt="Read D1 to D3 and give it your own read of fit. There is no checklist here on purpose." type="list">
-      <formula1>=Lists!$I$2:$I$6</formula1>
+    <dataValidation sqref="F28:U28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Clinician fit, 0–4" prompt="Read D1 to D3 and give it your own read of fit. There is no checklist here on purpose." type="list">
+      <formula1>=Clin_List</formula1>
     </dataValidation>
-    <dataValidation sqref="E31:T31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Partnership, 0–4" prompt="Are they able and willing to build this with us, and open to us holding a stake in what a wider market might buy? A discount is a discount." type="list">
-      <formula1>=Lists!$K$2:$K$6</formula1>
+    <dataValidation sqref="F31:U31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Partnership, 0–4" prompt="Are they able and willing to build this with us, and open to us holding a stake in what a wider market might buy? A discount is a discount." type="list">
+      <formula1>=Part_List</formula1>
     </dataValidation>
-    <dataValidation sqref="E15:T15 E16:T16 E25:T25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Flag" prompt="A stop-check is resolved before advancing, not traded against points." type="list">
+    <dataValidation sqref="F15:U15 F16:U16 F25:U25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Flag" prompt="A stop-check is resolved before advancing, not traded against points." type="list">
       <formula1>"OK,Watch,STOP-CHECK"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1827,14 +1901,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:T36"/>
+  <dimension ref="B2:U36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
@@ -1850,6 +1924,7 @@
     <col width="13" customWidth="1" min="18" max="18"/>
     <col width="13" customWidth="1" min="19" max="19"/>
     <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -1881,791 +1956,847 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
           <t>Vendor 01</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>Vendor 02</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>Vendor 03</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="I6" s="6" t="inlineStr">
         <is>
           <t>Vendor 04</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="J6" s="6" t="inlineStr">
         <is>
           <t>Vendor 05</t>
         </is>
       </c>
-      <c r="J6" s="5" t="inlineStr">
+      <c r="K6" s="6" t="inlineStr">
         <is>
           <t>Vendor 06</t>
         </is>
       </c>
-      <c r="K6" s="5" t="inlineStr">
+      <c r="L6" s="6" t="inlineStr">
         <is>
           <t>Vendor 07</t>
         </is>
       </c>
-      <c r="L6" s="5" t="inlineStr">
+      <c r="M6" s="6" t="inlineStr">
         <is>
           <t>Vendor 08</t>
         </is>
       </c>
-      <c r="M6" s="5" t="inlineStr">
+      <c r="N6" s="6" t="inlineStr">
         <is>
           <t>Vendor 09</t>
         </is>
       </c>
-      <c r="N6" s="5" t="inlineStr">
+      <c r="O6" s="6" t="inlineStr">
         <is>
           <t>Vendor 10</t>
         </is>
       </c>
-      <c r="O6" s="5" t="inlineStr">
+      <c r="P6" s="6" t="inlineStr">
         <is>
           <t>Vendor 11</t>
         </is>
       </c>
-      <c r="P6" s="5" t="inlineStr">
+      <c r="Q6" s="6" t="inlineStr">
         <is>
           <t>Vendor 12</t>
         </is>
       </c>
-      <c r="Q6" s="5" t="inlineStr">
+      <c r="R6" s="6" t="inlineStr">
         <is>
           <t>Vendor 13</t>
         </is>
       </c>
-      <c r="R6" s="5" t="inlineStr">
+      <c r="S6" s="6" t="inlineStr">
         <is>
           <t>Vendor 14</t>
         </is>
       </c>
-      <c r="S6" s="5" t="inlineStr">
+      <c r="T6" s="6" t="inlineStr">
         <is>
           <t>Vendor 15</t>
         </is>
       </c>
-      <c r="T6" s="5" t="inlineStr">
+      <c r="U6" s="6" t="inlineStr">
         <is>
           <t>Vendor 16</t>
         </is>
       </c>
     </row>
     <row r="8" ht="21" customHeight="1">
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>SCORE</t>
         </is>
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>of 100</t>
         </is>
       </c>
-      <c r="E9" s="9">
-        <f>IF(E14="","",IFERROR(VLOOKUP(E14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(E19,1)),0)/5*12+IFERROR(VALUE(LEFT(E20,1)),0)/5*12+IFERROR(VALUE(LEFT(E21,1)),0)/5*12+IFERROR(VALUE(LEFT(E24,1)),0)/4*20+IFERROR(VALUE(LEFT(E28,1)),0)/4*12+IFERROR(VALUE(LEFT(E31,1)),0)/4*12)</f>
-        <v/>
-      </c>
-      <c r="F9" s="9">
+      <c r="F9" s="10">
         <f>IF(F14="","",IFERROR(VLOOKUP(F14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(F19,1)),0)/5*12+IFERROR(VALUE(LEFT(F20,1)),0)/5*12+IFERROR(VALUE(LEFT(F21,1)),0)/5*12+IFERROR(VALUE(LEFT(F24,1)),0)/4*20+IFERROR(VALUE(LEFT(F28,1)),0)/4*12+IFERROR(VALUE(LEFT(F31,1)),0)/4*12)</f>
         <v/>
       </c>
-      <c r="G9" s="9">
+      <c r="G9" s="10">
         <f>IF(G14="","",IFERROR(VLOOKUP(G14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(G19,1)),0)/5*12+IFERROR(VALUE(LEFT(G20,1)),0)/5*12+IFERROR(VALUE(LEFT(G21,1)),0)/5*12+IFERROR(VALUE(LEFT(G24,1)),0)/4*20+IFERROR(VALUE(LEFT(G28,1)),0)/4*12+IFERROR(VALUE(LEFT(G31,1)),0)/4*12)</f>
         <v/>
       </c>
-      <c r="H9" s="9">
+      <c r="H9" s="10">
         <f>IF(H14="","",IFERROR(VLOOKUP(H14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(H19,1)),0)/5*12+IFERROR(VALUE(LEFT(H20,1)),0)/5*12+IFERROR(VALUE(LEFT(H21,1)),0)/5*12+IFERROR(VALUE(LEFT(H24,1)),0)/4*20+IFERROR(VALUE(LEFT(H28,1)),0)/4*12+IFERROR(VALUE(LEFT(H31,1)),0)/4*12)</f>
         <v/>
       </c>
-      <c r="I9" s="9">
+      <c r="I9" s="10">
         <f>IF(I14="","",IFERROR(VLOOKUP(I14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(I19,1)),0)/5*12+IFERROR(VALUE(LEFT(I20,1)),0)/5*12+IFERROR(VALUE(LEFT(I21,1)),0)/5*12+IFERROR(VALUE(LEFT(I24,1)),0)/4*20+IFERROR(VALUE(LEFT(I28,1)),0)/4*12+IFERROR(VALUE(LEFT(I31,1)),0)/4*12)</f>
         <v/>
       </c>
-      <c r="J9" s="9">
+      <c r="J9" s="10">
         <f>IF(J14="","",IFERROR(VLOOKUP(J14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(J19,1)),0)/5*12+IFERROR(VALUE(LEFT(J20,1)),0)/5*12+IFERROR(VALUE(LEFT(J21,1)),0)/5*12+IFERROR(VALUE(LEFT(J24,1)),0)/4*20+IFERROR(VALUE(LEFT(J28,1)),0)/4*12+IFERROR(VALUE(LEFT(J31,1)),0)/4*12)</f>
         <v/>
       </c>
-      <c r="K9" s="9">
+      <c r="K9" s="10">
         <f>IF(K14="","",IFERROR(VLOOKUP(K14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(K19,1)),0)/5*12+IFERROR(VALUE(LEFT(K20,1)),0)/5*12+IFERROR(VALUE(LEFT(K21,1)),0)/5*12+IFERROR(VALUE(LEFT(K24,1)),0)/4*20+IFERROR(VALUE(LEFT(K28,1)),0)/4*12+IFERROR(VALUE(LEFT(K31,1)),0)/4*12)</f>
         <v/>
       </c>
-      <c r="L9" s="9">
+      <c r="L9" s="10">
         <f>IF(L14="","",IFERROR(VLOOKUP(L14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(L19,1)),0)/5*12+IFERROR(VALUE(LEFT(L20,1)),0)/5*12+IFERROR(VALUE(LEFT(L21,1)),0)/5*12+IFERROR(VALUE(LEFT(L24,1)),0)/4*20+IFERROR(VALUE(LEFT(L28,1)),0)/4*12+IFERROR(VALUE(LEFT(L31,1)),0)/4*12)</f>
         <v/>
       </c>
-      <c r="M9" s="9">
+      <c r="M9" s="10">
         <f>IF(M14="","",IFERROR(VLOOKUP(M14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(M19,1)),0)/5*12+IFERROR(VALUE(LEFT(M20,1)),0)/5*12+IFERROR(VALUE(LEFT(M21,1)),0)/5*12+IFERROR(VALUE(LEFT(M24,1)),0)/4*20+IFERROR(VALUE(LEFT(M28,1)),0)/4*12+IFERROR(VALUE(LEFT(M31,1)),0)/4*12)</f>
         <v/>
       </c>
-      <c r="N9" s="9">
+      <c r="N9" s="10">
         <f>IF(N14="","",IFERROR(VLOOKUP(N14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(N19,1)),0)/5*12+IFERROR(VALUE(LEFT(N20,1)),0)/5*12+IFERROR(VALUE(LEFT(N21,1)),0)/5*12+IFERROR(VALUE(LEFT(N24,1)),0)/4*20+IFERROR(VALUE(LEFT(N28,1)),0)/4*12+IFERROR(VALUE(LEFT(N31,1)),0)/4*12)</f>
         <v/>
       </c>
-      <c r="O9" s="9">
+      <c r="O9" s="10">
         <f>IF(O14="","",IFERROR(VLOOKUP(O14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(O19,1)),0)/5*12+IFERROR(VALUE(LEFT(O20,1)),0)/5*12+IFERROR(VALUE(LEFT(O21,1)),0)/5*12+IFERROR(VALUE(LEFT(O24,1)),0)/4*20+IFERROR(VALUE(LEFT(O28,1)),0)/4*12+IFERROR(VALUE(LEFT(O31,1)),0)/4*12)</f>
         <v/>
       </c>
-      <c r="P9" s="9">
+      <c r="P9" s="10">
         <f>IF(P14="","",IFERROR(VLOOKUP(P14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(P19,1)),0)/5*12+IFERROR(VALUE(LEFT(P20,1)),0)/5*12+IFERROR(VALUE(LEFT(P21,1)),0)/5*12+IFERROR(VALUE(LEFT(P24,1)),0)/4*20+IFERROR(VALUE(LEFT(P28,1)),0)/4*12+IFERROR(VALUE(LEFT(P31,1)),0)/4*12)</f>
         <v/>
       </c>
-      <c r="Q9" s="9">
+      <c r="Q9" s="10">
         <f>IF(Q14="","",IFERROR(VLOOKUP(Q14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(Q19,1)),0)/5*12+IFERROR(VALUE(LEFT(Q20,1)),0)/5*12+IFERROR(VALUE(LEFT(Q21,1)),0)/5*12+IFERROR(VALUE(LEFT(Q24,1)),0)/4*20+IFERROR(VALUE(LEFT(Q28,1)),0)/4*12+IFERROR(VALUE(LEFT(Q31,1)),0)/4*12)</f>
         <v/>
       </c>
-      <c r="R9" s="9">
+      <c r="R9" s="10">
         <f>IF(R14="","",IFERROR(VLOOKUP(R14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(R19,1)),0)/5*12+IFERROR(VALUE(LEFT(R20,1)),0)/5*12+IFERROR(VALUE(LEFT(R21,1)),0)/5*12+IFERROR(VALUE(LEFT(R24,1)),0)/4*20+IFERROR(VALUE(LEFT(R28,1)),0)/4*12+IFERROR(VALUE(LEFT(R31,1)),0)/4*12)</f>
         <v/>
       </c>
-      <c r="S9" s="9">
+      <c r="S9" s="10">
         <f>IF(S14="","",IFERROR(VLOOKUP(S14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(S19,1)),0)/5*12+IFERROR(VALUE(LEFT(S20,1)),0)/5*12+IFERROR(VALUE(LEFT(S21,1)),0)/5*12+IFERROR(VALUE(LEFT(S24,1)),0)/4*20+IFERROR(VALUE(LEFT(S28,1)),0)/4*12+IFERROR(VALUE(LEFT(S31,1)),0)/4*12)</f>
         <v/>
       </c>
-      <c r="T9" s="9">
+      <c r="T9" s="10">
         <f>IF(T14="","",IFERROR(VLOOKUP(T14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(T19,1)),0)/5*12+IFERROR(VALUE(LEFT(T20,1)),0)/5*12+IFERROR(VALUE(LEFT(T21,1)),0)/5*12+IFERROR(VALUE(LEFT(T24,1)),0)/4*20+IFERROR(VALUE(LEFT(T28,1)),0)/4*12+IFERROR(VALUE(LEFT(T31,1)),0)/4*12)</f>
         <v/>
       </c>
+      <c r="U9" s="10">
+        <f>IF(U14="","",IFERROR(VLOOKUP(U14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(U19,1)),0)/5*12+IFERROR(VALUE(LEFT(U20,1)),0)/5*12+IFERROR(VALUE(LEFT(U21,1)),0)/5*12+IFERROR(VALUE(LEFT(U24,1)),0)/4*20+IFERROR(VALUE(LEFT(U28,1)),0)/4*12+IFERROR(VALUE(LEFT(U31,1)),0)/4*12)</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>Band</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>80 Advance · 65 Consider · 50 Hold</t>
         </is>
       </c>
-      <c r="E10" s="11">
-        <f>IF(E14="","",IF(IFERROR(VLOOKUP(E14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(E9&gt;=80,"Advance",IF(E9&gt;=65,"Consider",IF(E9&gt;=50,"Hold","Decline"))))</f>
-        <v/>
-      </c>
-      <c r="F10" s="11">
+      <c r="F10" s="12">
         <f>IF(F14="","",IF(IFERROR(VLOOKUP(F14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(F9&gt;=80,"Advance",IF(F9&gt;=65,"Consider",IF(F9&gt;=50,"Hold","Decline"))))</f>
         <v/>
       </c>
-      <c r="G10" s="11">
+      <c r="G10" s="12">
         <f>IF(G14="","",IF(IFERROR(VLOOKUP(G14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(G9&gt;=80,"Advance",IF(G9&gt;=65,"Consider",IF(G9&gt;=50,"Hold","Decline"))))</f>
         <v/>
       </c>
-      <c r="H10" s="11">
+      <c r="H10" s="12">
         <f>IF(H14="","",IF(IFERROR(VLOOKUP(H14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(H9&gt;=80,"Advance",IF(H9&gt;=65,"Consider",IF(H9&gt;=50,"Hold","Decline"))))</f>
         <v/>
       </c>
-      <c r="I10" s="11">
+      <c r="I10" s="12">
         <f>IF(I14="","",IF(IFERROR(VLOOKUP(I14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(I9&gt;=80,"Advance",IF(I9&gt;=65,"Consider",IF(I9&gt;=50,"Hold","Decline"))))</f>
         <v/>
       </c>
-      <c r="J10" s="11">
+      <c r="J10" s="12">
         <f>IF(J14="","",IF(IFERROR(VLOOKUP(J14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(J9&gt;=80,"Advance",IF(J9&gt;=65,"Consider",IF(J9&gt;=50,"Hold","Decline"))))</f>
         <v/>
       </c>
-      <c r="K10" s="11">
+      <c r="K10" s="12">
         <f>IF(K14="","",IF(IFERROR(VLOOKUP(K14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(K9&gt;=80,"Advance",IF(K9&gt;=65,"Consider",IF(K9&gt;=50,"Hold","Decline"))))</f>
         <v/>
       </c>
-      <c r="L10" s="11">
+      <c r="L10" s="12">
         <f>IF(L14="","",IF(IFERROR(VLOOKUP(L14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(L9&gt;=80,"Advance",IF(L9&gt;=65,"Consider",IF(L9&gt;=50,"Hold","Decline"))))</f>
         <v/>
       </c>
-      <c r="M10" s="11">
+      <c r="M10" s="12">
         <f>IF(M14="","",IF(IFERROR(VLOOKUP(M14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(M9&gt;=80,"Advance",IF(M9&gt;=65,"Consider",IF(M9&gt;=50,"Hold","Decline"))))</f>
         <v/>
       </c>
-      <c r="N10" s="11">
+      <c r="N10" s="12">
         <f>IF(N14="","",IF(IFERROR(VLOOKUP(N14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(N9&gt;=80,"Advance",IF(N9&gt;=65,"Consider",IF(N9&gt;=50,"Hold","Decline"))))</f>
         <v/>
       </c>
-      <c r="O10" s="11">
+      <c r="O10" s="12">
         <f>IF(O14="","",IF(IFERROR(VLOOKUP(O14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(O9&gt;=80,"Advance",IF(O9&gt;=65,"Consider",IF(O9&gt;=50,"Hold","Decline"))))</f>
         <v/>
       </c>
-      <c r="P10" s="11">
+      <c r="P10" s="12">
         <f>IF(P14="","",IF(IFERROR(VLOOKUP(P14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(P9&gt;=80,"Advance",IF(P9&gt;=65,"Consider",IF(P9&gt;=50,"Hold","Decline"))))</f>
         <v/>
       </c>
-      <c r="Q10" s="11">
+      <c r="Q10" s="12">
         <f>IF(Q14="","",IF(IFERROR(VLOOKUP(Q14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(Q9&gt;=80,"Advance",IF(Q9&gt;=65,"Consider",IF(Q9&gt;=50,"Hold","Decline"))))</f>
         <v/>
       </c>
-      <c r="R10" s="11">
+      <c r="R10" s="12">
         <f>IF(R14="","",IF(IFERROR(VLOOKUP(R14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(R9&gt;=80,"Advance",IF(R9&gt;=65,"Consider",IF(R9&gt;=50,"Hold","Decline"))))</f>
         <v/>
       </c>
-      <c r="S10" s="11">
+      <c r="S10" s="12">
         <f>IF(S14="","",IF(IFERROR(VLOOKUP(S14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(S9&gt;=80,"Advance",IF(S9&gt;=65,"Consider",IF(S9&gt;=50,"Hold","Decline"))))</f>
         <v/>
       </c>
-      <c r="T10" s="11">
+      <c r="T10" s="12">
         <f>IF(T14="","",IF(IFERROR(VLOOKUP(T14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(T9&gt;=80,"Advance",IF(T9&gt;=65,"Consider",IF(T9&gt;=50,"Hold","Decline"))))</f>
         <v/>
       </c>
+      <c r="U10" s="12">
+        <f>IF(U14="","",IF(IFERROR(VLOOKUP(U14,Lists!$B$2:$C$7,2,FALSE),0)&lt;12,"Conditional — ","")&amp;IF(U9&gt;=80,"Advance",IF(U9&gt;=65,"Consider",IF(U9&gt;=50,"Hold","Decline"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>Flags</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>stop-checks raised, of three</t>
         </is>
       </c>
-      <c r="E11" s="13">
-        <f>IF(E14="","",IF(E15="STOP-CHECK",1,0)+IF(E16="STOP-CHECK",1,0)+IF(E25="STOP-CHECK",1,0))</f>
-        <v/>
-      </c>
-      <c r="F11" s="13">
+      <c r="F11" s="14">
         <f>IF(F14="","",IF(F15="STOP-CHECK",1,0)+IF(F16="STOP-CHECK",1,0)+IF(F25="STOP-CHECK",1,0))</f>
         <v/>
       </c>
-      <c r="G11" s="13">
+      <c r="G11" s="14">
         <f>IF(G14="","",IF(G15="STOP-CHECK",1,0)+IF(G16="STOP-CHECK",1,0)+IF(G25="STOP-CHECK",1,0))</f>
         <v/>
       </c>
-      <c r="H11" s="13">
+      <c r="H11" s="14">
         <f>IF(H14="","",IF(H15="STOP-CHECK",1,0)+IF(H16="STOP-CHECK",1,0)+IF(H25="STOP-CHECK",1,0))</f>
         <v/>
       </c>
-      <c r="I11" s="13">
+      <c r="I11" s="14">
         <f>IF(I14="","",IF(I15="STOP-CHECK",1,0)+IF(I16="STOP-CHECK",1,0)+IF(I25="STOP-CHECK",1,0))</f>
         <v/>
       </c>
-      <c r="J11" s="13">
+      <c r="J11" s="14">
         <f>IF(J14="","",IF(J15="STOP-CHECK",1,0)+IF(J16="STOP-CHECK",1,0)+IF(J25="STOP-CHECK",1,0))</f>
         <v/>
       </c>
-      <c r="K11" s="13">
+      <c r="K11" s="14">
         <f>IF(K14="","",IF(K15="STOP-CHECK",1,0)+IF(K16="STOP-CHECK",1,0)+IF(K25="STOP-CHECK",1,0))</f>
         <v/>
       </c>
-      <c r="L11" s="13">
+      <c r="L11" s="14">
         <f>IF(L14="","",IF(L15="STOP-CHECK",1,0)+IF(L16="STOP-CHECK",1,0)+IF(L25="STOP-CHECK",1,0))</f>
         <v/>
       </c>
-      <c r="M11" s="13">
+      <c r="M11" s="14">
         <f>IF(M14="","",IF(M15="STOP-CHECK",1,0)+IF(M16="STOP-CHECK",1,0)+IF(M25="STOP-CHECK",1,0))</f>
         <v/>
       </c>
-      <c r="N11" s="13">
+      <c r="N11" s="14">
         <f>IF(N14="","",IF(N15="STOP-CHECK",1,0)+IF(N16="STOP-CHECK",1,0)+IF(N25="STOP-CHECK",1,0))</f>
         <v/>
       </c>
-      <c r="O11" s="13">
+      <c r="O11" s="14">
         <f>IF(O14="","",IF(O15="STOP-CHECK",1,0)+IF(O16="STOP-CHECK",1,0)+IF(O25="STOP-CHECK",1,0))</f>
         <v/>
       </c>
-      <c r="P11" s="13">
+      <c r="P11" s="14">
         <f>IF(P14="","",IF(P15="STOP-CHECK",1,0)+IF(P16="STOP-CHECK",1,0)+IF(P25="STOP-CHECK",1,0))</f>
         <v/>
       </c>
-      <c r="Q11" s="13">
+      <c r="Q11" s="14">
         <f>IF(Q14="","",IF(Q15="STOP-CHECK",1,0)+IF(Q16="STOP-CHECK",1,0)+IF(Q25="STOP-CHECK",1,0))</f>
         <v/>
       </c>
-      <c r="R11" s="13">
+      <c r="R11" s="14">
         <f>IF(R14="","",IF(R15="STOP-CHECK",1,0)+IF(R16="STOP-CHECK",1,0)+IF(R25="STOP-CHECK",1,0))</f>
         <v/>
       </c>
-      <c r="S11" s="13">
+      <c r="S11" s="14">
         <f>IF(S14="","",IF(S15="STOP-CHECK",1,0)+IF(S16="STOP-CHECK",1,0)+IF(S25="STOP-CHECK",1,0))</f>
         <v/>
       </c>
-      <c r="T11" s="13">
+      <c r="T11" s="14">
         <f>IF(T14="","",IF(T15="STOP-CHECK",1,0)+IF(T16="STOP-CHECK",1,0)+IF(T25="STOP-CHECK",1,0))</f>
         <v/>
       </c>
+      <c r="U11" s="14">
+        <f>IF(U14="","",IF(U15="STOP-CHECK",1,0)+IF(U16="STOP-CHECK",1,0)+IF(U25="STOP-CHECK",1,0))</f>
+        <v/>
+      </c>
     </row>
     <row r="13" ht="21" customHeight="1">
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>A  ·  COMPANY AND PRODUCT</t>
         </is>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="B14" s="14" t="inlineStr">
+      <c r="B14" s="15" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
-      <c r="C14" s="15" t="inlineStr">
+      <c r="C14" s="16" t="inlineStr">
         <is>
           <t>Home Care Home Base integration</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>Pick one line  ·  20 points</t>
-        </is>
-      </c>
-      <c r="E14" s="16" t="n"/>
-      <c r="F14" s="16" t="n"/>
-      <c r="G14" s="16" t="n"/>
-      <c r="H14" s="16" t="n"/>
-      <c r="I14" s="16" t="n"/>
-      <c r="J14" s="16" t="n"/>
-      <c r="K14" s="16" t="n"/>
-      <c r="L14" s="16" t="n"/>
-      <c r="M14" s="16" t="n"/>
-      <c r="N14" s="16" t="n"/>
-      <c r="O14" s="16" t="n"/>
-      <c r="P14" s="16" t="n"/>
-      <c r="Q14" s="16" t="n"/>
-      <c r="R14" s="16" t="n"/>
-      <c r="S14" s="16" t="n"/>
-      <c r="T14" s="16" t="n"/>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>Pick the line that matches their answer</t>
+        </is>
+      </c>
+      <c r="E14" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="F14" s="17" t="n"/>
+      <c r="G14" s="17" t="n"/>
+      <c r="H14" s="17" t="n"/>
+      <c r="I14" s="17" t="n"/>
+      <c r="J14" s="17" t="n"/>
+      <c r="K14" s="17" t="n"/>
+      <c r="L14" s="17" t="n"/>
+      <c r="M14" s="17" t="n"/>
+      <c r="N14" s="17" t="n"/>
+      <c r="O14" s="17" t="n"/>
+      <c r="P14" s="17" t="n"/>
+      <c r="Q14" s="17" t="n"/>
+      <c r="R14" s="17" t="n"/>
+      <c r="S14" s="17" t="n"/>
+      <c r="T14" s="17" t="n"/>
+      <c r="U14" s="17" t="n"/>
     </row>
     <row r="15" ht="19" customHeight="1">
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="18" t="inlineStr">
         <is>
           <t>A2</t>
         </is>
       </c>
-      <c r="C15" s="15" t="inlineStr">
+      <c r="C15" s="16" t="inlineStr">
         <is>
           <t>Customers, scale and references</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>Flag  ·  stop-check if one customer or no references</t>
-        </is>
-      </c>
-      <c r="E15" s="18" t="n"/>
-      <c r="F15" s="18" t="n"/>
-      <c r="G15" s="18" t="n"/>
-      <c r="H15" s="18" t="n"/>
-      <c r="I15" s="18" t="n"/>
-      <c r="J15" s="18" t="n"/>
-      <c r="K15" s="18" t="n"/>
-      <c r="L15" s="18" t="n"/>
-      <c r="M15" s="18" t="n"/>
-      <c r="N15" s="18" t="n"/>
-      <c r="O15" s="18" t="n"/>
-      <c r="P15" s="18" t="n"/>
-      <c r="Q15" s="18" t="n"/>
-      <c r="R15" s="18" t="n"/>
-      <c r="S15" s="18" t="n"/>
-      <c r="T15" s="18" t="n"/>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>Stop-check if one customer, or no references offered</t>
+        </is>
+      </c>
+      <c r="E15" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" s="20" t="n"/>
+      <c r="G15" s="20" t="n"/>
+      <c r="H15" s="20" t="n"/>
+      <c r="I15" s="20" t="n"/>
+      <c r="J15" s="20" t="n"/>
+      <c r="K15" s="20" t="n"/>
+      <c r="L15" s="20" t="n"/>
+      <c r="M15" s="20" t="n"/>
+      <c r="N15" s="20" t="n"/>
+      <c r="O15" s="20" t="n"/>
+      <c r="P15" s="20" t="n"/>
+      <c r="Q15" s="20" t="n"/>
+      <c r="R15" s="20" t="n"/>
+      <c r="S15" s="20" t="n"/>
+      <c r="T15" s="20" t="n"/>
+      <c r="U15" s="20" t="n"/>
     </row>
     <row r="16" ht="19" customHeight="1">
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="18" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="C16" s="15" t="inlineStr">
+      <c r="C16" s="16" t="inlineStr">
         <is>
           <t>Measured impact</t>
         </is>
       </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>Flag  ·  watch if no baseline or period</t>
-        </is>
-      </c>
-      <c r="E16" s="18" t="n"/>
-      <c r="F16" s="18" t="n"/>
-      <c r="G16" s="18" t="n"/>
-      <c r="H16" s="18" t="n"/>
-      <c r="I16" s="18" t="n"/>
-      <c r="J16" s="18" t="n"/>
-      <c r="K16" s="18" t="n"/>
-      <c r="L16" s="18" t="n"/>
-      <c r="M16" s="18" t="n"/>
-      <c r="N16" s="18" t="n"/>
-      <c r="O16" s="18" t="n"/>
-      <c r="P16" s="18" t="n"/>
-      <c r="Q16" s="18" t="n"/>
-      <c r="R16" s="18" t="n"/>
-      <c r="S16" s="18" t="n"/>
-      <c r="T16" s="18" t="n"/>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>Watch if claimed with no baseline or period</t>
+        </is>
+      </c>
+      <c r="E16" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="20" t="n"/>
+      <c r="G16" s="20" t="n"/>
+      <c r="H16" s="20" t="n"/>
+      <c r="I16" s="20" t="n"/>
+      <c r="J16" s="20" t="n"/>
+      <c r="K16" s="20" t="n"/>
+      <c r="L16" s="20" t="n"/>
+      <c r="M16" s="20" t="n"/>
+      <c r="N16" s="20" t="n"/>
+      <c r="O16" s="20" t="n"/>
+      <c r="P16" s="20" t="n"/>
+      <c r="Q16" s="20" t="n"/>
+      <c r="R16" s="20" t="n"/>
+      <c r="S16" s="20" t="n"/>
+      <c r="T16" s="20" t="n"/>
+      <c r="U16" s="20" t="n"/>
     </row>
     <row r="18" ht="21" customHeight="1">
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>B  ·  COVERAGE SELF-ASSESSMENT   —   how much of our scope they cover</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="19" customHeight="1">
-      <c r="B19" s="19" t="inlineStr">
+    <row r="19" ht="30" customHeight="1">
+      <c r="B19" s="21" t="inlineStr">
         <is>
           <t>Section B</t>
         </is>
       </c>
-      <c r="C19" s="15" t="inlineStr">
+      <c r="C19" s="16" t="inlineStr">
         <is>
           <t>Capacity</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>Workforce supply · availability &amp; reach · the capacity math  ·  0–5  ·  12 points</t>
-        </is>
-      </c>
-      <c r="E19" s="20" t="n"/>
-      <c r="F19" s="20" t="n"/>
-      <c r="G19" s="20" t="n"/>
-      <c r="H19" s="20" t="n"/>
-      <c r="I19" s="20" t="n"/>
-      <c r="J19" s="20" t="n"/>
-      <c r="K19" s="20" t="n"/>
-      <c r="L19" s="20" t="n"/>
-      <c r="M19" s="20" t="n"/>
-      <c r="N19" s="20" t="n"/>
-      <c r="O19" s="20" t="n"/>
-      <c r="P19" s="20" t="n"/>
-      <c r="Q19" s="20" t="n"/>
-      <c r="R19" s="20" t="n"/>
-      <c r="S19" s="20" t="n"/>
-      <c r="T19" s="20" t="n"/>
-    </row>
-    <row r="20" ht="19" customHeight="1">
-      <c r="B20" s="21" t="inlineStr">
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>Workforce supply · availability &amp; reach · the capacity math</t>
+        </is>
+      </c>
+      <c r="E19" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="F19" s="22" t="n"/>
+      <c r="G19" s="22" t="n"/>
+      <c r="H19" s="22" t="n"/>
+      <c r="I19" s="22" t="n"/>
+      <c r="J19" s="22" t="n"/>
+      <c r="K19" s="22" t="n"/>
+      <c r="L19" s="22" t="n"/>
+      <c r="M19" s="22" t="n"/>
+      <c r="N19" s="22" t="n"/>
+      <c r="O19" s="22" t="n"/>
+      <c r="P19" s="22" t="n"/>
+      <c r="Q19" s="22" t="n"/>
+      <c r="R19" s="22" t="n"/>
+      <c r="S19" s="22" t="n"/>
+      <c r="T19" s="22" t="n"/>
+      <c r="U19" s="22" t="n"/>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>Section B</t>
         </is>
       </c>
-      <c r="C20" s="15" t="inlineStr">
+      <c r="C20" s="16" t="inlineStr">
         <is>
           <t>Scheduling</t>
         </is>
       </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>Demand · matching · routing &amp; the week · exceptions  ·  0–5  ·  12 points</t>
-        </is>
-      </c>
-      <c r="E20" s="20" t="n"/>
-      <c r="F20" s="20" t="n"/>
-      <c r="G20" s="20" t="n"/>
-      <c r="H20" s="20" t="n"/>
-      <c r="I20" s="20" t="n"/>
-      <c r="J20" s="20" t="n"/>
-      <c r="K20" s="20" t="n"/>
-      <c r="L20" s="20" t="n"/>
-      <c r="M20" s="20" t="n"/>
-      <c r="N20" s="20" t="n"/>
-      <c r="O20" s="20" t="n"/>
-      <c r="P20" s="20" t="n"/>
-      <c r="Q20" s="20" t="n"/>
-      <c r="R20" s="20" t="n"/>
-      <c r="S20" s="20" t="n"/>
-      <c r="T20" s="20" t="n"/>
-    </row>
-    <row r="21" ht="19" customHeight="1">
-      <c r="B21" s="22" t="inlineStr">
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>Demand · matching · routing &amp; the week · exceptions</t>
+        </is>
+      </c>
+      <c r="E20" s="23" t="n">
+        <v>12</v>
+      </c>
+      <c r="F20" s="22" t="n"/>
+      <c r="G20" s="22" t="n"/>
+      <c r="H20" s="22" t="n"/>
+      <c r="I20" s="22" t="n"/>
+      <c r="J20" s="22" t="n"/>
+      <c r="K20" s="22" t="n"/>
+      <c r="L20" s="22" t="n"/>
+      <c r="M20" s="22" t="n"/>
+      <c r="N20" s="22" t="n"/>
+      <c r="O20" s="22" t="n"/>
+      <c r="P20" s="22" t="n"/>
+      <c r="Q20" s="22" t="n"/>
+      <c r="R20" s="22" t="n"/>
+      <c r="S20" s="22" t="n"/>
+      <c r="T20" s="22" t="n"/>
+      <c r="U20" s="22" t="n"/>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="B21" s="24" t="inlineStr">
         <is>
           <t>Section B</t>
         </is>
       </c>
-      <c r="C21" s="15" t="inlineStr">
+      <c r="C21" s="16" t="inlineStr">
         <is>
           <t>Engagement</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>Before the visit · when plans change · incentives · care team  ·  0–5  ·  12 points</t>
-        </is>
-      </c>
-      <c r="E21" s="20" t="n"/>
-      <c r="F21" s="20" t="n"/>
-      <c r="G21" s="20" t="n"/>
-      <c r="H21" s="20" t="n"/>
-      <c r="I21" s="20" t="n"/>
-      <c r="J21" s="20" t="n"/>
-      <c r="K21" s="20" t="n"/>
-      <c r="L21" s="20" t="n"/>
-      <c r="M21" s="20" t="n"/>
-      <c r="N21" s="20" t="n"/>
-      <c r="O21" s="20" t="n"/>
-      <c r="P21" s="20" t="n"/>
-      <c r="Q21" s="20" t="n"/>
-      <c r="R21" s="20" t="n"/>
-      <c r="S21" s="20" t="n"/>
-      <c r="T21" s="20" t="n"/>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>Before the visit · when plans change · incentives · care team</t>
+        </is>
+      </c>
+      <c r="E21" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="F21" s="22" t="n"/>
+      <c r="G21" s="22" t="n"/>
+      <c r="H21" s="22" t="n"/>
+      <c r="I21" s="22" t="n"/>
+      <c r="J21" s="22" t="n"/>
+      <c r="K21" s="22" t="n"/>
+      <c r="L21" s="22" t="n"/>
+      <c r="M21" s="22" t="n"/>
+      <c r="N21" s="22" t="n"/>
+      <c r="O21" s="22" t="n"/>
+      <c r="P21" s="22" t="n"/>
+      <c r="Q21" s="22" t="n"/>
+      <c r="R21" s="22" t="n"/>
+      <c r="S21" s="22" t="n"/>
+      <c r="T21" s="22" t="n"/>
+      <c r="U21" s="22" t="n"/>
     </row>
     <row r="23" ht="21" customHeight="1">
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>C  ·  HOW YOUR PRODUCT WORKS</t>
         </is>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1">
-      <c r="B24" s="23" t="inlineStr">
+      <c r="B24" s="25" t="inlineStr">
         <is>
           <t>Section C</t>
         </is>
       </c>
-      <c r="C24" s="15" t="inlineStr">
+      <c r="C24" s="16" t="inlineStr">
         <is>
           <t>Sophistication</t>
         </is>
       </c>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t>How much of the work it does  ·  0–4  ·  20 points</t>
-        </is>
-      </c>
-      <c r="E24" s="20" t="n"/>
-      <c r="F24" s="20" t="n"/>
-      <c r="G24" s="20" t="n"/>
-      <c r="H24" s="20" t="n"/>
-      <c r="I24" s="20" t="n"/>
-      <c r="J24" s="20" t="n"/>
-      <c r="K24" s="20" t="n"/>
-      <c r="L24" s="20" t="n"/>
-      <c r="M24" s="20" t="n"/>
-      <c r="N24" s="20" t="n"/>
-      <c r="O24" s="20" t="n"/>
-      <c r="P24" s="20" t="n"/>
-      <c r="Q24" s="20" t="n"/>
-      <c r="R24" s="20" t="n"/>
-      <c r="S24" s="20" t="n"/>
-      <c r="T24" s="20" t="n"/>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>How much of the work the product does</t>
+        </is>
+      </c>
+      <c r="E24" s="25" t="n">
+        <v>20</v>
+      </c>
+      <c r="F24" s="22" t="n"/>
+      <c r="G24" s="22" t="n"/>
+      <c r="H24" s="22" t="n"/>
+      <c r="I24" s="22" t="n"/>
+      <c r="J24" s="22" t="n"/>
+      <c r="K24" s="22" t="n"/>
+      <c r="L24" s="22" t="n"/>
+      <c r="M24" s="22" t="n"/>
+      <c r="N24" s="22" t="n"/>
+      <c r="O24" s="22" t="n"/>
+      <c r="P24" s="22" t="n"/>
+      <c r="Q24" s="22" t="n"/>
+      <c r="R24" s="22" t="n"/>
+      <c r="S24" s="22" t="n"/>
+      <c r="T24" s="22" t="n"/>
+      <c r="U24" s="22" t="n"/>
     </row>
     <row r="25" ht="19" customHeight="1">
-      <c r="B25" s="17" t="inlineStr">
+      <c r="B25" s="18" t="inlineStr">
         <is>
           <t>C6</t>
         </is>
       </c>
-      <c r="C25" s="15" t="inlineStr">
+      <c r="C25" s="16" t="inlineStr">
         <is>
           <t>When your product is down</t>
         </is>
       </c>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>Flag  ·  stop-check if no uptime figure or commitment</t>
-        </is>
-      </c>
-      <c r="E25" s="18" t="n"/>
-      <c r="F25" s="18" t="n"/>
-      <c r="G25" s="18" t="n"/>
-      <c r="H25" s="18" t="n"/>
-      <c r="I25" s="18" t="n"/>
-      <c r="J25" s="18" t="n"/>
-      <c r="K25" s="18" t="n"/>
-      <c r="L25" s="18" t="n"/>
-      <c r="M25" s="18" t="n"/>
-      <c r="N25" s="18" t="n"/>
-      <c r="O25" s="18" t="n"/>
-      <c r="P25" s="18" t="n"/>
-      <c r="Q25" s="18" t="n"/>
-      <c r="R25" s="18" t="n"/>
-      <c r="S25" s="18" t="n"/>
-      <c r="T25" s="18" t="n"/>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>Stop-check if no uptime figure or contractual commitment</t>
+        </is>
+      </c>
+      <c r="E25" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F25" s="20" t="n"/>
+      <c r="G25" s="20" t="n"/>
+      <c r="H25" s="20" t="n"/>
+      <c r="I25" s="20" t="n"/>
+      <c r="J25" s="20" t="n"/>
+      <c r="K25" s="20" t="n"/>
+      <c r="L25" s="20" t="n"/>
+      <c r="M25" s="20" t="n"/>
+      <c r="N25" s="20" t="n"/>
+      <c r="O25" s="20" t="n"/>
+      <c r="P25" s="20" t="n"/>
+      <c r="Q25" s="20" t="n"/>
+      <c r="R25" s="20" t="n"/>
+      <c r="S25" s="20" t="n"/>
+      <c r="T25" s="20" t="n"/>
+      <c r="U25" s="20" t="n"/>
     </row>
     <row r="27" ht="21" customHeight="1">
-      <c r="B27" s="6" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>D  ·  THE CLINICIAN'S PLACE IN THE MODEL</t>
         </is>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1">
-      <c r="B28" s="24" t="inlineStr">
+      <c r="B28" s="26" t="inlineStr">
         <is>
           <t>D1–D3</t>
         </is>
       </c>
-      <c r="C28" s="15" t="inlineStr">
+      <c r="C28" s="16" t="inlineStr">
         <is>
           <t>Clinician fit</t>
         </is>
       </c>
-      <c r="D28" s="8" t="inlineStr">
-        <is>
-          <t>Our read of fit  ·  0–4  ·  12 points</t>
-        </is>
-      </c>
-      <c r="E28" s="20" t="n"/>
-      <c r="F28" s="20" t="n"/>
-      <c r="G28" s="20" t="n"/>
-      <c r="H28" s="20" t="n"/>
-      <c r="I28" s="20" t="n"/>
-      <c r="J28" s="20" t="n"/>
-      <c r="K28" s="20" t="n"/>
-      <c r="L28" s="20" t="n"/>
-      <c r="M28" s="20" t="n"/>
-      <c r="N28" s="20" t="n"/>
-      <c r="O28" s="20" t="n"/>
-      <c r="P28" s="20" t="n"/>
-      <c r="Q28" s="20" t="n"/>
-      <c r="R28" s="20" t="n"/>
-      <c r="S28" s="20" t="n"/>
-      <c r="T28" s="20" t="n"/>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>Our own read of fit — no checklist, on purpose</t>
+        </is>
+      </c>
+      <c r="E28" s="26" t="n">
+        <v>12</v>
+      </c>
+      <c r="F28" s="22" t="n"/>
+      <c r="G28" s="22" t="n"/>
+      <c r="H28" s="22" t="n"/>
+      <c r="I28" s="22" t="n"/>
+      <c r="J28" s="22" t="n"/>
+      <c r="K28" s="22" t="n"/>
+      <c r="L28" s="22" t="n"/>
+      <c r="M28" s="22" t="n"/>
+      <c r="N28" s="22" t="n"/>
+      <c r="O28" s="22" t="n"/>
+      <c r="P28" s="22" t="n"/>
+      <c r="Q28" s="22" t="n"/>
+      <c r="R28" s="22" t="n"/>
+      <c r="S28" s="22" t="n"/>
+      <c r="T28" s="22" t="n"/>
+      <c r="U28" s="22" t="n"/>
     </row>
     <row r="30" ht="21" customHeight="1">
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>E  ·  FIT AND PARTNERSHIP</t>
         </is>
       </c>
     </row>
     <row r="31" ht="24" customHeight="1">
-      <c r="B31" s="24" t="inlineStr">
+      <c r="B31" s="26" t="inlineStr">
         <is>
           <t>E1–E4</t>
         </is>
       </c>
-      <c r="C31" s="15" t="inlineStr">
+      <c r="C31" s="16" t="inlineStr">
         <is>
           <t>Partnership</t>
         </is>
       </c>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t>Willing to build it with us, and open to a stake  ·  0–4  ·  12 points</t>
-        </is>
-      </c>
-      <c r="E31" s="20" t="n"/>
-      <c r="F31" s="20" t="n"/>
-      <c r="G31" s="20" t="n"/>
-      <c r="H31" s="20" t="n"/>
-      <c r="I31" s="20" t="n"/>
-      <c r="J31" s="20" t="n"/>
-      <c r="K31" s="20" t="n"/>
-      <c r="L31" s="20" t="n"/>
-      <c r="M31" s="20" t="n"/>
-      <c r="N31" s="20" t="n"/>
-      <c r="O31" s="20" t="n"/>
-      <c r="P31" s="20" t="n"/>
-      <c r="Q31" s="20" t="n"/>
-      <c r="R31" s="20" t="n"/>
-      <c r="S31" s="20" t="n"/>
-      <c r="T31" s="20" t="n"/>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>Willing to build it with us, and open to a stake</t>
+        </is>
+      </c>
+      <c r="E31" s="26" t="n">
+        <v>12</v>
+      </c>
+      <c r="F31" s="22" t="n"/>
+      <c r="G31" s="22" t="n"/>
+      <c r="H31" s="22" t="n"/>
+      <c r="I31" s="22" t="n"/>
+      <c r="J31" s="22" t="n"/>
+      <c r="K31" s="22" t="n"/>
+      <c r="L31" s="22" t="n"/>
+      <c r="M31" s="22" t="n"/>
+      <c r="N31" s="22" t="n"/>
+      <c r="O31" s="22" t="n"/>
+      <c r="P31" s="22" t="n"/>
+      <c r="Q31" s="22" t="n"/>
+      <c r="R31" s="22" t="n"/>
+      <c r="S31" s="22" t="n"/>
+      <c r="T31" s="22" t="n"/>
+      <c r="U31" s="22" t="n"/>
     </row>
     <row r="33" ht="21" customHeight="1">
-      <c r="B33" s="25" t="inlineStr">
+      <c r="B33" s="27" t="inlineStr">
         <is>
           <t>NOTES   —   one line each.  This is what we go and ask.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="62" customHeight="1">
-      <c r="B34" s="26" t="inlineStr"/>
-      <c r="C34" s="27" t="inlineStr">
+      <c r="B34" s="28" t="inlineStr"/>
+      <c r="C34" s="29" t="inlineStr">
         <is>
           <t>What stands out</t>
         </is>
       </c>
-      <c r="D34" s="28" t="inlineStr">
+      <c r="D34" s="30" t="inlineStr">
         <is>
           <t>against the field, or against our own thinking</t>
         </is>
       </c>
-      <c r="E34" s="29" t="n"/>
-      <c r="F34" s="29" t="n"/>
-      <c r="G34" s="29" t="n"/>
-      <c r="H34" s="29" t="n"/>
-      <c r="I34" s="29" t="n"/>
-      <c r="J34" s="29" t="n"/>
-      <c r="K34" s="29" t="n"/>
-      <c r="L34" s="29" t="n"/>
-      <c r="M34" s="29" t="n"/>
-      <c r="N34" s="29" t="n"/>
-      <c r="O34" s="29" t="n"/>
-      <c r="P34" s="29" t="n"/>
-      <c r="Q34" s="29" t="n"/>
-      <c r="R34" s="29" t="n"/>
-      <c r="S34" s="29" t="n"/>
-      <c r="T34" s="29" t="n"/>
+      <c r="E34" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F34" s="31" t="n"/>
+      <c r="G34" s="31" t="n"/>
+      <c r="H34" s="31" t="n"/>
+      <c r="I34" s="31" t="n"/>
+      <c r="J34" s="31" t="n"/>
+      <c r="K34" s="31" t="n"/>
+      <c r="L34" s="31" t="n"/>
+      <c r="M34" s="31" t="n"/>
+      <c r="N34" s="31" t="n"/>
+      <c r="O34" s="31" t="n"/>
+      <c r="P34" s="31" t="n"/>
+      <c r="Q34" s="31" t="n"/>
+      <c r="R34" s="31" t="n"/>
+      <c r="S34" s="31" t="n"/>
+      <c r="T34" s="31" t="n"/>
+      <c r="U34" s="31" t="n"/>
     </row>
     <row r="35" ht="62" customHeight="1">
-      <c r="B35" s="26" t="inlineStr"/>
-      <c r="C35" s="27" t="inlineStr">
+      <c r="B35" s="28" t="inlineStr"/>
+      <c r="C35" s="29" t="inlineStr">
         <is>
           <t>What worries me</t>
         </is>
       </c>
-      <c r="D35" s="28" t="inlineStr">
+      <c r="D35" s="30" t="inlineStr">
         <is>
           <t>including anything flagged above</t>
         </is>
       </c>
-      <c r="E35" s="29" t="n"/>
-      <c r="F35" s="29" t="n"/>
-      <c r="G35" s="29" t="n"/>
-      <c r="H35" s="29" t="n"/>
-      <c r="I35" s="29" t="n"/>
-      <c r="J35" s="29" t="n"/>
-      <c r="K35" s="29" t="n"/>
-      <c r="L35" s="29" t="n"/>
-      <c r="M35" s="29" t="n"/>
-      <c r="N35" s="29" t="n"/>
-      <c r="O35" s="29" t="n"/>
-      <c r="P35" s="29" t="n"/>
-      <c r="Q35" s="29" t="n"/>
-      <c r="R35" s="29" t="n"/>
-      <c r="S35" s="29" t="n"/>
-      <c r="T35" s="29" t="n"/>
+      <c r="E35" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F35" s="31" t="n"/>
+      <c r="G35" s="31" t="n"/>
+      <c r="H35" s="31" t="n"/>
+      <c r="I35" s="31" t="n"/>
+      <c r="J35" s="31" t="n"/>
+      <c r="K35" s="31" t="n"/>
+      <c r="L35" s="31" t="n"/>
+      <c r="M35" s="31" t="n"/>
+      <c r="N35" s="31" t="n"/>
+      <c r="O35" s="31" t="n"/>
+      <c r="P35" s="31" t="n"/>
+      <c r="Q35" s="31" t="n"/>
+      <c r="R35" s="31" t="n"/>
+      <c r="S35" s="31" t="n"/>
+      <c r="T35" s="31" t="n"/>
+      <c r="U35" s="31" t="n"/>
     </row>
     <row r="36" ht="62" customHeight="1">
-      <c r="B36" s="26" t="inlineStr"/>
-      <c r="C36" s="27" t="inlineStr">
+      <c r="B36" s="28" t="inlineStr"/>
+      <c r="C36" s="29" t="inlineStr">
         <is>
           <t>What to go and ask</t>
         </is>
       </c>
-      <c r="D36" s="28" t="inlineStr">
+      <c r="D36" s="30" t="inlineStr">
         <is>
           <t>the demo agenda</t>
         </is>
       </c>
-      <c r="E36" s="29" t="n"/>
-      <c r="F36" s="29" t="n"/>
-      <c r="G36" s="29" t="n"/>
-      <c r="H36" s="29" t="n"/>
-      <c r="I36" s="29" t="n"/>
-      <c r="J36" s="29" t="n"/>
-      <c r="K36" s="29" t="n"/>
-      <c r="L36" s="29" t="n"/>
-      <c r="M36" s="29" t="n"/>
-      <c r="N36" s="29" t="n"/>
-      <c r="O36" s="29" t="n"/>
-      <c r="P36" s="29" t="n"/>
-      <c r="Q36" s="29" t="n"/>
-      <c r="R36" s="29" t="n"/>
-      <c r="S36" s="29" t="n"/>
-      <c r="T36" s="29" t="n"/>
+      <c r="E36" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F36" s="31" t="n"/>
+      <c r="G36" s="31" t="n"/>
+      <c r="H36" s="31" t="n"/>
+      <c r="I36" s="31" t="n"/>
+      <c r="J36" s="31" t="n"/>
+      <c r="K36" s="31" t="n"/>
+      <c r="L36" s="31" t="n"/>
+      <c r="M36" s="31" t="n"/>
+      <c r="N36" s="31" t="n"/>
+      <c r="O36" s="31" t="n"/>
+      <c r="P36" s="31" t="n"/>
+      <c r="Q36" s="31" t="n"/>
+      <c r="R36" s="31" t="n"/>
+      <c r="S36" s="31" t="n"/>
+      <c r="T36" s="31" t="n"/>
+      <c r="U36" s="31" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="B23:T23"/>
-    <mergeCell ref="B8:T8"/>
-    <mergeCell ref="B18:T18"/>
-    <mergeCell ref="B13:T13"/>
-    <mergeCell ref="B27:T27"/>
-    <mergeCell ref="B4:T4"/>
-    <mergeCell ref="B30:T30"/>
-    <mergeCell ref="B33:T33"/>
+    <mergeCell ref="B23:U23"/>
+    <mergeCell ref="B27:U27"/>
+    <mergeCell ref="B8:U8"/>
+    <mergeCell ref="B4:U4"/>
+    <mergeCell ref="B18:U18"/>
+    <mergeCell ref="B13:U13"/>
+    <mergeCell ref="B30:U30"/>
+    <mergeCell ref="B33:U33"/>
   </mergeCells>
-  <conditionalFormatting sqref="E9:T9">
+  <conditionalFormatting sqref="F9:U9">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="40"/>
@@ -2677,32 +2808,32 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E10:T10">
+  <conditionalFormatting sqref="F10:U10">
     <cfRule type="expression" priority="2" dxfId="0">
-      <formula>ISNUMBER(SEARCH("Conditional",E10))</formula>
+      <formula>ISNUMBER(SEARCH("Conditional",F10))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E11:T11">
+  <conditionalFormatting sqref="F11:U11">
     <cfRule type="expression" priority="3" dxfId="0">
-      <formula>E11&gt;0</formula>
+      <formula>F11&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E15:T15">
+  <conditionalFormatting sqref="F15:U15">
     <cfRule type="expression" priority="4" dxfId="1">
-      <formula>E15="STOP-CHECK"</formula>
+      <formula>F15="STOP-CHECK"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E16:T16">
+  <conditionalFormatting sqref="F16:U16">
     <cfRule type="expression" priority="5" dxfId="1">
-      <formula>E16="STOP-CHECK"</formula>
+      <formula>F16="STOP-CHECK"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E25:T25">
+  <conditionalFormatting sqref="F25:U25">
     <cfRule type="expression" priority="6" dxfId="1">
-      <formula>E25="STOP-CHECK"</formula>
+      <formula>F25="STOP-CHECK"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E19:T19">
+  <conditionalFormatting sqref="F19:U19">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -2712,7 +2843,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E20:T20">
+  <conditionalFormatting sqref="F20:U20">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -2722,7 +2853,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E21:T21">
+  <conditionalFormatting sqref="F21:U21">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -2733,22 +2864,22 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="6">
-    <dataValidation sqref="E14:T14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="A1 — Home Care Home Base" prompt="Pick one line. Ambiguous? Take the lower one and say so in Notes." type="list">
-      <formula1>=Lists!$B$2:$B$7</formula1>
+    <dataValidation sqref="F14:U14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="A1 — Home Care Home Base" prompt="Pick one line. Ambiguous? Take the lower one and say so in Notes." type="list">
+      <formula1>=HCHB_List</formula1>
     </dataValidation>
-    <dataValidation sqref="E19:T19 E20:T20 E21:T21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Scope, 0–5" prompt="How much of this arena they cover. Most of it is the ceiling — our spec is original, so nobody covers all of it." type="list">
-      <formula1>=Lists!$E$2:$E$7</formula1>
+    <dataValidation sqref="F19:U19 F20:U20 F21:U21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Scope, 0–5" prompt="How much of this arena they cover. Most of it is the ceiling — our spec is original, so nobody covers all of it." type="list">
+      <formula1>=Scope_List</formula1>
     </dataValidation>
-    <dataValidation sqref="E24:T24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Sophistication, 0–4" prompt="1 shows it · 2 checks it · 3 recommends it · 4 runs it. Score what the product does, not how much they wrote about it." type="list">
-      <formula1>=Lists!$G$2:$G$6</formula1>
+    <dataValidation sqref="F24:U24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Sophistication, 0–4" prompt="1 shows it · 2 checks it · 3 recommends it · 4 runs it. Score what the product does, not how much they wrote about it." type="list">
+      <formula1>=Soph_List</formula1>
     </dataValidation>
-    <dataValidation sqref="E28:T28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Clinician fit, 0–4" prompt="Read D1 to D3 and give it your own read of fit. There is no checklist here on purpose." type="list">
-      <formula1>=Lists!$I$2:$I$6</formula1>
+    <dataValidation sqref="F28:U28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Clinician fit, 0–4" prompt="Read D1 to D3 and give it your own read of fit. There is no checklist here on purpose." type="list">
+      <formula1>=Clin_List</formula1>
     </dataValidation>
-    <dataValidation sqref="E31:T31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Partnership, 0–4" prompt="Are they able and willing to build this with us, and open to us holding a stake in what a wider market might buy? A discount is a discount." type="list">
-      <formula1>=Lists!$K$2:$K$6</formula1>
+    <dataValidation sqref="F31:U31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Partnership, 0–4" prompt="Are they able and willing to build this with us, and open to us holding a stake in what a wider market might buy? A discount is a discount." type="list">
+      <formula1>=Part_List</formula1>
     </dataValidation>
-    <dataValidation sqref="E15:T15 E16:T16 E25:T25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Flag" prompt="A stop-check is resolved before advancing, not traded against points." type="list">
+    <dataValidation sqref="F15:U15 F16:U16 F25:U25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Flag" prompt="A stop-check is resolved before advancing, not traded against points." type="list">
       <formula1>"OK,Watch,STOP-CHECK"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2780,14 +2911,14 @@
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="B3" s="30" t="inlineStr">
+      <c r="B3" s="32" t="inlineStr">
         <is>
           <t>Vendor Scorecard — Fast</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="31" t="inlineStr">
+      <c r="B4" s="33" t="inlineStr">
         <is>
           <t>The questionnaire is the rubric. Read the return top to bottom and fill the sheet top to bottom. Seven marks a vendor.</t>
         </is>
@@ -2795,21 +2926,21 @@
     </row>
     <row r="6" ht="10" customHeight="1"/>
     <row r="7" ht="22" customHeight="1">
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>HOW IT WORKS</t>
         </is>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
-      <c r="B8" s="32" t="inlineStr">
+      <c r="B8" s="34" t="inlineStr">
         <is>
           <t>Every one of the 17 questions on the questionnaire has a row on the Scorecard tab, in the order it appears on the form. Seven rows take a mark. The rest raise a flag or a note — and they say so, so nothing looks forgotten. What isn't scored becomes what we go and ask at the demo.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1">
-      <c r="B9" s="32" t="inlineStr">
+      <c r="B9" s="34" t="inlineStr">
         <is>
           <t>Scored on the same 100 points and the same bands as the full scorecard, so the two are directly comparable. This one is coarser, not different: it gives one mark where the full sheet gives several, so the two can disagree on a close call. That is the trade for speed.</t>
         </is>
@@ -2817,156 +2948,156 @@
     </row>
     <row r="10" ht="10" customHeight="1"/>
     <row r="11" ht="22" customHeight="1">
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>THE SEVEN MARKS</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="33" t="inlineStr">
+      <c r="B12" s="35" t="inlineStr">
         <is>
           <t>Question</t>
         </is>
       </c>
-      <c r="C12" s="33" t="inlineStr">
+      <c r="C12" s="35" t="inlineStr">
         <is>
           <t>Mark</t>
         </is>
       </c>
-      <c r="D12" s="33" t="inlineStr">
+      <c r="D12" s="35" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
       </c>
     </row>
     <row r="13" ht="21" customHeight="1">
-      <c r="B13" s="34" t="inlineStr">
+      <c r="B13" s="36" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
-      <c r="C13" s="32" t="inlineStr">
+      <c r="C13" s="34" t="inlineStr">
         <is>
           <t>Home Care Home Base integration</t>
         </is>
       </c>
-      <c r="D13" s="35" t="inlineStr">
+      <c r="D13" s="37" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
     </row>
     <row r="14" ht="21" customHeight="1">
-      <c r="B14" s="34" t="inlineStr">
+      <c r="B14" s="36" t="inlineStr">
         <is>
           <t>Section B</t>
         </is>
       </c>
-      <c r="C14" s="32" t="inlineStr">
+      <c r="C14" s="34" t="inlineStr">
         <is>
           <t>Capacity — how much of it they cover</t>
         </is>
       </c>
-      <c r="D14" s="35" t="inlineStr">
+      <c r="D14" s="37" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
     </row>
     <row r="15" ht="21" customHeight="1">
-      <c r="B15" s="34" t="inlineStr">
+      <c r="B15" s="36" t="inlineStr">
         <is>
           <t>Section B</t>
         </is>
       </c>
-      <c r="C15" s="32" t="inlineStr">
+      <c r="C15" s="34" t="inlineStr">
         <is>
           <t>Scheduling — how much of it they cover</t>
         </is>
       </c>
-      <c r="D15" s="35" t="inlineStr">
+      <c r="D15" s="37" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
     </row>
     <row r="16" ht="21" customHeight="1">
-      <c r="B16" s="34" t="inlineStr">
+      <c r="B16" s="36" t="inlineStr">
         <is>
           <t>Section B</t>
         </is>
       </c>
-      <c r="C16" s="32" t="inlineStr">
+      <c r="C16" s="34" t="inlineStr">
         <is>
           <t>Engagement — how much of it they cover</t>
         </is>
       </c>
-      <c r="D16" s="35" t="inlineStr">
+      <c r="D16" s="37" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
     </row>
     <row r="17" ht="21" customHeight="1">
-      <c r="B17" s="34" t="inlineStr">
+      <c r="B17" s="36" t="inlineStr">
         <is>
           <t>Section C</t>
         </is>
       </c>
-      <c r="C17" s="32" t="inlineStr">
+      <c r="C17" s="34" t="inlineStr">
         <is>
           <t>Sophistication — how much of the work the product does</t>
         </is>
       </c>
-      <c r="D17" s="35" t="inlineStr">
+      <c r="D17" s="37" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
     </row>
     <row r="18" ht="21" customHeight="1">
-      <c r="B18" s="34" t="inlineStr">
+      <c r="B18" s="36" t="inlineStr">
         <is>
           <t>D1–D3</t>
         </is>
       </c>
-      <c r="C18" s="32" t="inlineStr">
+      <c r="C18" s="34" t="inlineStr">
         <is>
           <t>Clinician fit</t>
         </is>
       </c>
-      <c r="D18" s="35" t="inlineStr">
+      <c r="D18" s="37" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
     </row>
     <row r="19" ht="21" customHeight="1">
-      <c r="B19" s="34" t="inlineStr">
+      <c r="B19" s="36" t="inlineStr">
         <is>
           <t>E1–E4</t>
         </is>
       </c>
-      <c r="C19" s="32" t="inlineStr">
+      <c r="C19" s="34" t="inlineStr">
         <is>
           <t>Partnership</t>
         </is>
       </c>
-      <c r="D19" s="35" t="inlineStr">
+      <c r="D19" s="37" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
     </row>
     <row r="20" ht="21" customHeight="1">
-      <c r="B20" s="34" t="inlineStr"/>
-      <c r="C20" s="36" t="inlineStr">
+      <c r="B20" s="36" t="inlineStr"/>
+      <c r="C20" s="38" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="D20" s="35" t="inlineStr">
+      <c r="D20" s="37" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -2974,199 +3105,199 @@
     </row>
     <row r="21" ht="10" customHeight="1"/>
     <row r="22" ht="22" customHeight="1">
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>A1  ·  HOME CARE HOME BASE   —   pick one line</t>
         </is>
       </c>
     </row>
     <row r="23" ht="28" customHeight="1">
-      <c r="B23" s="32" t="inlineStr">
+      <c r="B23" s="34" t="inlineStr">
         <is>
           <t>Three of the six rungs are live integrations, because live through a partner is still live. Anything not yet live shows as Conditional on the score, whatever the total.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="21" customHeight="1">
-      <c r="B24" s="34" t="inlineStr">
+      <c r="B24" s="36" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="C24" s="32" t="inlineStr">
+      <c r="C24" s="34" t="inlineStr">
         <is>
           <t>Live — established customer base</t>
         </is>
       </c>
-      <c r="D24" s="35" t="inlineStr"/>
+      <c r="D24" s="37" t="inlineStr"/>
     </row>
     <row r="25" ht="21" customHeight="1">
-      <c r="B25" s="34" t="inlineStr">
+      <c r="B25" s="36" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="32" t="inlineStr">
+      <c r="C25" s="34" t="inlineStr">
         <is>
           <t>Live — small customer base</t>
         </is>
       </c>
-      <c r="D25" s="35" t="inlineStr"/>
+      <c r="D25" s="37" t="inlineStr"/>
     </row>
     <row r="26" ht="21" customHeight="1">
-      <c r="B26" s="34" t="inlineStr">
+      <c r="B26" s="36" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="C26" s="32" t="inlineStr">
+      <c r="C26" s="34" t="inlineStr">
         <is>
           <t>Live — through a partner</t>
         </is>
       </c>
-      <c r="D26" s="35" t="inlineStr"/>
+      <c r="D26" s="37" t="inlineStr"/>
     </row>
     <row r="27" ht="21" customHeight="1">
-      <c r="B27" s="34" t="inlineStr">
+      <c r="B27" s="36" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="C27" s="32" t="inlineStr">
+      <c r="C27" s="34" t="inlineStr">
         <is>
           <t>In development — with a date</t>
         </is>
       </c>
-      <c r="D27" s="35" t="inlineStr"/>
+      <c r="D27" s="37" t="inlineStr"/>
     </row>
     <row r="28" ht="21" customHeight="1">
-      <c r="B28" s="34" t="inlineStr">
+      <c r="B28" s="36" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C28" s="32" t="inlineStr">
+      <c r="C28" s="34" t="inlineStr">
         <is>
           <t>On the roadmap — no date</t>
         </is>
       </c>
-      <c r="D28" s="35" t="inlineStr"/>
+      <c r="D28" s="37" t="inlineStr"/>
     </row>
     <row r="29" ht="21" customHeight="1">
-      <c r="B29" s="34" t="inlineStr">
+      <c r="B29" s="36" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C29" s="32" t="inlineStr">
+      <c r="C29" s="34" t="inlineStr">
         <is>
           <t>None, and no path to one</t>
         </is>
       </c>
-      <c r="D29" s="35" t="inlineStr"/>
+      <c r="D29" s="37" t="inlineStr"/>
     </row>
     <row r="30" ht="10" customHeight="1"/>
     <row r="31" ht="22" customHeight="1">
-      <c r="B31" s="6" t="inlineStr">
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>SECTION B  ·  SCOPE   —   one mark per arena, 0 to 5</t>
         </is>
       </c>
     </row>
     <row r="32" ht="28" customHeight="1">
-      <c r="B32" s="32" t="inlineStr">
+      <c r="B32" s="34" t="inlineStr">
         <is>
           <t>Read the eleven areas each vendor rated themselves on, then give one mark per arena. The areas in each arena are printed on the row, so the checklist is in front of you. Where Section C contradicts Section B, believe Section C.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="41" customHeight="1">
-      <c r="B33" s="32" t="inlineStr">
+      <c r="B33" s="34" t="inlineStr">
         <is>
           <t>The mark is your read of how much of that arena — as our one-pager describes it — the product reaches. It is not a count of areas: Capacity has 3 and the others 4, so counting would never divide cleanly, and an area covered thinly is not the same as one covered properly. Weigh breadth and depth together.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="21" customHeight="1">
-      <c r="B34" s="34" t="inlineStr">
+      <c r="B34" s="36" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="C34" s="32" t="inlineStr">
+      <c r="C34" s="34" t="inlineStr">
         <is>
           <t>Most of it</t>
         </is>
       </c>
-      <c r="D34" s="35" t="inlineStr"/>
+      <c r="D34" s="37" t="inlineStr"/>
     </row>
     <row r="35" ht="21" customHeight="1">
-      <c r="B35" s="34" t="inlineStr">
+      <c r="B35" s="36" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="C35" s="32" t="inlineStr">
+      <c r="C35" s="34" t="inlineStr">
         <is>
           <t>More than half</t>
         </is>
       </c>
-      <c r="D35" s="35" t="inlineStr"/>
+      <c r="D35" s="37" t="inlineStr"/>
     </row>
     <row r="36" ht="21" customHeight="1">
-      <c r="B36" s="34" t="inlineStr">
+      <c r="B36" s="36" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C36" s="32" t="inlineStr">
+      <c r="C36" s="34" t="inlineStr">
         <is>
           <t>About half</t>
         </is>
       </c>
-      <c r="D36" s="35" t="inlineStr"/>
+      <c r="D36" s="37" t="inlineStr"/>
     </row>
     <row r="37" ht="21" customHeight="1">
-      <c r="B37" s="34" t="inlineStr">
+      <c r="B37" s="36" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C37" s="32" t="inlineStr">
+      <c r="C37" s="34" t="inlineStr">
         <is>
           <t>Less than half</t>
         </is>
       </c>
-      <c r="D37" s="35" t="inlineStr"/>
+      <c r="D37" s="37" t="inlineStr"/>
     </row>
     <row r="38" ht="21" customHeight="1">
-      <c r="B38" s="34" t="inlineStr">
+      <c r="B38" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C38" s="32" t="inlineStr">
+      <c r="C38" s="34" t="inlineStr">
         <is>
           <t>A corner of it</t>
         </is>
       </c>
-      <c r="D38" s="35" t="inlineStr"/>
+      <c r="D38" s="37" t="inlineStr"/>
     </row>
     <row r="39" ht="21" customHeight="1">
-      <c r="B39" s="34" t="inlineStr">
+      <c r="B39" s="36" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C39" s="32" t="inlineStr">
+      <c r="C39" s="34" t="inlineStr">
         <is>
           <t>Nothing here</t>
         </is>
       </c>
-      <c r="D39" s="35" t="inlineStr"/>
+      <c r="D39" s="37" t="inlineStr"/>
     </row>
     <row r="40" ht="28" customHeight="1">
-      <c r="B40" s="32" t="inlineStr">
+      <c r="B40" s="34" t="inlineStr">
         <is>
           <t>Most of it is the ceiling on purpose. The scope on our one-pager is original and these are point solutions, so nobody will cover all of it — a rung for that would sit unused and squeeze everyone else into the bottom half of the scale. All six rungs here are live.</t>
         </is>
@@ -3174,86 +3305,86 @@
     </row>
     <row r="41" ht="10" customHeight="1"/>
     <row r="42" ht="22" customHeight="1">
-      <c r="B42" s="6" t="inlineStr">
+      <c r="B42" s="7" t="inlineStr">
         <is>
           <t>SECTION C  ·  SOPHISTICATION   —   one mark, 0 to 4</t>
         </is>
       </c>
     </row>
     <row r="43" ht="41" customHeight="1">
-      <c r="B43" s="32" t="inlineStr">
+      <c r="B43" s="34" t="inlineStr">
         <is>
           <t>How much of the work the product does. This is the Read / Assist / Control language already in our workbook. Score what the product does, not how much the vendor wrote about it — a short answer describing an optimiser still scores 4. How it does it is a demo question, not a reason to mark it down.</t>
         </is>
       </c>
     </row>
     <row r="44" ht="21" customHeight="1">
-      <c r="B44" s="34" t="inlineStr">
+      <c r="B44" s="36" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="C44" s="32" t="inlineStr">
+      <c r="C44" s="34" t="inlineStr">
         <is>
           <t>Runs it — decides across the whole picture, and re-decides when things change</t>
         </is>
       </c>
-      <c r="D44" s="35" t="inlineStr"/>
+      <c r="D44" s="37" t="inlineStr"/>
     </row>
     <row r="45" ht="21" customHeight="1">
-      <c r="B45" s="34" t="inlineStr">
+      <c r="B45" s="36" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C45" s="32" t="inlineStr">
+      <c r="C45" s="34" t="inlineStr">
         <is>
           <t>Recommends it — works out the answer and proposes it; a person confirms</t>
         </is>
       </c>
-      <c r="D45" s="35" t="inlineStr"/>
+      <c r="D45" s="37" t="inlineStr"/>
     </row>
     <row r="46" ht="21" customHeight="1">
-      <c r="B46" s="34" t="inlineStr">
+      <c r="B46" s="36" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C46" s="32" t="inlineStr">
+      <c r="C46" s="34" t="inlineStr">
         <is>
           <t>Checks it — applies rules and flags problems; a person still works it</t>
         </is>
       </c>
-      <c r="D46" s="35" t="inlineStr"/>
+      <c r="D46" s="37" t="inlineStr"/>
     </row>
     <row r="47" ht="21" customHeight="1">
-      <c r="B47" s="34" t="inlineStr">
+      <c r="B47" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C47" s="32" t="inlineStr">
+      <c r="C47" s="34" t="inlineStr">
         <is>
           <t>Shows it — surfaces the information; a person does all the work</t>
         </is>
       </c>
-      <c r="D47" s="35" t="inlineStr"/>
+      <c r="D47" s="37" t="inlineStr"/>
     </row>
     <row r="48" ht="21" customHeight="1">
-      <c r="B48" s="34" t="inlineStr">
+      <c r="B48" s="36" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C48" s="32" t="inlineStr">
+      <c r="C48" s="34" t="inlineStr">
         <is>
           <t>Not addressed</t>
         </is>
       </c>
-      <c r="D48" s="35" t="inlineStr"/>
+      <c r="D48" s="37" t="inlineStr"/>
     </row>
     <row r="49" ht="15" customHeight="1">
-      <c r="B49" s="32" t="inlineStr">
+      <c r="B49" s="34" t="inlineStr">
         <is>
           <t>A 4 is not automatically what we want. Where we said Assist, a product that decides on its own is a risk worth a note.</t>
         </is>
@@ -3261,86 +3392,86 @@
     </row>
     <row r="50" ht="10" customHeight="1"/>
     <row r="51" ht="22" customHeight="1">
-      <c r="B51" s="6" t="inlineStr">
+      <c r="B51" s="7" t="inlineStr">
         <is>
           <t>SECTION D  ·  CLINICIAN FIT   —   one mark, 0 to 4</t>
         </is>
       </c>
     </row>
     <row r="52" ht="21" customHeight="1">
-      <c r="B52" s="34" t="inlineStr">
+      <c r="B52" s="36" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="C52" s="32" t="inlineStr">
+      <c r="C52" s="34" t="inlineStr">
         <is>
           <t>Strong fit</t>
         </is>
       </c>
-      <c r="D52" s="35" t="inlineStr"/>
+      <c r="D52" s="37" t="inlineStr"/>
     </row>
     <row r="53" ht="21" customHeight="1">
-      <c r="B53" s="34" t="inlineStr">
+      <c r="B53" s="36" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C53" s="32" t="inlineStr">
+      <c r="C53" s="34" t="inlineStr">
         <is>
           <t>Good fit</t>
         </is>
       </c>
-      <c r="D53" s="35" t="inlineStr"/>
+      <c r="D53" s="37" t="inlineStr"/>
     </row>
     <row r="54" ht="21" customHeight="1">
-      <c r="B54" s="34" t="inlineStr">
+      <c r="B54" s="36" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C54" s="32" t="inlineStr">
+      <c r="C54" s="34" t="inlineStr">
         <is>
           <t>Workable</t>
         </is>
       </c>
-      <c r="D54" s="35" t="inlineStr"/>
+      <c r="D54" s="37" t="inlineStr"/>
     </row>
     <row r="55" ht="21" customHeight="1">
-      <c r="B55" s="34" t="inlineStr">
+      <c r="B55" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C55" s="32" t="inlineStr">
+      <c r="C55" s="34" t="inlineStr">
         <is>
           <t>Poor fit</t>
         </is>
       </c>
-      <c r="D55" s="35" t="inlineStr"/>
+      <c r="D55" s="37" t="inlineStr"/>
     </row>
     <row r="56" ht="21" customHeight="1">
-      <c r="B56" s="34" t="inlineStr">
+      <c r="B56" s="36" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C56" s="32" t="inlineStr">
+      <c r="C56" s="34" t="inlineStr">
         <is>
           <t>Not answered</t>
         </is>
       </c>
-      <c r="D56" s="35" t="inlineStr"/>
+      <c r="D56" s="37" t="inlineStr"/>
     </row>
     <row r="57" ht="28" customHeight="1">
-      <c r="B57" s="32" t="inlineStr">
+      <c r="B57" s="34" t="inlineStr">
         <is>
           <t>No descriptions here on purpose. Read D1 to D3 and give it your own read. We know how our clinicians work and what they will accept; a rubric that spelled out what earns a 4 would only substitute a guess for that.</t>
         </is>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1">
-      <c r="B58" s="32" t="inlineStr">
+      <c r="B58" s="34" t="inlineStr">
         <is>
           <t>Say why in the Notes, though — that one line is what a colleague reads when they score the same vendor differently.</t>
         </is>
@@ -3348,86 +3479,86 @@
     </row>
     <row r="59" ht="10" customHeight="1"/>
     <row r="60" ht="22" customHeight="1">
-      <c r="B60" s="6" t="inlineStr">
+      <c r="B60" s="7" t="inlineStr">
         <is>
           <t>SECTION E  ·  PARTNERSHIP   —   one mark, 0 to 4</t>
         </is>
       </c>
     </row>
     <row r="61" ht="28" customHeight="1">
-      <c r="B61" s="32" t="inlineStr">
+      <c r="B61" s="34" t="inlineStr">
         <is>
           <t>What we are looking for is a company with the willingness and the environment to build this with us around our needs — and open to us holding equity, so that a product for the general market becomes a real possibility. The rungs run from vendor to co-owner.</t>
         </is>
       </c>
     </row>
     <row r="62" ht="21" customHeight="1">
-      <c r="B62" s="34" t="inlineStr">
+      <c r="B62" s="36" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="C62" s="32" t="inlineStr">
+      <c r="C62" s="34" t="inlineStr">
         <is>
           <t>Open to equity or a stake in what we build, and set up to build it with us</t>
         </is>
       </c>
-      <c r="D62" s="35" t="inlineStr"/>
+      <c r="D62" s="37" t="inlineStr"/>
     </row>
     <row r="63" ht="21" customHeight="1">
-      <c r="B63" s="34" t="inlineStr">
+      <c r="B63" s="36" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C63" s="32" t="inlineStr">
+      <c r="C63" s="34" t="inlineStr">
         <is>
           <t>Ready to build to our needs as a design partner; ownership not addressed</t>
         </is>
       </c>
-      <c r="D63" s="35" t="inlineStr"/>
+      <c r="D63" s="37" t="inlineStr"/>
     </row>
     <row r="64" ht="21" customHeight="1">
-      <c r="B64" s="34" t="inlineStr">
+      <c r="B64" s="36" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C64" s="32" t="inlineStr">
+      <c r="C64" s="34" t="inlineStr">
         <is>
           <t>Will take our input, but they own the roadmap and the product</t>
         </is>
       </c>
-      <c r="D64" s="35" t="inlineStr"/>
+      <c r="D64" s="37" t="inlineStr"/>
     </row>
     <row r="65" ht="21" customHeight="1">
-      <c r="B65" s="34" t="inlineStr">
+      <c r="B65" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C65" s="32" t="inlineStr">
+      <c r="C65" s="34" t="inlineStr">
         <is>
           <t>A standard customer relationship — we buy what already exists</t>
         </is>
       </c>
-      <c r="D65" s="35" t="inlineStr"/>
+      <c r="D65" s="37" t="inlineStr"/>
     </row>
     <row r="66" ht="21" customHeight="1">
-      <c r="B66" s="34" t="inlineStr">
+      <c r="B66" s="36" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C66" s="32" t="inlineStr">
+      <c r="C66" s="34" t="inlineStr">
         <is>
           <t>Not answered</t>
         </is>
       </c>
-      <c r="D66" s="35" t="inlineStr"/>
+      <c r="D66" s="37" t="inlineStr"/>
     </row>
     <row r="67" ht="28" customHeight="1">
-      <c r="B67" s="32" t="inlineStr">
+      <c r="B67" s="34" t="inlineStr">
         <is>
           <t>Read all four E answers, not only E2. A vendor who never mentions ownership but describes a real co-development practice is a 3, and worth the conversation. A discount is a discount.</t>
         </is>
@@ -3435,133 +3566,133 @@
     </row>
     <row r="68" ht="10" customHeight="1"/>
     <row r="69" ht="22" customHeight="1">
-      <c r="B69" s="6" t="inlineStr">
+      <c r="B69" s="7" t="inlineStr">
         <is>
           <t>THE THREE QUESTIONS THAT RAISE A FLAG INSTEAD</t>
         </is>
       </c>
     </row>
     <row r="70" ht="28" customHeight="1">
-      <c r="B70" s="32" t="inlineStr">
+      <c r="B70" s="34" t="inlineStr">
         <is>
           <t>A vendor with no continuity commitment should be stopped and asked, not quietly docked a few points. Same for a vendor with one customer, or impact numbers with no baseline. Mark these OK, Watch or STOP-CHECK.</t>
         </is>
       </c>
     </row>
     <row r="71" ht="21" customHeight="1">
-      <c r="B71" s="34" t="inlineStr">
+      <c r="B71" s="36" t="inlineStr">
         <is>
           <t>A2</t>
         </is>
       </c>
-      <c r="C71" s="32" t="inlineStr">
+      <c r="C71" s="34" t="inlineStr">
         <is>
           <t>Customers, scale and references — STOP-CHECK if one customer, or no references offered</t>
         </is>
       </c>
-      <c r="D71" s="35" t="inlineStr"/>
+      <c r="D71" s="37" t="inlineStr"/>
     </row>
     <row r="72" ht="21" customHeight="1">
-      <c r="B72" s="34" t="inlineStr">
+      <c r="B72" s="36" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="C72" s="32" t="inlineStr">
+      <c r="C72" s="34" t="inlineStr">
         <is>
           <t>Measured impact — Watch if claimed with no baseline or period</t>
         </is>
       </c>
-      <c r="D72" s="35" t="inlineStr"/>
+      <c r="D72" s="37" t="inlineStr"/>
     </row>
     <row r="73" ht="21" customHeight="1">
-      <c r="B73" s="34" t="inlineStr">
+      <c r="B73" s="36" t="inlineStr">
         <is>
           <t>C6</t>
         </is>
       </c>
-      <c r="C73" s="32" t="inlineStr">
+      <c r="C73" s="34" t="inlineStr">
         <is>
           <t>When your product is down — STOP-CHECK if no uptime figure or contractual commitment</t>
         </is>
       </c>
-      <c r="D73" s="35" t="inlineStr"/>
+      <c r="D73" s="37" t="inlineStr"/>
     </row>
     <row r="74" ht="10" customHeight="1"/>
     <row r="75" ht="22" customHeight="1">
-      <c r="B75" s="6" t="inlineStr">
+      <c r="B75" s="7" t="inlineStr">
         <is>
           <t>BANDS   —   the same as the full scorecard</t>
         </is>
       </c>
     </row>
     <row r="76" ht="21" customHeight="1">
-      <c r="B76" s="34" t="inlineStr">
+      <c r="B76" s="36" t="inlineStr">
         <is>
           <t>80–100</t>
         </is>
       </c>
-      <c r="C76" s="32" t="inlineStr">
+      <c r="C76" s="34" t="inlineStr">
         <is>
           <t>Advance — demo, references, deeper diligence</t>
         </is>
       </c>
-      <c r="D76" s="35" t="inlineStr"/>
+      <c r="D76" s="37" t="inlineStr"/>
     </row>
     <row r="77" ht="21" customHeight="1">
-      <c r="B77" s="34" t="inlineStr">
+      <c r="B77" s="36" t="inlineStr">
         <is>
           <t>65–79</t>
         </is>
       </c>
-      <c r="C77" s="32" t="inlineStr">
+      <c r="C77" s="34" t="inlineStr">
         <is>
           <t>Consider — only if something specific justifies it</t>
         </is>
       </c>
-      <c r="D77" s="35" t="inlineStr"/>
+      <c r="D77" s="37" t="inlineStr"/>
     </row>
     <row r="78" ht="21" customHeight="1">
-      <c r="B78" s="34" t="inlineStr">
+      <c r="B78" s="36" t="inlineStr">
         <is>
           <t>50–64</t>
         </is>
       </c>
-      <c r="C78" s="32" t="inlineStr">
+      <c r="C78" s="34" t="inlineStr">
         <is>
           <t>Hold — park unless the field thins</t>
         </is>
       </c>
-      <c r="D78" s="35" t="inlineStr"/>
+      <c r="D78" s="37" t="inlineStr"/>
     </row>
     <row r="79" ht="21" customHeight="1">
-      <c r="B79" s="34" t="inlineStr">
+      <c r="B79" s="36" t="inlineStr">
         <is>
           <t>&lt; 50</t>
         </is>
       </c>
-      <c r="C79" s="32" t="inlineStr">
+      <c r="C79" s="34" t="inlineStr">
         <is>
           <t>Decline — close out with thanks</t>
         </is>
       </c>
-      <c r="D79" s="35" t="inlineStr"/>
+      <c r="D79" s="37" t="inlineStr"/>
     </row>
     <row r="80" ht="34" customHeight="1">
-      <c r="B80" s="34" t="inlineStr">
+      <c r="B80" s="36" t="inlineStr">
         <is>
           <t>Conditional</t>
         </is>
       </c>
-      <c r="C80" s="32" t="inlineStr">
+      <c r="C80" s="34" t="inlineStr">
         <is>
           <t>Shown whenever the integration is not yet live. Advancing means accepting an integration still to be built, on their timeline, at our risk.</t>
         </is>
       </c>
-      <c r="D80" s="35" t="inlineStr"/>
+      <c r="D80" s="37" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="B82" s="37" t="inlineStr">
+      <c r="B82" s="39" t="inlineStr">
         <is>
           <t>Fast scorecard v2.0  ·  questionnaire form_version 2026-08-19</t>
         </is>

--- a/agents/compassus-capacity-pm/vendor-evaluation/Vendor-Scorecard-SIMPLE.xlsx
+++ b/agents/compassus-capacity-pm/vendor-evaluation/Vendor-Scorecard-SIMPLE.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="HCHB_List">Lists!$B$2:$B$7</definedName>
-    <definedName name="Scope_List">Lists!$E$2:$E$7</definedName>
+    <definedName name="Scope_List">Lists!$E$2:$E$6</definedName>
     <definedName name="Soph_List">Lists!$G$2:$G$6</definedName>
     <definedName name="Clin_List">Lists!$I$2:$I$6</definedName>
     <definedName name="Part_List">Lists!$K$2:$K$6</definedName>
@@ -165,7 +165,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -195,6 +195,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FDF7F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F6F78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E599D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004E8A5B"/>
       </patternFill>
     </fill>
     <fill>
@@ -253,7 +268,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -278,7 +293,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="21" fillId="11" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -311,14 +326,23 @@
     <xf numFmtId="0" fontId="15" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -329,7 +353,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -752,7 +776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:U36"/>
+  <dimension ref="B2:U45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -910,67 +934,67 @@
         </is>
       </c>
       <c r="F9" s="10">
-        <f>IF(F14="","",IFERROR(VLOOKUP(F14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(F19,1)),0)/5*12+IFERROR(VALUE(LEFT(F20,1)),0)/5*12+IFERROR(VALUE(LEFT(F21,1)),0)/5*12+IFERROR(VALUE(LEFT(F24,1)),0)/4*20+IFERROR(VALUE(LEFT(F28,1)),0)/4*12+IFERROR(VALUE(LEFT(F31,1)),0)/4*12)</f>
+        <f>IF(F14="","",IFERROR(VLOOKUP(F14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(F20,1)),0)/4*4+IFERROR(VALUE(LEFT(F21,1)),0)/4*4+IFERROR(VALUE(LEFT(F22,1)),0)/4*4+IFERROR(VALUE(LEFT(F24,1)),0)/4*4+IFERROR(VALUE(LEFT(F25,1)),0)/4*4+IFERROR(VALUE(LEFT(F26,1)),0)/4*4+IFERROR(VALUE(LEFT(F28,1)),0)/4*4+IFERROR(VALUE(LEFT(F29,1)),0)/4*4+IFERROR(VALUE(LEFT(F30,1)),0)/4*4+IFERROR(VALUE(LEFT(F33,1)),0)/4*20+IFERROR(VALUE(LEFT(F37,1)),0)/4*12+IFERROR(VALUE(LEFT(F40,1)),0)/4*12)</f>
         <v/>
       </c>
       <c r="G9" s="10">
-        <f>IF(G14="","",IFERROR(VLOOKUP(G14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(G19,1)),0)/5*12+IFERROR(VALUE(LEFT(G20,1)),0)/5*12+IFERROR(VALUE(LEFT(G21,1)),0)/5*12+IFERROR(VALUE(LEFT(G24,1)),0)/4*20+IFERROR(VALUE(LEFT(G28,1)),0)/4*12+IFERROR(VALUE(LEFT(G31,1)),0)/4*12)</f>
+        <f>IF(G14="","",IFERROR(VLOOKUP(G14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(G20,1)),0)/4*4+IFERROR(VALUE(LEFT(G21,1)),0)/4*4+IFERROR(VALUE(LEFT(G22,1)),0)/4*4+IFERROR(VALUE(LEFT(G24,1)),0)/4*4+IFERROR(VALUE(LEFT(G25,1)),0)/4*4+IFERROR(VALUE(LEFT(G26,1)),0)/4*4+IFERROR(VALUE(LEFT(G28,1)),0)/4*4+IFERROR(VALUE(LEFT(G29,1)),0)/4*4+IFERROR(VALUE(LEFT(G30,1)),0)/4*4+IFERROR(VALUE(LEFT(G33,1)),0)/4*20+IFERROR(VALUE(LEFT(G37,1)),0)/4*12+IFERROR(VALUE(LEFT(G40,1)),0)/4*12)</f>
         <v/>
       </c>
       <c r="H9" s="10">
-        <f>IF(H14="","",IFERROR(VLOOKUP(H14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(H19,1)),0)/5*12+IFERROR(VALUE(LEFT(H20,1)),0)/5*12+IFERROR(VALUE(LEFT(H21,1)),0)/5*12+IFERROR(VALUE(LEFT(H24,1)),0)/4*20+IFERROR(VALUE(LEFT(H28,1)),0)/4*12+IFERROR(VALUE(LEFT(H31,1)),0)/4*12)</f>
+        <f>IF(H14="","",IFERROR(VLOOKUP(H14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(H20,1)),0)/4*4+IFERROR(VALUE(LEFT(H21,1)),0)/4*4+IFERROR(VALUE(LEFT(H22,1)),0)/4*4+IFERROR(VALUE(LEFT(H24,1)),0)/4*4+IFERROR(VALUE(LEFT(H25,1)),0)/4*4+IFERROR(VALUE(LEFT(H26,1)),0)/4*4+IFERROR(VALUE(LEFT(H28,1)),0)/4*4+IFERROR(VALUE(LEFT(H29,1)),0)/4*4+IFERROR(VALUE(LEFT(H30,1)),0)/4*4+IFERROR(VALUE(LEFT(H33,1)),0)/4*20+IFERROR(VALUE(LEFT(H37,1)),0)/4*12+IFERROR(VALUE(LEFT(H40,1)),0)/4*12)</f>
         <v/>
       </c>
       <c r="I9" s="10">
-        <f>IF(I14="","",IFERROR(VLOOKUP(I14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(I19,1)),0)/5*12+IFERROR(VALUE(LEFT(I20,1)),0)/5*12+IFERROR(VALUE(LEFT(I21,1)),0)/5*12+IFERROR(VALUE(LEFT(I24,1)),0)/4*20+IFERROR(VALUE(LEFT(I28,1)),0)/4*12+IFERROR(VALUE(LEFT(I31,1)),0)/4*12)</f>
+        <f>IF(I14="","",IFERROR(VLOOKUP(I14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(I20,1)),0)/4*4+IFERROR(VALUE(LEFT(I21,1)),0)/4*4+IFERROR(VALUE(LEFT(I22,1)),0)/4*4+IFERROR(VALUE(LEFT(I24,1)),0)/4*4+IFERROR(VALUE(LEFT(I25,1)),0)/4*4+IFERROR(VALUE(LEFT(I26,1)),0)/4*4+IFERROR(VALUE(LEFT(I28,1)),0)/4*4+IFERROR(VALUE(LEFT(I29,1)),0)/4*4+IFERROR(VALUE(LEFT(I30,1)),0)/4*4+IFERROR(VALUE(LEFT(I33,1)),0)/4*20+IFERROR(VALUE(LEFT(I37,1)),0)/4*12+IFERROR(VALUE(LEFT(I40,1)),0)/4*12)</f>
         <v/>
       </c>
       <c r="J9" s="10">
-        <f>IF(J14="","",IFERROR(VLOOKUP(J14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(J19,1)),0)/5*12+IFERROR(VALUE(LEFT(J20,1)),0)/5*12+IFERROR(VALUE(LEFT(J21,1)),0)/5*12+IFERROR(VALUE(LEFT(J24,1)),0)/4*20+IFERROR(VALUE(LEFT(J28,1)),0)/4*12+IFERROR(VALUE(LEFT(J31,1)),0)/4*12)</f>
+        <f>IF(J14="","",IFERROR(VLOOKUP(J14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(J20,1)),0)/4*4+IFERROR(VALUE(LEFT(J21,1)),0)/4*4+IFERROR(VALUE(LEFT(J22,1)),0)/4*4+IFERROR(VALUE(LEFT(J24,1)),0)/4*4+IFERROR(VALUE(LEFT(J25,1)),0)/4*4+IFERROR(VALUE(LEFT(J26,1)),0)/4*4+IFERROR(VALUE(LEFT(J28,1)),0)/4*4+IFERROR(VALUE(LEFT(J29,1)),0)/4*4+IFERROR(VALUE(LEFT(J30,1)),0)/4*4+IFERROR(VALUE(LEFT(J33,1)),0)/4*20+IFERROR(VALUE(LEFT(J37,1)),0)/4*12+IFERROR(VALUE(LEFT(J40,1)),0)/4*12)</f>
         <v/>
       </c>
       <c r="K9" s="10">
-        <f>IF(K14="","",IFERROR(VLOOKUP(K14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(K19,1)),0)/5*12+IFERROR(VALUE(LEFT(K20,1)),0)/5*12+IFERROR(VALUE(LEFT(K21,1)),0)/5*12+IFERROR(VALUE(LEFT(K24,1)),0)/4*20+IFERROR(VALUE(LEFT(K28,1)),0)/4*12+IFERROR(VALUE(LEFT(K31,1)),0)/4*12)</f>
+        <f>IF(K14="","",IFERROR(VLOOKUP(K14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(K20,1)),0)/4*4+IFERROR(VALUE(LEFT(K21,1)),0)/4*4+IFERROR(VALUE(LEFT(K22,1)),0)/4*4+IFERROR(VALUE(LEFT(K24,1)),0)/4*4+IFERROR(VALUE(LEFT(K25,1)),0)/4*4+IFERROR(VALUE(LEFT(K26,1)),0)/4*4+IFERROR(VALUE(LEFT(K28,1)),0)/4*4+IFERROR(VALUE(LEFT(K29,1)),0)/4*4+IFERROR(VALUE(LEFT(K30,1)),0)/4*4+IFERROR(VALUE(LEFT(K33,1)),0)/4*20+IFERROR(VALUE(LEFT(K37,1)),0)/4*12+IFERROR(VALUE(LEFT(K40,1)),0)/4*12)</f>
         <v/>
       </c>
       <c r="L9" s="10">
-        <f>IF(L14="","",IFERROR(VLOOKUP(L14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(L19,1)),0)/5*12+IFERROR(VALUE(LEFT(L20,1)),0)/5*12+IFERROR(VALUE(LEFT(L21,1)),0)/5*12+IFERROR(VALUE(LEFT(L24,1)),0)/4*20+IFERROR(VALUE(LEFT(L28,1)),0)/4*12+IFERROR(VALUE(LEFT(L31,1)),0)/4*12)</f>
+        <f>IF(L14="","",IFERROR(VLOOKUP(L14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(L20,1)),0)/4*4+IFERROR(VALUE(LEFT(L21,1)),0)/4*4+IFERROR(VALUE(LEFT(L22,1)),0)/4*4+IFERROR(VALUE(LEFT(L24,1)),0)/4*4+IFERROR(VALUE(LEFT(L25,1)),0)/4*4+IFERROR(VALUE(LEFT(L26,1)),0)/4*4+IFERROR(VALUE(LEFT(L28,1)),0)/4*4+IFERROR(VALUE(LEFT(L29,1)),0)/4*4+IFERROR(VALUE(LEFT(L30,1)),0)/4*4+IFERROR(VALUE(LEFT(L33,1)),0)/4*20+IFERROR(VALUE(LEFT(L37,1)),0)/4*12+IFERROR(VALUE(LEFT(L40,1)),0)/4*12)</f>
         <v/>
       </c>
       <c r="M9" s="10">
-        <f>IF(M14="","",IFERROR(VLOOKUP(M14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(M19,1)),0)/5*12+IFERROR(VALUE(LEFT(M20,1)),0)/5*12+IFERROR(VALUE(LEFT(M21,1)),0)/5*12+IFERROR(VALUE(LEFT(M24,1)),0)/4*20+IFERROR(VALUE(LEFT(M28,1)),0)/4*12+IFERROR(VALUE(LEFT(M31,1)),0)/4*12)</f>
+        <f>IF(M14="","",IFERROR(VLOOKUP(M14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(M20,1)),0)/4*4+IFERROR(VALUE(LEFT(M21,1)),0)/4*4+IFERROR(VALUE(LEFT(M22,1)),0)/4*4+IFERROR(VALUE(LEFT(M24,1)),0)/4*4+IFERROR(VALUE(LEFT(M25,1)),0)/4*4+IFERROR(VALUE(LEFT(M26,1)),0)/4*4+IFERROR(VALUE(LEFT(M28,1)),0)/4*4+IFERROR(VALUE(LEFT(M29,1)),0)/4*4+IFERROR(VALUE(LEFT(M30,1)),0)/4*4+IFERROR(VALUE(LEFT(M33,1)),0)/4*20+IFERROR(VALUE(LEFT(M37,1)),0)/4*12+IFERROR(VALUE(LEFT(M40,1)),0)/4*12)</f>
         <v/>
       </c>
       <c r="N9" s="10">
-        <f>IF(N14="","",IFERROR(VLOOKUP(N14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(N19,1)),0)/5*12+IFERROR(VALUE(LEFT(N20,1)),0)/5*12+IFERROR(VALUE(LEFT(N21,1)),0)/5*12+IFERROR(VALUE(LEFT(N24,1)),0)/4*20+IFERROR(VALUE(LEFT(N28,1)),0)/4*12+IFERROR(VALUE(LEFT(N31,1)),0)/4*12)</f>
+        <f>IF(N14="","",IFERROR(VLOOKUP(N14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(N20,1)),0)/4*4+IFERROR(VALUE(LEFT(N21,1)),0)/4*4+IFERROR(VALUE(LEFT(N22,1)),0)/4*4+IFERROR(VALUE(LEFT(N24,1)),0)/4*4+IFERROR(VALUE(LEFT(N25,1)),0)/4*4+IFERROR(VALUE(LEFT(N26,1)),0)/4*4+IFERROR(VALUE(LEFT(N28,1)),0)/4*4+IFERROR(VALUE(LEFT(N29,1)),0)/4*4+IFERROR(VALUE(LEFT(N30,1)),0)/4*4+IFERROR(VALUE(LEFT(N33,1)),0)/4*20+IFERROR(VALUE(LEFT(N37,1)),0)/4*12+IFERROR(VALUE(LEFT(N40,1)),0)/4*12)</f>
         <v/>
       </c>
       <c r="O9" s="10">
-        <f>IF(O14="","",IFERROR(VLOOKUP(O14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(O19,1)),0)/5*12+IFERROR(VALUE(LEFT(O20,1)),0)/5*12+IFERROR(VALUE(LEFT(O21,1)),0)/5*12+IFERROR(VALUE(LEFT(O24,1)),0)/4*20+IFERROR(VALUE(LEFT(O28,1)),0)/4*12+IFERROR(VALUE(LEFT(O31,1)),0)/4*12)</f>
+        <f>IF(O14="","",IFERROR(VLOOKUP(O14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(O20,1)),0)/4*4+IFERROR(VALUE(LEFT(O21,1)),0)/4*4+IFERROR(VALUE(LEFT(O22,1)),0)/4*4+IFERROR(VALUE(LEFT(O24,1)),0)/4*4+IFERROR(VALUE(LEFT(O25,1)),0)/4*4+IFERROR(VALUE(LEFT(O26,1)),0)/4*4+IFERROR(VALUE(LEFT(O28,1)),0)/4*4+IFERROR(VALUE(LEFT(O29,1)),0)/4*4+IFERROR(VALUE(LEFT(O30,1)),0)/4*4+IFERROR(VALUE(LEFT(O33,1)),0)/4*20+IFERROR(VALUE(LEFT(O37,1)),0)/4*12+IFERROR(VALUE(LEFT(O40,1)),0)/4*12)</f>
         <v/>
       </c>
       <c r="P9" s="10">
-        <f>IF(P14="","",IFERROR(VLOOKUP(P14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(P19,1)),0)/5*12+IFERROR(VALUE(LEFT(P20,1)),0)/5*12+IFERROR(VALUE(LEFT(P21,1)),0)/5*12+IFERROR(VALUE(LEFT(P24,1)),0)/4*20+IFERROR(VALUE(LEFT(P28,1)),0)/4*12+IFERROR(VALUE(LEFT(P31,1)),0)/4*12)</f>
+        <f>IF(P14="","",IFERROR(VLOOKUP(P14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(P20,1)),0)/4*4+IFERROR(VALUE(LEFT(P21,1)),0)/4*4+IFERROR(VALUE(LEFT(P22,1)),0)/4*4+IFERROR(VALUE(LEFT(P24,1)),0)/4*4+IFERROR(VALUE(LEFT(P25,1)),0)/4*4+IFERROR(VALUE(LEFT(P26,1)),0)/4*4+IFERROR(VALUE(LEFT(P28,1)),0)/4*4+IFERROR(VALUE(LEFT(P29,1)),0)/4*4+IFERROR(VALUE(LEFT(P30,1)),0)/4*4+IFERROR(VALUE(LEFT(P33,1)),0)/4*20+IFERROR(VALUE(LEFT(P37,1)),0)/4*12+IFERROR(VALUE(LEFT(P40,1)),0)/4*12)</f>
         <v/>
       </c>
       <c r="Q9" s="10">
-        <f>IF(Q14="","",IFERROR(VLOOKUP(Q14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(Q19,1)),0)/5*12+IFERROR(VALUE(LEFT(Q20,1)),0)/5*12+IFERROR(VALUE(LEFT(Q21,1)),0)/5*12+IFERROR(VALUE(LEFT(Q24,1)),0)/4*20+IFERROR(VALUE(LEFT(Q28,1)),0)/4*12+IFERROR(VALUE(LEFT(Q31,1)),0)/4*12)</f>
+        <f>IF(Q14="","",IFERROR(VLOOKUP(Q14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(Q20,1)),0)/4*4+IFERROR(VALUE(LEFT(Q21,1)),0)/4*4+IFERROR(VALUE(LEFT(Q22,1)),0)/4*4+IFERROR(VALUE(LEFT(Q24,1)),0)/4*4+IFERROR(VALUE(LEFT(Q25,1)),0)/4*4+IFERROR(VALUE(LEFT(Q26,1)),0)/4*4+IFERROR(VALUE(LEFT(Q28,1)),0)/4*4+IFERROR(VALUE(LEFT(Q29,1)),0)/4*4+IFERROR(VALUE(LEFT(Q30,1)),0)/4*4+IFERROR(VALUE(LEFT(Q33,1)),0)/4*20+IFERROR(VALUE(LEFT(Q37,1)),0)/4*12+IFERROR(VALUE(LEFT(Q40,1)),0)/4*12)</f>
         <v/>
       </c>
       <c r="R9" s="10">
-        <f>IF(R14="","",IFERROR(VLOOKUP(R14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(R19,1)),0)/5*12+IFERROR(VALUE(LEFT(R20,1)),0)/5*12+IFERROR(VALUE(LEFT(R21,1)),0)/5*12+IFERROR(VALUE(LEFT(R24,1)),0)/4*20+IFERROR(VALUE(LEFT(R28,1)),0)/4*12+IFERROR(VALUE(LEFT(R31,1)),0)/4*12)</f>
+        <f>IF(R14="","",IFERROR(VLOOKUP(R14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(R20,1)),0)/4*4+IFERROR(VALUE(LEFT(R21,1)),0)/4*4+IFERROR(VALUE(LEFT(R22,1)),0)/4*4+IFERROR(VALUE(LEFT(R24,1)),0)/4*4+IFERROR(VALUE(LEFT(R25,1)),0)/4*4+IFERROR(VALUE(LEFT(R26,1)),0)/4*4+IFERROR(VALUE(LEFT(R28,1)),0)/4*4+IFERROR(VALUE(LEFT(R29,1)),0)/4*4+IFERROR(VALUE(LEFT(R30,1)),0)/4*4+IFERROR(VALUE(LEFT(R33,1)),0)/4*20+IFERROR(VALUE(LEFT(R37,1)),0)/4*12+IFERROR(VALUE(LEFT(R40,1)),0)/4*12)</f>
         <v/>
       </c>
       <c r="S9" s="10">
-        <f>IF(S14="","",IFERROR(VLOOKUP(S14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(S19,1)),0)/5*12+IFERROR(VALUE(LEFT(S20,1)),0)/5*12+IFERROR(VALUE(LEFT(S21,1)),0)/5*12+IFERROR(VALUE(LEFT(S24,1)),0)/4*20+IFERROR(VALUE(LEFT(S28,1)),0)/4*12+IFERROR(VALUE(LEFT(S31,1)),0)/4*12)</f>
+        <f>IF(S14="","",IFERROR(VLOOKUP(S14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(S20,1)),0)/4*4+IFERROR(VALUE(LEFT(S21,1)),0)/4*4+IFERROR(VALUE(LEFT(S22,1)),0)/4*4+IFERROR(VALUE(LEFT(S24,1)),0)/4*4+IFERROR(VALUE(LEFT(S25,1)),0)/4*4+IFERROR(VALUE(LEFT(S26,1)),0)/4*4+IFERROR(VALUE(LEFT(S28,1)),0)/4*4+IFERROR(VALUE(LEFT(S29,1)),0)/4*4+IFERROR(VALUE(LEFT(S30,1)),0)/4*4+IFERROR(VALUE(LEFT(S33,1)),0)/4*20+IFERROR(VALUE(LEFT(S37,1)),0)/4*12+IFERROR(VALUE(LEFT(S40,1)),0)/4*12)</f>
         <v/>
       </c>
       <c r="T9" s="10">
-        <f>IF(T14="","",IFERROR(VLOOKUP(T14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(T19,1)),0)/5*12+IFERROR(VALUE(LEFT(T20,1)),0)/5*12+IFERROR(VALUE(LEFT(T21,1)),0)/5*12+IFERROR(VALUE(LEFT(T24,1)),0)/4*20+IFERROR(VALUE(LEFT(T28,1)),0)/4*12+IFERROR(VALUE(LEFT(T31,1)),0)/4*12)</f>
+        <f>IF(T14="","",IFERROR(VLOOKUP(T14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(T20,1)),0)/4*4+IFERROR(VALUE(LEFT(T21,1)),0)/4*4+IFERROR(VALUE(LEFT(T22,1)),0)/4*4+IFERROR(VALUE(LEFT(T24,1)),0)/4*4+IFERROR(VALUE(LEFT(T25,1)),0)/4*4+IFERROR(VALUE(LEFT(T26,1)),0)/4*4+IFERROR(VALUE(LEFT(T28,1)),0)/4*4+IFERROR(VALUE(LEFT(T29,1)),0)/4*4+IFERROR(VALUE(LEFT(T30,1)),0)/4*4+IFERROR(VALUE(LEFT(T33,1)),0)/4*20+IFERROR(VALUE(LEFT(T37,1)),0)/4*12+IFERROR(VALUE(LEFT(T40,1)),0)/4*12)</f>
         <v/>
       </c>
       <c r="U9" s="10">
-        <f>IF(U14="","",IFERROR(VLOOKUP(U14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(U19,1)),0)/5*12+IFERROR(VALUE(LEFT(U20,1)),0)/5*12+IFERROR(VALUE(LEFT(U21,1)),0)/5*12+IFERROR(VALUE(LEFT(U24,1)),0)/4*20+IFERROR(VALUE(LEFT(U28,1)),0)/4*12+IFERROR(VALUE(LEFT(U31,1)),0)/4*12)</f>
+        <f>IF(U14="","",IFERROR(VLOOKUP(U14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(U20,1)),0)/4*4+IFERROR(VALUE(LEFT(U21,1)),0)/4*4+IFERROR(VALUE(LEFT(U22,1)),0)/4*4+IFERROR(VALUE(LEFT(U24,1)),0)/4*4+IFERROR(VALUE(LEFT(U25,1)),0)/4*4+IFERROR(VALUE(LEFT(U26,1)),0)/4*4+IFERROR(VALUE(LEFT(U28,1)),0)/4*4+IFERROR(VALUE(LEFT(U29,1)),0)/4*4+IFERROR(VALUE(LEFT(U30,1)),0)/4*4+IFERROR(VALUE(LEFT(U33,1)),0)/4*20+IFERROR(VALUE(LEFT(U37,1)),0)/4*12+IFERROR(VALUE(LEFT(U40,1)),0)/4*12)</f>
         <v/>
       </c>
     </row>
@@ -1062,67 +1086,67 @@
         </is>
       </c>
       <c r="F11" s="14">
-        <f>IF(F14="","",IF(F15="STOP-CHECK",1,0)+IF(F16="STOP-CHECK",1,0)+IF(F25="STOP-CHECK",1,0))</f>
+        <f>IF(F14="","",IF(F15="STOP-CHECK",1,0)+IF(F16="STOP-CHECK",1,0)+IF(F34="STOP-CHECK",1,0))</f>
         <v/>
       </c>
       <c r="G11" s="14">
-        <f>IF(G14="","",IF(G15="STOP-CHECK",1,0)+IF(G16="STOP-CHECK",1,0)+IF(G25="STOP-CHECK",1,0))</f>
+        <f>IF(G14="","",IF(G15="STOP-CHECK",1,0)+IF(G16="STOP-CHECK",1,0)+IF(G34="STOP-CHECK",1,0))</f>
         <v/>
       </c>
       <c r="H11" s="14">
-        <f>IF(H14="","",IF(H15="STOP-CHECK",1,0)+IF(H16="STOP-CHECK",1,0)+IF(H25="STOP-CHECK",1,0))</f>
+        <f>IF(H14="","",IF(H15="STOP-CHECK",1,0)+IF(H16="STOP-CHECK",1,0)+IF(H34="STOP-CHECK",1,0))</f>
         <v/>
       </c>
       <c r="I11" s="14">
-        <f>IF(I14="","",IF(I15="STOP-CHECK",1,0)+IF(I16="STOP-CHECK",1,0)+IF(I25="STOP-CHECK",1,0))</f>
+        <f>IF(I14="","",IF(I15="STOP-CHECK",1,0)+IF(I16="STOP-CHECK",1,0)+IF(I34="STOP-CHECK",1,0))</f>
         <v/>
       </c>
       <c r="J11" s="14">
-        <f>IF(J14="","",IF(J15="STOP-CHECK",1,0)+IF(J16="STOP-CHECK",1,0)+IF(J25="STOP-CHECK",1,0))</f>
+        <f>IF(J14="","",IF(J15="STOP-CHECK",1,0)+IF(J16="STOP-CHECK",1,0)+IF(J34="STOP-CHECK",1,0))</f>
         <v/>
       </c>
       <c r="K11" s="14">
-        <f>IF(K14="","",IF(K15="STOP-CHECK",1,0)+IF(K16="STOP-CHECK",1,0)+IF(K25="STOP-CHECK",1,0))</f>
+        <f>IF(K14="","",IF(K15="STOP-CHECK",1,0)+IF(K16="STOP-CHECK",1,0)+IF(K34="STOP-CHECK",1,0))</f>
         <v/>
       </c>
       <c r="L11" s="14">
-        <f>IF(L14="","",IF(L15="STOP-CHECK",1,0)+IF(L16="STOP-CHECK",1,0)+IF(L25="STOP-CHECK",1,0))</f>
+        <f>IF(L14="","",IF(L15="STOP-CHECK",1,0)+IF(L16="STOP-CHECK",1,0)+IF(L34="STOP-CHECK",1,0))</f>
         <v/>
       </c>
       <c r="M11" s="14">
-        <f>IF(M14="","",IF(M15="STOP-CHECK",1,0)+IF(M16="STOP-CHECK",1,0)+IF(M25="STOP-CHECK",1,0))</f>
+        <f>IF(M14="","",IF(M15="STOP-CHECK",1,0)+IF(M16="STOP-CHECK",1,0)+IF(M34="STOP-CHECK",1,0))</f>
         <v/>
       </c>
       <c r="N11" s="14">
-        <f>IF(N14="","",IF(N15="STOP-CHECK",1,0)+IF(N16="STOP-CHECK",1,0)+IF(N25="STOP-CHECK",1,0))</f>
+        <f>IF(N14="","",IF(N15="STOP-CHECK",1,0)+IF(N16="STOP-CHECK",1,0)+IF(N34="STOP-CHECK",1,0))</f>
         <v/>
       </c>
       <c r="O11" s="14">
-        <f>IF(O14="","",IF(O15="STOP-CHECK",1,0)+IF(O16="STOP-CHECK",1,0)+IF(O25="STOP-CHECK",1,0))</f>
+        <f>IF(O14="","",IF(O15="STOP-CHECK",1,0)+IF(O16="STOP-CHECK",1,0)+IF(O34="STOP-CHECK",1,0))</f>
         <v/>
       </c>
       <c r="P11" s="14">
-        <f>IF(P14="","",IF(P15="STOP-CHECK",1,0)+IF(P16="STOP-CHECK",1,0)+IF(P25="STOP-CHECK",1,0))</f>
+        <f>IF(P14="","",IF(P15="STOP-CHECK",1,0)+IF(P16="STOP-CHECK",1,0)+IF(P34="STOP-CHECK",1,0))</f>
         <v/>
       </c>
       <c r="Q11" s="14">
-        <f>IF(Q14="","",IF(Q15="STOP-CHECK",1,0)+IF(Q16="STOP-CHECK",1,0)+IF(Q25="STOP-CHECK",1,0))</f>
+        <f>IF(Q14="","",IF(Q15="STOP-CHECK",1,0)+IF(Q16="STOP-CHECK",1,0)+IF(Q34="STOP-CHECK",1,0))</f>
         <v/>
       </c>
       <c r="R11" s="14">
-        <f>IF(R14="","",IF(R15="STOP-CHECK",1,0)+IF(R16="STOP-CHECK",1,0)+IF(R25="STOP-CHECK",1,0))</f>
+        <f>IF(R14="","",IF(R15="STOP-CHECK",1,0)+IF(R16="STOP-CHECK",1,0)+IF(R34="STOP-CHECK",1,0))</f>
         <v/>
       </c>
       <c r="S11" s="14">
-        <f>IF(S14="","",IF(S15="STOP-CHECK",1,0)+IF(S16="STOP-CHECK",1,0)+IF(S25="STOP-CHECK",1,0))</f>
+        <f>IF(S14="","",IF(S15="STOP-CHECK",1,0)+IF(S16="STOP-CHECK",1,0)+IF(S34="STOP-CHECK",1,0))</f>
         <v/>
       </c>
       <c r="T11" s="14">
-        <f>IF(T14="","",IF(T15="STOP-CHECK",1,0)+IF(T16="STOP-CHECK",1,0)+IF(T25="STOP-CHECK",1,0))</f>
+        <f>IF(T14="","",IF(T15="STOP-CHECK",1,0)+IF(T16="STOP-CHECK",1,0)+IF(T34="STOP-CHECK",1,0))</f>
         <v/>
       </c>
       <c r="U11" s="14">
-        <f>IF(U14="","",IF(U15="STOP-CHECK",1,0)+IF(U16="STOP-CHECK",1,0)+IF(U25="STOP-CHECK",1,0))</f>
+        <f>IF(U14="","",IF(U15="STOP-CHECK",1,0)+IF(U16="STOP-CHECK",1,0)+IF(U34="STOP-CHECK",1,0))</f>
         <v/>
       </c>
     </row>
@@ -1288,520 +1312,832 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="30" customHeight="1">
+    <row r="19" ht="17" customHeight="1">
       <c r="B19" s="21" t="inlineStr">
         <is>
+          <t>CAPACITY   —   three marks, 12 points</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="B20" s="22" t="inlineStr">
+        <is>
           <t>Section B</t>
         </is>
       </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>Capacity</t>
-        </is>
-      </c>
-      <c r="D19" s="9" t="inlineStr">
-        <is>
-          <t>Workforce supply · availability &amp; reach · the capacity math</t>
-        </is>
-      </c>
-      <c r="E19" s="21" t="n">
+      <c r="C20" s="16" t="inlineStr">
+        <is>
+          <t>Workforce supply</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>Roster, disciplines, roles, competencies, ramp, float pool</t>
+        </is>
+      </c>
+      <c r="E20" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="F20" s="23" t="inlineStr">
+        <is>
+          <t>4 — Most of it</t>
+        </is>
+      </c>
+      <c r="G20" s="23" t="inlineStr">
+        <is>
+          <t>2 — About half</t>
+        </is>
+      </c>
+      <c r="H20" s="23" t="inlineStr">
+        <is>
+          <t>2 — About half</t>
+        </is>
+      </c>
+      <c r="I20" s="23" t="n"/>
+      <c r="J20" s="23" t="n"/>
+      <c r="K20" s="23" t="n"/>
+      <c r="L20" s="23" t="n"/>
+      <c r="M20" s="23" t="n"/>
+      <c r="N20" s="23" t="n"/>
+      <c r="O20" s="23" t="n"/>
+      <c r="P20" s="23" t="n"/>
+      <c r="Q20" s="23" t="n"/>
+      <c r="R20" s="23" t="n"/>
+      <c r="S20" s="23" t="n"/>
+      <c r="T20" s="23" t="n"/>
+      <c r="U20" s="23" t="n"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>Section B</t>
+        </is>
+      </c>
+      <c r="C21" s="16" t="inlineStr">
+        <is>
+          <t>Availability &amp; reach</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>Availability and time off, territory, drive-time reachability</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="F21" s="23" t="inlineStr">
+        <is>
+          <t>3 — More than half</t>
+        </is>
+      </c>
+      <c r="G21" s="23" t="inlineStr">
+        <is>
+          <t>1 — A corner of it</t>
+        </is>
+      </c>
+      <c r="H21" s="23" t="inlineStr">
+        <is>
+          <t>2 — About half</t>
+        </is>
+      </c>
+      <c r="I21" s="23" t="n"/>
+      <c r="J21" s="23" t="n"/>
+      <c r="K21" s="23" t="n"/>
+      <c r="L21" s="23" t="n"/>
+      <c r="M21" s="23" t="n"/>
+      <c r="N21" s="23" t="n"/>
+      <c r="O21" s="23" t="n"/>
+      <c r="P21" s="23" t="n"/>
+      <c r="Q21" s="23" t="n"/>
+      <c r="R21" s="23" t="n"/>
+      <c r="S21" s="23" t="n"/>
+      <c r="T21" s="23" t="n"/>
+      <c r="U21" s="23" t="n"/>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>Section B</t>
+        </is>
+      </c>
+      <c r="C22" s="16" t="inlineStr">
+        <is>
+          <t>The capacity math</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>Visit weighting, targets and ceilings, committed load vs. open room</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="F22" s="23" t="inlineStr">
+        <is>
+          <t>4 — Most of it</t>
+        </is>
+      </c>
+      <c r="G22" s="23" t="inlineStr">
+        <is>
+          <t>1 — A corner of it</t>
+        </is>
+      </c>
+      <c r="H22" s="23" t="inlineStr">
+        <is>
+          <t>3 — More than half</t>
+        </is>
+      </c>
+      <c r="I22" s="23" t="n"/>
+      <c r="J22" s="23" t="n"/>
+      <c r="K22" s="23" t="n"/>
+      <c r="L22" s="23" t="n"/>
+      <c r="M22" s="23" t="n"/>
+      <c r="N22" s="23" t="n"/>
+      <c r="O22" s="23" t="n"/>
+      <c r="P22" s="23" t="n"/>
+      <c r="Q22" s="23" t="n"/>
+      <c r="R22" s="23" t="n"/>
+      <c r="S22" s="23" t="n"/>
+      <c r="T22" s="23" t="n"/>
+      <c r="U22" s="23" t="n"/>
+    </row>
+    <row r="23" ht="17" customHeight="1">
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>SCHEDULING   —   three marks, 12 points</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="B24" s="25" t="inlineStr">
+        <is>
+          <t>Section B</t>
+        </is>
+      </c>
+      <c r="C24" s="16" t="inlineStr">
+        <is>
+          <t>Demand &amp; matching</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>Ordered visits, authorization, readiness — and who fits them</t>
+        </is>
+      </c>
+      <c r="E24" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="F24" s="23" t="inlineStr">
+        <is>
+          <t>4 — Most of it</t>
+        </is>
+      </c>
+      <c r="G24" s="23" t="inlineStr">
+        <is>
+          <t>3 — More than half</t>
+        </is>
+      </c>
+      <c r="H24" s="23" t="inlineStr">
+        <is>
+          <t>3 — More than half</t>
+        </is>
+      </c>
+      <c r="I24" s="23" t="n"/>
+      <c r="J24" s="23" t="n"/>
+      <c r="K24" s="23" t="n"/>
+      <c r="L24" s="23" t="n"/>
+      <c r="M24" s="23" t="n"/>
+      <c r="N24" s="23" t="n"/>
+      <c r="O24" s="23" t="n"/>
+      <c r="P24" s="23" t="n"/>
+      <c r="Q24" s="23" t="n"/>
+      <c r="R24" s="23" t="n"/>
+      <c r="S24" s="23" t="n"/>
+      <c r="T24" s="23" t="n"/>
+      <c r="U24" s="23" t="n"/>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="B25" s="25" t="inlineStr">
+        <is>
+          <t>Section B</t>
+        </is>
+      </c>
+      <c r="C25" s="16" t="inlineStr">
+        <is>
+          <t>Routing &amp; the week</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>Routing, sequencing, front-loading, week balancing</t>
+        </is>
+      </c>
+      <c r="E25" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="F25" s="23" t="inlineStr">
+        <is>
+          <t>4 — Most of it</t>
+        </is>
+      </c>
+      <c r="G25" s="23" t="inlineStr">
+        <is>
+          <t>4 — Most of it</t>
+        </is>
+      </c>
+      <c r="H25" s="23" t="inlineStr">
+        <is>
+          <t>3 — More than half</t>
+        </is>
+      </c>
+      <c r="I25" s="23" t="n"/>
+      <c r="J25" s="23" t="n"/>
+      <c r="K25" s="23" t="n"/>
+      <c r="L25" s="23" t="n"/>
+      <c r="M25" s="23" t="n"/>
+      <c r="N25" s="23" t="n"/>
+      <c r="O25" s="23" t="n"/>
+      <c r="P25" s="23" t="n"/>
+      <c r="Q25" s="23" t="n"/>
+      <c r="R25" s="23" t="n"/>
+      <c r="S25" s="23" t="n"/>
+      <c r="T25" s="23" t="n"/>
+      <c r="U25" s="23" t="n"/>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="B26" s="25" t="inlineStr">
+        <is>
+          <t>Section B</t>
+        </is>
+      </c>
+      <c r="C26" s="16" t="inlineStr">
+        <is>
+          <t>Exceptions</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>Missed visits, call-outs, reassignment, coverage, rebooking</t>
+        </is>
+      </c>
+      <c r="E26" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="F26" s="23" t="inlineStr">
+        <is>
+          <t>3 — More than half</t>
+        </is>
+      </c>
+      <c r="G26" s="23" t="inlineStr">
+        <is>
+          <t>2 — About half</t>
+        </is>
+      </c>
+      <c r="H26" s="23" t="inlineStr">
+        <is>
+          <t>3 — More than half</t>
+        </is>
+      </c>
+      <c r="I26" s="23" t="n"/>
+      <c r="J26" s="23" t="n"/>
+      <c r="K26" s="23" t="n"/>
+      <c r="L26" s="23" t="n"/>
+      <c r="M26" s="23" t="n"/>
+      <c r="N26" s="23" t="n"/>
+      <c r="O26" s="23" t="n"/>
+      <c r="P26" s="23" t="n"/>
+      <c r="Q26" s="23" t="n"/>
+      <c r="R26" s="23" t="n"/>
+      <c r="S26" s="23" t="n"/>
+      <c r="T26" s="23" t="n"/>
+      <c r="U26" s="23" t="n"/>
+    </row>
+    <row r="27" ht="17" customHeight="1">
+      <c r="B27" s="26" t="inlineStr">
+        <is>
+          <t>ENGAGEMENT   —   three marks, 12 points</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="B28" s="27" t="inlineStr">
+        <is>
+          <t>Section B</t>
+        </is>
+      </c>
+      <c r="C28" s="16" t="inlineStr">
+        <is>
+          <t>Before the visit</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>Welcome call, availability capture, reminders, confirmation, en-route</t>
+        </is>
+      </c>
+      <c r="E28" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="F28" s="23" t="inlineStr">
+        <is>
+          <t>2 — About half</t>
+        </is>
+      </c>
+      <c r="G28" s="23" t="inlineStr">
+        <is>
+          <t>1 — A corner of it</t>
+        </is>
+      </c>
+      <c r="H28" s="23" t="inlineStr">
+        <is>
+          <t>3 — More than half</t>
+        </is>
+      </c>
+      <c r="I28" s="23" t="n"/>
+      <c r="J28" s="23" t="n"/>
+      <c r="K28" s="23" t="n"/>
+      <c r="L28" s="23" t="n"/>
+      <c r="M28" s="23" t="n"/>
+      <c r="N28" s="23" t="n"/>
+      <c r="O28" s="23" t="n"/>
+      <c r="P28" s="23" t="n"/>
+      <c r="Q28" s="23" t="n"/>
+      <c r="R28" s="23" t="n"/>
+      <c r="S28" s="23" t="n"/>
+      <c r="T28" s="23" t="n"/>
+      <c r="U28" s="23" t="n"/>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="B29" s="27" t="inlineStr">
+        <is>
+          <t>Section B</t>
+        </is>
+      </c>
+      <c r="C29" s="16" t="inlineStr">
+        <is>
+          <t>When plans change</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>Reschedule, coverage outreach, urgent same-day needs, incentives</t>
+        </is>
+      </c>
+      <c r="E29" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="F29" s="23" t="inlineStr">
+        <is>
+          <t>2 — About half</t>
+        </is>
+      </c>
+      <c r="G29" s="23" t="inlineStr">
+        <is>
+          <t>1 — A corner of it</t>
+        </is>
+      </c>
+      <c r="H29" s="23" t="inlineStr">
+        <is>
+          <t>4 — Most of it</t>
+        </is>
+      </c>
+      <c r="I29" s="23" t="n"/>
+      <c r="J29" s="23" t="n"/>
+      <c r="K29" s="23" t="n"/>
+      <c r="L29" s="23" t="n"/>
+      <c r="M29" s="23" t="n"/>
+      <c r="N29" s="23" t="n"/>
+      <c r="O29" s="23" t="n"/>
+      <c r="P29" s="23" t="n"/>
+      <c r="Q29" s="23" t="n"/>
+      <c r="R29" s="23" t="n"/>
+      <c r="S29" s="23" t="n"/>
+      <c r="T29" s="23" t="n"/>
+      <c r="U29" s="23" t="n"/>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="B30" s="27" t="inlineStr">
+        <is>
+          <t>Section B</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>Across the care team</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>Multi-discipline coordination, clinician and office updates</t>
+        </is>
+      </c>
+      <c r="E30" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="F30" s="23" t="inlineStr">
+        <is>
+          <t>1 — A corner of it</t>
+        </is>
+      </c>
+      <c r="G30" s="23" t="inlineStr">
+        <is>
+          <t>0 — Nothing here</t>
+        </is>
+      </c>
+      <c r="H30" s="23" t="inlineStr">
+        <is>
+          <t>2 — About half</t>
+        </is>
+      </c>
+      <c r="I30" s="23" t="n"/>
+      <c r="J30" s="23" t="n"/>
+      <c r="K30" s="23" t="n"/>
+      <c r="L30" s="23" t="n"/>
+      <c r="M30" s="23" t="n"/>
+      <c r="N30" s="23" t="n"/>
+      <c r="O30" s="23" t="n"/>
+      <c r="P30" s="23" t="n"/>
+      <c r="Q30" s="23" t="n"/>
+      <c r="R30" s="23" t="n"/>
+      <c r="S30" s="23" t="n"/>
+      <c r="T30" s="23" t="n"/>
+      <c r="U30" s="23" t="n"/>
+    </row>
+    <row r="32" ht="21" customHeight="1">
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>C  ·  HOW YOUR PRODUCT WORKS</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="24" customHeight="1">
+      <c r="B33" s="28" t="inlineStr">
+        <is>
+          <t>Section C</t>
+        </is>
+      </c>
+      <c r="C33" s="16" t="inlineStr">
+        <is>
+          <t>Sophistication</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>How much of the work the product does</t>
+        </is>
+      </c>
+      <c r="E33" s="28" t="n">
+        <v>20</v>
+      </c>
+      <c r="F33" s="23" t="inlineStr">
+        <is>
+          <t>4 — Runs it</t>
+        </is>
+      </c>
+      <c r="G33" s="23" t="inlineStr">
+        <is>
+          <t>3 — Recommends it</t>
+        </is>
+      </c>
+      <c r="H33" s="23" t="inlineStr">
+        <is>
+          <t>3 — Recommends it</t>
+        </is>
+      </c>
+      <c r="I33" s="23" t="n"/>
+      <c r="J33" s="23" t="n"/>
+      <c r="K33" s="23" t="n"/>
+      <c r="L33" s="23" t="n"/>
+      <c r="M33" s="23" t="n"/>
+      <c r="N33" s="23" t="n"/>
+      <c r="O33" s="23" t="n"/>
+      <c r="P33" s="23" t="n"/>
+      <c r="Q33" s="23" t="n"/>
+      <c r="R33" s="23" t="n"/>
+      <c r="S33" s="23" t="n"/>
+      <c r="T33" s="23" t="n"/>
+      <c r="U33" s="23" t="n"/>
+    </row>
+    <row r="34" ht="19" customHeight="1">
+      <c r="B34" s="18" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="C34" s="16" t="inlineStr">
+        <is>
+          <t>When your product is down</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>Stop-check if no uptime figure or contractual commitment</t>
+        </is>
+      </c>
+      <c r="E34" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F34" s="20" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G34" s="20" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H34" s="20" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="I34" s="20" t="n"/>
+      <c r="J34" s="20" t="n"/>
+      <c r="K34" s="20" t="n"/>
+      <c r="L34" s="20" t="n"/>
+      <c r="M34" s="20" t="n"/>
+      <c r="N34" s="20" t="n"/>
+      <c r="O34" s="20" t="n"/>
+      <c r="P34" s="20" t="n"/>
+      <c r="Q34" s="20" t="n"/>
+      <c r="R34" s="20" t="n"/>
+      <c r="S34" s="20" t="n"/>
+      <c r="T34" s="20" t="n"/>
+      <c r="U34" s="20" t="n"/>
+    </row>
+    <row r="36" ht="21" customHeight="1">
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>D  ·  THE CLINICIAN'S PLACE IN THE MODEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="B37" s="29" t="inlineStr">
+        <is>
+          <t>D1–D3</t>
+        </is>
+      </c>
+      <c r="C37" s="16" t="inlineStr">
+        <is>
+          <t>Clinician fit</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>Our own read of fit — no checklist, on purpose</t>
+        </is>
+      </c>
+      <c r="E37" s="29" t="n">
         <v>12</v>
       </c>
-      <c r="F19" s="22" t="inlineStr">
-        <is>
-          <t>4 — More than half</t>
-        </is>
-      </c>
-      <c r="G19" s="22" t="inlineStr">
-        <is>
-          <t>2 — Less than half</t>
-        </is>
-      </c>
-      <c r="H19" s="22" t="inlineStr">
-        <is>
-          <t>3 — About half</t>
-        </is>
-      </c>
-      <c r="I19" s="22" t="n"/>
-      <c r="J19" s="22" t="n"/>
-      <c r="K19" s="22" t="n"/>
-      <c r="L19" s="22" t="n"/>
-      <c r="M19" s="22" t="n"/>
-      <c r="N19" s="22" t="n"/>
-      <c r="O19" s="22" t="n"/>
-      <c r="P19" s="22" t="n"/>
-      <c r="Q19" s="22" t="n"/>
-      <c r="R19" s="22" t="n"/>
-      <c r="S19" s="22" t="n"/>
-      <c r="T19" s="22" t="n"/>
-      <c r="U19" s="22" t="n"/>
-    </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="B20" s="23" t="inlineStr">
-        <is>
-          <t>Section B</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>Scheduling</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>Demand · matching · routing &amp; the week · exceptions</t>
-        </is>
-      </c>
-      <c r="E20" s="23" t="n">
+      <c r="F37" s="23" t="inlineStr">
+        <is>
+          <t>3 — Good fit</t>
+        </is>
+      </c>
+      <c r="G37" s="23" t="inlineStr">
+        <is>
+          <t>2 — Workable</t>
+        </is>
+      </c>
+      <c r="H37" s="23" t="inlineStr">
+        <is>
+          <t>3 — Good fit</t>
+        </is>
+      </c>
+      <c r="I37" s="23" t="n"/>
+      <c r="J37" s="23" t="n"/>
+      <c r="K37" s="23" t="n"/>
+      <c r="L37" s="23" t="n"/>
+      <c r="M37" s="23" t="n"/>
+      <c r="N37" s="23" t="n"/>
+      <c r="O37" s="23" t="n"/>
+      <c r="P37" s="23" t="n"/>
+      <c r="Q37" s="23" t="n"/>
+      <c r="R37" s="23" t="n"/>
+      <c r="S37" s="23" t="n"/>
+      <c r="T37" s="23" t="n"/>
+      <c r="U37" s="23" t="n"/>
+    </row>
+    <row r="39" ht="21" customHeight="1">
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>E  ·  FIT AND PARTNERSHIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="24" customHeight="1">
+      <c r="B40" s="29" t="inlineStr">
+        <is>
+          <t>E1–E4</t>
+        </is>
+      </c>
+      <c r="C40" s="16" t="inlineStr">
+        <is>
+          <t>Partnership</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>Willing to build it with us, and open to a stake</t>
+        </is>
+      </c>
+      <c r="E40" s="29" t="n">
         <v>12</v>
       </c>
-      <c r="F20" s="22" t="inlineStr">
-        <is>
-          <t>5 — Most of it</t>
-        </is>
-      </c>
-      <c r="G20" s="22" t="inlineStr">
-        <is>
-          <t>3 — About half</t>
-        </is>
-      </c>
-      <c r="H20" s="22" t="inlineStr">
-        <is>
-          <t>4 — More than half</t>
-        </is>
-      </c>
-      <c r="I20" s="22" t="n"/>
-      <c r="J20" s="22" t="n"/>
-      <c r="K20" s="22" t="n"/>
-      <c r="L20" s="22" t="n"/>
-      <c r="M20" s="22" t="n"/>
-      <c r="N20" s="22" t="n"/>
-      <c r="O20" s="22" t="n"/>
-      <c r="P20" s="22" t="n"/>
-      <c r="Q20" s="22" t="n"/>
-      <c r="R20" s="22" t="n"/>
-      <c r="S20" s="22" t="n"/>
-      <c r="T20" s="22" t="n"/>
-      <c r="U20" s="22" t="n"/>
-    </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="B21" s="24" t="inlineStr">
-        <is>
-          <t>Section B</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="D21" s="9" t="inlineStr">
-        <is>
-          <t>Before the visit · when plans change · incentives · care team</t>
-        </is>
-      </c>
-      <c r="E21" s="24" t="n">
-        <v>12</v>
-      </c>
-      <c r="F21" s="22" t="inlineStr">
-        <is>
-          <t>2 — Less than half</t>
-        </is>
-      </c>
-      <c r="G21" s="22" t="inlineStr">
-        <is>
-          <t>1 — A corner of it</t>
-        </is>
-      </c>
-      <c r="H21" s="22" t="inlineStr">
-        <is>
-          <t>3 — About half</t>
-        </is>
-      </c>
-      <c r="I21" s="22" t="n"/>
-      <c r="J21" s="22" t="n"/>
-      <c r="K21" s="22" t="n"/>
-      <c r="L21" s="22" t="n"/>
-      <c r="M21" s="22" t="n"/>
-      <c r="N21" s="22" t="n"/>
-      <c r="O21" s="22" t="n"/>
-      <c r="P21" s="22" t="n"/>
-      <c r="Q21" s="22" t="n"/>
-      <c r="R21" s="22" t="n"/>
-      <c r="S21" s="22" t="n"/>
-      <c r="T21" s="22" t="n"/>
-      <c r="U21" s="22" t="n"/>
-    </row>
-    <row r="23" ht="21" customHeight="1">
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>C  ·  HOW YOUR PRODUCT WORKS</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="24" customHeight="1">
-      <c r="B24" s="25" t="inlineStr">
-        <is>
-          <t>Section C</t>
-        </is>
-      </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>Sophistication</t>
-        </is>
-      </c>
-      <c r="D24" s="9" t="inlineStr">
-        <is>
-          <t>How much of the work the product does</t>
-        </is>
-      </c>
-      <c r="E24" s="25" t="n">
-        <v>20</v>
-      </c>
-      <c r="F24" s="22" t="inlineStr">
-        <is>
-          <t>4 — Runs it</t>
-        </is>
-      </c>
-      <c r="G24" s="22" t="inlineStr">
-        <is>
-          <t>3 — Recommends it</t>
-        </is>
-      </c>
-      <c r="H24" s="22" t="inlineStr">
-        <is>
-          <t>3 — Recommends it</t>
-        </is>
-      </c>
-      <c r="I24" s="22" t="n"/>
-      <c r="J24" s="22" t="n"/>
-      <c r="K24" s="22" t="n"/>
-      <c r="L24" s="22" t="n"/>
-      <c r="M24" s="22" t="n"/>
-      <c r="N24" s="22" t="n"/>
-      <c r="O24" s="22" t="n"/>
-      <c r="P24" s="22" t="n"/>
-      <c r="Q24" s="22" t="n"/>
-      <c r="R24" s="22" t="n"/>
-      <c r="S24" s="22" t="n"/>
-      <c r="T24" s="22" t="n"/>
-      <c r="U24" s="22" t="n"/>
-    </row>
-    <row r="25" ht="19" customHeight="1">
-      <c r="B25" s="18" t="inlineStr">
-        <is>
-          <t>C6</t>
-        </is>
-      </c>
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>When your product is down</t>
-        </is>
-      </c>
-      <c r="D25" s="9" t="inlineStr">
-        <is>
-          <t>Stop-check if no uptime figure or contractual commitment</t>
-        </is>
-      </c>
-      <c r="E25" s="19" t="inlineStr">
+      <c r="F40" s="23" t="inlineStr">
+        <is>
+          <t>3 — Ready to build to our needs as a design partner; ownership not addressed</t>
+        </is>
+      </c>
+      <c r="G40" s="23" t="inlineStr">
+        <is>
+          <t>2 — Will take our input, but they own the roadmap and the product</t>
+        </is>
+      </c>
+      <c r="H40" s="23" t="inlineStr">
+        <is>
+          <t>4 — Open to equity or a stake in what we build, and set up to build it with us</t>
+        </is>
+      </c>
+      <c r="I40" s="23" t="n"/>
+      <c r="J40" s="23" t="n"/>
+      <c r="K40" s="23" t="n"/>
+      <c r="L40" s="23" t="n"/>
+      <c r="M40" s="23" t="n"/>
+      <c r="N40" s="23" t="n"/>
+      <c r="O40" s="23" t="n"/>
+      <c r="P40" s="23" t="n"/>
+      <c r="Q40" s="23" t="n"/>
+      <c r="R40" s="23" t="n"/>
+      <c r="S40" s="23" t="n"/>
+      <c r="T40" s="23" t="n"/>
+      <c r="U40" s="23" t="n"/>
+    </row>
+    <row r="42" ht="21" customHeight="1">
+      <c r="B42" s="30" t="inlineStr">
+        <is>
+          <t>NOTES   —   one line each.  This is what we go and ask.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="62" customHeight="1">
+      <c r="B43" s="31" t="inlineStr"/>
+      <c r="C43" s="32" t="inlineStr">
+        <is>
+          <t>What stands out</t>
+        </is>
+      </c>
+      <c r="D43" s="33" t="inlineStr">
+        <is>
+          <t>against the field, or against our own thinking</t>
+        </is>
+      </c>
+      <c r="E43" s="19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F25" s="20" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="G25" s="20" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="H25" s="20" t="inlineStr">
-        <is>
-          <t>Watch</t>
-        </is>
-      </c>
-      <c r="I25" s="20" t="n"/>
-      <c r="J25" s="20" t="n"/>
-      <c r="K25" s="20" t="n"/>
-      <c r="L25" s="20" t="n"/>
-      <c r="M25" s="20" t="n"/>
-      <c r="N25" s="20" t="n"/>
-      <c r="O25" s="20" t="n"/>
-      <c r="P25" s="20" t="n"/>
-      <c r="Q25" s="20" t="n"/>
-      <c r="R25" s="20" t="n"/>
-      <c r="S25" s="20" t="n"/>
-      <c r="T25" s="20" t="n"/>
-      <c r="U25" s="20" t="n"/>
-    </row>
-    <row r="27" ht="21" customHeight="1">
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>D  ·  THE CLINICIAN'S PLACE IN THE MODEL</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="24" customHeight="1">
-      <c r="B28" s="26" t="inlineStr">
-        <is>
-          <t>D1–D3</t>
-        </is>
-      </c>
-      <c r="C28" s="16" t="inlineStr">
-        <is>
-          <t>Clinician fit</t>
-        </is>
-      </c>
-      <c r="D28" s="9" t="inlineStr">
-        <is>
-          <t>Our own read of fit — no checklist, on purpose</t>
-        </is>
-      </c>
-      <c r="E28" s="26" t="n">
-        <v>12</v>
-      </c>
-      <c r="F28" s="22" t="inlineStr">
-        <is>
-          <t>3 — Good fit</t>
-        </is>
-      </c>
-      <c r="G28" s="22" t="inlineStr">
-        <is>
-          <t>2 — Workable</t>
-        </is>
-      </c>
-      <c r="H28" s="22" t="inlineStr">
-        <is>
-          <t>3 — Good fit</t>
-        </is>
-      </c>
-      <c r="I28" s="22" t="n"/>
-      <c r="J28" s="22" t="n"/>
-      <c r="K28" s="22" t="n"/>
-      <c r="L28" s="22" t="n"/>
-      <c r="M28" s="22" t="n"/>
-      <c r="N28" s="22" t="n"/>
-      <c r="O28" s="22" t="n"/>
-      <c r="P28" s="22" t="n"/>
-      <c r="Q28" s="22" t="n"/>
-      <c r="R28" s="22" t="n"/>
-      <c r="S28" s="22" t="n"/>
-      <c r="T28" s="22" t="n"/>
-      <c r="U28" s="22" t="n"/>
-    </row>
-    <row r="30" ht="21" customHeight="1">
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>E  ·  FIT AND PARTNERSHIP</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="24" customHeight="1">
-      <c r="B31" s="26" t="inlineStr">
-        <is>
-          <t>E1–E4</t>
-        </is>
-      </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>Partnership</t>
-        </is>
-      </c>
-      <c r="D31" s="9" t="inlineStr">
-        <is>
-          <t>Willing to build it with us, and open to a stake</t>
-        </is>
-      </c>
-      <c r="E31" s="26" t="n">
-        <v>12</v>
-      </c>
-      <c r="F31" s="22" t="inlineStr">
-        <is>
-          <t>3 — Ready to build to our needs as a design partner; ownership not addressed</t>
-        </is>
-      </c>
-      <c r="G31" s="22" t="inlineStr">
-        <is>
-          <t>2 — Will take our input, but they own the roadmap and the product</t>
-        </is>
-      </c>
-      <c r="H31" s="22" t="inlineStr">
-        <is>
-          <t>4 — Open to equity or a stake in what we build, and set up to build it with us</t>
-        </is>
-      </c>
-      <c r="I31" s="22" t="n"/>
-      <c r="J31" s="22" t="n"/>
-      <c r="K31" s="22" t="n"/>
-      <c r="L31" s="22" t="n"/>
-      <c r="M31" s="22" t="n"/>
-      <c r="N31" s="22" t="n"/>
-      <c r="O31" s="22" t="n"/>
-      <c r="P31" s="22" t="n"/>
-      <c r="Q31" s="22" t="n"/>
-      <c r="R31" s="22" t="n"/>
-      <c r="S31" s="22" t="n"/>
-      <c r="T31" s="22" t="n"/>
-      <c r="U31" s="22" t="n"/>
-    </row>
-    <row r="33" ht="21" customHeight="1">
-      <c r="B33" s="27" t="inlineStr">
-        <is>
-          <t>NOTES   —   one line each.  This is what we go and ask.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="62" customHeight="1">
-      <c r="B34" s="28" t="inlineStr"/>
-      <c r="C34" s="29" t="inlineStr">
-        <is>
-          <t>What stands out</t>
-        </is>
-      </c>
-      <c r="D34" s="30" t="inlineStr">
-        <is>
-          <t>against the field, or against our own thinking</t>
-        </is>
-      </c>
-      <c r="E34" s="19" t="inlineStr">
+      <c r="F43" s="34" t="inlineStr">
+        <is>
+          <t>Only answer that shows a branch leader the envelope impact of a referral before accepting it.</t>
+        </is>
+      </c>
+      <c r="G43" s="34" t="inlineStr">
+        <is>
+          <t>Strong routing engine, almost nothing on the patient side.</t>
+        </is>
+      </c>
+      <c r="H43" s="34" t="inlineStr">
+        <is>
+          <t>Raised payer-mix-aware sequencing — not on our one-pager, probably should be.</t>
+        </is>
+      </c>
+      <c r="I43" s="34" t="n"/>
+      <c r="J43" s="34" t="n"/>
+      <c r="K43" s="34" t="n"/>
+      <c r="L43" s="34" t="n"/>
+      <c r="M43" s="34" t="n"/>
+      <c r="N43" s="34" t="n"/>
+      <c r="O43" s="34" t="n"/>
+      <c r="P43" s="34" t="n"/>
+      <c r="Q43" s="34" t="n"/>
+      <c r="R43" s="34" t="n"/>
+      <c r="S43" s="34" t="n"/>
+      <c r="T43" s="34" t="n"/>
+      <c r="U43" s="34" t="n"/>
+    </row>
+    <row r="44" ht="62" customHeight="1">
+      <c r="B44" s="31" t="inlineStr"/>
+      <c r="C44" s="32" t="inlineStr">
+        <is>
+          <t>What worries me</t>
+        </is>
+      </c>
+      <c r="D44" s="33" t="inlineStr">
+        <is>
+          <t>including anything flagged above</t>
+        </is>
+      </c>
+      <c r="E44" s="19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F34" s="31" t="inlineStr">
-        <is>
-          <t>Only answer that shows a branch leader the envelope impact of a referral before accepting it.</t>
-        </is>
-      </c>
-      <c r="G34" s="31" t="inlineStr">
-        <is>
-          <t>Strong routing engine, almost nothing on the patient side.</t>
-        </is>
-      </c>
-      <c r="H34" s="31" t="inlineStr">
-        <is>
-          <t>Raised payer-mix-aware sequencing — not on our one-pager, probably should be.</t>
-        </is>
-      </c>
-      <c r="I34" s="31" t="n"/>
-      <c r="J34" s="31" t="n"/>
-      <c r="K34" s="31" t="n"/>
-      <c r="L34" s="31" t="n"/>
-      <c r="M34" s="31" t="n"/>
-      <c r="N34" s="31" t="n"/>
-      <c r="O34" s="31" t="n"/>
-      <c r="P34" s="31" t="n"/>
-      <c r="Q34" s="31" t="n"/>
-      <c r="R34" s="31" t="n"/>
-      <c r="S34" s="31" t="n"/>
-      <c r="T34" s="31" t="n"/>
-      <c r="U34" s="31" t="n"/>
-    </row>
-    <row r="35" ht="62" customHeight="1">
-      <c r="B35" s="28" t="inlineStr"/>
-      <c r="C35" s="29" t="inlineStr">
-        <is>
-          <t>What worries me</t>
-        </is>
-      </c>
-      <c r="D35" s="30" t="inlineStr">
-        <is>
-          <t>including anything flagged above</t>
-        </is>
-      </c>
-      <c r="E35" s="19" t="inlineStr">
+      <c r="F44" s="34" t="inlineStr">
+        <is>
+          <t>Impact figures come from one site.</t>
+        </is>
+      </c>
+      <c r="G44" s="34" t="inlineStr">
+        <is>
+          <t>One customer, references not offered.</t>
+        </is>
+      </c>
+      <c r="H44" s="34" t="inlineStr">
+        <is>
+          <t>Integration is a promise on their timeline, not ours.</t>
+        </is>
+      </c>
+      <c r="I44" s="34" t="n"/>
+      <c r="J44" s="34" t="n"/>
+      <c r="K44" s="34" t="n"/>
+      <c r="L44" s="34" t="n"/>
+      <c r="M44" s="34" t="n"/>
+      <c r="N44" s="34" t="n"/>
+      <c r="O44" s="34" t="n"/>
+      <c r="P44" s="34" t="n"/>
+      <c r="Q44" s="34" t="n"/>
+      <c r="R44" s="34" t="n"/>
+      <c r="S44" s="34" t="n"/>
+      <c r="T44" s="34" t="n"/>
+      <c r="U44" s="34" t="n"/>
+    </row>
+    <row r="45" ht="62" customHeight="1">
+      <c r="B45" s="31" t="inlineStr"/>
+      <c r="C45" s="32" t="inlineStr">
+        <is>
+          <t>What to go and ask</t>
+        </is>
+      </c>
+      <c r="D45" s="33" t="inlineStr">
+        <is>
+          <t>the demo agenda</t>
+        </is>
+      </c>
+      <c r="E45" s="19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F35" s="31" t="inlineStr">
-        <is>
-          <t>Impact figures come from one site.</t>
-        </is>
-      </c>
-      <c r="G35" s="31" t="inlineStr">
-        <is>
-          <t>One customer, references not offered.</t>
-        </is>
-      </c>
-      <c r="H35" s="31" t="inlineStr">
-        <is>
-          <t>Integration is a promise on their timeline, not ours.</t>
-        </is>
-      </c>
-      <c r="I35" s="31" t="n"/>
-      <c r="J35" s="31" t="n"/>
-      <c r="K35" s="31" t="n"/>
-      <c r="L35" s="31" t="n"/>
-      <c r="M35" s="31" t="n"/>
-      <c r="N35" s="31" t="n"/>
-      <c r="O35" s="31" t="n"/>
-      <c r="P35" s="31" t="n"/>
-      <c r="Q35" s="31" t="n"/>
-      <c r="R35" s="31" t="n"/>
-      <c r="S35" s="31" t="n"/>
-      <c r="T35" s="31" t="n"/>
-      <c r="U35" s="31" t="n"/>
-    </row>
-    <row r="36" ht="62" customHeight="1">
-      <c r="B36" s="28" t="inlineStr"/>
-      <c r="C36" s="29" t="inlineStr">
-        <is>
-          <t>What to go and ask</t>
-        </is>
-      </c>
-      <c r="D36" s="30" t="inlineStr">
-        <is>
-          <t>the demo agenda</t>
-        </is>
-      </c>
-      <c r="E36" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F36" s="31" t="inlineStr">
+      <c r="F45" s="34" t="inlineStr">
         <is>
           <t>Would they discuss a stake? Never mentioned it.</t>
         </is>
       </c>
-      <c r="G36" s="31" t="inlineStr">
+      <c r="G45" s="34" t="inlineStr">
         <is>
           <t>What does the day-before confirmation round cost in staff hours at our scale?</t>
         </is>
       </c>
-      <c r="H36" s="31" t="inlineStr">
+      <c r="H45" s="34" t="inlineStr">
         <is>
           <t>What exactly is committed on the integration date, and by whom?</t>
         </is>
       </c>
-      <c r="I36" s="31" t="n"/>
-      <c r="J36" s="31" t="n"/>
-      <c r="K36" s="31" t="n"/>
-      <c r="L36" s="31" t="n"/>
-      <c r="M36" s="31" t="n"/>
-      <c r="N36" s="31" t="n"/>
-      <c r="O36" s="31" t="n"/>
-      <c r="P36" s="31" t="n"/>
-      <c r="Q36" s="31" t="n"/>
-      <c r="R36" s="31" t="n"/>
-      <c r="S36" s="31" t="n"/>
-      <c r="T36" s="31" t="n"/>
-      <c r="U36" s="31" t="n"/>
+      <c r="I45" s="34" t="n"/>
+      <c r="J45" s="34" t="n"/>
+      <c r="K45" s="34" t="n"/>
+      <c r="L45" s="34" t="n"/>
+      <c r="M45" s="34" t="n"/>
+      <c r="N45" s="34" t="n"/>
+      <c r="O45" s="34" t="n"/>
+      <c r="P45" s="34" t="n"/>
+      <c r="Q45" s="34" t="n"/>
+      <c r="R45" s="34" t="n"/>
+      <c r="S45" s="34" t="n"/>
+      <c r="T45" s="34" t="n"/>
+      <c r="U45" s="34" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="11">
     <mergeCell ref="B23:U23"/>
     <mergeCell ref="B27:U27"/>
     <mergeCell ref="B8:U8"/>
+    <mergeCell ref="B32:U32"/>
     <mergeCell ref="B4:U4"/>
     <mergeCell ref="B18:U18"/>
     <mergeCell ref="B13:U13"/>
-    <mergeCell ref="B30:U30"/>
-    <mergeCell ref="B33:U33"/>
+    <mergeCell ref="B39:U39"/>
+    <mergeCell ref="B42:U42"/>
+    <mergeCell ref="B19:U19"/>
+    <mergeCell ref="B36:U36"/>
   </mergeCells>
   <conditionalFormatting sqref="F9:U9">
     <cfRule type="colorScale" priority="1">
@@ -1835,36 +2171,96 @@
       <formula>F16="STOP-CHECK"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F25:U25">
+  <conditionalFormatting sqref="F34:U34">
     <cfRule type="expression" priority="6" dxfId="1">
-      <formula>F25="STOP-CHECK"</formula>
+      <formula>F34="STOP-CHECK"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F19:U19">
+  <conditionalFormatting sqref="F20:U20">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="num" val="0"/>
-        <cfvo type="num" val="5"/>
+        <cfvo type="num" val="4"/>
         <color rgb="00FFFFFF"/>
         <color rgb="001F6F78"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F20:U20">
+  <conditionalFormatting sqref="F21:U21">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="num" val="0"/>
-        <cfvo type="num" val="5"/>
+        <cfvo type="num" val="4"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="001F6F78"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F22:U22">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="4"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="001F6F78"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F24:U24">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="4"/>
         <color rgb="00FFFFFF"/>
         <color rgb="002E599D"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F21:U21">
-    <cfRule type="colorScale" priority="9">
+  <conditionalFormatting sqref="F25:U25">
+    <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="num" val="0"/>
-        <cfvo type="num" val="5"/>
+        <cfvo type="num" val="4"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="002E599D"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F26:U26">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="4"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="002E599D"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F28:U28">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="4"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="004E8A5B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F29:U29">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="4"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="004E8A5B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F30:U30">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="4"/>
         <color rgb="00FFFFFF"/>
         <color rgb="004E8A5B"/>
       </colorScale>
@@ -1874,19 +2270,19 @@
     <dataValidation sqref="F14:U14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="A1 — Home Care Home Base" prompt="Pick one line. Ambiguous? Take the lower one and say so in Notes." type="list">
       <formula1>=HCHB_List</formula1>
     </dataValidation>
-    <dataValidation sqref="F19:U19 F20:U20 F21:U21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Scope, 0–5" prompt="How much of this arena they cover. Most of it is the ceiling — our spec is original, so nobody covers all of it." type="list">
+    <dataValidation sqref="F20:U20 F21:U21 F22:U22 F24:U24 F25:U25 F26:U26 F28:U28 F29:U29 F30:U30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Scope, 0–4" prompt="How much of this area they cover. The mark is the points: a 3 adds 3. Most of it is the ceiling — our spec is original." type="list">
       <formula1>=Scope_List</formula1>
     </dataValidation>
-    <dataValidation sqref="F24:U24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Sophistication, 0–4" prompt="1 shows it · 2 checks it · 3 recommends it · 4 runs it. Score what the product does, not how much they wrote about it." type="list">
+    <dataValidation sqref="F33:U33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Sophistication, 0–4" prompt="1 shows it · 2 checks it · 3 recommends it · 4 runs it. Score what the product does, not how much they wrote about it." type="list">
       <formula1>=Soph_List</formula1>
     </dataValidation>
-    <dataValidation sqref="F28:U28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Clinician fit, 0–4" prompt="Read D1 to D3 and give it your own read of fit. There is no checklist here on purpose." type="list">
+    <dataValidation sqref="F37:U37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Clinician fit, 0–4" prompt="Read D1 to D3 and give it your own read of fit. There is no checklist here on purpose." type="list">
       <formula1>=Clin_List</formula1>
     </dataValidation>
-    <dataValidation sqref="F31:U31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Partnership, 0–4" prompt="Are they able and willing to build this with us, and open to us holding a stake in what a wider market might buy? A discount is a discount." type="list">
+    <dataValidation sqref="F40:U40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Partnership, 0–4" prompt="Are they able and willing to build this with us, and open to us holding a stake in what a wider market might buy? A discount is a discount." type="list">
       <formula1>=Part_List</formula1>
     </dataValidation>
-    <dataValidation sqref="F15:U15 F16:U16 F25:U25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Flag" prompt="A stop-check is resolved before advancing, not traded against points." type="list">
+    <dataValidation sqref="F15:U15 F16:U16 F34:U34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Flag" prompt="A stop-check is resolved before advancing, not traded against points." type="list">
       <formula1>"OK,Watch,STOP-CHECK"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1901,7 +2297,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:U36"/>
+  <dimension ref="B2:U45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -2059,67 +2455,67 @@
         </is>
       </c>
       <c r="F9" s="10">
-        <f>IF(F14="","",IFERROR(VLOOKUP(F14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(F19,1)),0)/5*12+IFERROR(VALUE(LEFT(F20,1)),0)/5*12+IFERROR(VALUE(LEFT(F21,1)),0)/5*12+IFERROR(VALUE(LEFT(F24,1)),0)/4*20+IFERROR(VALUE(LEFT(F28,1)),0)/4*12+IFERROR(VALUE(LEFT(F31,1)),0)/4*12)</f>
+        <f>IF(F14="","",IFERROR(VLOOKUP(F14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(F20,1)),0)/4*4+IFERROR(VALUE(LEFT(F21,1)),0)/4*4+IFERROR(VALUE(LEFT(F22,1)),0)/4*4+IFERROR(VALUE(LEFT(F24,1)),0)/4*4+IFERROR(VALUE(LEFT(F25,1)),0)/4*4+IFERROR(VALUE(LEFT(F26,1)),0)/4*4+IFERROR(VALUE(LEFT(F28,1)),0)/4*4+IFERROR(VALUE(LEFT(F29,1)),0)/4*4+IFERROR(VALUE(LEFT(F30,1)),0)/4*4+IFERROR(VALUE(LEFT(F33,1)),0)/4*20+IFERROR(VALUE(LEFT(F37,1)),0)/4*12+IFERROR(VALUE(LEFT(F40,1)),0)/4*12)</f>
         <v/>
       </c>
       <c r="G9" s="10">
-        <f>IF(G14="","",IFERROR(VLOOKUP(G14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(G19,1)),0)/5*12+IFERROR(VALUE(LEFT(G20,1)),0)/5*12+IFERROR(VALUE(LEFT(G21,1)),0)/5*12+IFERROR(VALUE(LEFT(G24,1)),0)/4*20+IFERROR(VALUE(LEFT(G28,1)),0)/4*12+IFERROR(VALUE(LEFT(G31,1)),0)/4*12)</f>
+        <f>IF(G14="","",IFERROR(VLOOKUP(G14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(G20,1)),0)/4*4+IFERROR(VALUE(LEFT(G21,1)),0)/4*4+IFERROR(VALUE(LEFT(G22,1)),0)/4*4+IFERROR(VALUE(LEFT(G24,1)),0)/4*4+IFERROR(VALUE(LEFT(G25,1)),0)/4*4+IFERROR(VALUE(LEFT(G26,1)),0)/4*4+IFERROR(VALUE(LEFT(G28,1)),0)/4*4+IFERROR(VALUE(LEFT(G29,1)),0)/4*4+IFERROR(VALUE(LEFT(G30,1)),0)/4*4+IFERROR(VALUE(LEFT(G33,1)),0)/4*20+IFERROR(VALUE(LEFT(G37,1)),0)/4*12+IFERROR(VALUE(LEFT(G40,1)),0)/4*12)</f>
         <v/>
       </c>
       <c r="H9" s="10">
-        <f>IF(H14="","",IFERROR(VLOOKUP(H14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(H19,1)),0)/5*12+IFERROR(VALUE(LEFT(H20,1)),0)/5*12+IFERROR(VALUE(LEFT(H21,1)),0)/5*12+IFERROR(VALUE(LEFT(H24,1)),0)/4*20+IFERROR(VALUE(LEFT(H28,1)),0)/4*12+IFERROR(VALUE(LEFT(H31,1)),0)/4*12)</f>
+        <f>IF(H14="","",IFERROR(VLOOKUP(H14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(H20,1)),0)/4*4+IFERROR(VALUE(LEFT(H21,1)),0)/4*4+IFERROR(VALUE(LEFT(H22,1)),0)/4*4+IFERROR(VALUE(LEFT(H24,1)),0)/4*4+IFERROR(VALUE(LEFT(H25,1)),0)/4*4+IFERROR(VALUE(LEFT(H26,1)),0)/4*4+IFERROR(VALUE(LEFT(H28,1)),0)/4*4+IFERROR(VALUE(LEFT(H29,1)),0)/4*4+IFERROR(VALUE(LEFT(H30,1)),0)/4*4+IFERROR(VALUE(LEFT(H33,1)),0)/4*20+IFERROR(VALUE(LEFT(H37,1)),0)/4*12+IFERROR(VALUE(LEFT(H40,1)),0)/4*12)</f>
         <v/>
       </c>
       <c r="I9" s="10">
-        <f>IF(I14="","",IFERROR(VLOOKUP(I14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(I19,1)),0)/5*12+IFERROR(VALUE(LEFT(I20,1)),0)/5*12+IFERROR(VALUE(LEFT(I21,1)),0)/5*12+IFERROR(VALUE(LEFT(I24,1)),0)/4*20+IFERROR(VALUE(LEFT(I28,1)),0)/4*12+IFERROR(VALUE(LEFT(I31,1)),0)/4*12)</f>
+        <f>IF(I14="","",IFERROR(VLOOKUP(I14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(I20,1)),0)/4*4+IFERROR(VALUE(LEFT(I21,1)),0)/4*4+IFERROR(VALUE(LEFT(I22,1)),0)/4*4+IFERROR(VALUE(LEFT(I24,1)),0)/4*4+IFERROR(VALUE(LEFT(I25,1)),0)/4*4+IFERROR(VALUE(LEFT(I26,1)),0)/4*4+IFERROR(VALUE(LEFT(I28,1)),0)/4*4+IFERROR(VALUE(LEFT(I29,1)),0)/4*4+IFERROR(VALUE(LEFT(I30,1)),0)/4*4+IFERROR(VALUE(LEFT(I33,1)),0)/4*20+IFERROR(VALUE(LEFT(I37,1)),0)/4*12+IFERROR(VALUE(LEFT(I40,1)),0)/4*12)</f>
         <v/>
       </c>
       <c r="J9" s="10">
-        <f>IF(J14="","",IFERROR(VLOOKUP(J14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(J19,1)),0)/5*12+IFERROR(VALUE(LEFT(J20,1)),0)/5*12+IFERROR(VALUE(LEFT(J21,1)),0)/5*12+IFERROR(VALUE(LEFT(J24,1)),0)/4*20+IFERROR(VALUE(LEFT(J28,1)),0)/4*12+IFERROR(VALUE(LEFT(J31,1)),0)/4*12)</f>
+        <f>IF(J14="","",IFERROR(VLOOKUP(J14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(J20,1)),0)/4*4+IFERROR(VALUE(LEFT(J21,1)),0)/4*4+IFERROR(VALUE(LEFT(J22,1)),0)/4*4+IFERROR(VALUE(LEFT(J24,1)),0)/4*4+IFERROR(VALUE(LEFT(J25,1)),0)/4*4+IFERROR(VALUE(LEFT(J26,1)),0)/4*4+IFERROR(VALUE(LEFT(J28,1)),0)/4*4+IFERROR(VALUE(LEFT(J29,1)),0)/4*4+IFERROR(VALUE(LEFT(J30,1)),0)/4*4+IFERROR(VALUE(LEFT(J33,1)),0)/4*20+IFERROR(VALUE(LEFT(J37,1)),0)/4*12+IFERROR(VALUE(LEFT(J40,1)),0)/4*12)</f>
         <v/>
       </c>
       <c r="K9" s="10">
-        <f>IF(K14="","",IFERROR(VLOOKUP(K14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(K19,1)),0)/5*12+IFERROR(VALUE(LEFT(K20,1)),0)/5*12+IFERROR(VALUE(LEFT(K21,1)),0)/5*12+IFERROR(VALUE(LEFT(K24,1)),0)/4*20+IFERROR(VALUE(LEFT(K28,1)),0)/4*12+IFERROR(VALUE(LEFT(K31,1)),0)/4*12)</f>
+        <f>IF(K14="","",IFERROR(VLOOKUP(K14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(K20,1)),0)/4*4+IFERROR(VALUE(LEFT(K21,1)),0)/4*4+IFERROR(VALUE(LEFT(K22,1)),0)/4*4+IFERROR(VALUE(LEFT(K24,1)),0)/4*4+IFERROR(VALUE(LEFT(K25,1)),0)/4*4+IFERROR(VALUE(LEFT(K26,1)),0)/4*4+IFERROR(VALUE(LEFT(K28,1)),0)/4*4+IFERROR(VALUE(LEFT(K29,1)),0)/4*4+IFERROR(VALUE(LEFT(K30,1)),0)/4*4+IFERROR(VALUE(LEFT(K33,1)),0)/4*20+IFERROR(VALUE(LEFT(K37,1)),0)/4*12+IFERROR(VALUE(LEFT(K40,1)),0)/4*12)</f>
         <v/>
       </c>
       <c r="L9" s="10">
-        <f>IF(L14="","",IFERROR(VLOOKUP(L14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(L19,1)),0)/5*12+IFERROR(VALUE(LEFT(L20,1)),0)/5*12+IFERROR(VALUE(LEFT(L21,1)),0)/5*12+IFERROR(VALUE(LEFT(L24,1)),0)/4*20+IFERROR(VALUE(LEFT(L28,1)),0)/4*12+IFERROR(VALUE(LEFT(L31,1)),0)/4*12)</f>
+        <f>IF(L14="","",IFERROR(VLOOKUP(L14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(L20,1)),0)/4*4+IFERROR(VALUE(LEFT(L21,1)),0)/4*4+IFERROR(VALUE(LEFT(L22,1)),0)/4*4+IFERROR(VALUE(LEFT(L24,1)),0)/4*4+IFERROR(VALUE(LEFT(L25,1)),0)/4*4+IFERROR(VALUE(LEFT(L26,1)),0)/4*4+IFERROR(VALUE(LEFT(L28,1)),0)/4*4+IFERROR(VALUE(LEFT(L29,1)),0)/4*4+IFERROR(VALUE(LEFT(L30,1)),0)/4*4+IFERROR(VALUE(LEFT(L33,1)),0)/4*20+IFERROR(VALUE(LEFT(L37,1)),0)/4*12+IFERROR(VALUE(LEFT(L40,1)),0)/4*12)</f>
         <v/>
       </c>
       <c r="M9" s="10">
-        <f>IF(M14="","",IFERROR(VLOOKUP(M14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(M19,1)),0)/5*12+IFERROR(VALUE(LEFT(M20,1)),0)/5*12+IFERROR(VALUE(LEFT(M21,1)),0)/5*12+IFERROR(VALUE(LEFT(M24,1)),0)/4*20+IFERROR(VALUE(LEFT(M28,1)),0)/4*12+IFERROR(VALUE(LEFT(M31,1)),0)/4*12)</f>
+        <f>IF(M14="","",IFERROR(VLOOKUP(M14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(M20,1)),0)/4*4+IFERROR(VALUE(LEFT(M21,1)),0)/4*4+IFERROR(VALUE(LEFT(M22,1)),0)/4*4+IFERROR(VALUE(LEFT(M24,1)),0)/4*4+IFERROR(VALUE(LEFT(M25,1)),0)/4*4+IFERROR(VALUE(LEFT(M26,1)),0)/4*4+IFERROR(VALUE(LEFT(M28,1)),0)/4*4+IFERROR(VALUE(LEFT(M29,1)),0)/4*4+IFERROR(VALUE(LEFT(M30,1)),0)/4*4+IFERROR(VALUE(LEFT(M33,1)),0)/4*20+IFERROR(VALUE(LEFT(M37,1)),0)/4*12+IFERROR(VALUE(LEFT(M40,1)),0)/4*12)</f>
         <v/>
       </c>
       <c r="N9" s="10">
-        <f>IF(N14="","",IFERROR(VLOOKUP(N14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(N19,1)),0)/5*12+IFERROR(VALUE(LEFT(N20,1)),0)/5*12+IFERROR(VALUE(LEFT(N21,1)),0)/5*12+IFERROR(VALUE(LEFT(N24,1)),0)/4*20+IFERROR(VALUE(LEFT(N28,1)),0)/4*12+IFERROR(VALUE(LEFT(N31,1)),0)/4*12)</f>
+        <f>IF(N14="","",IFERROR(VLOOKUP(N14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(N20,1)),0)/4*4+IFERROR(VALUE(LEFT(N21,1)),0)/4*4+IFERROR(VALUE(LEFT(N22,1)),0)/4*4+IFERROR(VALUE(LEFT(N24,1)),0)/4*4+IFERROR(VALUE(LEFT(N25,1)),0)/4*4+IFERROR(VALUE(LEFT(N26,1)),0)/4*4+IFERROR(VALUE(LEFT(N28,1)),0)/4*4+IFERROR(VALUE(LEFT(N29,1)),0)/4*4+IFERROR(VALUE(LEFT(N30,1)),0)/4*4+IFERROR(VALUE(LEFT(N33,1)),0)/4*20+IFERROR(VALUE(LEFT(N37,1)),0)/4*12+IFERROR(VALUE(LEFT(N40,1)),0)/4*12)</f>
         <v/>
       </c>
       <c r="O9" s="10">
-        <f>IF(O14="","",IFERROR(VLOOKUP(O14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(O19,1)),0)/5*12+IFERROR(VALUE(LEFT(O20,1)),0)/5*12+IFERROR(VALUE(LEFT(O21,1)),0)/5*12+IFERROR(VALUE(LEFT(O24,1)),0)/4*20+IFERROR(VALUE(LEFT(O28,1)),0)/4*12+IFERROR(VALUE(LEFT(O31,1)),0)/4*12)</f>
+        <f>IF(O14="","",IFERROR(VLOOKUP(O14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(O20,1)),0)/4*4+IFERROR(VALUE(LEFT(O21,1)),0)/4*4+IFERROR(VALUE(LEFT(O22,1)),0)/4*4+IFERROR(VALUE(LEFT(O24,1)),0)/4*4+IFERROR(VALUE(LEFT(O25,1)),0)/4*4+IFERROR(VALUE(LEFT(O26,1)),0)/4*4+IFERROR(VALUE(LEFT(O28,1)),0)/4*4+IFERROR(VALUE(LEFT(O29,1)),0)/4*4+IFERROR(VALUE(LEFT(O30,1)),0)/4*4+IFERROR(VALUE(LEFT(O33,1)),0)/4*20+IFERROR(VALUE(LEFT(O37,1)),0)/4*12+IFERROR(VALUE(LEFT(O40,1)),0)/4*12)</f>
         <v/>
       </c>
       <c r="P9" s="10">
-        <f>IF(P14="","",IFERROR(VLOOKUP(P14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(P19,1)),0)/5*12+IFERROR(VALUE(LEFT(P20,1)),0)/5*12+IFERROR(VALUE(LEFT(P21,1)),0)/5*12+IFERROR(VALUE(LEFT(P24,1)),0)/4*20+IFERROR(VALUE(LEFT(P28,1)),0)/4*12+IFERROR(VALUE(LEFT(P31,1)),0)/4*12)</f>
+        <f>IF(P14="","",IFERROR(VLOOKUP(P14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(P20,1)),0)/4*4+IFERROR(VALUE(LEFT(P21,1)),0)/4*4+IFERROR(VALUE(LEFT(P22,1)),0)/4*4+IFERROR(VALUE(LEFT(P24,1)),0)/4*4+IFERROR(VALUE(LEFT(P25,1)),0)/4*4+IFERROR(VALUE(LEFT(P26,1)),0)/4*4+IFERROR(VALUE(LEFT(P28,1)),0)/4*4+IFERROR(VALUE(LEFT(P29,1)),0)/4*4+IFERROR(VALUE(LEFT(P30,1)),0)/4*4+IFERROR(VALUE(LEFT(P33,1)),0)/4*20+IFERROR(VALUE(LEFT(P37,1)),0)/4*12+IFERROR(VALUE(LEFT(P40,1)),0)/4*12)</f>
         <v/>
       </c>
       <c r="Q9" s="10">
-        <f>IF(Q14="","",IFERROR(VLOOKUP(Q14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(Q19,1)),0)/5*12+IFERROR(VALUE(LEFT(Q20,1)),0)/5*12+IFERROR(VALUE(LEFT(Q21,1)),0)/5*12+IFERROR(VALUE(LEFT(Q24,1)),0)/4*20+IFERROR(VALUE(LEFT(Q28,1)),0)/4*12+IFERROR(VALUE(LEFT(Q31,1)),0)/4*12)</f>
+        <f>IF(Q14="","",IFERROR(VLOOKUP(Q14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(Q20,1)),0)/4*4+IFERROR(VALUE(LEFT(Q21,1)),0)/4*4+IFERROR(VALUE(LEFT(Q22,1)),0)/4*4+IFERROR(VALUE(LEFT(Q24,1)),0)/4*4+IFERROR(VALUE(LEFT(Q25,1)),0)/4*4+IFERROR(VALUE(LEFT(Q26,1)),0)/4*4+IFERROR(VALUE(LEFT(Q28,1)),0)/4*4+IFERROR(VALUE(LEFT(Q29,1)),0)/4*4+IFERROR(VALUE(LEFT(Q30,1)),0)/4*4+IFERROR(VALUE(LEFT(Q33,1)),0)/4*20+IFERROR(VALUE(LEFT(Q37,1)),0)/4*12+IFERROR(VALUE(LEFT(Q40,1)),0)/4*12)</f>
         <v/>
       </c>
       <c r="R9" s="10">
-        <f>IF(R14="","",IFERROR(VLOOKUP(R14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(R19,1)),0)/5*12+IFERROR(VALUE(LEFT(R20,1)),0)/5*12+IFERROR(VALUE(LEFT(R21,1)),0)/5*12+IFERROR(VALUE(LEFT(R24,1)),0)/4*20+IFERROR(VALUE(LEFT(R28,1)),0)/4*12+IFERROR(VALUE(LEFT(R31,1)),0)/4*12)</f>
+        <f>IF(R14="","",IFERROR(VLOOKUP(R14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(R20,1)),0)/4*4+IFERROR(VALUE(LEFT(R21,1)),0)/4*4+IFERROR(VALUE(LEFT(R22,1)),0)/4*4+IFERROR(VALUE(LEFT(R24,1)),0)/4*4+IFERROR(VALUE(LEFT(R25,1)),0)/4*4+IFERROR(VALUE(LEFT(R26,1)),0)/4*4+IFERROR(VALUE(LEFT(R28,1)),0)/4*4+IFERROR(VALUE(LEFT(R29,1)),0)/4*4+IFERROR(VALUE(LEFT(R30,1)),0)/4*4+IFERROR(VALUE(LEFT(R33,1)),0)/4*20+IFERROR(VALUE(LEFT(R37,1)),0)/4*12+IFERROR(VALUE(LEFT(R40,1)),0)/4*12)</f>
         <v/>
       </c>
       <c r="S9" s="10">
-        <f>IF(S14="","",IFERROR(VLOOKUP(S14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(S19,1)),0)/5*12+IFERROR(VALUE(LEFT(S20,1)),0)/5*12+IFERROR(VALUE(LEFT(S21,1)),0)/5*12+IFERROR(VALUE(LEFT(S24,1)),0)/4*20+IFERROR(VALUE(LEFT(S28,1)),0)/4*12+IFERROR(VALUE(LEFT(S31,1)),0)/4*12)</f>
+        <f>IF(S14="","",IFERROR(VLOOKUP(S14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(S20,1)),0)/4*4+IFERROR(VALUE(LEFT(S21,1)),0)/4*4+IFERROR(VALUE(LEFT(S22,1)),0)/4*4+IFERROR(VALUE(LEFT(S24,1)),0)/4*4+IFERROR(VALUE(LEFT(S25,1)),0)/4*4+IFERROR(VALUE(LEFT(S26,1)),0)/4*4+IFERROR(VALUE(LEFT(S28,1)),0)/4*4+IFERROR(VALUE(LEFT(S29,1)),0)/4*4+IFERROR(VALUE(LEFT(S30,1)),0)/4*4+IFERROR(VALUE(LEFT(S33,1)),0)/4*20+IFERROR(VALUE(LEFT(S37,1)),0)/4*12+IFERROR(VALUE(LEFT(S40,1)),0)/4*12)</f>
         <v/>
       </c>
       <c r="T9" s="10">
-        <f>IF(T14="","",IFERROR(VLOOKUP(T14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(T19,1)),0)/5*12+IFERROR(VALUE(LEFT(T20,1)),0)/5*12+IFERROR(VALUE(LEFT(T21,1)),0)/5*12+IFERROR(VALUE(LEFT(T24,1)),0)/4*20+IFERROR(VALUE(LEFT(T28,1)),0)/4*12+IFERROR(VALUE(LEFT(T31,1)),0)/4*12)</f>
+        <f>IF(T14="","",IFERROR(VLOOKUP(T14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(T20,1)),0)/4*4+IFERROR(VALUE(LEFT(T21,1)),0)/4*4+IFERROR(VALUE(LEFT(T22,1)),0)/4*4+IFERROR(VALUE(LEFT(T24,1)),0)/4*4+IFERROR(VALUE(LEFT(T25,1)),0)/4*4+IFERROR(VALUE(LEFT(T26,1)),0)/4*4+IFERROR(VALUE(LEFT(T28,1)),0)/4*4+IFERROR(VALUE(LEFT(T29,1)),0)/4*4+IFERROR(VALUE(LEFT(T30,1)),0)/4*4+IFERROR(VALUE(LEFT(T33,1)),0)/4*20+IFERROR(VALUE(LEFT(T37,1)),0)/4*12+IFERROR(VALUE(LEFT(T40,1)),0)/4*12)</f>
         <v/>
       </c>
       <c r="U9" s="10">
-        <f>IF(U14="","",IFERROR(VLOOKUP(U14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(U19,1)),0)/5*12+IFERROR(VALUE(LEFT(U20,1)),0)/5*12+IFERROR(VALUE(LEFT(U21,1)),0)/5*12+IFERROR(VALUE(LEFT(U24,1)),0)/4*20+IFERROR(VALUE(LEFT(U28,1)),0)/4*12+IFERROR(VALUE(LEFT(U31,1)),0)/4*12)</f>
+        <f>IF(U14="","",IFERROR(VLOOKUP(U14,Lists!$B$2:$C$7,2,FALSE),0)+IFERROR(VALUE(LEFT(U20,1)),0)/4*4+IFERROR(VALUE(LEFT(U21,1)),0)/4*4+IFERROR(VALUE(LEFT(U22,1)),0)/4*4+IFERROR(VALUE(LEFT(U24,1)),0)/4*4+IFERROR(VALUE(LEFT(U25,1)),0)/4*4+IFERROR(VALUE(LEFT(U26,1)),0)/4*4+IFERROR(VALUE(LEFT(U28,1)),0)/4*4+IFERROR(VALUE(LEFT(U29,1)),0)/4*4+IFERROR(VALUE(LEFT(U30,1)),0)/4*4+IFERROR(VALUE(LEFT(U33,1)),0)/4*20+IFERROR(VALUE(LEFT(U37,1)),0)/4*12+IFERROR(VALUE(LEFT(U40,1)),0)/4*12)</f>
         <v/>
       </c>
     </row>
@@ -2211,67 +2607,67 @@
         </is>
       </c>
       <c r="F11" s="14">
-        <f>IF(F14="","",IF(F15="STOP-CHECK",1,0)+IF(F16="STOP-CHECK",1,0)+IF(F25="STOP-CHECK",1,0))</f>
+        <f>IF(F14="","",IF(F15="STOP-CHECK",1,0)+IF(F16="STOP-CHECK",1,0)+IF(F34="STOP-CHECK",1,0))</f>
         <v/>
       </c>
       <c r="G11" s="14">
-        <f>IF(G14="","",IF(G15="STOP-CHECK",1,0)+IF(G16="STOP-CHECK",1,0)+IF(G25="STOP-CHECK",1,0))</f>
+        <f>IF(G14="","",IF(G15="STOP-CHECK",1,0)+IF(G16="STOP-CHECK",1,0)+IF(G34="STOP-CHECK",1,0))</f>
         <v/>
       </c>
       <c r="H11" s="14">
-        <f>IF(H14="","",IF(H15="STOP-CHECK",1,0)+IF(H16="STOP-CHECK",1,0)+IF(H25="STOP-CHECK",1,0))</f>
+        <f>IF(H14="","",IF(H15="STOP-CHECK",1,0)+IF(H16="STOP-CHECK",1,0)+IF(H34="STOP-CHECK",1,0))</f>
         <v/>
       </c>
       <c r="I11" s="14">
-        <f>IF(I14="","",IF(I15="STOP-CHECK",1,0)+IF(I16="STOP-CHECK",1,0)+IF(I25="STOP-CHECK",1,0))</f>
+        <f>IF(I14="","",IF(I15="STOP-CHECK",1,0)+IF(I16="STOP-CHECK",1,0)+IF(I34="STOP-CHECK",1,0))</f>
         <v/>
       </c>
       <c r="J11" s="14">
-        <f>IF(J14="","",IF(J15="STOP-CHECK",1,0)+IF(J16="STOP-CHECK",1,0)+IF(J25="STOP-CHECK",1,0))</f>
+        <f>IF(J14="","",IF(J15="STOP-CHECK",1,0)+IF(J16="STOP-CHECK",1,0)+IF(J34="STOP-CHECK",1,0))</f>
         <v/>
       </c>
       <c r="K11" s="14">
-        <f>IF(K14="","",IF(K15="STOP-CHECK",1,0)+IF(K16="STOP-CHECK",1,0)+IF(K25="STOP-CHECK",1,0))</f>
+        <f>IF(K14="","",IF(K15="STOP-CHECK",1,0)+IF(K16="STOP-CHECK",1,0)+IF(K34="STOP-CHECK",1,0))</f>
         <v/>
       </c>
       <c r="L11" s="14">
-        <f>IF(L14="","",IF(L15="STOP-CHECK",1,0)+IF(L16="STOP-CHECK",1,0)+IF(L25="STOP-CHECK",1,0))</f>
+        <f>IF(L14="","",IF(L15="STOP-CHECK",1,0)+IF(L16="STOP-CHECK",1,0)+IF(L34="STOP-CHECK",1,0))</f>
         <v/>
       </c>
       <c r="M11" s="14">
-        <f>IF(M14="","",IF(M15="STOP-CHECK",1,0)+IF(M16="STOP-CHECK",1,0)+IF(M25="STOP-CHECK",1,0))</f>
+        <f>IF(M14="","",IF(M15="STOP-CHECK",1,0)+IF(M16="STOP-CHECK",1,0)+IF(M34="STOP-CHECK",1,0))</f>
         <v/>
       </c>
       <c r="N11" s="14">
-        <f>IF(N14="","",IF(N15="STOP-CHECK",1,0)+IF(N16="STOP-CHECK",1,0)+IF(N25="STOP-CHECK",1,0))</f>
+        <f>IF(N14="","",IF(N15="STOP-CHECK",1,0)+IF(N16="STOP-CHECK",1,0)+IF(N34="STOP-CHECK",1,0))</f>
         <v/>
       </c>
       <c r="O11" s="14">
-        <f>IF(O14="","",IF(O15="STOP-CHECK",1,0)+IF(O16="STOP-CHECK",1,0)+IF(O25="STOP-CHECK",1,0))</f>
+        <f>IF(O14="","",IF(O15="STOP-CHECK",1,0)+IF(O16="STOP-CHECK",1,0)+IF(O34="STOP-CHECK",1,0))</f>
         <v/>
       </c>
       <c r="P11" s="14">
-        <f>IF(P14="","",IF(P15="STOP-CHECK",1,0)+IF(P16="STOP-CHECK",1,0)+IF(P25="STOP-CHECK",1,0))</f>
+        <f>IF(P14="","",IF(P15="STOP-CHECK",1,0)+IF(P16="STOP-CHECK",1,0)+IF(P34="STOP-CHECK",1,0))</f>
         <v/>
       </c>
       <c r="Q11" s="14">
-        <f>IF(Q14="","",IF(Q15="STOP-CHECK",1,0)+IF(Q16="STOP-CHECK",1,0)+IF(Q25="STOP-CHECK",1,0))</f>
+        <f>IF(Q14="","",IF(Q15="STOP-CHECK",1,0)+IF(Q16="STOP-CHECK",1,0)+IF(Q34="STOP-CHECK",1,0))</f>
         <v/>
       </c>
       <c r="R11" s="14">
-        <f>IF(R14="","",IF(R15="STOP-CHECK",1,0)+IF(R16="STOP-CHECK",1,0)+IF(R25="STOP-CHECK",1,0))</f>
+        <f>IF(R14="","",IF(R15="STOP-CHECK",1,0)+IF(R16="STOP-CHECK",1,0)+IF(R34="STOP-CHECK",1,0))</f>
         <v/>
       </c>
       <c r="S11" s="14">
-        <f>IF(S14="","",IF(S15="STOP-CHECK",1,0)+IF(S16="STOP-CHECK",1,0)+IF(S25="STOP-CHECK",1,0))</f>
+        <f>IF(S14="","",IF(S15="STOP-CHECK",1,0)+IF(S16="STOP-CHECK",1,0)+IF(S34="STOP-CHECK",1,0))</f>
         <v/>
       </c>
       <c r="T11" s="14">
-        <f>IF(T14="","",IF(T15="STOP-CHECK",1,0)+IF(T16="STOP-CHECK",1,0)+IF(T25="STOP-CHECK",1,0))</f>
+        <f>IF(T14="","",IF(T15="STOP-CHECK",1,0)+IF(T16="STOP-CHECK",1,0)+IF(T34="STOP-CHECK",1,0))</f>
         <v/>
       </c>
       <c r="U11" s="14">
-        <f>IF(U14="","",IF(U15="STOP-CHECK",1,0)+IF(U16="STOP-CHECK",1,0)+IF(U25="STOP-CHECK",1,0))</f>
+        <f>IF(U14="","",IF(U15="STOP-CHECK",1,0)+IF(U16="STOP-CHECK",1,0)+IF(U34="STOP-CHECK",1,0))</f>
         <v/>
       </c>
     </row>
@@ -2401,400 +2797,640 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="30" customHeight="1">
+    <row r="19" ht="17" customHeight="1">
       <c r="B19" s="21" t="inlineStr">
         <is>
+          <t>CAPACITY   —   three marks, 12 points</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="B20" s="22" t="inlineStr">
+        <is>
           <t>Section B</t>
         </is>
       </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>Capacity</t>
-        </is>
-      </c>
-      <c r="D19" s="9" t="inlineStr">
-        <is>
-          <t>Workforce supply · availability &amp; reach · the capacity math</t>
-        </is>
-      </c>
-      <c r="E19" s="21" t="n">
+      <c r="C20" s="16" t="inlineStr">
+        <is>
+          <t>Workforce supply</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>Roster, disciplines, roles, competencies, ramp, float pool</t>
+        </is>
+      </c>
+      <c r="E20" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="F20" s="23" t="n"/>
+      <c r="G20" s="23" t="n"/>
+      <c r="H20" s="23" t="n"/>
+      <c r="I20" s="23" t="n"/>
+      <c r="J20" s="23" t="n"/>
+      <c r="K20" s="23" t="n"/>
+      <c r="L20" s="23" t="n"/>
+      <c r="M20" s="23" t="n"/>
+      <c r="N20" s="23" t="n"/>
+      <c r="O20" s="23" t="n"/>
+      <c r="P20" s="23" t="n"/>
+      <c r="Q20" s="23" t="n"/>
+      <c r="R20" s="23" t="n"/>
+      <c r="S20" s="23" t="n"/>
+      <c r="T20" s="23" t="n"/>
+      <c r="U20" s="23" t="n"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>Section B</t>
+        </is>
+      </c>
+      <c r="C21" s="16" t="inlineStr">
+        <is>
+          <t>Availability &amp; reach</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>Availability and time off, territory, drive-time reachability</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="F21" s="23" t="n"/>
+      <c r="G21" s="23" t="n"/>
+      <c r="H21" s="23" t="n"/>
+      <c r="I21" s="23" t="n"/>
+      <c r="J21" s="23" t="n"/>
+      <c r="K21" s="23" t="n"/>
+      <c r="L21" s="23" t="n"/>
+      <c r="M21" s="23" t="n"/>
+      <c r="N21" s="23" t="n"/>
+      <c r="O21" s="23" t="n"/>
+      <c r="P21" s="23" t="n"/>
+      <c r="Q21" s="23" t="n"/>
+      <c r="R21" s="23" t="n"/>
+      <c r="S21" s="23" t="n"/>
+      <c r="T21" s="23" t="n"/>
+      <c r="U21" s="23" t="n"/>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>Section B</t>
+        </is>
+      </c>
+      <c r="C22" s="16" t="inlineStr">
+        <is>
+          <t>The capacity math</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>Visit weighting, targets and ceilings, committed load vs. open room</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="F22" s="23" t="n"/>
+      <c r="G22" s="23" t="n"/>
+      <c r="H22" s="23" t="n"/>
+      <c r="I22" s="23" t="n"/>
+      <c r="J22" s="23" t="n"/>
+      <c r="K22" s="23" t="n"/>
+      <c r="L22" s="23" t="n"/>
+      <c r="M22" s="23" t="n"/>
+      <c r="N22" s="23" t="n"/>
+      <c r="O22" s="23" t="n"/>
+      <c r="P22" s="23" t="n"/>
+      <c r="Q22" s="23" t="n"/>
+      <c r="R22" s="23" t="n"/>
+      <c r="S22" s="23" t="n"/>
+      <c r="T22" s="23" t="n"/>
+      <c r="U22" s="23" t="n"/>
+    </row>
+    <row r="23" ht="17" customHeight="1">
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>SCHEDULING   —   three marks, 12 points</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="B24" s="25" t="inlineStr">
+        <is>
+          <t>Section B</t>
+        </is>
+      </c>
+      <c r="C24" s="16" t="inlineStr">
+        <is>
+          <t>Demand &amp; matching</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>Ordered visits, authorization, readiness — and who fits them</t>
+        </is>
+      </c>
+      <c r="E24" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="F24" s="23" t="n"/>
+      <c r="G24" s="23" t="n"/>
+      <c r="H24" s="23" t="n"/>
+      <c r="I24" s="23" t="n"/>
+      <c r="J24" s="23" t="n"/>
+      <c r="K24" s="23" t="n"/>
+      <c r="L24" s="23" t="n"/>
+      <c r="M24" s="23" t="n"/>
+      <c r="N24" s="23" t="n"/>
+      <c r="O24" s="23" t="n"/>
+      <c r="P24" s="23" t="n"/>
+      <c r="Q24" s="23" t="n"/>
+      <c r="R24" s="23" t="n"/>
+      <c r="S24" s="23" t="n"/>
+      <c r="T24" s="23" t="n"/>
+      <c r="U24" s="23" t="n"/>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="B25" s="25" t="inlineStr">
+        <is>
+          <t>Section B</t>
+        </is>
+      </c>
+      <c r="C25" s="16" t="inlineStr">
+        <is>
+          <t>Routing &amp; the week</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>Routing, sequencing, front-loading, week balancing</t>
+        </is>
+      </c>
+      <c r="E25" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="F25" s="23" t="n"/>
+      <c r="G25" s="23" t="n"/>
+      <c r="H25" s="23" t="n"/>
+      <c r="I25" s="23" t="n"/>
+      <c r="J25" s="23" t="n"/>
+      <c r="K25" s="23" t="n"/>
+      <c r="L25" s="23" t="n"/>
+      <c r="M25" s="23" t="n"/>
+      <c r="N25" s="23" t="n"/>
+      <c r="O25" s="23" t="n"/>
+      <c r="P25" s="23" t="n"/>
+      <c r="Q25" s="23" t="n"/>
+      <c r="R25" s="23" t="n"/>
+      <c r="S25" s="23" t="n"/>
+      <c r="T25" s="23" t="n"/>
+      <c r="U25" s="23" t="n"/>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="B26" s="25" t="inlineStr">
+        <is>
+          <t>Section B</t>
+        </is>
+      </c>
+      <c r="C26" s="16" t="inlineStr">
+        <is>
+          <t>Exceptions</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>Missed visits, call-outs, reassignment, coverage, rebooking</t>
+        </is>
+      </c>
+      <c r="E26" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="F26" s="23" t="n"/>
+      <c r="G26" s="23" t="n"/>
+      <c r="H26" s="23" t="n"/>
+      <c r="I26" s="23" t="n"/>
+      <c r="J26" s="23" t="n"/>
+      <c r="K26" s="23" t="n"/>
+      <c r="L26" s="23" t="n"/>
+      <c r="M26" s="23" t="n"/>
+      <c r="N26" s="23" t="n"/>
+      <c r="O26" s="23" t="n"/>
+      <c r="P26" s="23" t="n"/>
+      <c r="Q26" s="23" t="n"/>
+      <c r="R26" s="23" t="n"/>
+      <c r="S26" s="23" t="n"/>
+      <c r="T26" s="23" t="n"/>
+      <c r="U26" s="23" t="n"/>
+    </row>
+    <row r="27" ht="17" customHeight="1">
+      <c r="B27" s="26" t="inlineStr">
+        <is>
+          <t>ENGAGEMENT   —   three marks, 12 points</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="B28" s="27" t="inlineStr">
+        <is>
+          <t>Section B</t>
+        </is>
+      </c>
+      <c r="C28" s="16" t="inlineStr">
+        <is>
+          <t>Before the visit</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>Welcome call, availability capture, reminders, confirmation, en-route</t>
+        </is>
+      </c>
+      <c r="E28" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="F28" s="23" t="n"/>
+      <c r="G28" s="23" t="n"/>
+      <c r="H28" s="23" t="n"/>
+      <c r="I28" s="23" t="n"/>
+      <c r="J28" s="23" t="n"/>
+      <c r="K28" s="23" t="n"/>
+      <c r="L28" s="23" t="n"/>
+      <c r="M28" s="23" t="n"/>
+      <c r="N28" s="23" t="n"/>
+      <c r="O28" s="23" t="n"/>
+      <c r="P28" s="23" t="n"/>
+      <c r="Q28" s="23" t="n"/>
+      <c r="R28" s="23" t="n"/>
+      <c r="S28" s="23" t="n"/>
+      <c r="T28" s="23" t="n"/>
+      <c r="U28" s="23" t="n"/>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="B29" s="27" t="inlineStr">
+        <is>
+          <t>Section B</t>
+        </is>
+      </c>
+      <c r="C29" s="16" t="inlineStr">
+        <is>
+          <t>When plans change</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>Reschedule, coverage outreach, urgent same-day needs, incentives</t>
+        </is>
+      </c>
+      <c r="E29" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="F29" s="23" t="n"/>
+      <c r="G29" s="23" t="n"/>
+      <c r="H29" s="23" t="n"/>
+      <c r="I29" s="23" t="n"/>
+      <c r="J29" s="23" t="n"/>
+      <c r="K29" s="23" t="n"/>
+      <c r="L29" s="23" t="n"/>
+      <c r="M29" s="23" t="n"/>
+      <c r="N29" s="23" t="n"/>
+      <c r="O29" s="23" t="n"/>
+      <c r="P29" s="23" t="n"/>
+      <c r="Q29" s="23" t="n"/>
+      <c r="R29" s="23" t="n"/>
+      <c r="S29" s="23" t="n"/>
+      <c r="T29" s="23" t="n"/>
+      <c r="U29" s="23" t="n"/>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="B30" s="27" t="inlineStr">
+        <is>
+          <t>Section B</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>Across the care team</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>Multi-discipline coordination, clinician and office updates</t>
+        </is>
+      </c>
+      <c r="E30" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="F30" s="23" t="n"/>
+      <c r="G30" s="23" t="n"/>
+      <c r="H30" s="23" t="n"/>
+      <c r="I30" s="23" t="n"/>
+      <c r="J30" s="23" t="n"/>
+      <c r="K30" s="23" t="n"/>
+      <c r="L30" s="23" t="n"/>
+      <c r="M30" s="23" t="n"/>
+      <c r="N30" s="23" t="n"/>
+      <c r="O30" s="23" t="n"/>
+      <c r="P30" s="23" t="n"/>
+      <c r="Q30" s="23" t="n"/>
+      <c r="R30" s="23" t="n"/>
+      <c r="S30" s="23" t="n"/>
+      <c r="T30" s="23" t="n"/>
+      <c r="U30" s="23" t="n"/>
+    </row>
+    <row r="32" ht="21" customHeight="1">
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>C  ·  HOW YOUR PRODUCT WORKS</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="24" customHeight="1">
+      <c r="B33" s="28" t="inlineStr">
+        <is>
+          <t>Section C</t>
+        </is>
+      </c>
+      <c r="C33" s="16" t="inlineStr">
+        <is>
+          <t>Sophistication</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>How much of the work the product does</t>
+        </is>
+      </c>
+      <c r="E33" s="28" t="n">
+        <v>20</v>
+      </c>
+      <c r="F33" s="23" t="n"/>
+      <c r="G33" s="23" t="n"/>
+      <c r="H33" s="23" t="n"/>
+      <c r="I33" s="23" t="n"/>
+      <c r="J33" s="23" t="n"/>
+      <c r="K33" s="23" t="n"/>
+      <c r="L33" s="23" t="n"/>
+      <c r="M33" s="23" t="n"/>
+      <c r="N33" s="23" t="n"/>
+      <c r="O33" s="23" t="n"/>
+      <c r="P33" s="23" t="n"/>
+      <c r="Q33" s="23" t="n"/>
+      <c r="R33" s="23" t="n"/>
+      <c r="S33" s="23" t="n"/>
+      <c r="T33" s="23" t="n"/>
+      <c r="U33" s="23" t="n"/>
+    </row>
+    <row r="34" ht="19" customHeight="1">
+      <c r="B34" s="18" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="C34" s="16" t="inlineStr">
+        <is>
+          <t>When your product is down</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>Stop-check if no uptime figure or contractual commitment</t>
+        </is>
+      </c>
+      <c r="E34" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F34" s="20" t="n"/>
+      <c r="G34" s="20" t="n"/>
+      <c r="H34" s="20" t="n"/>
+      <c r="I34" s="20" t="n"/>
+      <c r="J34" s="20" t="n"/>
+      <c r="K34" s="20" t="n"/>
+      <c r="L34" s="20" t="n"/>
+      <c r="M34" s="20" t="n"/>
+      <c r="N34" s="20" t="n"/>
+      <c r="O34" s="20" t="n"/>
+      <c r="P34" s="20" t="n"/>
+      <c r="Q34" s="20" t="n"/>
+      <c r="R34" s="20" t="n"/>
+      <c r="S34" s="20" t="n"/>
+      <c r="T34" s="20" t="n"/>
+      <c r="U34" s="20" t="n"/>
+    </row>
+    <row r="36" ht="21" customHeight="1">
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>D  ·  THE CLINICIAN'S PLACE IN THE MODEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="B37" s="29" t="inlineStr">
+        <is>
+          <t>D1–D3</t>
+        </is>
+      </c>
+      <c r="C37" s="16" t="inlineStr">
+        <is>
+          <t>Clinician fit</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>Our own read of fit — no checklist, on purpose</t>
+        </is>
+      </c>
+      <c r="E37" s="29" t="n">
         <v>12</v>
       </c>
-      <c r="F19" s="22" t="n"/>
-      <c r="G19" s="22" t="n"/>
-      <c r="H19" s="22" t="n"/>
-      <c r="I19" s="22" t="n"/>
-      <c r="J19" s="22" t="n"/>
-      <c r="K19" s="22" t="n"/>
-      <c r="L19" s="22" t="n"/>
-      <c r="M19" s="22" t="n"/>
-      <c r="N19" s="22" t="n"/>
-      <c r="O19" s="22" t="n"/>
-      <c r="P19" s="22" t="n"/>
-      <c r="Q19" s="22" t="n"/>
-      <c r="R19" s="22" t="n"/>
-      <c r="S19" s="22" t="n"/>
-      <c r="T19" s="22" t="n"/>
-      <c r="U19" s="22" t="n"/>
-    </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="B20" s="23" t="inlineStr">
-        <is>
-          <t>Section B</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>Scheduling</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>Demand · matching · routing &amp; the week · exceptions</t>
-        </is>
-      </c>
-      <c r="E20" s="23" t="n">
+      <c r="F37" s="23" t="n"/>
+      <c r="G37" s="23" t="n"/>
+      <c r="H37" s="23" t="n"/>
+      <c r="I37" s="23" t="n"/>
+      <c r="J37" s="23" t="n"/>
+      <c r="K37" s="23" t="n"/>
+      <c r="L37" s="23" t="n"/>
+      <c r="M37" s="23" t="n"/>
+      <c r="N37" s="23" t="n"/>
+      <c r="O37" s="23" t="n"/>
+      <c r="P37" s="23" t="n"/>
+      <c r="Q37" s="23" t="n"/>
+      <c r="R37" s="23" t="n"/>
+      <c r="S37" s="23" t="n"/>
+      <c r="T37" s="23" t="n"/>
+      <c r="U37" s="23" t="n"/>
+    </row>
+    <row r="39" ht="21" customHeight="1">
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>E  ·  FIT AND PARTNERSHIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="24" customHeight="1">
+      <c r="B40" s="29" t="inlineStr">
+        <is>
+          <t>E1–E4</t>
+        </is>
+      </c>
+      <c r="C40" s="16" t="inlineStr">
+        <is>
+          <t>Partnership</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>Willing to build it with us, and open to a stake</t>
+        </is>
+      </c>
+      <c r="E40" s="29" t="n">
         <v>12</v>
       </c>
-      <c r="F20" s="22" t="n"/>
-      <c r="G20" s="22" t="n"/>
-      <c r="H20" s="22" t="n"/>
-      <c r="I20" s="22" t="n"/>
-      <c r="J20" s="22" t="n"/>
-      <c r="K20" s="22" t="n"/>
-      <c r="L20" s="22" t="n"/>
-      <c r="M20" s="22" t="n"/>
-      <c r="N20" s="22" t="n"/>
-      <c r="O20" s="22" t="n"/>
-      <c r="P20" s="22" t="n"/>
-      <c r="Q20" s="22" t="n"/>
-      <c r="R20" s="22" t="n"/>
-      <c r="S20" s="22" t="n"/>
-      <c r="T20" s="22" t="n"/>
-      <c r="U20" s="22" t="n"/>
-    </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="B21" s="24" t="inlineStr">
-        <is>
-          <t>Section B</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="D21" s="9" t="inlineStr">
-        <is>
-          <t>Before the visit · when plans change · incentives · care team</t>
-        </is>
-      </c>
-      <c r="E21" s="24" t="n">
-        <v>12</v>
-      </c>
-      <c r="F21" s="22" t="n"/>
-      <c r="G21" s="22" t="n"/>
-      <c r="H21" s="22" t="n"/>
-      <c r="I21" s="22" t="n"/>
-      <c r="J21" s="22" t="n"/>
-      <c r="K21" s="22" t="n"/>
-      <c r="L21" s="22" t="n"/>
-      <c r="M21" s="22" t="n"/>
-      <c r="N21" s="22" t="n"/>
-      <c r="O21" s="22" t="n"/>
-      <c r="P21" s="22" t="n"/>
-      <c r="Q21" s="22" t="n"/>
-      <c r="R21" s="22" t="n"/>
-      <c r="S21" s="22" t="n"/>
-      <c r="T21" s="22" t="n"/>
-      <c r="U21" s="22" t="n"/>
-    </row>
-    <row r="23" ht="21" customHeight="1">
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>C  ·  HOW YOUR PRODUCT WORKS</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="24" customHeight="1">
-      <c r="B24" s="25" t="inlineStr">
-        <is>
-          <t>Section C</t>
-        </is>
-      </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>Sophistication</t>
-        </is>
-      </c>
-      <c r="D24" s="9" t="inlineStr">
-        <is>
-          <t>How much of the work the product does</t>
-        </is>
-      </c>
-      <c r="E24" s="25" t="n">
-        <v>20</v>
-      </c>
-      <c r="F24" s="22" t="n"/>
-      <c r="G24" s="22" t="n"/>
-      <c r="H24" s="22" t="n"/>
-      <c r="I24" s="22" t="n"/>
-      <c r="J24" s="22" t="n"/>
-      <c r="K24" s="22" t="n"/>
-      <c r="L24" s="22" t="n"/>
-      <c r="M24" s="22" t="n"/>
-      <c r="N24" s="22" t="n"/>
-      <c r="O24" s="22" t="n"/>
-      <c r="P24" s="22" t="n"/>
-      <c r="Q24" s="22" t="n"/>
-      <c r="R24" s="22" t="n"/>
-      <c r="S24" s="22" t="n"/>
-      <c r="T24" s="22" t="n"/>
-      <c r="U24" s="22" t="n"/>
-    </row>
-    <row r="25" ht="19" customHeight="1">
-      <c r="B25" s="18" t="inlineStr">
-        <is>
-          <t>C6</t>
-        </is>
-      </c>
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>When your product is down</t>
-        </is>
-      </c>
-      <c r="D25" s="9" t="inlineStr">
-        <is>
-          <t>Stop-check if no uptime figure or contractual commitment</t>
-        </is>
-      </c>
-      <c r="E25" s="19" t="inlineStr">
+      <c r="F40" s="23" t="n"/>
+      <c r="G40" s="23" t="n"/>
+      <c r="H40" s="23" t="n"/>
+      <c r="I40" s="23" t="n"/>
+      <c r="J40" s="23" t="n"/>
+      <c r="K40" s="23" t="n"/>
+      <c r="L40" s="23" t="n"/>
+      <c r="M40" s="23" t="n"/>
+      <c r="N40" s="23" t="n"/>
+      <c r="O40" s="23" t="n"/>
+      <c r="P40" s="23" t="n"/>
+      <c r="Q40" s="23" t="n"/>
+      <c r="R40" s="23" t="n"/>
+      <c r="S40" s="23" t="n"/>
+      <c r="T40" s="23" t="n"/>
+      <c r="U40" s="23" t="n"/>
+    </row>
+    <row r="42" ht="21" customHeight="1">
+      <c r="B42" s="30" t="inlineStr">
+        <is>
+          <t>NOTES   —   one line each.  This is what we go and ask.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="62" customHeight="1">
+      <c r="B43" s="31" t="inlineStr"/>
+      <c r="C43" s="32" t="inlineStr">
+        <is>
+          <t>What stands out</t>
+        </is>
+      </c>
+      <c r="D43" s="33" t="inlineStr">
+        <is>
+          <t>against the field, or against our own thinking</t>
+        </is>
+      </c>
+      <c r="E43" s="19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F25" s="20" t="n"/>
-      <c r="G25" s="20" t="n"/>
-      <c r="H25" s="20" t="n"/>
-      <c r="I25" s="20" t="n"/>
-      <c r="J25" s="20" t="n"/>
-      <c r="K25" s="20" t="n"/>
-      <c r="L25" s="20" t="n"/>
-      <c r="M25" s="20" t="n"/>
-      <c r="N25" s="20" t="n"/>
-      <c r="O25" s="20" t="n"/>
-      <c r="P25" s="20" t="n"/>
-      <c r="Q25" s="20" t="n"/>
-      <c r="R25" s="20" t="n"/>
-      <c r="S25" s="20" t="n"/>
-      <c r="T25" s="20" t="n"/>
-      <c r="U25" s="20" t="n"/>
-    </row>
-    <row r="27" ht="21" customHeight="1">
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>D  ·  THE CLINICIAN'S PLACE IN THE MODEL</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="24" customHeight="1">
-      <c r="B28" s="26" t="inlineStr">
-        <is>
-          <t>D1–D3</t>
-        </is>
-      </c>
-      <c r="C28" s="16" t="inlineStr">
-        <is>
-          <t>Clinician fit</t>
-        </is>
-      </c>
-      <c r="D28" s="9" t="inlineStr">
-        <is>
-          <t>Our own read of fit — no checklist, on purpose</t>
-        </is>
-      </c>
-      <c r="E28" s="26" t="n">
-        <v>12</v>
-      </c>
-      <c r="F28" s="22" t="n"/>
-      <c r="G28" s="22" t="n"/>
-      <c r="H28" s="22" t="n"/>
-      <c r="I28" s="22" t="n"/>
-      <c r="J28" s="22" t="n"/>
-      <c r="K28" s="22" t="n"/>
-      <c r="L28" s="22" t="n"/>
-      <c r="M28" s="22" t="n"/>
-      <c r="N28" s="22" t="n"/>
-      <c r="O28" s="22" t="n"/>
-      <c r="P28" s="22" t="n"/>
-      <c r="Q28" s="22" t="n"/>
-      <c r="R28" s="22" t="n"/>
-      <c r="S28" s="22" t="n"/>
-      <c r="T28" s="22" t="n"/>
-      <c r="U28" s="22" t="n"/>
-    </row>
-    <row r="30" ht="21" customHeight="1">
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>E  ·  FIT AND PARTNERSHIP</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="24" customHeight="1">
-      <c r="B31" s="26" t="inlineStr">
-        <is>
-          <t>E1–E4</t>
-        </is>
-      </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>Partnership</t>
-        </is>
-      </c>
-      <c r="D31" s="9" t="inlineStr">
-        <is>
-          <t>Willing to build it with us, and open to a stake</t>
-        </is>
-      </c>
-      <c r="E31" s="26" t="n">
-        <v>12</v>
-      </c>
-      <c r="F31" s="22" t="n"/>
-      <c r="G31" s="22" t="n"/>
-      <c r="H31" s="22" t="n"/>
-      <c r="I31" s="22" t="n"/>
-      <c r="J31" s="22" t="n"/>
-      <c r="K31" s="22" t="n"/>
-      <c r="L31" s="22" t="n"/>
-      <c r="M31" s="22" t="n"/>
-      <c r="N31" s="22" t="n"/>
-      <c r="O31" s="22" t="n"/>
-      <c r="P31" s="22" t="n"/>
-      <c r="Q31" s="22" t="n"/>
-      <c r="R31" s="22" t="n"/>
-      <c r="S31" s="22" t="n"/>
-      <c r="T31" s="22" t="n"/>
-      <c r="U31" s="22" t="n"/>
-    </row>
-    <row r="33" ht="21" customHeight="1">
-      <c r="B33" s="27" t="inlineStr">
-        <is>
-          <t>NOTES   —   one line each.  This is what we go and ask.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="62" customHeight="1">
-      <c r="B34" s="28" t="inlineStr"/>
-      <c r="C34" s="29" t="inlineStr">
-        <is>
-          <t>What stands out</t>
-        </is>
-      </c>
-      <c r="D34" s="30" t="inlineStr">
-        <is>
-          <t>against the field, or against our own thinking</t>
-        </is>
-      </c>
-      <c r="E34" s="19" t="inlineStr">
+      <c r="F43" s="34" t="n"/>
+      <c r="G43" s="34" t="n"/>
+      <c r="H43" s="34" t="n"/>
+      <c r="I43" s="34" t="n"/>
+      <c r="J43" s="34" t="n"/>
+      <c r="K43" s="34" t="n"/>
+      <c r="L43" s="34" t="n"/>
+      <c r="M43" s="34" t="n"/>
+      <c r="N43" s="34" t="n"/>
+      <c r="O43" s="34" t="n"/>
+      <c r="P43" s="34" t="n"/>
+      <c r="Q43" s="34" t="n"/>
+      <c r="R43" s="34" t="n"/>
+      <c r="S43" s="34" t="n"/>
+      <c r="T43" s="34" t="n"/>
+      <c r="U43" s="34" t="n"/>
+    </row>
+    <row r="44" ht="62" customHeight="1">
+      <c r="B44" s="31" t="inlineStr"/>
+      <c r="C44" s="32" t="inlineStr">
+        <is>
+          <t>What worries me</t>
+        </is>
+      </c>
+      <c r="D44" s="33" t="inlineStr">
+        <is>
+          <t>including anything flagged above</t>
+        </is>
+      </c>
+      <c r="E44" s="19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F34" s="31" t="n"/>
-      <c r="G34" s="31" t="n"/>
-      <c r="H34" s="31" t="n"/>
-      <c r="I34" s="31" t="n"/>
-      <c r="J34" s="31" t="n"/>
-      <c r="K34" s="31" t="n"/>
-      <c r="L34" s="31" t="n"/>
-      <c r="M34" s="31" t="n"/>
-      <c r="N34" s="31" t="n"/>
-      <c r="O34" s="31" t="n"/>
-      <c r="P34" s="31" t="n"/>
-      <c r="Q34" s="31" t="n"/>
-      <c r="R34" s="31" t="n"/>
-      <c r="S34" s="31" t="n"/>
-      <c r="T34" s="31" t="n"/>
-      <c r="U34" s="31" t="n"/>
-    </row>
-    <row r="35" ht="62" customHeight="1">
-      <c r="B35" s="28" t="inlineStr"/>
-      <c r="C35" s="29" t="inlineStr">
-        <is>
-          <t>What worries me</t>
-        </is>
-      </c>
-      <c r="D35" s="30" t="inlineStr">
-        <is>
-          <t>including anything flagged above</t>
-        </is>
-      </c>
-      <c r="E35" s="19" t="inlineStr">
+      <c r="F44" s="34" t="n"/>
+      <c r="G44" s="34" t="n"/>
+      <c r="H44" s="34" t="n"/>
+      <c r="I44" s="34" t="n"/>
+      <c r="J44" s="34" t="n"/>
+      <c r="K44" s="34" t="n"/>
+      <c r="L44" s="34" t="n"/>
+      <c r="M44" s="34" t="n"/>
+      <c r="N44" s="34" t="n"/>
+      <c r="O44" s="34" t="n"/>
+      <c r="P44" s="34" t="n"/>
+      <c r="Q44" s="34" t="n"/>
+      <c r="R44" s="34" t="n"/>
+      <c r="S44" s="34" t="n"/>
+      <c r="T44" s="34" t="n"/>
+      <c r="U44" s="34" t="n"/>
+    </row>
+    <row r="45" ht="62" customHeight="1">
+      <c r="B45" s="31" t="inlineStr"/>
+      <c r="C45" s="32" t="inlineStr">
+        <is>
+          <t>What to go and ask</t>
+        </is>
+      </c>
+      <c r="D45" s="33" t="inlineStr">
+        <is>
+          <t>the demo agenda</t>
+        </is>
+      </c>
+      <c r="E45" s="19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F35" s="31" t="n"/>
-      <c r="G35" s="31" t="n"/>
-      <c r="H35" s="31" t="n"/>
-      <c r="I35" s="31" t="n"/>
-      <c r="J35" s="31" t="n"/>
-      <c r="K35" s="31" t="n"/>
-      <c r="L35" s="31" t="n"/>
-      <c r="M35" s="31" t="n"/>
-      <c r="N35" s="31" t="n"/>
-      <c r="O35" s="31" t="n"/>
-      <c r="P35" s="31" t="n"/>
-      <c r="Q35" s="31" t="n"/>
-      <c r="R35" s="31" t="n"/>
-      <c r="S35" s="31" t="n"/>
-      <c r="T35" s="31" t="n"/>
-      <c r="U35" s="31" t="n"/>
-    </row>
-    <row r="36" ht="62" customHeight="1">
-      <c r="B36" s="28" t="inlineStr"/>
-      <c r="C36" s="29" t="inlineStr">
-        <is>
-          <t>What to go and ask</t>
-        </is>
-      </c>
-      <c r="D36" s="30" t="inlineStr">
-        <is>
-          <t>the demo agenda</t>
-        </is>
-      </c>
-      <c r="E36" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F36" s="31" t="n"/>
-      <c r="G36" s="31" t="n"/>
-      <c r="H36" s="31" t="n"/>
-      <c r="I36" s="31" t="n"/>
-      <c r="J36" s="31" t="n"/>
-      <c r="K36" s="31" t="n"/>
-      <c r="L36" s="31" t="n"/>
-      <c r="M36" s="31" t="n"/>
-      <c r="N36" s="31" t="n"/>
-      <c r="O36" s="31" t="n"/>
-      <c r="P36" s="31" t="n"/>
-      <c r="Q36" s="31" t="n"/>
-      <c r="R36" s="31" t="n"/>
-      <c r="S36" s="31" t="n"/>
-      <c r="T36" s="31" t="n"/>
-      <c r="U36" s="31" t="n"/>
+      <c r="F45" s="34" t="n"/>
+      <c r="G45" s="34" t="n"/>
+      <c r="H45" s="34" t="n"/>
+      <c r="I45" s="34" t="n"/>
+      <c r="J45" s="34" t="n"/>
+      <c r="K45" s="34" t="n"/>
+      <c r="L45" s="34" t="n"/>
+      <c r="M45" s="34" t="n"/>
+      <c r="N45" s="34" t="n"/>
+      <c r="O45" s="34" t="n"/>
+      <c r="P45" s="34" t="n"/>
+      <c r="Q45" s="34" t="n"/>
+      <c r="R45" s="34" t="n"/>
+      <c r="S45" s="34" t="n"/>
+      <c r="T45" s="34" t="n"/>
+      <c r="U45" s="34" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="11">
     <mergeCell ref="B23:U23"/>
     <mergeCell ref="B27:U27"/>
     <mergeCell ref="B8:U8"/>
+    <mergeCell ref="B32:U32"/>
     <mergeCell ref="B4:U4"/>
     <mergeCell ref="B18:U18"/>
     <mergeCell ref="B13:U13"/>
-    <mergeCell ref="B30:U30"/>
-    <mergeCell ref="B33:U33"/>
+    <mergeCell ref="B39:U39"/>
+    <mergeCell ref="B42:U42"/>
+    <mergeCell ref="B19:U19"/>
+    <mergeCell ref="B36:U36"/>
   </mergeCells>
   <conditionalFormatting sqref="F9:U9">
     <cfRule type="colorScale" priority="1">
@@ -2828,36 +3464,96 @@
       <formula>F16="STOP-CHECK"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F25:U25">
+  <conditionalFormatting sqref="F34:U34">
     <cfRule type="expression" priority="6" dxfId="1">
-      <formula>F25="STOP-CHECK"</formula>
+      <formula>F34="STOP-CHECK"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F19:U19">
+  <conditionalFormatting sqref="F20:U20">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="num" val="0"/>
-        <cfvo type="num" val="5"/>
+        <cfvo type="num" val="4"/>
         <color rgb="00FFFFFF"/>
         <color rgb="001F6F78"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F20:U20">
+  <conditionalFormatting sqref="F21:U21">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="num" val="0"/>
-        <cfvo type="num" val="5"/>
+        <cfvo type="num" val="4"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="001F6F78"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F22:U22">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="4"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="001F6F78"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F24:U24">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="4"/>
         <color rgb="00FFFFFF"/>
         <color rgb="002E599D"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F21:U21">
-    <cfRule type="colorScale" priority="9">
+  <conditionalFormatting sqref="F25:U25">
+    <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="num" val="0"/>
-        <cfvo type="num" val="5"/>
+        <cfvo type="num" val="4"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="002E599D"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F26:U26">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="4"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="002E599D"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F28:U28">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="4"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="004E8A5B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F29:U29">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="4"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="004E8A5B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F30:U30">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="4"/>
         <color rgb="00FFFFFF"/>
         <color rgb="004E8A5B"/>
       </colorScale>
@@ -2867,19 +3563,19 @@
     <dataValidation sqref="F14:U14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="A1 — Home Care Home Base" prompt="Pick one line. Ambiguous? Take the lower one and say so in Notes." type="list">
       <formula1>=HCHB_List</formula1>
     </dataValidation>
-    <dataValidation sqref="F19:U19 F20:U20 F21:U21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Scope, 0–5" prompt="How much of this arena they cover. Most of it is the ceiling — our spec is original, so nobody covers all of it." type="list">
+    <dataValidation sqref="F20:U20 F21:U21 F22:U22 F24:U24 F25:U25 F26:U26 F28:U28 F29:U29 F30:U30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Scope, 0–4" prompt="How much of this area they cover. The mark is the points: a 3 adds 3. Most of it is the ceiling — our spec is original." type="list">
       <formula1>=Scope_List</formula1>
     </dataValidation>
-    <dataValidation sqref="F24:U24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Sophistication, 0–4" prompt="1 shows it · 2 checks it · 3 recommends it · 4 runs it. Score what the product does, not how much they wrote about it." type="list">
+    <dataValidation sqref="F33:U33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Sophistication, 0–4" prompt="1 shows it · 2 checks it · 3 recommends it · 4 runs it. Score what the product does, not how much they wrote about it." type="list">
       <formula1>=Soph_List</formula1>
     </dataValidation>
-    <dataValidation sqref="F28:U28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Clinician fit, 0–4" prompt="Read D1 to D3 and give it your own read of fit. There is no checklist here on purpose." type="list">
+    <dataValidation sqref="F37:U37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Clinician fit, 0–4" prompt="Read D1 to D3 and give it your own read of fit. There is no checklist here on purpose." type="list">
       <formula1>=Clin_List</formula1>
     </dataValidation>
-    <dataValidation sqref="F31:U31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Partnership, 0–4" prompt="Are they able and willing to build this with us, and open to us holding a stake in what a wider market might buy? A discount is a discount." type="list">
+    <dataValidation sqref="F40:U40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Partnership, 0–4" prompt="Are they able and willing to build this with us, and open to us holding a stake in what a wider market might buy? A discount is a discount." type="list">
       <formula1>=Part_List</formula1>
     </dataValidation>
-    <dataValidation sqref="F15:U15 F16:U16 F25:U25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Flag" prompt="A stop-check is resolved before advancing, not traded against points." type="list">
+    <dataValidation sqref="F15:U15 F16:U16 F34:U34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Flag" prompt="A stop-check is resolved before advancing, not traded against points." type="list">
       <formula1>"OK,Watch,STOP-CHECK"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2911,14 +3607,14 @@
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="B3" s="32" t="inlineStr">
+      <c r="B3" s="35" t="inlineStr">
         <is>
           <t>Vendor Scorecard — Fast</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="33" t="inlineStr">
+      <c r="B4" s="36" t="inlineStr">
         <is>
           <t>The questionnaire is the rubric. Read the return top to bottom and fill the sheet top to bottom. Seven marks a vendor.</t>
         </is>
@@ -2933,14 +3629,14 @@
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
-      <c r="B8" s="34" t="inlineStr">
+      <c r="B8" s="37" t="inlineStr">
         <is>
           <t>Every one of the 17 questions on the questionnaire has a row on the Scorecard tab, in the order it appears on the form. Seven rows take a mark. The rest raise a flag or a note — and they say so, so nothing looks forgotten. What isn't scored becomes what we go and ask at the demo.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1">
-      <c r="B9" s="34" t="inlineStr">
+      <c r="B9" s="37" t="inlineStr">
         <is>
           <t>Scored on the same 100 points and the same bands as the full scorecard, so the two are directly comparable. This one is coarser, not different: it gives one mark where the full sheet gives several, so the two can disagree on a close call. That is the trade for speed.</t>
         </is>
@@ -2955,149 +3651,149 @@
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="35" t="inlineStr">
+      <c r="B12" s="38" t="inlineStr">
         <is>
           <t>Question</t>
         </is>
       </c>
-      <c r="C12" s="35" t="inlineStr">
+      <c r="C12" s="38" t="inlineStr">
         <is>
           <t>Mark</t>
         </is>
       </c>
-      <c r="D12" s="35" t="inlineStr">
+      <c r="D12" s="38" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
       </c>
     </row>
     <row r="13" ht="21" customHeight="1">
-      <c r="B13" s="36" t="inlineStr">
+      <c r="B13" s="39" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
-      <c r="C13" s="34" t="inlineStr">
+      <c r="C13" s="37" t="inlineStr">
         <is>
           <t>Home Care Home Base integration</t>
         </is>
       </c>
-      <c r="D13" s="37" t="inlineStr">
+      <c r="D13" s="40" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
     </row>
     <row r="14" ht="21" customHeight="1">
-      <c r="B14" s="36" t="inlineStr">
+      <c r="B14" s="39" t="inlineStr">
         <is>
           <t>Section B</t>
         </is>
       </c>
-      <c r="C14" s="34" t="inlineStr">
-        <is>
-          <t>Capacity — how much of it they cover</t>
-        </is>
-      </c>
-      <c r="D14" s="37" t="inlineStr">
+      <c r="C14" s="37" t="inlineStr">
+        <is>
+          <t>Capacity — three marks of 0–4</t>
+        </is>
+      </c>
+      <c r="D14" s="40" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
     </row>
     <row r="15" ht="21" customHeight="1">
-      <c r="B15" s="36" t="inlineStr">
+      <c r="B15" s="39" t="inlineStr">
         <is>
           <t>Section B</t>
         </is>
       </c>
-      <c r="C15" s="34" t="inlineStr">
-        <is>
-          <t>Scheduling — how much of it they cover</t>
-        </is>
-      </c>
-      <c r="D15" s="37" t="inlineStr">
+      <c r="C15" s="37" t="inlineStr">
+        <is>
+          <t>Scheduling — three marks of 0–4</t>
+        </is>
+      </c>
+      <c r="D15" s="40" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
     </row>
     <row r="16" ht="21" customHeight="1">
-      <c r="B16" s="36" t="inlineStr">
+      <c r="B16" s="39" t="inlineStr">
         <is>
           <t>Section B</t>
         </is>
       </c>
-      <c r="C16" s="34" t="inlineStr">
-        <is>
-          <t>Engagement — how much of it they cover</t>
-        </is>
-      </c>
-      <c r="D16" s="37" t="inlineStr">
+      <c r="C16" s="37" t="inlineStr">
+        <is>
+          <t>Engagement — three marks of 0–4</t>
+        </is>
+      </c>
+      <c r="D16" s="40" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
     </row>
     <row r="17" ht="21" customHeight="1">
-      <c r="B17" s="36" t="inlineStr">
+      <c r="B17" s="39" t="inlineStr">
         <is>
           <t>Section C</t>
         </is>
       </c>
-      <c r="C17" s="34" t="inlineStr">
+      <c r="C17" s="37" t="inlineStr">
         <is>
           <t>Sophistication — how much of the work the product does</t>
         </is>
       </c>
-      <c r="D17" s="37" t="inlineStr">
+      <c r="D17" s="40" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
     </row>
     <row r="18" ht="21" customHeight="1">
-      <c r="B18" s="36" t="inlineStr">
+      <c r="B18" s="39" t="inlineStr">
         <is>
           <t>D1–D3</t>
         </is>
       </c>
-      <c r="C18" s="34" t="inlineStr">
+      <c r="C18" s="37" t="inlineStr">
         <is>
           <t>Clinician fit</t>
         </is>
       </c>
-      <c r="D18" s="37" t="inlineStr">
+      <c r="D18" s="40" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
     </row>
     <row r="19" ht="21" customHeight="1">
-      <c r="B19" s="36" t="inlineStr">
+      <c r="B19" s="39" t="inlineStr">
         <is>
           <t>E1–E4</t>
         </is>
       </c>
-      <c r="C19" s="34" t="inlineStr">
+      <c r="C19" s="37" t="inlineStr">
         <is>
           <t>Partnership</t>
         </is>
       </c>
-      <c r="D19" s="37" t="inlineStr">
+      <c r="D19" s="40" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
     </row>
     <row r="20" ht="21" customHeight="1">
-      <c r="B20" s="36" t="inlineStr"/>
-      <c r="C20" s="38" t="inlineStr">
+      <c r="B20" s="39" t="inlineStr"/>
+      <c r="C20" s="41" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="D20" s="37" t="inlineStr">
+      <c r="D20" s="40" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -3112,192 +3808,186 @@
       </c>
     </row>
     <row r="23" ht="28" customHeight="1">
-      <c r="B23" s="34" t="inlineStr">
+      <c r="B23" s="37" t="inlineStr">
         <is>
           <t>Three of the six rungs are live integrations, because live through a partner is still live. Anything not yet live shows as Conditional on the score, whatever the total.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="21" customHeight="1">
-      <c r="B24" s="36" t="inlineStr">
+      <c r="B24" s="39" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="C24" s="34" t="inlineStr">
+      <c r="C24" s="37" t="inlineStr">
         <is>
           <t>Live — established customer base</t>
         </is>
       </c>
-      <c r="D24" s="37" t="inlineStr"/>
+      <c r="D24" s="40" t="inlineStr"/>
     </row>
     <row r="25" ht="21" customHeight="1">
-      <c r="B25" s="36" t="inlineStr">
+      <c r="B25" s="39" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="34" t="inlineStr">
+      <c r="C25" s="37" t="inlineStr">
         <is>
           <t>Live — small customer base</t>
         </is>
       </c>
-      <c r="D25" s="37" t="inlineStr"/>
+      <c r="D25" s="40" t="inlineStr"/>
     </row>
     <row r="26" ht="21" customHeight="1">
-      <c r="B26" s="36" t="inlineStr">
+      <c r="B26" s="39" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="C26" s="34" t="inlineStr">
+      <c r="C26" s="37" t="inlineStr">
         <is>
           <t>Live — through a partner</t>
         </is>
       </c>
-      <c r="D26" s="37" t="inlineStr"/>
+      <c r="D26" s="40" t="inlineStr"/>
     </row>
     <row r="27" ht="21" customHeight="1">
-      <c r="B27" s="36" t="inlineStr">
+      <c r="B27" s="39" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="C27" s="34" t="inlineStr">
+      <c r="C27" s="37" t="inlineStr">
         <is>
           <t>In development — with a date</t>
         </is>
       </c>
-      <c r="D27" s="37" t="inlineStr"/>
+      <c r="D27" s="40" t="inlineStr"/>
     </row>
     <row r="28" ht="21" customHeight="1">
-      <c r="B28" s="36" t="inlineStr">
+      <c r="B28" s="39" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C28" s="34" t="inlineStr">
+      <c r="C28" s="37" t="inlineStr">
         <is>
           <t>On the roadmap — no date</t>
         </is>
       </c>
-      <c r="D28" s="37" t="inlineStr"/>
+      <c r="D28" s="40" t="inlineStr"/>
     </row>
     <row r="29" ht="21" customHeight="1">
-      <c r="B29" s="36" t="inlineStr">
+      <c r="B29" s="39" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C29" s="34" t="inlineStr">
+      <c r="C29" s="37" t="inlineStr">
         <is>
           <t>None, and no path to one</t>
         </is>
       </c>
-      <c r="D29" s="37" t="inlineStr"/>
+      <c r="D29" s="40" t="inlineStr"/>
     </row>
     <row r="30" ht="10" customHeight="1"/>
     <row r="31" ht="22" customHeight="1">
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>SECTION B  ·  SCOPE   —   one mark per arena, 0 to 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="28" customHeight="1">
-      <c r="B32" s="34" t="inlineStr">
-        <is>
-          <t>Read the eleven areas each vendor rated themselves on, then give one mark per arena. The areas in each arena are printed on the row, so the checklist is in front of you. Where Section C contradicts Section B, believe Section C.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="41" customHeight="1">
-      <c r="B33" s="34" t="inlineStr">
-        <is>
-          <t>The mark is your read of how much of that arena — as our one-pager describes it — the product reaches. It is not a count of areas: Capacity has 3 and the others 4, so counting would never divide cleanly, and an area covered thinly is not the same as one covered properly. Weigh breadth and depth together.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="21" customHeight="1">
-      <c r="B34" s="36" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C34" s="34" t="inlineStr">
+          <t>SECTION B  ·  SCOPE   —   three marks per arena, 0 to 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1">
+      <c r="B32" s="37" t="inlineStr">
+        <is>
+          <t>Each row names the area and what sits inside it, so the checklist is in front of you. Where Section C contradicts Section B, believe Section C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="28" customHeight="1">
+      <c r="B33" s="37" t="inlineStr">
+        <is>
+          <t>The mark is the points. A 3 adds 3, a 0 adds nothing — there is no conversion to follow. Three marks of 0 to 4 give each arena 12 points, so Capacity, Scheduling and Engagement carry exactly the same weight.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="28" customHeight="1">
+      <c r="B34" s="37" t="inlineStr">
+        <is>
+          <t>Capacity's three areas map one to one. Scheduling and Engagement have four apiece, so the two that belong together are paired — demand with matching, and plan changes with the incentives used to fill them — rather than inventing a split the one-pager cannot carry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="21" customHeight="1">
+      <c r="B35" s="39" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C35" s="37" t="inlineStr">
         <is>
           <t>Most of it</t>
         </is>
       </c>
-      <c r="D34" s="37" t="inlineStr"/>
-    </row>
-    <row r="35" ht="21" customHeight="1">
-      <c r="B35" s="36" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C35" s="34" t="inlineStr">
+      <c r="D35" s="40" t="inlineStr"/>
+    </row>
+    <row r="36" ht="21" customHeight="1">
+      <c r="B36" s="39" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C36" s="37" t="inlineStr">
         <is>
           <t>More than half</t>
         </is>
       </c>
-      <c r="D35" s="37" t="inlineStr"/>
-    </row>
-    <row r="36" ht="21" customHeight="1">
-      <c r="B36" s="36" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C36" s="34" t="inlineStr">
+      <c r="D36" s="40" t="inlineStr"/>
+    </row>
+    <row r="37" ht="21" customHeight="1">
+      <c r="B37" s="39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C37" s="37" t="inlineStr">
         <is>
           <t>About half</t>
         </is>
       </c>
-      <c r="D36" s="37" t="inlineStr"/>
-    </row>
-    <row r="37" ht="21" customHeight="1">
-      <c r="B37" s="36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C37" s="34" t="inlineStr">
-        <is>
-          <t>Less than half</t>
-        </is>
-      </c>
-      <c r="D37" s="37" t="inlineStr"/>
+      <c r="D37" s="40" t="inlineStr"/>
     </row>
     <row r="38" ht="21" customHeight="1">
-      <c r="B38" s="36" t="inlineStr">
+      <c r="B38" s="39" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C38" s="34" t="inlineStr">
+      <c r="C38" s="37" t="inlineStr">
         <is>
           <t>A corner of it</t>
         </is>
       </c>
-      <c r="D38" s="37" t="inlineStr"/>
+      <c r="D38" s="40" t="inlineStr"/>
     </row>
     <row r="39" ht="21" customHeight="1">
-      <c r="B39" s="36" t="inlineStr">
+      <c r="B39" s="39" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C39" s="34" t="inlineStr">
+      <c r="C39" s="37" t="inlineStr">
         <is>
           <t>Nothing here</t>
         </is>
       </c>
-      <c r="D39" s="37" t="inlineStr"/>
+      <c r="D39" s="40" t="inlineStr"/>
     </row>
     <row r="40" ht="28" customHeight="1">
-      <c r="B40" s="34" t="inlineStr">
+      <c r="B40" s="37" t="inlineStr">
         <is>
           <t>Most of it is the ceiling on purpose. The scope on our one-pager is original and these are point solutions, so nobody will cover all of it — a rung for that would sit unused and squeeze everyone else into the bottom half of the scale. All six rungs here are live.</t>
         </is>
@@ -3312,79 +4002,79 @@
       </c>
     </row>
     <row r="43" ht="41" customHeight="1">
-      <c r="B43" s="34" t="inlineStr">
+      <c r="B43" s="37" t="inlineStr">
         <is>
           <t>How much of the work the product does. This is the Read / Assist / Control language already in our workbook. Score what the product does, not how much the vendor wrote about it — a short answer describing an optimiser still scores 4. How it does it is a demo question, not a reason to mark it down.</t>
         </is>
       </c>
     </row>
     <row r="44" ht="21" customHeight="1">
-      <c r="B44" s="36" t="inlineStr">
+      <c r="B44" s="39" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="C44" s="34" t="inlineStr">
+      <c r="C44" s="37" t="inlineStr">
         <is>
           <t>Runs it — decides across the whole picture, and re-decides when things change</t>
         </is>
       </c>
-      <c r="D44" s="37" t="inlineStr"/>
+      <c r="D44" s="40" t="inlineStr"/>
     </row>
     <row r="45" ht="21" customHeight="1">
-      <c r="B45" s="36" t="inlineStr">
+      <c r="B45" s="39" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C45" s="34" t="inlineStr">
+      <c r="C45" s="37" t="inlineStr">
         <is>
           <t>Recommends it — works out the answer and proposes it; a person confirms</t>
         </is>
       </c>
-      <c r="D45" s="37" t="inlineStr"/>
+      <c r="D45" s="40" t="inlineStr"/>
     </row>
     <row r="46" ht="21" customHeight="1">
-      <c r="B46" s="36" t="inlineStr">
+      <c r="B46" s="39" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C46" s="34" t="inlineStr">
+      <c r="C46" s="37" t="inlineStr">
         <is>
           <t>Checks it — applies rules and flags problems; a person still works it</t>
         </is>
       </c>
-      <c r="D46" s="37" t="inlineStr"/>
+      <c r="D46" s="40" t="inlineStr"/>
     </row>
     <row r="47" ht="21" customHeight="1">
-      <c r="B47" s="36" t="inlineStr">
+      <c r="B47" s="39" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C47" s="34" t="inlineStr">
+      <c r="C47" s="37" t="inlineStr">
         <is>
           <t>Shows it — surfaces the information; a person does all the work</t>
         </is>
       </c>
-      <c r="D47" s="37" t="inlineStr"/>
+      <c r="D47" s="40" t="inlineStr"/>
     </row>
     <row r="48" ht="21" customHeight="1">
-      <c r="B48" s="36" t="inlineStr">
+      <c r="B48" s="39" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C48" s="34" t="inlineStr">
+      <c r="C48" s="37" t="inlineStr">
         <is>
           <t>Not addressed</t>
         </is>
       </c>
-      <c r="D48" s="37" t="inlineStr"/>
+      <c r="D48" s="40" t="inlineStr"/>
     </row>
     <row r="49" ht="15" customHeight="1">
-      <c r="B49" s="34" t="inlineStr">
+      <c r="B49" s="37" t="inlineStr">
         <is>
           <t>A 4 is not automatically what we want. Where we said Assist, a product that decides on its own is a risk worth a note.</t>
         </is>
@@ -3399,79 +4089,79 @@
       </c>
     </row>
     <row r="52" ht="21" customHeight="1">
-      <c r="B52" s="36" t="inlineStr">
+      <c r="B52" s="39" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="C52" s="34" t="inlineStr">
+      <c r="C52" s="37" t="inlineStr">
         <is>
           <t>Strong fit</t>
         </is>
       </c>
-      <c r="D52" s="37" t="inlineStr"/>
+      <c r="D52" s="40" t="inlineStr"/>
     </row>
     <row r="53" ht="21" customHeight="1">
-      <c r="B53" s="36" t="inlineStr">
+      <c r="B53" s="39" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C53" s="34" t="inlineStr">
+      <c r="C53" s="37" t="inlineStr">
         <is>
           <t>Good fit</t>
         </is>
       </c>
-      <c r="D53" s="37" t="inlineStr"/>
+      <c r="D53" s="40" t="inlineStr"/>
     </row>
     <row r="54" ht="21" customHeight="1">
-      <c r="B54" s="36" t="inlineStr">
+      <c r="B54" s="39" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C54" s="34" t="inlineStr">
+      <c r="C54" s="37" t="inlineStr">
         <is>
           <t>Workable</t>
         </is>
       </c>
-      <c r="D54" s="37" t="inlineStr"/>
+      <c r="D54" s="40" t="inlineStr"/>
     </row>
     <row r="55" ht="21" customHeight="1">
-      <c r="B55" s="36" t="inlineStr">
+      <c r="B55" s="39" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C55" s="34" t="inlineStr">
+      <c r="C55" s="37" t="inlineStr">
         <is>
           <t>Poor fit</t>
         </is>
       </c>
-      <c r="D55" s="37" t="inlineStr"/>
+      <c r="D55" s="40" t="inlineStr"/>
     </row>
     <row r="56" ht="21" customHeight="1">
-      <c r="B56" s="36" t="inlineStr">
+      <c r="B56" s="39" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C56" s="34" t="inlineStr">
+      <c r="C56" s="37" t="inlineStr">
         <is>
           <t>Not answered</t>
         </is>
       </c>
-      <c r="D56" s="37" t="inlineStr"/>
+      <c r="D56" s="40" t="inlineStr"/>
     </row>
     <row r="57" ht="28" customHeight="1">
-      <c r="B57" s="34" t="inlineStr">
+      <c r="B57" s="37" t="inlineStr">
         <is>
           <t>No descriptions here on purpose. Read D1 to D3 and give it your own read. We know how our clinicians work and what they will accept; a rubric that spelled out what earns a 4 would only substitute a guess for that.</t>
         </is>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1">
-      <c r="B58" s="34" t="inlineStr">
+      <c r="B58" s="37" t="inlineStr">
         <is>
           <t>Say why in the Notes, though — that one line is what a colleague reads when they score the same vendor differently.</t>
         </is>
@@ -3486,79 +4176,79 @@
       </c>
     </row>
     <row r="61" ht="28" customHeight="1">
-      <c r="B61" s="34" t="inlineStr">
+      <c r="B61" s="37" t="inlineStr">
         <is>
           <t>What we are looking for is a company with the willingness and the environment to build this with us around our needs — and open to us holding equity, so that a product for the general market becomes a real possibility. The rungs run from vendor to co-owner.</t>
         </is>
       </c>
     </row>
     <row r="62" ht="21" customHeight="1">
-      <c r="B62" s="36" t="inlineStr">
+      <c r="B62" s="39" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="C62" s="34" t="inlineStr">
+      <c r="C62" s="37" t="inlineStr">
         <is>
           <t>Open to equity or a stake in what we build, and set up to build it with us</t>
         </is>
       </c>
-      <c r="D62" s="37" t="inlineStr"/>
+      <c r="D62" s="40" t="inlineStr"/>
     </row>
     <row r="63" ht="21" customHeight="1">
-      <c r="B63" s="36" t="inlineStr">
+      <c r="B63" s="39" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C63" s="34" t="inlineStr">
+      <c r="C63" s="37" t="inlineStr">
         <is>
           <t>Ready to build to our needs as a design partner; ownership not addressed</t>
         </is>
       </c>
-      <c r="D63" s="37" t="inlineStr"/>
+      <c r="D63" s="40" t="inlineStr"/>
     </row>
     <row r="64" ht="21" customHeight="1">
-      <c r="B64" s="36" t="inlineStr">
+      <c r="B64" s="39" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C64" s="34" t="inlineStr">
+      <c r="C64" s="37" t="inlineStr">
         <is>
           <t>Will take our input, but they own the roadmap and the product</t>
         </is>
       </c>
-      <c r="D64" s="37" t="inlineStr"/>
+      <c r="D64" s="40" t="inlineStr"/>
     </row>
     <row r="65" ht="21" customHeight="1">
-      <c r="B65" s="36" t="inlineStr">
+      <c r="B65" s="39" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C65" s="34" t="inlineStr">
+      <c r="C65" s="37" t="inlineStr">
         <is>
           <t>A standard customer relationship — we buy what already exists</t>
         </is>
       </c>
-      <c r="D65" s="37" t="inlineStr"/>
+      <c r="D65" s="40" t="inlineStr"/>
     </row>
     <row r="66" ht="21" customHeight="1">
-      <c r="B66" s="36" t="inlineStr">
+      <c r="B66" s="39" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C66" s="34" t="inlineStr">
+      <c r="C66" s="37" t="inlineStr">
         <is>
           <t>Not answered</t>
         </is>
       </c>
-      <c r="D66" s="37" t="inlineStr"/>
+      <c r="D66" s="40" t="inlineStr"/>
     </row>
     <row r="67" ht="28" customHeight="1">
-      <c r="B67" s="34" t="inlineStr">
+      <c r="B67" s="37" t="inlineStr">
         <is>
           <t>Read all four E answers, not only E2. A vendor who never mentions ownership but describes a real co-development practice is a 3, and worth the conversation. A discount is a discount.</t>
         </is>
@@ -3573,50 +4263,50 @@
       </c>
     </row>
     <row r="70" ht="28" customHeight="1">
-      <c r="B70" s="34" t="inlineStr">
+      <c r="B70" s="37" t="inlineStr">
         <is>
           <t>A vendor with no continuity commitment should be stopped and asked, not quietly docked a few points. Same for a vendor with one customer, or impact numbers with no baseline. Mark these OK, Watch or STOP-CHECK.</t>
         </is>
       </c>
     </row>
     <row r="71" ht="21" customHeight="1">
-      <c r="B71" s="36" t="inlineStr">
+      <c r="B71" s="39" t="inlineStr">
         <is>
           <t>A2</t>
         </is>
       </c>
-      <c r="C71" s="34" t="inlineStr">
+      <c r="C71" s="37" t="inlineStr">
         <is>
           <t>Customers, scale and references — STOP-CHECK if one customer, or no references offered</t>
         </is>
       </c>
-      <c r="D71" s="37" t="inlineStr"/>
+      <c r="D71" s="40" t="inlineStr"/>
     </row>
     <row r="72" ht="21" customHeight="1">
-      <c r="B72" s="36" t="inlineStr">
+      <c r="B72" s="39" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="C72" s="34" t="inlineStr">
+      <c r="C72" s="37" t="inlineStr">
         <is>
           <t>Measured impact — Watch if claimed with no baseline or period</t>
         </is>
       </c>
-      <c r="D72" s="37" t="inlineStr"/>
+      <c r="D72" s="40" t="inlineStr"/>
     </row>
     <row r="73" ht="21" customHeight="1">
-      <c r="B73" s="36" t="inlineStr">
+      <c r="B73" s="39" t="inlineStr">
         <is>
           <t>C6</t>
         </is>
       </c>
-      <c r="C73" s="34" t="inlineStr">
+      <c r="C73" s="37" t="inlineStr">
         <is>
           <t>When your product is down — STOP-CHECK if no uptime figure or contractual commitment</t>
         </is>
       </c>
-      <c r="D73" s="37" t="inlineStr"/>
+      <c r="D73" s="40" t="inlineStr"/>
     </row>
     <row r="74" ht="10" customHeight="1"/>
     <row r="75" ht="22" customHeight="1">
@@ -3627,79 +4317,79 @@
       </c>
     </row>
     <row r="76" ht="21" customHeight="1">
-      <c r="B76" s="36" t="inlineStr">
+      <c r="B76" s="39" t="inlineStr">
         <is>
           <t>80–100</t>
         </is>
       </c>
-      <c r="C76" s="34" t="inlineStr">
+      <c r="C76" s="37" t="inlineStr">
         <is>
           <t>Advance — demo, references, deeper diligence</t>
         </is>
       </c>
-      <c r="D76" s="37" t="inlineStr"/>
+      <c r="D76" s="40" t="inlineStr"/>
     </row>
     <row r="77" ht="21" customHeight="1">
-      <c r="B77" s="36" t="inlineStr">
+      <c r="B77" s="39" t="inlineStr">
         <is>
           <t>65–79</t>
         </is>
       </c>
-      <c r="C77" s="34" t="inlineStr">
+      <c r="C77" s="37" t="inlineStr">
         <is>
           <t>Consider — only if something specific justifies it</t>
         </is>
       </c>
-      <c r="D77" s="37" t="inlineStr"/>
+      <c r="D77" s="40" t="inlineStr"/>
     </row>
     <row r="78" ht="21" customHeight="1">
-      <c r="B78" s="36" t="inlineStr">
+      <c r="B78" s="39" t="inlineStr">
         <is>
           <t>50–64</t>
         </is>
       </c>
-      <c r="C78" s="34" t="inlineStr">
+      <c r="C78" s="37" t="inlineStr">
         <is>
           <t>Hold — park unless the field thins</t>
         </is>
       </c>
-      <c r="D78" s="37" t="inlineStr"/>
+      <c r="D78" s="40" t="inlineStr"/>
     </row>
     <row r="79" ht="21" customHeight="1">
-      <c r="B79" s="36" t="inlineStr">
+      <c r="B79" s="39" t="inlineStr">
         <is>
           <t>&lt; 50</t>
         </is>
       </c>
-      <c r="C79" s="34" t="inlineStr">
+      <c r="C79" s="37" t="inlineStr">
         <is>
           <t>Decline — close out with thanks</t>
         </is>
       </c>
-      <c r="D79" s="37" t="inlineStr"/>
+      <c r="D79" s="40" t="inlineStr"/>
     </row>
     <row r="80" ht="34" customHeight="1">
-      <c r="B80" s="36" t="inlineStr">
+      <c r="B80" s="39" t="inlineStr">
         <is>
           <t>Conditional</t>
         </is>
       </c>
-      <c r="C80" s="34" t="inlineStr">
+      <c r="C80" s="37" t="inlineStr">
         <is>
           <t>Shown whenever the integration is not yet live. Advancing means accepting an integration still to be built, on their timeline, at our risk.</t>
         </is>
       </c>
-      <c r="D80" s="37" t="inlineStr"/>
+      <c r="D80" s="40" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="B82" s="39" t="inlineStr">
+      <c r="B82" s="42" t="inlineStr">
         <is>
           <t>Fast scorecard v2.0  ·  questionnaire form_version 2026-08-19</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="24">
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="B42:D42"/>
     <mergeCell ref="B60:D60"/>
@@ -3709,6 +4399,7 @@
     <mergeCell ref="B57:D57"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="B69:D69"/>
+    <mergeCell ref="B34:D34"/>
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="B40:D40"/>
     <mergeCell ref="B9:D9"/>
@@ -3847,7 +4538,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2 — Less than half</t>
+          <t>2 — About half</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3877,7 +4568,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3 — About half</t>
+          <t>3 — More than half</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -3907,7 +4598,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>4 — More than half</t>
+          <t>4 — Most of it</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -3934,11 +4625,6 @@
       </c>
       <c r="C7" t="n">
         <v>0</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>5 — Most of it</t>
-        </is>
       </c>
     </row>
   </sheetData>
